--- a/orcamento.xlsx
+++ b/orcamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e87dc3a59766ad95/Documentos/Karams Estofados/Relatórios/Financeiro/Orçamento 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="538" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF99E30-591F-43F9-8581-7ECAF433E7E4}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16A8B5AC-78FD-4846-B5BA-9AEDEA49E7E1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
   </bookViews>
@@ -669,7 +669,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="mmm\-yy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
@@ -678,6 +678,7 @@
     <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="[$-416]mmm\-yy;@"/>
     <numFmt numFmtId="170" formatCode="0.00%;\-0.00%;\-"/>
+    <numFmt numFmtId="177" formatCode="0%;\-0%;\-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -787,7 +788,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -930,6 +931,9 @@
     <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,7 +941,28 @@
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
     <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -22561,8 +22586,8 @@
         <v>-290070.51999999938</v>
       </c>
       <c r="Q151" s="14">
-        <f>P151/N151-1</f>
-        <v>9.1818828692727283E-2</v>
+        <f t="shared" ref="Q151" si="30">IFERROR((P151*-1)/N151-1,"")</f>
+        <v>-2.0918188286927273</v>
       </c>
       <c r="R151" s="7">
         <v>-401.39105013805965</v>
@@ -22574,9 +22599,9 @@
         <f>T132-T134</f>
         <v>31995.680000000008</v>
       </c>
-      <c r="U151" s="14">
-        <f>T151/R151-1</f>
-        <v>-80.711991557846133</v>
+      <c r="U151" s="52">
+        <f>T151/R151</f>
+        <v>-79.711991557846133</v>
       </c>
       <c r="V151" s="7">
         <v>252502.16441826487</v>
@@ -22589,8 +22614,8 @@
         <v>620529.40999999968</v>
       </c>
       <c r="Y151" s="14">
-        <f>X151/V151-1</f>
-        <v>1.4575211520646807</v>
+        <f t="shared" ref="Y151" si="31">IFERROR((X151*-1)/V151-1,"")</f>
+        <v>-3.4575211520646807</v>
       </c>
       <c r="Z151" s="7">
         <v>96597.603831202126</v>
@@ -23021,24 +23046,42 @@
       <c r="O157" s="14">
         <v>-0.16364958562231682</v>
       </c>
-      <c r="P157" s="14"/>
-      <c r="Q157" s="14"/>
+      <c r="P157" s="48">
+        <f>P151-P153</f>
+        <v>-290070.51999999938</v>
+      </c>
+      <c r="Q157" s="14">
+        <f>P157/N157-1</f>
+        <v>9.1818828692727283E-2</v>
+      </c>
       <c r="R157" s="7">
         <v>-401.39105013805965</v>
       </c>
       <c r="S157" s="14">
         <v>-1.8032040031738545E-4</v>
       </c>
-      <c r="T157" s="14"/>
-      <c r="U157" s="14"/>
+      <c r="T157" s="48">
+        <f>T151-T153</f>
+        <v>31995.680000000008</v>
+      </c>
+      <c r="U157" s="52">
+        <f>T157/R157-1</f>
+        <v>-80.711991557846133</v>
+      </c>
       <c r="V157" s="7">
         <v>252502.16441826487</v>
       </c>
       <c r="W157" s="14">
         <v>9.0165538800023731E-2</v>
       </c>
-      <c r="X157" s="14"/>
-      <c r="Y157" s="14"/>
+      <c r="X157" s="48">
+        <f>X151-X153</f>
+        <v>620529.40999999968</v>
+      </c>
+      <c r="Y157" s="52">
+        <f>X157/V157-1</f>
+        <v>1.4575211520646807</v>
+      </c>
       <c r="Z157" s="7">
         <v>96597.603831202126</v>
       </c>
@@ -23112,22 +23155,37 @@
     <mergeCell ref="X4:Y4"/>
   </mergeCells>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="3" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="27" operator="equal">
       <formula>"rafael"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:Q1048576">
-    <cfRule type="cellIs" dxfId="2" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="26" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U1:U1048576">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="U1:U131 U133:U1048576">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y1:Y1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="Y1:Y131 Y133:Y156 Y158:Y1048576">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U132">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y132">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y157">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/orcamento.xlsx
+++ b/orcamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e87dc3a59766ad95/Documentos/Karams Estofados/Relatórios/Financeiro/Orçamento 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16A8B5AC-78FD-4846-B5BA-9AEDEA49E7E1}"/>
+  <xr:revisionPtr revIDLastSave="579" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{196A29E3-50BC-41F1-BB6A-BEA557AD3CA9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Acompanhamento Orçamento" sheetId="21" r:id="rId1"/>
@@ -678,7 +678,7 @@
     <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="[$-416]mmm\-yy;@"/>
     <numFmt numFmtId="170" formatCode="0.00%;\-0.00%;\-"/>
-    <numFmt numFmtId="177" formatCode="0%;\-0%;\-"/>
+    <numFmt numFmtId="171" formatCode="0%;\-0%;\-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -925,14 +925,14 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -941,28 +941,7 @@
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
     <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <b/>
@@ -1026,20 +1005,19 @@
       <sheetName val="CUSTO MOD"/>
       <sheetName val="RESUMO"/>
       <sheetName val="DESPESAS"/>
-      <sheetName val="Backup"/>
       <sheetName val="FORNECEDORES MANUTENÇÃO"/>
       <sheetName val="BASE"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9">
         <row r="5">
           <cell r="A5" t="str">
@@ -1052,40 +1030,25 @@
             <v>115564.43000000001</v>
           </cell>
           <cell r="D5">
-            <v>5788.56</v>
-          </cell>
-          <cell r="E5"/>
+            <v>169337.99</v>
+          </cell>
           <cell r="F5">
-            <v>257388.23</v>
-          </cell>
-          <cell r="G5"/>
-          <cell r="H5"/>
-          <cell r="I5"/>
-          <cell r="J5"/>
-          <cell r="K5"/>
-          <cell r="L5"/>
-          <cell r="M5"/>
+            <v>420937.66000000003</v>
+          </cell>
         </row>
         <row r="6">
           <cell r="A6" t="str">
             <v>COFINS</v>
           </cell>
-          <cell r="B6"/>
           <cell r="C6">
             <v>2460.61</v>
           </cell>
-          <cell r="D6"/>
-          <cell r="E6"/>
+          <cell r="D6">
+            <v>15906.25</v>
+          </cell>
           <cell r="F6">
-            <v>2460.61</v>
-          </cell>
-          <cell r="G6"/>
-          <cell r="H6"/>
-          <cell r="I6"/>
-          <cell r="J6"/>
-          <cell r="K6"/>
-          <cell r="L6"/>
-          <cell r="M6"/>
+            <v>18366.86</v>
+          </cell>
         </row>
         <row r="7">
           <cell r="A7" t="str">
@@ -1097,18 +1060,12 @@
           <cell r="C7">
             <v>18975.320000000003</v>
           </cell>
-          <cell r="D7"/>
-          <cell r="E7"/>
+          <cell r="D7">
+            <v>39057.060000000005</v>
+          </cell>
           <cell r="F7">
-            <v>79654.33</v>
-          </cell>
-          <cell r="G7"/>
-          <cell r="H7"/>
-          <cell r="I7"/>
-          <cell r="J7"/>
-          <cell r="K7"/>
-          <cell r="L7"/>
-          <cell r="M7"/>
+            <v>118711.39000000001</v>
+          </cell>
         </row>
         <row r="8">
           <cell r="A8" t="str">
@@ -1123,17 +1080,9 @@
           <cell r="D8">
             <v>5659.96</v>
           </cell>
-          <cell r="E8"/>
           <cell r="F8">
             <v>16979.88</v>
           </cell>
-          <cell r="G8"/>
-          <cell r="H8"/>
-          <cell r="I8"/>
-          <cell r="J8"/>
-          <cell r="K8"/>
-          <cell r="L8"/>
-          <cell r="M8"/>
         </row>
         <row r="9">
           <cell r="A9" t="str">
@@ -1145,18 +1094,12 @@
           <cell r="C9">
             <v>14761.73</v>
           </cell>
-          <cell r="D9"/>
-          <cell r="E9"/>
+          <cell r="D9">
+            <v>22197.7</v>
+          </cell>
           <cell r="F9">
-            <v>30636.12</v>
-          </cell>
-          <cell r="G9"/>
-          <cell r="H9"/>
-          <cell r="I9"/>
-          <cell r="J9"/>
-          <cell r="K9"/>
-          <cell r="L9"/>
-          <cell r="M9"/>
+            <v>52833.82</v>
+          </cell>
         </row>
         <row r="10">
           <cell r="A10" t="str">
@@ -1169,40 +1112,25 @@
             <v>1490.09</v>
           </cell>
           <cell r="D10">
-            <v>128.6</v>
-          </cell>
-          <cell r="E10"/>
+            <v>1921.23</v>
+          </cell>
           <cell r="F10">
-            <v>3062.31</v>
-          </cell>
-          <cell r="G10"/>
-          <cell r="H10"/>
-          <cell r="I10"/>
-          <cell r="J10"/>
-          <cell r="K10"/>
-          <cell r="L10"/>
-          <cell r="M10"/>
+            <v>4854.9400000000005</v>
+          </cell>
         </row>
         <row r="11">
           <cell r="A11" t="str">
             <v>PIS</v>
           </cell>
-          <cell r="B11"/>
           <cell r="C11">
             <v>496.96</v>
           </cell>
-          <cell r="D11"/>
-          <cell r="E11"/>
+          <cell r="D11">
+            <v>3431.3</v>
+          </cell>
           <cell r="F11">
-            <v>496.96</v>
-          </cell>
-          <cell r="G11"/>
-          <cell r="H11"/>
-          <cell r="I11"/>
-          <cell r="J11"/>
-          <cell r="K11"/>
-          <cell r="L11"/>
-          <cell r="M11"/>
+            <v>3928.26</v>
+          </cell>
         </row>
         <row r="12">
           <cell r="A12" t="str">
@@ -1214,18 +1142,12 @@
           <cell r="C12">
             <v>71719.760000000009</v>
           </cell>
-          <cell r="D12"/>
-          <cell r="E12"/>
+          <cell r="D12">
+            <v>81164.490000000005</v>
+          </cell>
           <cell r="F12">
-            <v>124098.02000000002</v>
-          </cell>
-          <cell r="G12"/>
-          <cell r="H12"/>
-          <cell r="I12"/>
-          <cell r="J12"/>
-          <cell r="K12"/>
-          <cell r="L12"/>
-          <cell r="M12"/>
+            <v>205262.51</v>
+          </cell>
         </row>
         <row r="13">
           <cell r="A13" t="str">
@@ -1240,17 +1162,9 @@
           <cell r="D13">
             <v>29480.909999999996</v>
           </cell>
-          <cell r="E13"/>
           <cell r="F13">
             <v>63025.459999999992</v>
           </cell>
-          <cell r="G13"/>
-          <cell r="H13"/>
-          <cell r="I13"/>
-          <cell r="J13"/>
-          <cell r="K13"/>
-          <cell r="L13"/>
-          <cell r="M13"/>
         </row>
         <row r="14">
           <cell r="A14" t="str">
@@ -1265,17 +1179,9 @@
           <cell r="D14">
             <v>1534.3</v>
           </cell>
-          <cell r="E14"/>
           <cell r="F14">
             <v>3085.9799999999996</v>
           </cell>
-          <cell r="G14"/>
-          <cell r="H14"/>
-          <cell r="I14"/>
-          <cell r="J14"/>
-          <cell r="K14"/>
-          <cell r="L14"/>
-          <cell r="M14"/>
         </row>
         <row r="15">
           <cell r="A15" t="str">
@@ -1290,17 +1196,9 @@
           <cell r="D15">
             <v>12217.75</v>
           </cell>
-          <cell r="E15"/>
           <cell r="F15">
             <v>14735.43</v>
           </cell>
-          <cell r="G15"/>
-          <cell r="H15"/>
-          <cell r="I15"/>
-          <cell r="J15"/>
-          <cell r="K15"/>
-          <cell r="L15"/>
-          <cell r="M15"/>
         </row>
         <row r="16">
           <cell r="A16" t="str">
@@ -1315,17 +1213,9 @@
           <cell r="D16">
             <v>15728.859999999995</v>
           </cell>
-          <cell r="E16"/>
           <cell r="F16">
             <v>45204.049999999996</v>
           </cell>
-          <cell r="G16"/>
-          <cell r="H16"/>
-          <cell r="I16"/>
-          <cell r="J16"/>
-          <cell r="K16"/>
-          <cell r="L16"/>
-          <cell r="M16"/>
         </row>
         <row r="17">
           <cell r="A17" t="str">
@@ -1341,18 +1231,11 @@
             <v>259701.91999999998</v>
           </cell>
           <cell r="E17">
-            <v>11537.52</v>
+            <v>13734.57</v>
           </cell>
           <cell r="F17">
-            <v>929529.21</v>
-          </cell>
-          <cell r="G17"/>
-          <cell r="H17"/>
-          <cell r="I17"/>
-          <cell r="J17"/>
-          <cell r="K17"/>
-          <cell r="L17"/>
-          <cell r="M17"/>
+            <v>931726.25999999989</v>
+          </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
@@ -1373,13 +1256,6 @@
           <cell r="F18">
             <v>2147.9</v>
           </cell>
-          <cell r="G18"/>
-          <cell r="H18"/>
-          <cell r="I18"/>
-          <cell r="J18"/>
-          <cell r="K18"/>
-          <cell r="L18"/>
-          <cell r="M18"/>
         </row>
         <row r="19">
           <cell r="A19" t="str">
@@ -1394,17 +1270,9 @@
           <cell r="D19">
             <v>8155.15</v>
           </cell>
-          <cell r="E19"/>
           <cell r="F19">
             <v>19604.21</v>
           </cell>
-          <cell r="G19"/>
-          <cell r="H19"/>
-          <cell r="I19"/>
-          <cell r="J19"/>
-          <cell r="K19"/>
-          <cell r="L19"/>
-          <cell r="M19"/>
         </row>
         <row r="20">
           <cell r="A20" t="str">
@@ -1416,18 +1284,9 @@
           <cell r="C20">
             <v>1694.1599999999999</v>
           </cell>
-          <cell r="D20"/>
-          <cell r="E20"/>
           <cell r="F20">
             <v>3593.3599999999997</v>
           </cell>
-          <cell r="G20"/>
-          <cell r="H20"/>
-          <cell r="I20"/>
-          <cell r="J20"/>
-          <cell r="K20"/>
-          <cell r="L20"/>
-          <cell r="M20"/>
         </row>
         <row r="21">
           <cell r="A21" t="str">
@@ -1448,13 +1307,6 @@
           <cell r="F21">
             <v>23852.809999999998</v>
           </cell>
-          <cell r="G21"/>
-          <cell r="H21"/>
-          <cell r="I21"/>
-          <cell r="J21"/>
-          <cell r="K21"/>
-          <cell r="L21"/>
-          <cell r="M21"/>
         </row>
         <row r="22">
           <cell r="A22" t="str">
@@ -1466,18 +1318,9 @@
           <cell r="C22">
             <v>32736.5</v>
           </cell>
-          <cell r="D22"/>
-          <cell r="E22"/>
           <cell r="F22">
             <v>67168.479999999996</v>
           </cell>
-          <cell r="G22"/>
-          <cell r="H22"/>
-          <cell r="I22"/>
-          <cell r="J22"/>
-          <cell r="K22"/>
-          <cell r="L22"/>
-          <cell r="M22"/>
         </row>
         <row r="23">
           <cell r="A23" t="str">
@@ -1492,17 +1335,9 @@
           <cell r="D23">
             <v>8223.1</v>
           </cell>
-          <cell r="E23"/>
           <cell r="F23">
             <v>25031.9</v>
           </cell>
-          <cell r="G23"/>
-          <cell r="H23"/>
-          <cell r="I23"/>
-          <cell r="J23"/>
-          <cell r="K23"/>
-          <cell r="L23"/>
-          <cell r="M23"/>
         </row>
         <row r="24">
           <cell r="A24" t="str">
@@ -1514,18 +1349,9 @@
           <cell r="C24">
             <v>42800.44</v>
           </cell>
-          <cell r="D24"/>
-          <cell r="E24"/>
           <cell r="F24">
             <v>87169.52</v>
           </cell>
-          <cell r="G24"/>
-          <cell r="H24"/>
-          <cell r="I24"/>
-          <cell r="J24"/>
-          <cell r="K24"/>
-          <cell r="L24"/>
-          <cell r="M24"/>
         </row>
         <row r="25">
           <cell r="A25" t="str">
@@ -1541,41 +1367,25 @@
             <v>9382.1299999999992</v>
           </cell>
           <cell r="E25">
-            <v>990</v>
+            <v>3187.05</v>
           </cell>
           <cell r="F25">
-            <v>46428.189999999995</v>
-          </cell>
-          <cell r="G25"/>
-          <cell r="H25"/>
-          <cell r="I25"/>
-          <cell r="J25"/>
-          <cell r="K25"/>
-          <cell r="L25"/>
-          <cell r="M25"/>
+            <v>48625.24</v>
+          </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
             <v>Rescisões MOD</v>
           </cell>
-          <cell r="B26"/>
           <cell r="C26">
             <v>30936.210000000003</v>
           </cell>
           <cell r="D26">
             <v>7839.08</v>
           </cell>
-          <cell r="E26"/>
           <cell r="F26">
             <v>38775.29</v>
           </cell>
-          <cell r="G26"/>
-          <cell r="H26"/>
-          <cell r="I26"/>
-          <cell r="J26"/>
-          <cell r="K26"/>
-          <cell r="L26"/>
-          <cell r="M26"/>
         </row>
         <row r="27">
           <cell r="A27" t="str">
@@ -1590,17 +1400,9 @@
           <cell r="D27">
             <v>218151.71</v>
           </cell>
-          <cell r="E27"/>
           <cell r="F27">
             <v>609909.85</v>
           </cell>
-          <cell r="G27"/>
-          <cell r="H27"/>
-          <cell r="I27"/>
-          <cell r="J27"/>
-          <cell r="K27"/>
-          <cell r="L27"/>
-          <cell r="M27"/>
         </row>
         <row r="28">
           <cell r="A28" t="str">
@@ -1615,17 +1417,9 @@
           <cell r="D28">
             <v>1980.53</v>
           </cell>
-          <cell r="E28"/>
           <cell r="F28">
             <v>5847.7</v>
           </cell>
-          <cell r="G28"/>
-          <cell r="H28"/>
-          <cell r="I28"/>
-          <cell r="J28"/>
-          <cell r="K28"/>
-          <cell r="L28"/>
-          <cell r="M28"/>
         </row>
         <row r="29">
           <cell r="A29" t="str">
@@ -1641,39 +1435,22 @@
             <v>94625.499999999985</v>
           </cell>
           <cell r="E29">
-            <v>2722.8199999999997</v>
+            <v>2834.8199999999997</v>
           </cell>
           <cell r="F29">
-            <v>250552.85999999996</v>
-          </cell>
-          <cell r="G29"/>
-          <cell r="H29"/>
-          <cell r="I29"/>
-          <cell r="J29"/>
-          <cell r="K29"/>
-          <cell r="L29"/>
-          <cell r="M29"/>
+            <v>250664.85999999996</v>
+          </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
             <v>Assistência Médica CIF</v>
           </cell>
-          <cell r="B30"/>
-          <cell r="C30"/>
-          <cell r="D30"/>
           <cell r="E30">
             <v>75</v>
           </cell>
           <cell r="F30">
             <v>75</v>
           </cell>
-          <cell r="G30"/>
-          <cell r="H30"/>
-          <cell r="I30"/>
-          <cell r="J30"/>
-          <cell r="K30"/>
-          <cell r="L30"/>
-          <cell r="M30"/>
         </row>
         <row r="31">
           <cell r="A31" t="str">
@@ -1688,24 +1465,14 @@
           <cell r="D31">
             <v>705.03</v>
           </cell>
-          <cell r="E31"/>
           <cell r="F31">
             <v>5027.6699999999992</v>
           </cell>
-          <cell r="G31"/>
-          <cell r="H31"/>
-          <cell r="I31"/>
-          <cell r="J31"/>
-          <cell r="K31"/>
-          <cell r="L31"/>
-          <cell r="M31"/>
         </row>
         <row r="32">
           <cell r="A32" t="str">
             <v>Férias CIF</v>
           </cell>
-          <cell r="B32"/>
-          <cell r="C32"/>
           <cell r="D32">
             <v>1458.08</v>
           </cell>
@@ -1715,13 +1482,6 @@
           <cell r="F32">
             <v>2774.3</v>
           </cell>
-          <cell r="G32"/>
-          <cell r="H32"/>
-          <cell r="I32"/>
-          <cell r="J32"/>
-          <cell r="K32"/>
-          <cell r="L32"/>
-          <cell r="M32"/>
         </row>
         <row r="33">
           <cell r="A33" t="str">
@@ -1733,18 +1493,9 @@
           <cell r="C33">
             <v>5251.66</v>
           </cell>
-          <cell r="D33"/>
-          <cell r="E33"/>
           <cell r="F33">
             <v>11749.61</v>
           </cell>
-          <cell r="G33"/>
-          <cell r="H33"/>
-          <cell r="I33"/>
-          <cell r="J33"/>
-          <cell r="K33"/>
-          <cell r="L33"/>
-          <cell r="M33"/>
         </row>
         <row r="34">
           <cell r="A34" t="str">
@@ -1759,17 +1510,9 @@
           <cell r="D34">
             <v>1589.46</v>
           </cell>
-          <cell r="E34"/>
           <cell r="F34">
             <v>7515.84</v>
           </cell>
-          <cell r="G34"/>
-          <cell r="H34"/>
-          <cell r="I34"/>
-          <cell r="J34"/>
-          <cell r="K34"/>
-          <cell r="L34"/>
-          <cell r="M34"/>
         </row>
         <row r="35">
           <cell r="A35" t="str">
@@ -1778,19 +1521,9 @@
           <cell r="B35">
             <v>230</v>
           </cell>
-          <cell r="C35"/>
-          <cell r="D35"/>
-          <cell r="E35"/>
           <cell r="F35">
             <v>230</v>
           </cell>
-          <cell r="G35"/>
-          <cell r="H35"/>
-          <cell r="I35"/>
-          <cell r="J35"/>
-          <cell r="K35"/>
-          <cell r="L35"/>
-          <cell r="M35"/>
         </row>
         <row r="36">
           <cell r="A36" t="str">
@@ -1802,18 +1535,9 @@
           <cell r="C36">
             <v>8297.76</v>
           </cell>
-          <cell r="D36"/>
-          <cell r="E36"/>
           <cell r="F36">
             <v>16324.37</v>
           </cell>
-          <cell r="G36"/>
-          <cell r="H36"/>
-          <cell r="I36"/>
-          <cell r="J36"/>
-          <cell r="K36"/>
-          <cell r="L36"/>
-          <cell r="M36"/>
         </row>
         <row r="37">
           <cell r="A37" t="str">
@@ -1834,13 +1558,6 @@
           <cell r="F37">
             <v>62614.86</v>
           </cell>
-          <cell r="G37"/>
-          <cell r="H37"/>
-          <cell r="I37"/>
-          <cell r="J37"/>
-          <cell r="K37"/>
-          <cell r="L37"/>
-          <cell r="M37"/>
         </row>
         <row r="38">
           <cell r="A38" t="str">
@@ -1855,17 +1572,12 @@
           <cell r="D38">
             <v>6703.59</v>
           </cell>
-          <cell r="E38"/>
+          <cell r="E38">
+            <v>112</v>
+          </cell>
           <cell r="F38">
-            <v>32959.56</v>
-          </cell>
-          <cell r="G38"/>
-          <cell r="H38"/>
-          <cell r="I38"/>
-          <cell r="J38"/>
-          <cell r="K38"/>
-          <cell r="L38"/>
-          <cell r="M38"/>
+            <v>33071.56</v>
+          </cell>
         </row>
         <row r="39">
           <cell r="A39" t="str">
@@ -1886,13 +1598,6 @@
           <cell r="F39">
             <v>6673.58</v>
           </cell>
-          <cell r="G39"/>
-          <cell r="H39"/>
-          <cell r="I39"/>
-          <cell r="J39"/>
-          <cell r="K39"/>
-          <cell r="L39"/>
-          <cell r="M39"/>
         </row>
         <row r="40">
           <cell r="A40" t="str">
@@ -1907,38 +1612,20 @@
           <cell r="D40">
             <v>2405.31</v>
           </cell>
-          <cell r="E40"/>
           <cell r="F40">
             <v>7126.77</v>
           </cell>
-          <cell r="G40"/>
-          <cell r="H40"/>
-          <cell r="I40"/>
-          <cell r="J40"/>
-          <cell r="K40"/>
-          <cell r="L40"/>
-          <cell r="M40"/>
         </row>
         <row r="41">
           <cell r="A41" t="str">
             <v>Medicina e Segurança do Trabalho MOD</v>
           </cell>
-          <cell r="B41"/>
-          <cell r="C41"/>
           <cell r="D41">
             <v>180</v>
           </cell>
-          <cell r="E41"/>
           <cell r="F41">
             <v>180</v>
           </cell>
-          <cell r="G41"/>
-          <cell r="H41"/>
-          <cell r="I41"/>
-          <cell r="J41"/>
-          <cell r="K41"/>
-          <cell r="L41"/>
-          <cell r="M41"/>
         </row>
         <row r="42">
           <cell r="A42" t="str">
@@ -1953,17 +1640,9 @@
           <cell r="D42">
             <v>28474.9</v>
           </cell>
-          <cell r="E42"/>
           <cell r="F42">
             <v>96424.299999999988</v>
           </cell>
-          <cell r="G42"/>
-          <cell r="H42"/>
-          <cell r="I42"/>
-          <cell r="J42"/>
-          <cell r="K42"/>
-          <cell r="L42"/>
-          <cell r="M42"/>
         </row>
         <row r="43">
           <cell r="A43" t="str">
@@ -1978,17 +1657,9 @@
           <cell r="D43">
             <v>272.03999999999996</v>
           </cell>
-          <cell r="E43"/>
           <cell r="F43">
             <v>877</v>
           </cell>
-          <cell r="G43"/>
-          <cell r="H43"/>
-          <cell r="I43"/>
-          <cell r="J43"/>
-          <cell r="K43"/>
-          <cell r="L43"/>
-          <cell r="M43"/>
         </row>
         <row r="44">
           <cell r="A44" t="str">
@@ -2004,39 +1675,22 @@
             <v>149071.4</v>
           </cell>
           <cell r="E44">
-            <v>32012.289999999997</v>
+            <v>32097.289999999997</v>
           </cell>
           <cell r="F44">
-            <v>515823.87000000005</v>
-          </cell>
-          <cell r="G44"/>
-          <cell r="H44"/>
-          <cell r="I44"/>
-          <cell r="J44"/>
-          <cell r="K44"/>
-          <cell r="L44"/>
-          <cell r="M44"/>
+            <v>515908.87000000005</v>
+          </cell>
         </row>
         <row r="45">
           <cell r="A45" t="str">
             <v>Assistência Médica (Adm)</v>
           </cell>
-          <cell r="B45"/>
           <cell r="C45">
             <v>75</v>
           </cell>
-          <cell r="D45"/>
-          <cell r="E45"/>
           <cell r="F45">
             <v>75</v>
           </cell>
-          <cell r="G45"/>
-          <cell r="H45"/>
-          <cell r="I45"/>
-          <cell r="J45"/>
-          <cell r="K45"/>
-          <cell r="L45"/>
-          <cell r="M45"/>
         </row>
         <row r="46">
           <cell r="A46" t="str">
@@ -2052,18 +1706,11 @@
             <v>1065.51</v>
           </cell>
           <cell r="E46">
-            <v>85.15</v>
+            <v>170.15</v>
           </cell>
           <cell r="F46">
-            <v>4850.9799999999996</v>
-          </cell>
-          <cell r="G46"/>
-          <cell r="H46"/>
-          <cell r="I46"/>
-          <cell r="J46"/>
-          <cell r="K46"/>
-          <cell r="L46"/>
-          <cell r="M46"/>
+            <v>4935.9799999999996</v>
+          </cell>
         </row>
         <row r="47">
           <cell r="A47" t="str">
@@ -2078,23 +1725,14 @@
           <cell r="D47">
             <v>1873.7600000000002</v>
           </cell>
-          <cell r="E47"/>
           <cell r="F47">
             <v>8529.58</v>
           </cell>
-          <cell r="G47"/>
-          <cell r="H47"/>
-          <cell r="I47"/>
-          <cell r="J47"/>
-          <cell r="K47"/>
-          <cell r="L47"/>
-          <cell r="M47"/>
         </row>
         <row r="48">
           <cell r="A48" t="str">
             <v>Ferias (Adm)</v>
           </cell>
-          <cell r="B48"/>
           <cell r="C48">
             <v>297.89999999999998</v>
           </cell>
@@ -2107,13 +1745,6 @@
           <cell r="F48">
             <v>3200.04</v>
           </cell>
-          <cell r="G48"/>
-          <cell r="H48"/>
-          <cell r="I48"/>
-          <cell r="J48"/>
-          <cell r="K48"/>
-          <cell r="L48"/>
-          <cell r="M48"/>
         </row>
         <row r="49">
           <cell r="A49" t="str">
@@ -2125,18 +1756,9 @@
           <cell r="C49">
             <v>9673.7099999999991</v>
           </cell>
-          <cell r="D49"/>
-          <cell r="E49"/>
           <cell r="F49">
             <v>18448.259999999998</v>
           </cell>
-          <cell r="G49"/>
-          <cell r="H49"/>
-          <cell r="I49"/>
-          <cell r="J49"/>
-          <cell r="K49"/>
-          <cell r="L49"/>
-          <cell r="M49"/>
         </row>
         <row r="50">
           <cell r="A50" t="str">
@@ -2151,17 +1773,9 @@
           <cell r="D50">
             <v>4955.24</v>
           </cell>
-          <cell r="E50"/>
           <cell r="F50">
             <v>12393.26</v>
           </cell>
-          <cell r="G50"/>
-          <cell r="H50"/>
-          <cell r="I50"/>
-          <cell r="J50"/>
-          <cell r="K50"/>
-          <cell r="L50"/>
-          <cell r="M50"/>
         </row>
         <row r="51">
           <cell r="A51" t="str">
@@ -2176,17 +1790,9 @@
           <cell r="D51">
             <v>178.31</v>
           </cell>
-          <cell r="E51"/>
           <cell r="F51">
             <v>40890.629999999997</v>
           </cell>
-          <cell r="G51"/>
-          <cell r="H51"/>
-          <cell r="I51"/>
-          <cell r="J51"/>
-          <cell r="K51"/>
-          <cell r="L51"/>
-          <cell r="M51"/>
         </row>
         <row r="52">
           <cell r="A52" t="str">
@@ -2201,17 +1807,9 @@
           <cell r="D52">
             <v>1143.7600000000002</v>
           </cell>
-          <cell r="E52"/>
           <cell r="F52">
             <v>5835.3600000000006</v>
           </cell>
-          <cell r="G52"/>
-          <cell r="H52"/>
-          <cell r="I52"/>
-          <cell r="J52"/>
-          <cell r="K52"/>
-          <cell r="L52"/>
-          <cell r="M52"/>
         </row>
         <row r="53">
           <cell r="A53" t="str">
@@ -2232,13 +1830,6 @@
           <cell r="F53">
             <v>215044.36000000002</v>
           </cell>
-          <cell r="G53"/>
-          <cell r="H53"/>
-          <cell r="I53"/>
-          <cell r="J53"/>
-          <cell r="K53"/>
-          <cell r="L53"/>
-          <cell r="M53"/>
         </row>
         <row r="54">
           <cell r="A54" t="str">
@@ -2247,21 +1838,12 @@
           <cell r="B54">
             <v>879.73</v>
           </cell>
-          <cell r="C54"/>
           <cell r="D54">
             <v>4483.63</v>
           </cell>
-          <cell r="E54"/>
           <cell r="F54">
             <v>5363.3600000000006</v>
           </cell>
-          <cell r="G54"/>
-          <cell r="H54"/>
-          <cell r="I54"/>
-          <cell r="J54"/>
-          <cell r="K54"/>
-          <cell r="L54"/>
-          <cell r="M54"/>
         </row>
         <row r="55">
           <cell r="A55" t="str">
@@ -2276,17 +1858,9 @@
           <cell r="D55">
             <v>73572.070000000007</v>
           </cell>
-          <cell r="E55"/>
           <cell r="F55">
             <v>199224.7</v>
           </cell>
-          <cell r="G55"/>
-          <cell r="H55"/>
-          <cell r="I55"/>
-          <cell r="J55"/>
-          <cell r="K55"/>
-          <cell r="L55"/>
-          <cell r="M55"/>
         </row>
         <row r="56">
           <cell r="A56" t="str">
@@ -2301,17 +1875,9 @@
           <cell r="D56">
             <v>596.62</v>
           </cell>
-          <cell r="E56"/>
           <cell r="F56">
             <v>1968.3400000000001</v>
           </cell>
-          <cell r="G56"/>
-          <cell r="H56"/>
-          <cell r="I56"/>
-          <cell r="J56"/>
-          <cell r="K56"/>
-          <cell r="L56"/>
-          <cell r="M56"/>
         </row>
         <row r="57">
           <cell r="A57" t="str">
@@ -2327,18 +1893,11 @@
             <v>17985.82</v>
           </cell>
           <cell r="E57">
-            <v>524.9</v>
+            <v>671.6</v>
           </cell>
           <cell r="F57">
-            <v>53826.44</v>
-          </cell>
-          <cell r="G57"/>
-          <cell r="H57"/>
-          <cell r="I57"/>
-          <cell r="J57"/>
-          <cell r="K57"/>
-          <cell r="L57"/>
-          <cell r="M57"/>
+            <v>53973.14</v>
+          </cell>
         </row>
         <row r="58">
           <cell r="A58" t="str">
@@ -2353,17 +1912,9 @@
           <cell r="D58">
             <v>32.229999999999997</v>
           </cell>
-          <cell r="E58"/>
           <cell r="F58">
             <v>96.69</v>
           </cell>
-          <cell r="G58"/>
-          <cell r="H58"/>
-          <cell r="I58"/>
-          <cell r="J58"/>
-          <cell r="K58"/>
-          <cell r="L58"/>
-          <cell r="M58"/>
         </row>
         <row r="59">
           <cell r="A59" t="str">
@@ -2379,18 +1930,11 @@
             <v>782.8</v>
           </cell>
           <cell r="E59">
-            <v>76.8</v>
+            <v>223.5</v>
           </cell>
           <cell r="F59">
-            <v>1493.93</v>
-          </cell>
-          <cell r="G59"/>
-          <cell r="H59"/>
-          <cell r="I59"/>
-          <cell r="J59"/>
-          <cell r="K59"/>
-          <cell r="L59"/>
-          <cell r="M59"/>
+            <v>1640.63</v>
+          </cell>
         </row>
         <row r="60">
           <cell r="A60" t="str">
@@ -2405,17 +1949,9 @@
           <cell r="D60">
             <v>900</v>
           </cell>
-          <cell r="E60"/>
           <cell r="F60">
             <v>2600</v>
           </cell>
-          <cell r="G60"/>
-          <cell r="H60"/>
-          <cell r="I60"/>
-          <cell r="J60"/>
-          <cell r="K60"/>
-          <cell r="L60"/>
-          <cell r="M60"/>
         </row>
         <row r="61">
           <cell r="A61" t="str">
@@ -2430,17 +1966,9 @@
           <cell r="D61">
             <v>780.64</v>
           </cell>
-          <cell r="E61"/>
           <cell r="F61">
             <v>2272.96</v>
           </cell>
-          <cell r="G61"/>
-          <cell r="H61"/>
-          <cell r="I61"/>
-          <cell r="J61"/>
-          <cell r="K61"/>
-          <cell r="L61"/>
-          <cell r="M61"/>
         </row>
         <row r="62">
           <cell r="A62" t="str">
@@ -2455,17 +1983,9 @@
           <cell r="D62">
             <v>150.63</v>
           </cell>
-          <cell r="E62"/>
           <cell r="F62">
             <v>535.22</v>
           </cell>
-          <cell r="G62"/>
-          <cell r="H62"/>
-          <cell r="I62"/>
-          <cell r="J62"/>
-          <cell r="K62"/>
-          <cell r="L62"/>
-          <cell r="M62"/>
         </row>
         <row r="63">
           <cell r="A63" t="str">
@@ -2480,17 +2000,9 @@
           <cell r="D63">
             <v>350.68</v>
           </cell>
-          <cell r="E63"/>
           <cell r="F63">
             <v>1294.56</v>
           </cell>
-          <cell r="G63"/>
-          <cell r="H63"/>
-          <cell r="I63"/>
-          <cell r="J63"/>
-          <cell r="K63"/>
-          <cell r="L63"/>
-          <cell r="M63"/>
         </row>
         <row r="64">
           <cell r="A64" t="str">
@@ -2505,17 +2017,9 @@
           <cell r="D64">
             <v>100</v>
           </cell>
-          <cell r="E64"/>
           <cell r="F64">
             <v>300</v>
           </cell>
-          <cell r="G64"/>
-          <cell r="H64"/>
-          <cell r="I64"/>
-          <cell r="J64"/>
-          <cell r="K64"/>
-          <cell r="L64"/>
-          <cell r="M64"/>
         </row>
         <row r="65">
           <cell r="A65" t="str">
@@ -2527,18 +2031,9 @@
           <cell r="C65">
             <v>91.95</v>
           </cell>
-          <cell r="D65"/>
-          <cell r="E65"/>
           <cell r="F65">
             <v>190.36</v>
           </cell>
-          <cell r="G65"/>
-          <cell r="H65"/>
-          <cell r="I65"/>
-          <cell r="J65"/>
-          <cell r="K65"/>
-          <cell r="L65"/>
-          <cell r="M65"/>
         </row>
         <row r="66">
           <cell r="A66" t="str">
@@ -2553,17 +2048,9 @@
           <cell r="D66">
             <v>382.17</v>
           </cell>
-          <cell r="E66"/>
           <cell r="F66">
             <v>867.32999999999993</v>
           </cell>
-          <cell r="G66"/>
-          <cell r="H66"/>
-          <cell r="I66"/>
-          <cell r="J66"/>
-          <cell r="K66"/>
-          <cell r="L66"/>
-          <cell r="M66"/>
         </row>
         <row r="67">
           <cell r="A67" t="str">
@@ -2584,13 +2071,6 @@
           <cell r="F67">
             <v>1820.6</v>
           </cell>
-          <cell r="G67"/>
-          <cell r="H67"/>
-          <cell r="I67"/>
-          <cell r="J67"/>
-          <cell r="K67"/>
-          <cell r="L67"/>
-          <cell r="M67"/>
         </row>
         <row r="68">
           <cell r="A68" t="str">
@@ -2605,17 +2085,9 @@
           <cell r="D68">
             <v>370</v>
           </cell>
-          <cell r="E68"/>
           <cell r="F68">
             <v>1110</v>
           </cell>
-          <cell r="G68"/>
-          <cell r="H68"/>
-          <cell r="I68"/>
-          <cell r="J68"/>
-          <cell r="K68"/>
-          <cell r="L68"/>
-          <cell r="M68"/>
         </row>
         <row r="69">
           <cell r="A69" t="str">
@@ -2630,17 +2102,9 @@
           <cell r="D69">
             <v>11212.419999999998</v>
           </cell>
-          <cell r="E69"/>
           <cell r="F69">
             <v>33637.259999999995</v>
           </cell>
-          <cell r="G69"/>
-          <cell r="H69"/>
-          <cell r="I69"/>
-          <cell r="J69"/>
-          <cell r="K69"/>
-          <cell r="L69"/>
-          <cell r="M69"/>
         </row>
         <row r="70">
           <cell r="A70" t="str">
@@ -2655,17 +2119,9 @@
           <cell r="D70">
             <v>351</v>
           </cell>
-          <cell r="E70"/>
           <cell r="F70">
             <v>1319.44</v>
           </cell>
-          <cell r="G70"/>
-          <cell r="H70"/>
-          <cell r="I70"/>
-          <cell r="J70"/>
-          <cell r="K70"/>
-          <cell r="L70"/>
-          <cell r="M70"/>
         </row>
         <row r="71">
           <cell r="A71" t="str">
@@ -2680,17 +2136,9 @@
           <cell r="D71">
             <v>2146.02</v>
           </cell>
-          <cell r="E71"/>
           <cell r="F71">
             <v>6288.09</v>
           </cell>
-          <cell r="G71"/>
-          <cell r="H71"/>
-          <cell r="I71"/>
-          <cell r="J71"/>
-          <cell r="K71"/>
-          <cell r="L71"/>
-          <cell r="M71"/>
         </row>
         <row r="72">
           <cell r="A72" t="str">
@@ -2703,21 +2151,14 @@
             <v>315472.21000000002</v>
           </cell>
           <cell r="D72">
-            <v>320421.34999999998</v>
+            <v>322781.34999999998</v>
           </cell>
           <cell r="E72">
-            <v>3612.2400000000002</v>
+            <v>3833</v>
           </cell>
           <cell r="F72">
-            <v>1041252.0899999999</v>
-          </cell>
-          <cell r="G72"/>
-          <cell r="H72"/>
-          <cell r="I72"/>
-          <cell r="J72"/>
-          <cell r="K72"/>
-          <cell r="L72"/>
-          <cell r="M72"/>
+            <v>1043832.8499999999</v>
+          </cell>
         </row>
         <row r="73">
           <cell r="A73" t="str">
@@ -2726,19 +2167,9 @@
           <cell r="B73">
             <v>1368</v>
           </cell>
-          <cell r="C73"/>
-          <cell r="D73"/>
-          <cell r="E73"/>
           <cell r="F73">
             <v>1368</v>
           </cell>
-          <cell r="G73"/>
-          <cell r="H73"/>
-          <cell r="I73"/>
-          <cell r="J73"/>
-          <cell r="K73"/>
-          <cell r="L73"/>
-          <cell r="M73"/>
         </row>
         <row r="74">
           <cell r="A74" t="str">
@@ -2751,19 +2182,11 @@
             <v>2415</v>
           </cell>
           <cell r="D74">
-            <v>182.48000000000002</v>
-          </cell>
-          <cell r="E74"/>
+            <v>3042.48</v>
+          </cell>
           <cell r="F74">
-            <v>4552.4799999999996</v>
-          </cell>
-          <cell r="G74"/>
-          <cell r="H74"/>
-          <cell r="I74"/>
-          <cell r="J74"/>
-          <cell r="K74"/>
-          <cell r="L74"/>
-          <cell r="M74"/>
+            <v>7412.48</v>
+          </cell>
         </row>
         <row r="75">
           <cell r="A75" t="str">
@@ -2778,17 +2201,9 @@
           <cell r="D75">
             <v>70184.260000000009</v>
           </cell>
-          <cell r="E75"/>
           <cell r="F75">
             <v>158828.48000000001</v>
           </cell>
-          <cell r="G75"/>
-          <cell r="H75"/>
-          <cell r="I75"/>
-          <cell r="J75"/>
-          <cell r="K75"/>
-          <cell r="L75"/>
-          <cell r="M75"/>
         </row>
         <row r="76">
           <cell r="A76" t="str">
@@ -2803,17 +2218,9 @@
           <cell r="D76">
             <v>88339.049999999988</v>
           </cell>
-          <cell r="E76"/>
           <cell r="F76">
             <v>284165.46999999991</v>
           </cell>
-          <cell r="G76"/>
-          <cell r="H76"/>
-          <cell r="I76"/>
-          <cell r="J76"/>
-          <cell r="K76"/>
-          <cell r="L76"/>
-          <cell r="M76"/>
         </row>
         <row r="77">
           <cell r="A77" t="str">
@@ -2828,17 +2235,9 @@
           <cell r="D77">
             <v>10515.810000000001</v>
           </cell>
-          <cell r="E77"/>
           <cell r="F77">
             <v>22781.65</v>
           </cell>
-          <cell r="G77"/>
-          <cell r="H77"/>
-          <cell r="I77"/>
-          <cell r="J77"/>
-          <cell r="K77"/>
-          <cell r="L77"/>
-          <cell r="M77"/>
         </row>
         <row r="78">
           <cell r="A78" t="str">
@@ -2851,19 +2250,14 @@
             <v>10422.07</v>
           </cell>
           <cell r="D78">
-            <v>14362.09</v>
-          </cell>
-          <cell r="E78"/>
+            <v>13862.09</v>
+          </cell>
+          <cell r="E78">
+            <v>220.76</v>
+          </cell>
           <cell r="F78">
-            <v>38462.050000000003</v>
-          </cell>
-          <cell r="G78"/>
-          <cell r="H78"/>
-          <cell r="I78"/>
-          <cell r="J78"/>
-          <cell r="K78"/>
-          <cell r="L78"/>
-          <cell r="M78"/>
+            <v>38182.810000000005</v>
+          </cell>
         </row>
         <row r="79">
           <cell r="A79" t="str">
@@ -2878,17 +2272,9 @@
           <cell r="D79">
             <v>24000</v>
           </cell>
-          <cell r="E79"/>
           <cell r="F79">
             <v>72000</v>
           </cell>
-          <cell r="G79"/>
-          <cell r="H79"/>
-          <cell r="I79"/>
-          <cell r="J79"/>
-          <cell r="K79"/>
-          <cell r="L79"/>
-          <cell r="M79"/>
         </row>
         <row r="80">
           <cell r="A80" t="str">
@@ -2909,36 +2295,20 @@
           <cell r="F80">
             <v>199557.97999999998</v>
           </cell>
-          <cell r="G80"/>
-          <cell r="H80"/>
-          <cell r="I80"/>
-          <cell r="J80"/>
-          <cell r="K80"/>
-          <cell r="L80"/>
-          <cell r="M80"/>
         </row>
         <row r="81">
           <cell r="A81" t="str">
             <v>Fretes</v>
           </cell>
-          <cell r="B81"/>
           <cell r="C81">
             <v>2334.16</v>
           </cell>
           <cell r="D81">
             <v>709</v>
           </cell>
-          <cell r="E81"/>
           <cell r="F81">
             <v>3043.16</v>
           </cell>
-          <cell r="G81"/>
-          <cell r="H81"/>
-          <cell r="I81"/>
-          <cell r="J81"/>
-          <cell r="K81"/>
-          <cell r="L81"/>
-          <cell r="M81"/>
         </row>
         <row r="82">
           <cell r="A82" t="str">
@@ -2953,17 +2323,9 @@
           <cell r="D82">
             <v>420.81</v>
           </cell>
-          <cell r="E82"/>
           <cell r="F82">
             <v>2737.9</v>
           </cell>
-          <cell r="G82"/>
-          <cell r="H82"/>
-          <cell r="I82"/>
-          <cell r="J82"/>
-          <cell r="K82"/>
-          <cell r="L82"/>
-          <cell r="M82"/>
         </row>
         <row r="83">
           <cell r="A83" t="str">
@@ -2978,17 +2340,9 @@
           <cell r="D83">
             <v>19808.55</v>
           </cell>
-          <cell r="E83"/>
           <cell r="F83">
             <v>48136.75</v>
           </cell>
-          <cell r="G83"/>
-          <cell r="H83"/>
-          <cell r="I83"/>
-          <cell r="J83"/>
-          <cell r="K83"/>
-          <cell r="L83"/>
-          <cell r="M83"/>
         </row>
         <row r="84">
           <cell r="A84" t="str">
@@ -3003,17 +2357,9 @@
           <cell r="D84">
             <v>4296.6099999999997</v>
           </cell>
-          <cell r="E84"/>
           <cell r="F84">
             <v>12889.829999999998</v>
           </cell>
-          <cell r="G84"/>
-          <cell r="H84"/>
-          <cell r="I84"/>
-          <cell r="J84"/>
-          <cell r="K84"/>
-          <cell r="L84"/>
-          <cell r="M84"/>
         </row>
         <row r="85">
           <cell r="A85" t="str">
@@ -3034,13 +2380,6 @@
           <cell r="F85">
             <v>17443.36</v>
           </cell>
-          <cell r="G85"/>
-          <cell r="H85"/>
-          <cell r="I85"/>
-          <cell r="J85"/>
-          <cell r="K85"/>
-          <cell r="L85"/>
-          <cell r="M85"/>
         </row>
         <row r="86">
           <cell r="A86" t="str">
@@ -3061,13 +2400,6 @@
           <cell r="F86">
             <v>2378.4299999999998</v>
           </cell>
-          <cell r="G86"/>
-          <cell r="H86"/>
-          <cell r="I86"/>
-          <cell r="J86"/>
-          <cell r="K86"/>
-          <cell r="L86"/>
-          <cell r="M86"/>
         </row>
         <row r="87">
           <cell r="A87" t="str">
@@ -3082,17 +2414,9 @@
           <cell r="D87">
             <v>9958.6499999999978</v>
           </cell>
-          <cell r="E87"/>
           <cell r="F87">
             <v>24550.729999999996</v>
           </cell>
-          <cell r="G87"/>
-          <cell r="H87"/>
-          <cell r="I87"/>
-          <cell r="J87"/>
-          <cell r="K87"/>
-          <cell r="L87"/>
-          <cell r="M87"/>
         </row>
         <row r="88">
           <cell r="A88" t="str">
@@ -3113,13 +2437,6 @@
           <cell r="F88">
             <v>13489.59</v>
           </cell>
-          <cell r="G88"/>
-          <cell r="H88"/>
-          <cell r="I88"/>
-          <cell r="J88"/>
-          <cell r="K88"/>
-          <cell r="L88"/>
-          <cell r="M88"/>
         </row>
         <row r="89">
           <cell r="A89" t="str">
@@ -3131,18 +2448,9 @@
           <cell r="C89">
             <v>45445.030000000006</v>
           </cell>
-          <cell r="D89"/>
-          <cell r="E89"/>
           <cell r="F89">
             <v>81144.87000000001</v>
           </cell>
-          <cell r="G89"/>
-          <cell r="H89"/>
-          <cell r="I89"/>
-          <cell r="J89"/>
-          <cell r="K89"/>
-          <cell r="L89"/>
-          <cell r="M89"/>
         </row>
         <row r="90">
           <cell r="A90" t="str">
@@ -3154,18 +2462,9 @@
           <cell r="C90">
             <v>1807.69</v>
           </cell>
-          <cell r="D90"/>
-          <cell r="E90"/>
           <cell r="F90">
             <v>2545.85</v>
           </cell>
-          <cell r="G90"/>
-          <cell r="H90"/>
-          <cell r="I90"/>
-          <cell r="J90"/>
-          <cell r="K90"/>
-          <cell r="L90"/>
-          <cell r="M90"/>
         </row>
         <row r="91">
           <cell r="A91" t="str">
@@ -3180,17 +2479,9 @@
           <cell r="D91">
             <v>21717.43</v>
           </cell>
-          <cell r="E91"/>
           <cell r="F91">
             <v>51175.509999999995</v>
           </cell>
-          <cell r="G91"/>
-          <cell r="H91"/>
-          <cell r="I91"/>
-          <cell r="J91"/>
-          <cell r="K91"/>
-          <cell r="L91"/>
-          <cell r="M91"/>
         </row>
         <row r="92">
           <cell r="A92" t="str">
@@ -3203,21 +2494,14 @@
             <v>63742.03</v>
           </cell>
           <cell r="D92">
-            <v>66912.58</v>
+            <v>67412.58</v>
           </cell>
           <cell r="E92">
-            <v>425.6</v>
+            <v>6603.51</v>
           </cell>
           <cell r="F92">
-            <v>205260.27</v>
-          </cell>
-          <cell r="G92"/>
-          <cell r="H92"/>
-          <cell r="I92"/>
-          <cell r="J92"/>
-          <cell r="K92"/>
-          <cell r="L92"/>
-          <cell r="M92"/>
+            <v>211938.18</v>
+          </cell>
         </row>
         <row r="93">
           <cell r="A93" t="str">
@@ -3230,19 +2514,14 @@
             <v>14452.9</v>
           </cell>
           <cell r="D93">
-            <v>19630.41</v>
-          </cell>
-          <cell r="E93"/>
+            <v>20130.41</v>
+          </cell>
+          <cell r="E93">
+            <v>5008.41</v>
+          </cell>
           <cell r="F93">
-            <v>50116.74</v>
-          </cell>
-          <cell r="G93"/>
-          <cell r="H93"/>
-          <cell r="I93"/>
-          <cell r="J93"/>
-          <cell r="K93"/>
-          <cell r="L93"/>
-          <cell r="M93"/>
+            <v>55625.149999999994</v>
+          </cell>
         </row>
         <row r="94">
           <cell r="A94" t="str">
@@ -3257,17 +2536,9 @@
           <cell r="D94">
             <v>6035.41</v>
           </cell>
-          <cell r="E94"/>
           <cell r="F94">
             <v>18106.23</v>
           </cell>
-          <cell r="G94"/>
-          <cell r="H94"/>
-          <cell r="I94"/>
-          <cell r="J94"/>
-          <cell r="K94"/>
-          <cell r="L94"/>
-          <cell r="M94"/>
         </row>
         <row r="95">
           <cell r="A95" t="str">
@@ -3282,17 +2553,12 @@
           <cell r="D95">
             <v>12244</v>
           </cell>
-          <cell r="E95"/>
+          <cell r="E95">
+            <v>715</v>
+          </cell>
           <cell r="F95">
-            <v>35947</v>
-          </cell>
-          <cell r="G95"/>
-          <cell r="H95"/>
-          <cell r="I95"/>
-          <cell r="J95"/>
-          <cell r="K95"/>
-          <cell r="L95"/>
-          <cell r="M95"/>
+            <v>36662</v>
+          </cell>
         </row>
         <row r="96">
           <cell r="A96" t="str">
@@ -3307,17 +2573,9 @@
           <cell r="D96">
             <v>9436</v>
           </cell>
-          <cell r="E96"/>
           <cell r="F96">
             <v>27838</v>
           </cell>
-          <cell r="G96"/>
-          <cell r="H96"/>
-          <cell r="I96"/>
-          <cell r="J96"/>
-          <cell r="K96"/>
-          <cell r="L96"/>
-          <cell r="M96"/>
         </row>
         <row r="97">
           <cell r="A97" t="str">
@@ -3332,17 +2590,9 @@
           <cell r="D97">
             <v>7769.93</v>
           </cell>
-          <cell r="E97"/>
           <cell r="F97">
             <v>23805.78</v>
           </cell>
-          <cell r="G97"/>
-          <cell r="H97"/>
-          <cell r="I97"/>
-          <cell r="J97"/>
-          <cell r="K97"/>
-          <cell r="L97"/>
-          <cell r="M97"/>
         </row>
         <row r="98">
           <cell r="A98" t="str">
@@ -3363,13 +2613,6 @@
           <cell r="F98">
             <v>46147.02</v>
           </cell>
-          <cell r="G98"/>
-          <cell r="H98"/>
-          <cell r="I98"/>
-          <cell r="J98"/>
-          <cell r="K98"/>
-          <cell r="L98"/>
-          <cell r="M98"/>
         </row>
         <row r="99">
           <cell r="A99" t="str">
@@ -3385,18 +2628,11 @@
             <v>978.5</v>
           </cell>
           <cell r="E99">
-            <v>44</v>
+            <v>498.5</v>
           </cell>
           <cell r="F99">
-            <v>3299.5</v>
-          </cell>
-          <cell r="G99"/>
-          <cell r="H99"/>
-          <cell r="I99"/>
-          <cell r="J99"/>
-          <cell r="K99"/>
-          <cell r="L99"/>
-          <cell r="M99"/>
+            <v>3754</v>
+          </cell>
         </row>
         <row r="100">
           <cell r="A100" t="str">
@@ -3412,18 +2648,11 @@
             <v>55657.97</v>
           </cell>
           <cell r="E100">
-            <v>13340.41</v>
+            <v>19187.699999999997</v>
           </cell>
           <cell r="F100">
-            <v>186998.71999999997</v>
-          </cell>
-          <cell r="G100"/>
-          <cell r="H100"/>
-          <cell r="I100"/>
-          <cell r="J100"/>
-          <cell r="K100"/>
-          <cell r="L100"/>
-          <cell r="M100"/>
+            <v>192846.00999999998</v>
+          </cell>
         </row>
         <row r="101">
           <cell r="A101" t="str">
@@ -3439,18 +2668,11 @@
             <v>9300.989999999998</v>
           </cell>
           <cell r="E101">
-            <v>1112.22</v>
+            <v>2596.56</v>
           </cell>
           <cell r="F101">
-            <v>29841.849999999991</v>
-          </cell>
-          <cell r="G101"/>
-          <cell r="H101"/>
-          <cell r="I101"/>
-          <cell r="J101"/>
-          <cell r="K101"/>
-          <cell r="L101"/>
-          <cell r="M101"/>
+            <v>31326.189999999991</v>
+          </cell>
         </row>
         <row r="102">
           <cell r="A102" t="str">
@@ -3466,18 +2688,11 @@
             <v>251.57000000000002</v>
           </cell>
           <cell r="E102">
-            <v>15.33</v>
+            <v>26.55</v>
           </cell>
           <cell r="F102">
-            <v>506.43</v>
-          </cell>
-          <cell r="G102"/>
-          <cell r="H102"/>
-          <cell r="I102"/>
-          <cell r="J102"/>
-          <cell r="K102"/>
-          <cell r="L102"/>
-          <cell r="M102"/>
+            <v>517.65</v>
+          </cell>
         </row>
         <row r="103">
           <cell r="A103" t="str">
@@ -3492,17 +2707,9 @@
           <cell r="D103">
             <v>13530.41</v>
           </cell>
-          <cell r="E103"/>
           <cell r="F103">
             <v>31520.240000000002</v>
           </cell>
-          <cell r="G103"/>
-          <cell r="H103"/>
-          <cell r="I103"/>
-          <cell r="J103"/>
-          <cell r="K103"/>
-          <cell r="L103"/>
-          <cell r="M103"/>
         </row>
         <row r="104">
           <cell r="A104" t="str">
@@ -3523,34 +2730,17 @@
           <cell r="F104">
             <v>32544.299999999996</v>
           </cell>
-          <cell r="G104"/>
-          <cell r="H104"/>
-          <cell r="I104"/>
-          <cell r="J104"/>
-          <cell r="K104"/>
-          <cell r="L104"/>
-          <cell r="M104"/>
         </row>
         <row r="105">
           <cell r="A105" t="str">
             <v>Juros Pagos</v>
           </cell>
-          <cell r="B105"/>
           <cell r="C105">
             <v>95.75</v>
           </cell>
-          <cell r="D105"/>
-          <cell r="E105"/>
           <cell r="F105">
             <v>95.75</v>
           </cell>
-          <cell r="G105"/>
-          <cell r="H105"/>
-          <cell r="I105"/>
-          <cell r="J105"/>
-          <cell r="K105"/>
-          <cell r="L105"/>
-          <cell r="M105"/>
         </row>
         <row r="106">
           <cell r="A106" t="str">
@@ -3566,18 +2756,11 @@
             <v>29003.100000000002</v>
           </cell>
           <cell r="E106">
-            <v>4523.3</v>
+            <v>8875.0299999999988</v>
           </cell>
           <cell r="F106">
-            <v>92490.15</v>
-          </cell>
-          <cell r="G106"/>
-          <cell r="H106"/>
-          <cell r="I106"/>
-          <cell r="J106"/>
-          <cell r="K106"/>
-          <cell r="L106"/>
-          <cell r="M106"/>
+            <v>96841.87999999999</v>
+          </cell>
         </row>
         <row r="107">
           <cell r="A107" t="str">
@@ -3598,13 +2781,6 @@
           <cell r="F107">
             <v>106704.95</v>
           </cell>
-          <cell r="G107"/>
-          <cell r="H107"/>
-          <cell r="I107"/>
-          <cell r="J107"/>
-          <cell r="K107"/>
-          <cell r="L107"/>
-          <cell r="M107"/>
         </row>
         <row r="108">
           <cell r="A108" t="str">
@@ -3619,17 +2795,9 @@
           <cell r="D108">
             <v>2407.11</v>
           </cell>
-          <cell r="E108"/>
           <cell r="F108">
             <v>16919.339999999997</v>
           </cell>
-          <cell r="G108"/>
-          <cell r="H108"/>
-          <cell r="I108"/>
-          <cell r="J108"/>
-          <cell r="K108"/>
-          <cell r="L108"/>
-          <cell r="M108"/>
         </row>
         <row r="109">
           <cell r="A109" t="str">
@@ -3644,17 +2812,9 @@
           <cell r="D109">
             <v>3037.44</v>
           </cell>
-          <cell r="E109"/>
           <cell r="F109">
             <v>9112.32</v>
           </cell>
-          <cell r="G109"/>
-          <cell r="H109"/>
-          <cell r="I109"/>
-          <cell r="J109"/>
-          <cell r="K109"/>
-          <cell r="L109"/>
-          <cell r="M109"/>
         </row>
         <row r="110">
           <cell r="A110" t="str">
@@ -3669,17 +2829,9 @@
           <cell r="D110">
             <v>2570</v>
           </cell>
-          <cell r="E110"/>
           <cell r="F110">
             <v>22294.41</v>
           </cell>
-          <cell r="G110"/>
-          <cell r="H110"/>
-          <cell r="I110"/>
-          <cell r="J110"/>
-          <cell r="K110"/>
-          <cell r="L110"/>
-          <cell r="M110"/>
         </row>
         <row r="111">
           <cell r="A111" t="str">
@@ -3700,34 +2852,17 @@
           <cell r="F111">
             <v>54293.880000000005</v>
           </cell>
-          <cell r="G111"/>
-          <cell r="H111"/>
-          <cell r="I111"/>
-          <cell r="J111"/>
-          <cell r="K111"/>
-          <cell r="L111"/>
-          <cell r="M111"/>
         </row>
         <row r="112">
           <cell r="A112" t="str">
             <v>Moveis e Utensilios</v>
           </cell>
-          <cell r="B112"/>
-          <cell r="C112"/>
           <cell r="D112">
             <v>4085</v>
           </cell>
-          <cell r="E112"/>
           <cell r="F112">
             <v>4085</v>
           </cell>
-          <cell r="G112"/>
-          <cell r="H112"/>
-          <cell r="I112"/>
-          <cell r="J112"/>
-          <cell r="K112"/>
-          <cell r="L112"/>
-          <cell r="M112"/>
         </row>
         <row r="113">
           <cell r="A113" t="str">
@@ -3740,282 +2875,19 @@
             <v>1221830.2699999996</v>
           </cell>
           <cell r="D113">
-            <v>1026479.7100000004</v>
+            <v>1192889.1400000004</v>
           </cell>
           <cell r="E113">
-            <v>64433.77</v>
+            <v>79220.48000000001</v>
           </cell>
           <cell r="F113">
-            <v>3610362.1000000006</v>
-          </cell>
-          <cell r="G113"/>
-          <cell r="H113"/>
-          <cell r="I113"/>
-          <cell r="J113"/>
-          <cell r="K113"/>
-          <cell r="L113"/>
-          <cell r="M113"/>
-        </row>
-        <row r="114">
-          <cell r="A114"/>
-          <cell r="B114"/>
-          <cell r="C114"/>
-          <cell r="D114"/>
-          <cell r="E114"/>
-          <cell r="F114"/>
-          <cell r="G114"/>
-          <cell r="H114"/>
-          <cell r="I114"/>
-          <cell r="J114"/>
-          <cell r="K114"/>
-          <cell r="L114"/>
-          <cell r="M114"/>
-        </row>
-        <row r="115">
-          <cell r="A115"/>
-          <cell r="B115"/>
-          <cell r="C115"/>
-          <cell r="D115"/>
-          <cell r="E115"/>
-          <cell r="F115"/>
-          <cell r="G115"/>
-          <cell r="H115"/>
-          <cell r="I115"/>
-          <cell r="J115"/>
-          <cell r="K115"/>
-          <cell r="L115"/>
-          <cell r="M115"/>
-        </row>
-        <row r="116">
-          <cell r="A116"/>
-          <cell r="B116"/>
-          <cell r="C116"/>
-          <cell r="D116"/>
-          <cell r="E116"/>
-          <cell r="F116"/>
-          <cell r="G116"/>
-          <cell r="H116"/>
-          <cell r="I116"/>
-          <cell r="J116"/>
-          <cell r="K116"/>
-          <cell r="L116"/>
-          <cell r="M116"/>
-        </row>
-        <row r="117">
-          <cell r="A117"/>
-          <cell r="B117"/>
-          <cell r="C117"/>
-          <cell r="D117"/>
-          <cell r="E117"/>
-          <cell r="F117"/>
-          <cell r="G117"/>
-          <cell r="H117"/>
-          <cell r="I117"/>
-          <cell r="J117"/>
-          <cell r="K117"/>
-          <cell r="L117"/>
-          <cell r="M117"/>
-        </row>
-        <row r="118">
-          <cell r="A118"/>
-          <cell r="B118"/>
-          <cell r="C118"/>
-          <cell r="D118"/>
-          <cell r="E118"/>
-          <cell r="F118"/>
-          <cell r="G118"/>
-          <cell r="H118"/>
-          <cell r="I118"/>
-          <cell r="J118"/>
-          <cell r="K118"/>
-          <cell r="L118"/>
-          <cell r="M118"/>
-        </row>
-        <row r="119">
-          <cell r="A119"/>
-          <cell r="B119"/>
-          <cell r="C119"/>
-          <cell r="D119"/>
-          <cell r="E119"/>
-          <cell r="F119"/>
-          <cell r="G119"/>
-          <cell r="H119"/>
-          <cell r="I119"/>
-          <cell r="J119"/>
-          <cell r="K119"/>
-          <cell r="L119"/>
-          <cell r="M119"/>
-        </row>
-        <row r="120">
-          <cell r="A120"/>
-          <cell r="B120"/>
-          <cell r="C120"/>
-          <cell r="D120"/>
-          <cell r="E120"/>
-          <cell r="F120"/>
-          <cell r="G120"/>
-          <cell r="H120"/>
-          <cell r="I120"/>
-          <cell r="J120"/>
-          <cell r="K120"/>
-          <cell r="L120"/>
-          <cell r="M120"/>
-        </row>
-        <row r="121">
-          <cell r="A121"/>
-          <cell r="B121"/>
-          <cell r="C121"/>
-          <cell r="D121"/>
-          <cell r="E121"/>
-          <cell r="F121"/>
-          <cell r="G121"/>
-          <cell r="H121"/>
-          <cell r="I121"/>
-          <cell r="J121"/>
-          <cell r="K121"/>
-          <cell r="L121"/>
-          <cell r="M121"/>
-        </row>
-        <row r="122">
-          <cell r="A122"/>
-          <cell r="B122"/>
-          <cell r="C122"/>
-          <cell r="D122"/>
-          <cell r="E122"/>
-          <cell r="F122"/>
-          <cell r="G122"/>
-          <cell r="H122"/>
-          <cell r="I122"/>
-          <cell r="J122"/>
-          <cell r="K122"/>
-          <cell r="L122"/>
-          <cell r="M122"/>
-        </row>
-        <row r="123">
-          <cell r="A123"/>
-          <cell r="B123"/>
-          <cell r="C123"/>
-          <cell r="D123"/>
-          <cell r="E123"/>
-          <cell r="F123"/>
-          <cell r="G123"/>
-          <cell r="H123"/>
-          <cell r="I123"/>
-          <cell r="J123"/>
-          <cell r="K123"/>
-          <cell r="L123"/>
-          <cell r="M123"/>
-        </row>
-        <row r="124">
-          <cell r="A124"/>
-          <cell r="B124"/>
-          <cell r="C124"/>
-          <cell r="D124"/>
-          <cell r="E124"/>
-          <cell r="F124"/>
-          <cell r="G124"/>
-          <cell r="H124"/>
-          <cell r="I124"/>
-          <cell r="J124"/>
-          <cell r="K124"/>
-          <cell r="L124"/>
-          <cell r="M124"/>
-        </row>
-        <row r="125">
-          <cell r="A125"/>
-          <cell r="B125"/>
-          <cell r="C125"/>
-          <cell r="D125"/>
-          <cell r="E125"/>
-          <cell r="F125"/>
-          <cell r="G125"/>
-          <cell r="H125"/>
-          <cell r="I125"/>
-          <cell r="J125"/>
-          <cell r="K125"/>
-          <cell r="L125"/>
-          <cell r="M125"/>
-        </row>
-        <row r="126">
-          <cell r="A126"/>
-          <cell r="B126"/>
-          <cell r="C126"/>
-          <cell r="D126"/>
-          <cell r="E126"/>
-          <cell r="F126"/>
-          <cell r="G126"/>
-          <cell r="H126"/>
-          <cell r="I126"/>
-          <cell r="J126"/>
-          <cell r="K126"/>
-          <cell r="L126"/>
-          <cell r="M126"/>
-        </row>
-        <row r="127">
-          <cell r="A127"/>
-          <cell r="B127"/>
-          <cell r="C127"/>
-          <cell r="D127"/>
-          <cell r="E127"/>
-          <cell r="F127"/>
-          <cell r="G127"/>
-          <cell r="H127"/>
-          <cell r="I127"/>
-          <cell r="J127"/>
-          <cell r="K127"/>
-          <cell r="L127"/>
-          <cell r="M127"/>
-        </row>
-        <row r="128">
-          <cell r="A128"/>
-          <cell r="B128"/>
-          <cell r="C128"/>
-          <cell r="D128"/>
-          <cell r="E128"/>
-          <cell r="F128"/>
-          <cell r="G128"/>
-          <cell r="H128"/>
-          <cell r="I128"/>
-          <cell r="J128"/>
-          <cell r="K128"/>
-          <cell r="L128"/>
-          <cell r="M128"/>
-        </row>
-        <row r="129">
-          <cell r="A129"/>
-          <cell r="B129"/>
-          <cell r="C129"/>
-          <cell r="D129"/>
-          <cell r="E129"/>
-          <cell r="F129"/>
-          <cell r="G129"/>
-          <cell r="H129"/>
-          <cell r="I129"/>
-          <cell r="J129"/>
-          <cell r="K129"/>
-          <cell r="L129"/>
-          <cell r="M129"/>
-        </row>
-        <row r="130">
-          <cell r="A130"/>
-          <cell r="B130"/>
-          <cell r="C130"/>
-          <cell r="D130"/>
-          <cell r="E130"/>
-          <cell r="F130"/>
-          <cell r="G130"/>
-          <cell r="H130"/>
-          <cell r="I130"/>
-          <cell r="J130"/>
-          <cell r="K130"/>
-          <cell r="L130"/>
-          <cell r="M130"/>
+            <v>3791558.2399999993</v>
+          </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4464,30 +3336,30 @@
         <v>157</v>
       </c>
       <c r="M4" s="43"/>
-      <c r="N4" s="50" t="s">
+      <c r="N4" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="51" t="s">
+      <c r="O4" s="51"/>
+      <c r="P4" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="51"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="44" t="s">
         <v>157</v>
       </c>
       <c r="S4" s="43"/>
-      <c r="T4" s="51" t="s">
+      <c r="T4" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="U4" s="51"/>
+      <c r="U4" s="52"/>
       <c r="V4" s="44" t="s">
         <v>157</v>
       </c>
       <c r="W4" s="43"/>
-      <c r="X4" s="51" t="s">
+      <c r="X4" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="Y4" s="51"/>
+      <c r="Y4" s="52"/>
       <c r="Z4" s="44" t="s">
         <v>157</v>
       </c>
@@ -5093,11 +3965,11 @@
       </c>
       <c r="X12" s="7">
         <f>SUM(X13:X19)</f>
-        <v>5788.56</v>
+        <v>169337.99000000002</v>
       </c>
       <c r="Y12" s="14">
         <f t="shared" ref="Y12:Y19" si="2">IFERROR((X12*-1)/V12-1,"")</f>
-        <v>-0.97343153771454372</v>
+        <v>-0.2227687022661996</v>
       </c>
       <c r="Z12" s="7">
         <v>-190322.90502026965</v>
@@ -5234,11 +4106,11 @@
       </c>
       <c r="X13" s="6">
         <f>IFERROR(VLOOKUP($I13,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>81164.490000000005</v>
       </c>
       <c r="Y13" s="46">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>0.10621680012152424</v>
       </c>
       <c r="Z13" s="6">
         <v>-64093.317628933997</v>
@@ -5374,11 +4246,11 @@
       </c>
       <c r="X14" s="6">
         <f>IFERROR(VLOOKUP($I14,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>39057.060000000005</v>
       </c>
       <c r="Y14" s="46">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>-0.43420630657245451</v>
       </c>
       <c r="Z14" s="6">
         <v>-60301.537387527591</v>
@@ -5514,11 +4386,11 @@
       </c>
       <c r="X15" s="6">
         <f>IFERROR(VLOOKUP($I15,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>3431.3</v>
       </c>
       <c r="Y15" s="46">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>-0.55444484425087404</v>
       </c>
       <c r="Z15" s="6">
         <v>-6727.3520412049038</v>
@@ -5654,11 +4526,11 @@
       </c>
       <c r="X16" s="6">
         <f>IFERROR(VLOOKUP($I16,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>22197.7</v>
       </c>
       <c r="Y16" s="46">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>-0.25221355341630158</v>
       </c>
       <c r="Z16" s="6">
         <v>-25930.884231553449</v>
@@ -5794,11 +4666,11 @@
       </c>
       <c r="X17" s="6">
         <f>IFERROR(VLOOKUP($I17,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>15906.25</v>
       </c>
       <c r="Y17" s="46">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>-0.55451498884559347</v>
       </c>
       <c r="Z17" s="6">
         <v>-31190.450372859104</v>
@@ -5934,11 +4806,11 @@
       </c>
       <c r="X18" s="6">
         <f>IFERROR(VLOOKUP($I18,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>128.6</v>
+        <v>1921.23</v>
       </c>
       <c r="Y18" s="46">
         <f t="shared" ref="Y18" si="4">IFERROR((X18*-1)/V18-1,"")</f>
-        <v>-0.94597465860797803</v>
+        <v>-0.19288408520533074</v>
       </c>
       <c r="Z18" s="6">
         <v>-2079.363358190607</v>
@@ -6202,11 +5074,11 @@
       </c>
       <c r="X21" s="48">
         <f>X10-X12</f>
-        <v>2620454.8399999994</v>
+        <v>2456905.4099999992</v>
       </c>
       <c r="Y21" s="14">
         <f>X21/V21-1</f>
-        <v>1.4675183670345815E-2</v>
+        <v>-4.8653344412370902E-2</v>
       </c>
       <c r="Z21" s="7">
         <v>2255986.9281451502</v>
@@ -11683,11 +10555,11 @@
       </c>
       <c r="X64" s="48">
         <f>X21-X23</f>
-        <v>1227006.6299999997</v>
+        <v>1063457.1999999995</v>
       </c>
       <c r="Y64" s="14">
         <f>X64/V64-1</f>
-        <v>0.15846260853875238</v>
+        <v>4.0495070359296559E-3</v>
       </c>
       <c r="Z64" s="7">
         <v>869130.19069200032</v>
@@ -11814,11 +10686,11 @@
       </c>
       <c r="X66" s="7">
         <f>SUM(X67+X85+X101+X123)</f>
-        <v>554391.15</v>
+        <v>557251.15</v>
       </c>
       <c r="Y66" s="14">
         <f t="shared" ref="Y66" si="18">IFERROR((X66*-1)/V66-1,"")</f>
-        <v>-0.24712655015902574</v>
+        <v>-0.24324261718761164</v>
       </c>
       <c r="Z66" s="7">
         <v>-702233.64180127438</v>
@@ -16508,11 +15380,11 @@
       </c>
       <c r="X101" s="8">
         <f>SUM(X102:X122)</f>
-        <v>320421.35000000003</v>
+        <v>322781.34999999998</v>
       </c>
       <c r="Y101" s="45">
         <f>(X101*-1)/V101-1</f>
-        <v>-0.31876017466872508</v>
+        <v>-0.31374263764198906</v>
       </c>
       <c r="Z101" s="8">
         <v>-436216.95079197281</v>
@@ -16649,11 +15521,11 @@
       </c>
       <c r="X102" s="6">
         <f>IFERROR(VLOOKUP($I102,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>182.48000000000002</v>
+        <v>3042.48</v>
       </c>
       <c r="Y102" s="46">
         <f t="shared" ref="Y102:Y122" si="24">IFERROR((X102*-1)/V102-1,"")</f>
-        <v>-0.95135259063628008</v>
+        <v>-0.18890415365557589</v>
       </c>
       <c r="Z102" s="6">
         <v>-3751.0733333333333</v>
@@ -18424,11 +17296,11 @@
       </c>
       <c r="X115" s="6">
         <f>IFERROR(VLOOKUP($I115,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>14362.09</v>
+        <v>13862.09</v>
       </c>
       <c r="Y115" s="46">
         <f t="shared" si="24"/>
-        <v>-0.16983683887502188</v>
+        <v>-0.19873803504928966</v>
       </c>
       <c r="Z115" s="6">
         <v>-17300.321999999996</v>
@@ -19502,11 +18374,11 @@
       </c>
       <c r="X123" s="8">
         <f>SUM(X124:X130)</f>
-        <v>66912.58</v>
+        <v>67412.58</v>
       </c>
       <c r="Y123" s="45">
         <f>(X123*-1)/V123-1</f>
-        <v>-5.4948638066430244E-2</v>
+        <v>-4.7886801847190408E-2</v>
       </c>
       <c r="Z123" s="8">
         <v>-70803.114724999963</v>
@@ -19767,11 +18639,11 @@
       </c>
       <c r="X125" s="6">
         <f>IFERROR(VLOOKUP($I125,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>19630.41</v>
+        <v>20130.41</v>
       </c>
       <c r="Y125" s="46">
         <f t="shared" si="26"/>
-        <v>-5.6089986221652288E-2</v>
+        <v>-3.204795108895897E-2</v>
       </c>
       <c r="Z125" s="6">
         <v>-20796.908299999963</v>
@@ -20559,11 +19431,11 @@
       </c>
       <c r="X132" s="48">
         <f>X64-X66</f>
-        <v>672615.47999999963</v>
+        <v>506206.04999999946</v>
       </c>
       <c r="Y132" s="14">
         <f>X132/V132-1</f>
-        <v>1.0836839163537046</v>
+        <v>0.56816700791058006</v>
       </c>
       <c r="Z132" s="7">
         <v>166896.54889072594</v>
@@ -22599,7 +21471,7 @@
         <f>T132-T134</f>
         <v>31995.680000000008</v>
       </c>
-      <c r="U151" s="52">
+      <c r="U151" s="50">
         <f>T151/R151</f>
         <v>-79.711991557846133</v>
       </c>
@@ -22611,11 +21483,11 @@
       </c>
       <c r="X151" s="48">
         <f>X132-X134</f>
-        <v>620529.40999999968</v>
+        <v>454119.97999999946</v>
       </c>
       <c r="Y151" s="14">
         <f t="shared" ref="Y151" si="31">IFERROR((X151*-1)/V151-1,"")</f>
-        <v>-3.4575211520646807</v>
+        <v>-2.7984795538138778</v>
       </c>
       <c r="Z151" s="7">
         <v>96597.603831202126</v>
@@ -23064,7 +21936,7 @@
         <f>T151-T153</f>
         <v>31995.680000000008</v>
       </c>
-      <c r="U157" s="52">
+      <c r="U157" s="50">
         <f>T157/R157-1</f>
         <v>-80.711991557846133</v>
       </c>
@@ -23076,11 +21948,11 @@
       </c>
       <c r="X157" s="48">
         <f>X151-X153</f>
-        <v>620529.40999999968</v>
-      </c>
-      <c r="Y157" s="52">
+        <v>454119.97999999946</v>
+      </c>
+      <c r="Y157" s="50">
         <f>X157/V157-1</f>
-        <v>1.4575211520646807</v>
+        <v>0.79847955381387803</v>
       </c>
       <c r="Z157" s="7">
         <v>96597.603831202126</v>
@@ -23155,36 +22027,21 @@
     <mergeCell ref="X4:Y4"/>
   </mergeCells>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="6" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="27" operator="equal">
       <formula>"rafael"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:Q1048576">
-    <cfRule type="cellIs" dxfId="5" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="26" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U1:U131 U133:U1048576">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThan">
+  <conditionalFormatting sqref="U1:U1048576">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y1:Y131 Y133:Y156 Y158:Y1048576">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U132">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y132">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y157">
+  <conditionalFormatting sqref="Y1:Y1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/orcamento.xlsx
+++ b/orcamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e87dc3a59766ad95/Documentos/Karams Estofados/Relatórios/Financeiro/Orçamento 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="579" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{196A29E3-50BC-41F1-BB6A-BEA557AD3CA9}"/>
+  <xr:revisionPtr revIDLastSave="629" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A65A51-856A-44A0-AC84-B62898BF0F30}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
   </bookViews>
@@ -733,7 +733,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -749,6 +749,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,7 +794,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -934,6 +940,8 @@
     <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1009,15 +1017,15 @@
       <sheetName val="BASE"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
       <sheetData sheetId="9">
         <row r="5">
           <cell r="A5" t="str">
@@ -1032,23 +1040,40 @@
           <cell r="D5">
             <v>169337.99</v>
           </cell>
+          <cell r="E5"/>
           <cell r="F5">
             <v>420937.66000000003</v>
           </cell>
+          <cell r="G5"/>
+          <cell r="H5"/>
+          <cell r="I5"/>
+          <cell r="J5"/>
+          <cell r="K5"/>
+          <cell r="L5"/>
+          <cell r="M5"/>
         </row>
         <row r="6">
           <cell r="A6" t="str">
             <v>COFINS</v>
           </cell>
+          <cell r="B6"/>
           <cell r="C6">
             <v>2460.61</v>
           </cell>
           <cell r="D6">
             <v>15906.25</v>
           </cell>
+          <cell r="E6"/>
           <cell r="F6">
             <v>18366.86</v>
           </cell>
+          <cell r="G6"/>
+          <cell r="H6"/>
+          <cell r="I6"/>
+          <cell r="J6"/>
+          <cell r="K6"/>
+          <cell r="L6"/>
+          <cell r="M6"/>
         </row>
         <row r="7">
           <cell r="A7" t="str">
@@ -1063,9 +1088,17 @@
           <cell r="D7">
             <v>39057.060000000005</v>
           </cell>
+          <cell r="E7"/>
           <cell r="F7">
             <v>118711.39000000001</v>
           </cell>
+          <cell r="G7"/>
+          <cell r="H7"/>
+          <cell r="I7"/>
+          <cell r="J7"/>
+          <cell r="K7"/>
+          <cell r="L7"/>
+          <cell r="M7"/>
         </row>
         <row r="8">
           <cell r="A8" t="str">
@@ -1080,9 +1113,17 @@
           <cell r="D8">
             <v>5659.96</v>
           </cell>
+          <cell r="E8"/>
           <cell r="F8">
             <v>16979.88</v>
           </cell>
+          <cell r="G8"/>
+          <cell r="H8"/>
+          <cell r="I8"/>
+          <cell r="J8"/>
+          <cell r="K8"/>
+          <cell r="L8"/>
+          <cell r="M8"/>
         </row>
         <row r="9">
           <cell r="A9" t="str">
@@ -1097,9 +1138,17 @@
           <cell r="D9">
             <v>22197.7</v>
           </cell>
+          <cell r="E9"/>
           <cell r="F9">
             <v>52833.82</v>
           </cell>
+          <cell r="G9"/>
+          <cell r="H9"/>
+          <cell r="I9"/>
+          <cell r="J9"/>
+          <cell r="K9"/>
+          <cell r="L9"/>
+          <cell r="M9"/>
         </row>
         <row r="10">
           <cell r="A10" t="str">
@@ -1114,23 +1163,40 @@
           <cell r="D10">
             <v>1921.23</v>
           </cell>
+          <cell r="E10"/>
           <cell r="F10">
             <v>4854.9400000000005</v>
           </cell>
+          <cell r="G10"/>
+          <cell r="H10"/>
+          <cell r="I10"/>
+          <cell r="J10"/>
+          <cell r="K10"/>
+          <cell r="L10"/>
+          <cell r="M10"/>
         </row>
         <row r="11">
           <cell r="A11" t="str">
             <v>PIS</v>
           </cell>
+          <cell r="B11"/>
           <cell r="C11">
             <v>496.96</v>
           </cell>
           <cell r="D11">
             <v>3431.3</v>
           </cell>
+          <cell r="E11"/>
           <cell r="F11">
             <v>3928.26</v>
           </cell>
+          <cell r="G11"/>
+          <cell r="H11"/>
+          <cell r="I11"/>
+          <cell r="J11"/>
+          <cell r="K11"/>
+          <cell r="L11"/>
+          <cell r="M11"/>
         </row>
         <row r="12">
           <cell r="A12" t="str">
@@ -1145,9 +1211,17 @@
           <cell r="D12">
             <v>81164.490000000005</v>
           </cell>
+          <cell r="E12"/>
           <cell r="F12">
             <v>205262.51</v>
           </cell>
+          <cell r="G12"/>
+          <cell r="H12"/>
+          <cell r="I12"/>
+          <cell r="J12"/>
+          <cell r="K12"/>
+          <cell r="L12"/>
+          <cell r="M12"/>
         </row>
         <row r="13">
           <cell r="A13" t="str">
@@ -1162,9 +1236,17 @@
           <cell r="D13">
             <v>29480.909999999996</v>
           </cell>
+          <cell r="E13"/>
           <cell r="F13">
             <v>63025.459999999992</v>
           </cell>
+          <cell r="G13"/>
+          <cell r="H13"/>
+          <cell r="I13"/>
+          <cell r="J13"/>
+          <cell r="K13"/>
+          <cell r="L13"/>
+          <cell r="M13"/>
         </row>
         <row r="14">
           <cell r="A14" t="str">
@@ -1179,9 +1261,17 @@
           <cell r="D14">
             <v>1534.3</v>
           </cell>
+          <cell r="E14"/>
           <cell r="F14">
             <v>3085.9799999999996</v>
           </cell>
+          <cell r="G14"/>
+          <cell r="H14"/>
+          <cell r="I14"/>
+          <cell r="J14"/>
+          <cell r="K14"/>
+          <cell r="L14"/>
+          <cell r="M14"/>
         </row>
         <row r="15">
           <cell r="A15" t="str">
@@ -1196,9 +1286,17 @@
           <cell r="D15">
             <v>12217.75</v>
           </cell>
+          <cell r="E15"/>
           <cell r="F15">
             <v>14735.43</v>
           </cell>
+          <cell r="G15"/>
+          <cell r="H15"/>
+          <cell r="I15"/>
+          <cell r="J15"/>
+          <cell r="K15"/>
+          <cell r="L15"/>
+          <cell r="M15"/>
         </row>
         <row r="16">
           <cell r="A16" t="str">
@@ -1213,9 +1311,17 @@
           <cell r="D16">
             <v>15728.859999999995</v>
           </cell>
+          <cell r="E16"/>
           <cell r="F16">
             <v>45204.049999999996</v>
           </cell>
+          <cell r="G16"/>
+          <cell r="H16"/>
+          <cell r="I16"/>
+          <cell r="J16"/>
+          <cell r="K16"/>
+          <cell r="L16"/>
+          <cell r="M16"/>
         </row>
         <row r="17">
           <cell r="A17" t="str">
@@ -1236,6 +1342,13 @@
           <cell r="F17">
             <v>931726.25999999989</v>
           </cell>
+          <cell r="G17"/>
+          <cell r="H17"/>
+          <cell r="I17"/>
+          <cell r="J17"/>
+          <cell r="K17"/>
+          <cell r="L17"/>
+          <cell r="M17"/>
         </row>
         <row r="18">
           <cell r="A18" t="str">
@@ -1256,6 +1369,13 @@
           <cell r="F18">
             <v>2147.9</v>
           </cell>
+          <cell r="G18"/>
+          <cell r="H18"/>
+          <cell r="I18"/>
+          <cell r="J18"/>
+          <cell r="K18"/>
+          <cell r="L18"/>
+          <cell r="M18"/>
         </row>
         <row r="19">
           <cell r="A19" t="str">
@@ -1270,9 +1390,17 @@
           <cell r="D19">
             <v>8155.15</v>
           </cell>
+          <cell r="E19"/>
           <cell r="F19">
             <v>19604.21</v>
           </cell>
+          <cell r="G19"/>
+          <cell r="H19"/>
+          <cell r="I19"/>
+          <cell r="J19"/>
+          <cell r="K19"/>
+          <cell r="L19"/>
+          <cell r="M19"/>
         </row>
         <row r="20">
           <cell r="A20" t="str">
@@ -1284,9 +1412,18 @@
           <cell r="C20">
             <v>1694.1599999999999</v>
           </cell>
+          <cell r="D20"/>
+          <cell r="E20"/>
           <cell r="F20">
             <v>3593.3599999999997</v>
           </cell>
+          <cell r="G20"/>
+          <cell r="H20"/>
+          <cell r="I20"/>
+          <cell r="J20"/>
+          <cell r="K20"/>
+          <cell r="L20"/>
+          <cell r="M20"/>
         </row>
         <row r="21">
           <cell r="A21" t="str">
@@ -1307,6 +1444,13 @@
           <cell r="F21">
             <v>23852.809999999998</v>
           </cell>
+          <cell r="G21"/>
+          <cell r="H21"/>
+          <cell r="I21"/>
+          <cell r="J21"/>
+          <cell r="K21"/>
+          <cell r="L21"/>
+          <cell r="M21"/>
         </row>
         <row r="22">
           <cell r="A22" t="str">
@@ -1318,9 +1462,18 @@
           <cell r="C22">
             <v>32736.5</v>
           </cell>
+          <cell r="D22"/>
+          <cell r="E22"/>
           <cell r="F22">
             <v>67168.479999999996</v>
           </cell>
+          <cell r="G22"/>
+          <cell r="H22"/>
+          <cell r="I22"/>
+          <cell r="J22"/>
+          <cell r="K22"/>
+          <cell r="L22"/>
+          <cell r="M22"/>
         </row>
         <row r="23">
           <cell r="A23" t="str">
@@ -1335,9 +1488,17 @@
           <cell r="D23">
             <v>8223.1</v>
           </cell>
+          <cell r="E23"/>
           <cell r="F23">
             <v>25031.9</v>
           </cell>
+          <cell r="G23"/>
+          <cell r="H23"/>
+          <cell r="I23"/>
+          <cell r="J23"/>
+          <cell r="K23"/>
+          <cell r="L23"/>
+          <cell r="M23"/>
         </row>
         <row r="24">
           <cell r="A24" t="str">
@@ -1349,9 +1510,18 @@
           <cell r="C24">
             <v>42800.44</v>
           </cell>
+          <cell r="D24"/>
+          <cell r="E24"/>
           <cell r="F24">
             <v>87169.52</v>
           </cell>
+          <cell r="G24"/>
+          <cell r="H24"/>
+          <cell r="I24"/>
+          <cell r="J24"/>
+          <cell r="K24"/>
+          <cell r="L24"/>
+          <cell r="M24"/>
         </row>
         <row r="25">
           <cell r="A25" t="str">
@@ -1372,20 +1542,36 @@
           <cell r="F25">
             <v>48625.24</v>
           </cell>
+          <cell r="G25"/>
+          <cell r="H25"/>
+          <cell r="I25"/>
+          <cell r="J25"/>
+          <cell r="K25"/>
+          <cell r="L25"/>
+          <cell r="M25"/>
         </row>
         <row r="26">
           <cell r="A26" t="str">
             <v>Rescisões MOD</v>
           </cell>
+          <cell r="B26"/>
           <cell r="C26">
             <v>30936.210000000003</v>
           </cell>
           <cell r="D26">
             <v>7839.08</v>
           </cell>
+          <cell r="E26"/>
           <cell r="F26">
             <v>38775.29</v>
           </cell>
+          <cell r="G26"/>
+          <cell r="H26"/>
+          <cell r="I26"/>
+          <cell r="J26"/>
+          <cell r="K26"/>
+          <cell r="L26"/>
+          <cell r="M26"/>
         </row>
         <row r="27">
           <cell r="A27" t="str">
@@ -1400,9 +1586,17 @@
           <cell r="D27">
             <v>218151.71</v>
           </cell>
+          <cell r="E27"/>
           <cell r="F27">
             <v>609909.85</v>
           </cell>
+          <cell r="G27"/>
+          <cell r="H27"/>
+          <cell r="I27"/>
+          <cell r="J27"/>
+          <cell r="K27"/>
+          <cell r="L27"/>
+          <cell r="M27"/>
         </row>
         <row r="28">
           <cell r="A28" t="str">
@@ -1417,9 +1611,17 @@
           <cell r="D28">
             <v>1980.53</v>
           </cell>
+          <cell r="E28"/>
           <cell r="F28">
             <v>5847.7</v>
           </cell>
+          <cell r="G28"/>
+          <cell r="H28"/>
+          <cell r="I28"/>
+          <cell r="J28"/>
+          <cell r="K28"/>
+          <cell r="L28"/>
+          <cell r="M28"/>
         </row>
         <row r="29">
           <cell r="A29" t="str">
@@ -1440,17 +1642,34 @@
           <cell r="F29">
             <v>250664.85999999996</v>
           </cell>
+          <cell r="G29"/>
+          <cell r="H29"/>
+          <cell r="I29"/>
+          <cell r="J29"/>
+          <cell r="K29"/>
+          <cell r="L29"/>
+          <cell r="M29"/>
         </row>
         <row r="30">
           <cell r="A30" t="str">
             <v>Assistência Médica CIF</v>
           </cell>
+          <cell r="B30"/>
+          <cell r="C30"/>
+          <cell r="D30"/>
           <cell r="E30">
             <v>75</v>
           </cell>
           <cell r="F30">
             <v>75</v>
           </cell>
+          <cell r="G30"/>
+          <cell r="H30"/>
+          <cell r="I30"/>
+          <cell r="J30"/>
+          <cell r="K30"/>
+          <cell r="L30"/>
+          <cell r="M30"/>
         </row>
         <row r="31">
           <cell r="A31" t="str">
@@ -1465,14 +1684,24 @@
           <cell r="D31">
             <v>705.03</v>
           </cell>
+          <cell r="E31"/>
           <cell r="F31">
             <v>5027.6699999999992</v>
           </cell>
+          <cell r="G31"/>
+          <cell r="H31"/>
+          <cell r="I31"/>
+          <cell r="J31"/>
+          <cell r="K31"/>
+          <cell r="L31"/>
+          <cell r="M31"/>
         </row>
         <row r="32">
           <cell r="A32" t="str">
             <v>Férias CIF</v>
           </cell>
+          <cell r="B32"/>
+          <cell r="C32"/>
           <cell r="D32">
             <v>1458.08</v>
           </cell>
@@ -1482,6 +1711,13 @@
           <cell r="F32">
             <v>2774.3</v>
           </cell>
+          <cell r="G32"/>
+          <cell r="H32"/>
+          <cell r="I32"/>
+          <cell r="J32"/>
+          <cell r="K32"/>
+          <cell r="L32"/>
+          <cell r="M32"/>
         </row>
         <row r="33">
           <cell r="A33" t="str">
@@ -1493,9 +1729,18 @@
           <cell r="C33">
             <v>5251.66</v>
           </cell>
+          <cell r="D33"/>
+          <cell r="E33"/>
           <cell r="F33">
             <v>11749.61</v>
           </cell>
+          <cell r="G33"/>
+          <cell r="H33"/>
+          <cell r="I33"/>
+          <cell r="J33"/>
+          <cell r="K33"/>
+          <cell r="L33"/>
+          <cell r="M33"/>
         </row>
         <row r="34">
           <cell r="A34" t="str">
@@ -1510,9 +1755,17 @@
           <cell r="D34">
             <v>1589.46</v>
           </cell>
+          <cell r="E34"/>
           <cell r="F34">
             <v>7515.84</v>
           </cell>
+          <cell r="G34"/>
+          <cell r="H34"/>
+          <cell r="I34"/>
+          <cell r="J34"/>
+          <cell r="K34"/>
+          <cell r="L34"/>
+          <cell r="M34"/>
         </row>
         <row r="35">
           <cell r="A35" t="str">
@@ -1521,9 +1774,19 @@
           <cell r="B35">
             <v>230</v>
           </cell>
+          <cell r="C35"/>
+          <cell r="D35"/>
+          <cell r="E35"/>
           <cell r="F35">
             <v>230</v>
           </cell>
+          <cell r="G35"/>
+          <cell r="H35"/>
+          <cell r="I35"/>
+          <cell r="J35"/>
+          <cell r="K35"/>
+          <cell r="L35"/>
+          <cell r="M35"/>
         </row>
         <row r="36">
           <cell r="A36" t="str">
@@ -1535,9 +1798,18 @@
           <cell r="C36">
             <v>8297.76</v>
           </cell>
+          <cell r="D36"/>
+          <cell r="E36"/>
           <cell r="F36">
             <v>16324.37</v>
           </cell>
+          <cell r="G36"/>
+          <cell r="H36"/>
+          <cell r="I36"/>
+          <cell r="J36"/>
+          <cell r="K36"/>
+          <cell r="L36"/>
+          <cell r="M36"/>
         </row>
         <row r="37">
           <cell r="A37" t="str">
@@ -1558,6 +1830,13 @@
           <cell r="F37">
             <v>62614.86</v>
           </cell>
+          <cell r="G37"/>
+          <cell r="H37"/>
+          <cell r="I37"/>
+          <cell r="J37"/>
+          <cell r="K37"/>
+          <cell r="L37"/>
+          <cell r="M37"/>
         </row>
         <row r="38">
           <cell r="A38" t="str">
@@ -1578,6 +1857,13 @@
           <cell r="F38">
             <v>33071.56</v>
           </cell>
+          <cell r="G38"/>
+          <cell r="H38"/>
+          <cell r="I38"/>
+          <cell r="J38"/>
+          <cell r="K38"/>
+          <cell r="L38"/>
+          <cell r="M38"/>
         </row>
         <row r="39">
           <cell r="A39" t="str">
@@ -1598,6 +1884,13 @@
           <cell r="F39">
             <v>6673.58</v>
           </cell>
+          <cell r="G39"/>
+          <cell r="H39"/>
+          <cell r="I39"/>
+          <cell r="J39"/>
+          <cell r="K39"/>
+          <cell r="L39"/>
+          <cell r="M39"/>
         </row>
         <row r="40">
           <cell r="A40" t="str">
@@ -1612,20 +1905,38 @@
           <cell r="D40">
             <v>2405.31</v>
           </cell>
+          <cell r="E40"/>
           <cell r="F40">
             <v>7126.77</v>
           </cell>
+          <cell r="G40"/>
+          <cell r="H40"/>
+          <cell r="I40"/>
+          <cell r="J40"/>
+          <cell r="K40"/>
+          <cell r="L40"/>
+          <cell r="M40"/>
         </row>
         <row r="41">
           <cell r="A41" t="str">
             <v>Medicina e Segurança do Trabalho MOD</v>
           </cell>
+          <cell r="B41"/>
+          <cell r="C41"/>
           <cell r="D41">
             <v>180</v>
           </cell>
+          <cell r="E41"/>
           <cell r="F41">
             <v>180</v>
           </cell>
+          <cell r="G41"/>
+          <cell r="H41"/>
+          <cell r="I41"/>
+          <cell r="J41"/>
+          <cell r="K41"/>
+          <cell r="L41"/>
+          <cell r="M41"/>
         </row>
         <row r="42">
           <cell r="A42" t="str">
@@ -1640,9 +1951,17 @@
           <cell r="D42">
             <v>28474.9</v>
           </cell>
+          <cell r="E42"/>
           <cell r="F42">
             <v>96424.299999999988</v>
           </cell>
+          <cell r="G42"/>
+          <cell r="H42"/>
+          <cell r="I42"/>
+          <cell r="J42"/>
+          <cell r="K42"/>
+          <cell r="L42"/>
+          <cell r="M42"/>
         </row>
         <row r="43">
           <cell r="A43" t="str">
@@ -1657,9 +1976,17 @@
           <cell r="D43">
             <v>272.03999999999996</v>
           </cell>
+          <cell r="E43"/>
           <cell r="F43">
             <v>877</v>
           </cell>
+          <cell r="G43"/>
+          <cell r="H43"/>
+          <cell r="I43"/>
+          <cell r="J43"/>
+          <cell r="K43"/>
+          <cell r="L43"/>
+          <cell r="M43"/>
         </row>
         <row r="44">
           <cell r="A44" t="str">
@@ -1680,17 +2007,34 @@
           <cell r="F44">
             <v>515908.87000000005</v>
           </cell>
+          <cell r="G44"/>
+          <cell r="H44"/>
+          <cell r="I44"/>
+          <cell r="J44"/>
+          <cell r="K44"/>
+          <cell r="L44"/>
+          <cell r="M44"/>
         </row>
         <row r="45">
           <cell r="A45" t="str">
             <v>Assistência Médica (Adm)</v>
           </cell>
+          <cell r="B45"/>
           <cell r="C45">
             <v>75</v>
           </cell>
+          <cell r="D45"/>
+          <cell r="E45"/>
           <cell r="F45">
             <v>75</v>
           </cell>
+          <cell r="G45"/>
+          <cell r="H45"/>
+          <cell r="I45"/>
+          <cell r="J45"/>
+          <cell r="K45"/>
+          <cell r="L45"/>
+          <cell r="M45"/>
         </row>
         <row r="46">
           <cell r="A46" t="str">
@@ -1711,6 +2055,13 @@
           <cell r="F46">
             <v>4935.9799999999996</v>
           </cell>
+          <cell r="G46"/>
+          <cell r="H46"/>
+          <cell r="I46"/>
+          <cell r="J46"/>
+          <cell r="K46"/>
+          <cell r="L46"/>
+          <cell r="M46"/>
         </row>
         <row r="47">
           <cell r="A47" t="str">
@@ -1725,14 +2076,23 @@
           <cell r="D47">
             <v>1873.7600000000002</v>
           </cell>
+          <cell r="E47"/>
           <cell r="F47">
             <v>8529.58</v>
           </cell>
+          <cell r="G47"/>
+          <cell r="H47"/>
+          <cell r="I47"/>
+          <cell r="J47"/>
+          <cell r="K47"/>
+          <cell r="L47"/>
+          <cell r="M47"/>
         </row>
         <row r="48">
           <cell r="A48" t="str">
             <v>Ferias (Adm)</v>
           </cell>
+          <cell r="B48"/>
           <cell r="C48">
             <v>297.89999999999998</v>
           </cell>
@@ -1745,6 +2105,13 @@
           <cell r="F48">
             <v>3200.04</v>
           </cell>
+          <cell r="G48"/>
+          <cell r="H48"/>
+          <cell r="I48"/>
+          <cell r="J48"/>
+          <cell r="K48"/>
+          <cell r="L48"/>
+          <cell r="M48"/>
         </row>
         <row r="49">
           <cell r="A49" t="str">
@@ -1756,9 +2123,18 @@
           <cell r="C49">
             <v>9673.7099999999991</v>
           </cell>
+          <cell r="D49"/>
+          <cell r="E49"/>
           <cell r="F49">
             <v>18448.259999999998</v>
           </cell>
+          <cell r="G49"/>
+          <cell r="H49"/>
+          <cell r="I49"/>
+          <cell r="J49"/>
+          <cell r="K49"/>
+          <cell r="L49"/>
+          <cell r="M49"/>
         </row>
         <row r="50">
           <cell r="A50" t="str">
@@ -1773,9 +2149,17 @@
           <cell r="D50">
             <v>4955.24</v>
           </cell>
+          <cell r="E50"/>
           <cell r="F50">
             <v>12393.26</v>
           </cell>
+          <cell r="G50"/>
+          <cell r="H50"/>
+          <cell r="I50"/>
+          <cell r="J50"/>
+          <cell r="K50"/>
+          <cell r="L50"/>
+          <cell r="M50"/>
         </row>
         <row r="51">
           <cell r="A51" t="str">
@@ -1790,9 +2174,17 @@
           <cell r="D51">
             <v>178.31</v>
           </cell>
+          <cell r="E51"/>
           <cell r="F51">
             <v>40890.629999999997</v>
           </cell>
+          <cell r="G51"/>
+          <cell r="H51"/>
+          <cell r="I51"/>
+          <cell r="J51"/>
+          <cell r="K51"/>
+          <cell r="L51"/>
+          <cell r="M51"/>
         </row>
         <row r="52">
           <cell r="A52" t="str">
@@ -1807,9 +2199,17 @@
           <cell r="D52">
             <v>1143.7600000000002</v>
           </cell>
+          <cell r="E52"/>
           <cell r="F52">
             <v>5835.3600000000006</v>
           </cell>
+          <cell r="G52"/>
+          <cell r="H52"/>
+          <cell r="I52"/>
+          <cell r="J52"/>
+          <cell r="K52"/>
+          <cell r="L52"/>
+          <cell r="M52"/>
         </row>
         <row r="53">
           <cell r="A53" t="str">
@@ -1830,6 +2230,13 @@
           <cell r="F53">
             <v>215044.36000000002</v>
           </cell>
+          <cell r="G53"/>
+          <cell r="H53"/>
+          <cell r="I53"/>
+          <cell r="J53"/>
+          <cell r="K53"/>
+          <cell r="L53"/>
+          <cell r="M53"/>
         </row>
         <row r="54">
           <cell r="A54" t="str">
@@ -1838,12 +2245,21 @@
           <cell r="B54">
             <v>879.73</v>
           </cell>
+          <cell r="C54"/>
           <cell r="D54">
             <v>4483.63</v>
           </cell>
+          <cell r="E54"/>
           <cell r="F54">
             <v>5363.3600000000006</v>
           </cell>
+          <cell r="G54"/>
+          <cell r="H54"/>
+          <cell r="I54"/>
+          <cell r="J54"/>
+          <cell r="K54"/>
+          <cell r="L54"/>
+          <cell r="M54"/>
         </row>
         <row r="55">
           <cell r="A55" t="str">
@@ -1858,9 +2274,17 @@
           <cell r="D55">
             <v>73572.070000000007</v>
           </cell>
+          <cell r="E55"/>
           <cell r="F55">
             <v>199224.7</v>
           </cell>
+          <cell r="G55"/>
+          <cell r="H55"/>
+          <cell r="I55"/>
+          <cell r="J55"/>
+          <cell r="K55"/>
+          <cell r="L55"/>
+          <cell r="M55"/>
         </row>
         <row r="56">
           <cell r="A56" t="str">
@@ -1875,9 +2299,17 @@
           <cell r="D56">
             <v>596.62</v>
           </cell>
+          <cell r="E56"/>
           <cell r="F56">
             <v>1968.3400000000001</v>
           </cell>
+          <cell r="G56"/>
+          <cell r="H56"/>
+          <cell r="I56"/>
+          <cell r="J56"/>
+          <cell r="K56"/>
+          <cell r="L56"/>
+          <cell r="M56"/>
         </row>
         <row r="57">
           <cell r="A57" t="str">
@@ -1898,6 +2330,13 @@
           <cell r="F57">
             <v>53973.14</v>
           </cell>
+          <cell r="G57"/>
+          <cell r="H57"/>
+          <cell r="I57"/>
+          <cell r="J57"/>
+          <cell r="K57"/>
+          <cell r="L57"/>
+          <cell r="M57"/>
         </row>
         <row r="58">
           <cell r="A58" t="str">
@@ -1912,9 +2351,17 @@
           <cell r="D58">
             <v>32.229999999999997</v>
           </cell>
+          <cell r="E58"/>
           <cell r="F58">
             <v>96.69</v>
           </cell>
+          <cell r="G58"/>
+          <cell r="H58"/>
+          <cell r="I58"/>
+          <cell r="J58"/>
+          <cell r="K58"/>
+          <cell r="L58"/>
+          <cell r="M58"/>
         </row>
         <row r="59">
           <cell r="A59" t="str">
@@ -1935,6 +2382,13 @@
           <cell r="F59">
             <v>1640.63</v>
           </cell>
+          <cell r="G59"/>
+          <cell r="H59"/>
+          <cell r="I59"/>
+          <cell r="J59"/>
+          <cell r="K59"/>
+          <cell r="L59"/>
+          <cell r="M59"/>
         </row>
         <row r="60">
           <cell r="A60" t="str">
@@ -1949,9 +2403,17 @@
           <cell r="D60">
             <v>900</v>
           </cell>
+          <cell r="E60"/>
           <cell r="F60">
             <v>2600</v>
           </cell>
+          <cell r="G60"/>
+          <cell r="H60"/>
+          <cell r="I60"/>
+          <cell r="J60"/>
+          <cell r="K60"/>
+          <cell r="L60"/>
+          <cell r="M60"/>
         </row>
         <row r="61">
           <cell r="A61" t="str">
@@ -1966,9 +2428,17 @@
           <cell r="D61">
             <v>780.64</v>
           </cell>
+          <cell r="E61"/>
           <cell r="F61">
             <v>2272.96</v>
           </cell>
+          <cell r="G61"/>
+          <cell r="H61"/>
+          <cell r="I61"/>
+          <cell r="J61"/>
+          <cell r="K61"/>
+          <cell r="L61"/>
+          <cell r="M61"/>
         </row>
         <row r="62">
           <cell r="A62" t="str">
@@ -1983,9 +2453,17 @@
           <cell r="D62">
             <v>150.63</v>
           </cell>
+          <cell r="E62"/>
           <cell r="F62">
             <v>535.22</v>
           </cell>
+          <cell r="G62"/>
+          <cell r="H62"/>
+          <cell r="I62"/>
+          <cell r="J62"/>
+          <cell r="K62"/>
+          <cell r="L62"/>
+          <cell r="M62"/>
         </row>
         <row r="63">
           <cell r="A63" t="str">
@@ -2000,9 +2478,17 @@
           <cell r="D63">
             <v>350.68</v>
           </cell>
+          <cell r="E63"/>
           <cell r="F63">
             <v>1294.56</v>
           </cell>
+          <cell r="G63"/>
+          <cell r="H63"/>
+          <cell r="I63"/>
+          <cell r="J63"/>
+          <cell r="K63"/>
+          <cell r="L63"/>
+          <cell r="M63"/>
         </row>
         <row r="64">
           <cell r="A64" t="str">
@@ -2017,9 +2503,17 @@
           <cell r="D64">
             <v>100</v>
           </cell>
+          <cell r="E64"/>
           <cell r="F64">
             <v>300</v>
           </cell>
+          <cell r="G64"/>
+          <cell r="H64"/>
+          <cell r="I64"/>
+          <cell r="J64"/>
+          <cell r="K64"/>
+          <cell r="L64"/>
+          <cell r="M64"/>
         </row>
         <row r="65">
           <cell r="A65" t="str">
@@ -2031,9 +2525,18 @@
           <cell r="C65">
             <v>91.95</v>
           </cell>
+          <cell r="D65"/>
+          <cell r="E65"/>
           <cell r="F65">
             <v>190.36</v>
           </cell>
+          <cell r="G65"/>
+          <cell r="H65"/>
+          <cell r="I65"/>
+          <cell r="J65"/>
+          <cell r="K65"/>
+          <cell r="L65"/>
+          <cell r="M65"/>
         </row>
         <row r="66">
           <cell r="A66" t="str">
@@ -2048,9 +2551,17 @@
           <cell r="D66">
             <v>382.17</v>
           </cell>
+          <cell r="E66"/>
           <cell r="F66">
             <v>867.32999999999993</v>
           </cell>
+          <cell r="G66"/>
+          <cell r="H66"/>
+          <cell r="I66"/>
+          <cell r="J66"/>
+          <cell r="K66"/>
+          <cell r="L66"/>
+          <cell r="M66"/>
         </row>
         <row r="67">
           <cell r="A67" t="str">
@@ -2071,6 +2582,13 @@
           <cell r="F67">
             <v>1820.6</v>
           </cell>
+          <cell r="G67"/>
+          <cell r="H67"/>
+          <cell r="I67"/>
+          <cell r="J67"/>
+          <cell r="K67"/>
+          <cell r="L67"/>
+          <cell r="M67"/>
         </row>
         <row r="68">
           <cell r="A68" t="str">
@@ -2085,9 +2603,17 @@
           <cell r="D68">
             <v>370</v>
           </cell>
+          <cell r="E68"/>
           <cell r="F68">
             <v>1110</v>
           </cell>
+          <cell r="G68"/>
+          <cell r="H68"/>
+          <cell r="I68"/>
+          <cell r="J68"/>
+          <cell r="K68"/>
+          <cell r="L68"/>
+          <cell r="M68"/>
         </row>
         <row r="69">
           <cell r="A69" t="str">
@@ -2102,9 +2628,17 @@
           <cell r="D69">
             <v>11212.419999999998</v>
           </cell>
+          <cell r="E69"/>
           <cell r="F69">
             <v>33637.259999999995</v>
           </cell>
+          <cell r="G69"/>
+          <cell r="H69"/>
+          <cell r="I69"/>
+          <cell r="J69"/>
+          <cell r="K69"/>
+          <cell r="L69"/>
+          <cell r="M69"/>
         </row>
         <row r="70">
           <cell r="A70" t="str">
@@ -2119,9 +2653,17 @@
           <cell r="D70">
             <v>351</v>
           </cell>
+          <cell r="E70"/>
           <cell r="F70">
             <v>1319.44</v>
           </cell>
+          <cell r="G70"/>
+          <cell r="H70"/>
+          <cell r="I70"/>
+          <cell r="J70"/>
+          <cell r="K70"/>
+          <cell r="L70"/>
+          <cell r="M70"/>
         </row>
         <row r="71">
           <cell r="A71" t="str">
@@ -2136,9 +2678,17 @@
           <cell r="D71">
             <v>2146.02</v>
           </cell>
+          <cell r="E71"/>
           <cell r="F71">
             <v>6288.09</v>
           </cell>
+          <cell r="G71"/>
+          <cell r="H71"/>
+          <cell r="I71"/>
+          <cell r="J71"/>
+          <cell r="K71"/>
+          <cell r="L71"/>
+          <cell r="M71"/>
         </row>
         <row r="72">
           <cell r="A72" t="str">
@@ -2159,6 +2709,13 @@
           <cell r="F72">
             <v>1043832.8499999999</v>
           </cell>
+          <cell r="G72"/>
+          <cell r="H72"/>
+          <cell r="I72"/>
+          <cell r="J72"/>
+          <cell r="K72"/>
+          <cell r="L72"/>
+          <cell r="M72"/>
         </row>
         <row r="73">
           <cell r="A73" t="str">
@@ -2167,9 +2724,19 @@
           <cell r="B73">
             <v>1368</v>
           </cell>
+          <cell r="C73"/>
+          <cell r="D73"/>
+          <cell r="E73"/>
           <cell r="F73">
             <v>1368</v>
           </cell>
+          <cell r="G73"/>
+          <cell r="H73"/>
+          <cell r="I73"/>
+          <cell r="J73"/>
+          <cell r="K73"/>
+          <cell r="L73"/>
+          <cell r="M73"/>
         </row>
         <row r="74">
           <cell r="A74" t="str">
@@ -2184,9 +2751,17 @@
           <cell r="D74">
             <v>3042.48</v>
           </cell>
+          <cell r="E74"/>
           <cell r="F74">
             <v>7412.48</v>
           </cell>
+          <cell r="G74"/>
+          <cell r="H74"/>
+          <cell r="I74"/>
+          <cell r="J74"/>
+          <cell r="K74"/>
+          <cell r="L74"/>
+          <cell r="M74"/>
         </row>
         <row r="75">
           <cell r="A75" t="str">
@@ -2201,9 +2776,17 @@
           <cell r="D75">
             <v>70184.260000000009</v>
           </cell>
+          <cell r="E75"/>
           <cell r="F75">
             <v>158828.48000000001</v>
           </cell>
+          <cell r="G75"/>
+          <cell r="H75"/>
+          <cell r="I75"/>
+          <cell r="J75"/>
+          <cell r="K75"/>
+          <cell r="L75"/>
+          <cell r="M75"/>
         </row>
         <row r="76">
           <cell r="A76" t="str">
@@ -2218,9 +2801,17 @@
           <cell r="D76">
             <v>88339.049999999988</v>
           </cell>
+          <cell r="E76"/>
           <cell r="F76">
             <v>284165.46999999991</v>
           </cell>
+          <cell r="G76"/>
+          <cell r="H76"/>
+          <cell r="I76"/>
+          <cell r="J76"/>
+          <cell r="K76"/>
+          <cell r="L76"/>
+          <cell r="M76"/>
         </row>
         <row r="77">
           <cell r="A77" t="str">
@@ -2235,9 +2826,17 @@
           <cell r="D77">
             <v>10515.810000000001</v>
           </cell>
+          <cell r="E77"/>
           <cell r="F77">
             <v>22781.65</v>
           </cell>
+          <cell r="G77"/>
+          <cell r="H77"/>
+          <cell r="I77"/>
+          <cell r="J77"/>
+          <cell r="K77"/>
+          <cell r="L77"/>
+          <cell r="M77"/>
         </row>
         <row r="78">
           <cell r="A78" t="str">
@@ -2258,6 +2857,13 @@
           <cell r="F78">
             <v>38182.810000000005</v>
           </cell>
+          <cell r="G78"/>
+          <cell r="H78"/>
+          <cell r="I78"/>
+          <cell r="J78"/>
+          <cell r="K78"/>
+          <cell r="L78"/>
+          <cell r="M78"/>
         </row>
         <row r="79">
           <cell r="A79" t="str">
@@ -2272,9 +2878,17 @@
           <cell r="D79">
             <v>24000</v>
           </cell>
+          <cell r="E79"/>
           <cell r="F79">
             <v>72000</v>
           </cell>
+          <cell r="G79"/>
+          <cell r="H79"/>
+          <cell r="I79"/>
+          <cell r="J79"/>
+          <cell r="K79"/>
+          <cell r="L79"/>
+          <cell r="M79"/>
         </row>
         <row r="80">
           <cell r="A80" t="str">
@@ -2295,20 +2909,36 @@
           <cell r="F80">
             <v>199557.97999999998</v>
           </cell>
+          <cell r="G80"/>
+          <cell r="H80"/>
+          <cell r="I80"/>
+          <cell r="J80"/>
+          <cell r="K80"/>
+          <cell r="L80"/>
+          <cell r="M80"/>
         </row>
         <row r="81">
           <cell r="A81" t="str">
             <v>Fretes</v>
           </cell>
+          <cell r="B81"/>
           <cell r="C81">
             <v>2334.16</v>
           </cell>
           <cell r="D81">
             <v>709</v>
           </cell>
+          <cell r="E81"/>
           <cell r="F81">
             <v>3043.16</v>
           </cell>
+          <cell r="G81"/>
+          <cell r="H81"/>
+          <cell r="I81"/>
+          <cell r="J81"/>
+          <cell r="K81"/>
+          <cell r="L81"/>
+          <cell r="M81"/>
         </row>
         <row r="82">
           <cell r="A82" t="str">
@@ -2323,9 +2953,17 @@
           <cell r="D82">
             <v>420.81</v>
           </cell>
+          <cell r="E82"/>
           <cell r="F82">
             <v>2737.9</v>
           </cell>
+          <cell r="G82"/>
+          <cell r="H82"/>
+          <cell r="I82"/>
+          <cell r="J82"/>
+          <cell r="K82"/>
+          <cell r="L82"/>
+          <cell r="M82"/>
         </row>
         <row r="83">
           <cell r="A83" t="str">
@@ -2340,9 +2978,17 @@
           <cell r="D83">
             <v>19808.55</v>
           </cell>
+          <cell r="E83"/>
           <cell r="F83">
             <v>48136.75</v>
           </cell>
+          <cell r="G83"/>
+          <cell r="H83"/>
+          <cell r="I83"/>
+          <cell r="J83"/>
+          <cell r="K83"/>
+          <cell r="L83"/>
+          <cell r="M83"/>
         </row>
         <row r="84">
           <cell r="A84" t="str">
@@ -2357,9 +3003,17 @@
           <cell r="D84">
             <v>4296.6099999999997</v>
           </cell>
+          <cell r="E84"/>
           <cell r="F84">
             <v>12889.829999999998</v>
           </cell>
+          <cell r="G84"/>
+          <cell r="H84"/>
+          <cell r="I84"/>
+          <cell r="J84"/>
+          <cell r="K84"/>
+          <cell r="L84"/>
+          <cell r="M84"/>
         </row>
         <row r="85">
           <cell r="A85" t="str">
@@ -2380,6 +3034,13 @@
           <cell r="F85">
             <v>17443.36</v>
           </cell>
+          <cell r="G85"/>
+          <cell r="H85"/>
+          <cell r="I85"/>
+          <cell r="J85"/>
+          <cell r="K85"/>
+          <cell r="L85"/>
+          <cell r="M85"/>
         </row>
         <row r="86">
           <cell r="A86" t="str">
@@ -2400,6 +3061,13 @@
           <cell r="F86">
             <v>2378.4299999999998</v>
           </cell>
+          <cell r="G86"/>
+          <cell r="H86"/>
+          <cell r="I86"/>
+          <cell r="J86"/>
+          <cell r="K86"/>
+          <cell r="L86"/>
+          <cell r="M86"/>
         </row>
         <row r="87">
           <cell r="A87" t="str">
@@ -2414,9 +3082,17 @@
           <cell r="D87">
             <v>9958.6499999999978</v>
           </cell>
+          <cell r="E87"/>
           <cell r="F87">
             <v>24550.729999999996</v>
           </cell>
+          <cell r="G87"/>
+          <cell r="H87"/>
+          <cell r="I87"/>
+          <cell r="J87"/>
+          <cell r="K87"/>
+          <cell r="L87"/>
+          <cell r="M87"/>
         </row>
         <row r="88">
           <cell r="A88" t="str">
@@ -2437,6 +3113,13 @@
           <cell r="F88">
             <v>13489.59</v>
           </cell>
+          <cell r="G88"/>
+          <cell r="H88"/>
+          <cell r="I88"/>
+          <cell r="J88"/>
+          <cell r="K88"/>
+          <cell r="L88"/>
+          <cell r="M88"/>
         </row>
         <row r="89">
           <cell r="A89" t="str">
@@ -2448,9 +3131,18 @@
           <cell r="C89">
             <v>45445.030000000006</v>
           </cell>
+          <cell r="D89"/>
+          <cell r="E89"/>
           <cell r="F89">
             <v>81144.87000000001</v>
           </cell>
+          <cell r="G89"/>
+          <cell r="H89"/>
+          <cell r="I89"/>
+          <cell r="J89"/>
+          <cell r="K89"/>
+          <cell r="L89"/>
+          <cell r="M89"/>
         </row>
         <row r="90">
           <cell r="A90" t="str">
@@ -2462,9 +3154,18 @@
           <cell r="C90">
             <v>1807.69</v>
           </cell>
+          <cell r="D90"/>
+          <cell r="E90"/>
           <cell r="F90">
             <v>2545.85</v>
           </cell>
+          <cell r="G90"/>
+          <cell r="H90"/>
+          <cell r="I90"/>
+          <cell r="J90"/>
+          <cell r="K90"/>
+          <cell r="L90"/>
+          <cell r="M90"/>
         </row>
         <row r="91">
           <cell r="A91" t="str">
@@ -2479,9 +3180,17 @@
           <cell r="D91">
             <v>21717.43</v>
           </cell>
+          <cell r="E91"/>
           <cell r="F91">
             <v>51175.509999999995</v>
           </cell>
+          <cell r="G91"/>
+          <cell r="H91"/>
+          <cell r="I91"/>
+          <cell r="J91"/>
+          <cell r="K91"/>
+          <cell r="L91"/>
+          <cell r="M91"/>
         </row>
         <row r="92">
           <cell r="A92" t="str">
@@ -2502,6 +3211,13 @@
           <cell r="F92">
             <v>211938.18</v>
           </cell>
+          <cell r="G92"/>
+          <cell r="H92"/>
+          <cell r="I92"/>
+          <cell r="J92"/>
+          <cell r="K92"/>
+          <cell r="L92"/>
+          <cell r="M92"/>
         </row>
         <row r="93">
           <cell r="A93" t="str">
@@ -2522,6 +3238,13 @@
           <cell r="F93">
             <v>55625.149999999994</v>
           </cell>
+          <cell r="G93"/>
+          <cell r="H93"/>
+          <cell r="I93"/>
+          <cell r="J93"/>
+          <cell r="K93"/>
+          <cell r="L93"/>
+          <cell r="M93"/>
         </row>
         <row r="94">
           <cell r="A94" t="str">
@@ -2536,9 +3259,17 @@
           <cell r="D94">
             <v>6035.41</v>
           </cell>
+          <cell r="E94"/>
           <cell r="F94">
             <v>18106.23</v>
           </cell>
+          <cell r="G94"/>
+          <cell r="H94"/>
+          <cell r="I94"/>
+          <cell r="J94"/>
+          <cell r="K94"/>
+          <cell r="L94"/>
+          <cell r="M94"/>
         </row>
         <row r="95">
           <cell r="A95" t="str">
@@ -2559,6 +3290,13 @@
           <cell r="F95">
             <v>36662</v>
           </cell>
+          <cell r="G95"/>
+          <cell r="H95"/>
+          <cell r="I95"/>
+          <cell r="J95"/>
+          <cell r="K95"/>
+          <cell r="L95"/>
+          <cell r="M95"/>
         </row>
         <row r="96">
           <cell r="A96" t="str">
@@ -2573,9 +3311,17 @@
           <cell r="D96">
             <v>9436</v>
           </cell>
+          <cell r="E96"/>
           <cell r="F96">
             <v>27838</v>
           </cell>
+          <cell r="G96"/>
+          <cell r="H96"/>
+          <cell r="I96"/>
+          <cell r="J96"/>
+          <cell r="K96"/>
+          <cell r="L96"/>
+          <cell r="M96"/>
         </row>
         <row r="97">
           <cell r="A97" t="str">
@@ -2590,9 +3336,17 @@
           <cell r="D97">
             <v>7769.93</v>
           </cell>
+          <cell r="E97"/>
           <cell r="F97">
             <v>23805.78</v>
           </cell>
+          <cell r="G97"/>
+          <cell r="H97"/>
+          <cell r="I97"/>
+          <cell r="J97"/>
+          <cell r="K97"/>
+          <cell r="L97"/>
+          <cell r="M97"/>
         </row>
         <row r="98">
           <cell r="A98" t="str">
@@ -2613,6 +3367,13 @@
           <cell r="F98">
             <v>46147.02</v>
           </cell>
+          <cell r="G98"/>
+          <cell r="H98"/>
+          <cell r="I98"/>
+          <cell r="J98"/>
+          <cell r="K98"/>
+          <cell r="L98"/>
+          <cell r="M98"/>
         </row>
         <row r="99">
           <cell r="A99" t="str">
@@ -2633,6 +3394,13 @@
           <cell r="F99">
             <v>3754</v>
           </cell>
+          <cell r="G99"/>
+          <cell r="H99"/>
+          <cell r="I99"/>
+          <cell r="J99"/>
+          <cell r="K99"/>
+          <cell r="L99"/>
+          <cell r="M99"/>
         </row>
         <row r="100">
           <cell r="A100" t="str">
@@ -2653,6 +3421,13 @@
           <cell r="F100">
             <v>192846.00999999998</v>
           </cell>
+          <cell r="G100"/>
+          <cell r="H100"/>
+          <cell r="I100"/>
+          <cell r="J100"/>
+          <cell r="K100"/>
+          <cell r="L100"/>
+          <cell r="M100"/>
         </row>
         <row r="101">
           <cell r="A101" t="str">
@@ -2673,6 +3448,13 @@
           <cell r="F101">
             <v>31326.189999999991</v>
           </cell>
+          <cell r="G101"/>
+          <cell r="H101"/>
+          <cell r="I101"/>
+          <cell r="J101"/>
+          <cell r="K101"/>
+          <cell r="L101"/>
+          <cell r="M101"/>
         </row>
         <row r="102">
           <cell r="A102" t="str">
@@ -2693,6 +3475,13 @@
           <cell r="F102">
             <v>517.65</v>
           </cell>
+          <cell r="G102"/>
+          <cell r="H102"/>
+          <cell r="I102"/>
+          <cell r="J102"/>
+          <cell r="K102"/>
+          <cell r="L102"/>
+          <cell r="M102"/>
         </row>
         <row r="103">
           <cell r="A103" t="str">
@@ -2707,9 +3496,17 @@
           <cell r="D103">
             <v>13530.41</v>
           </cell>
+          <cell r="E103"/>
           <cell r="F103">
             <v>31520.240000000002</v>
           </cell>
+          <cell r="G103"/>
+          <cell r="H103"/>
+          <cell r="I103"/>
+          <cell r="J103"/>
+          <cell r="K103"/>
+          <cell r="L103"/>
+          <cell r="M103"/>
         </row>
         <row r="104">
           <cell r="A104" t="str">
@@ -2730,17 +3527,34 @@
           <cell r="F104">
             <v>32544.299999999996</v>
           </cell>
+          <cell r="G104"/>
+          <cell r="H104"/>
+          <cell r="I104"/>
+          <cell r="J104"/>
+          <cell r="K104"/>
+          <cell r="L104"/>
+          <cell r="M104"/>
         </row>
         <row r="105">
           <cell r="A105" t="str">
             <v>Juros Pagos</v>
           </cell>
+          <cell r="B105"/>
           <cell r="C105">
             <v>95.75</v>
           </cell>
+          <cell r="D105"/>
+          <cell r="E105"/>
           <cell r="F105">
             <v>95.75</v>
           </cell>
+          <cell r="G105"/>
+          <cell r="H105"/>
+          <cell r="I105"/>
+          <cell r="J105"/>
+          <cell r="K105"/>
+          <cell r="L105"/>
+          <cell r="M105"/>
         </row>
         <row r="106">
           <cell r="A106" t="str">
@@ -2761,6 +3575,13 @@
           <cell r="F106">
             <v>96841.87999999999</v>
           </cell>
+          <cell r="G106"/>
+          <cell r="H106"/>
+          <cell r="I106"/>
+          <cell r="J106"/>
+          <cell r="K106"/>
+          <cell r="L106"/>
+          <cell r="M106"/>
         </row>
         <row r="107">
           <cell r="A107" t="str">
@@ -2781,6 +3602,13 @@
           <cell r="F107">
             <v>106704.95</v>
           </cell>
+          <cell r="G107"/>
+          <cell r="H107"/>
+          <cell r="I107"/>
+          <cell r="J107"/>
+          <cell r="K107"/>
+          <cell r="L107"/>
+          <cell r="M107"/>
         </row>
         <row r="108">
           <cell r="A108" t="str">
@@ -2795,9 +3623,17 @@
           <cell r="D108">
             <v>2407.11</v>
           </cell>
+          <cell r="E108"/>
           <cell r="F108">
             <v>16919.339999999997</v>
           </cell>
+          <cell r="G108"/>
+          <cell r="H108"/>
+          <cell r="I108"/>
+          <cell r="J108"/>
+          <cell r="K108"/>
+          <cell r="L108"/>
+          <cell r="M108"/>
         </row>
         <row r="109">
           <cell r="A109" t="str">
@@ -2812,9 +3648,17 @@
           <cell r="D109">
             <v>3037.44</v>
           </cell>
+          <cell r="E109"/>
           <cell r="F109">
             <v>9112.32</v>
           </cell>
+          <cell r="G109"/>
+          <cell r="H109"/>
+          <cell r="I109"/>
+          <cell r="J109"/>
+          <cell r="K109"/>
+          <cell r="L109"/>
+          <cell r="M109"/>
         </row>
         <row r="110">
           <cell r="A110" t="str">
@@ -2829,9 +3673,17 @@
           <cell r="D110">
             <v>2570</v>
           </cell>
+          <cell r="E110"/>
           <cell r="F110">
             <v>22294.41</v>
           </cell>
+          <cell r="G110"/>
+          <cell r="H110"/>
+          <cell r="I110"/>
+          <cell r="J110"/>
+          <cell r="K110"/>
+          <cell r="L110"/>
+          <cell r="M110"/>
         </row>
         <row r="111">
           <cell r="A111" t="str">
@@ -2852,17 +3704,34 @@
           <cell r="F111">
             <v>54293.880000000005</v>
           </cell>
+          <cell r="G111"/>
+          <cell r="H111"/>
+          <cell r="I111"/>
+          <cell r="J111"/>
+          <cell r="K111"/>
+          <cell r="L111"/>
+          <cell r="M111"/>
         </row>
         <row r="112">
           <cell r="A112" t="str">
             <v>Moveis e Utensilios</v>
           </cell>
+          <cell r="B112"/>
+          <cell r="C112"/>
           <cell r="D112">
             <v>4085</v>
           </cell>
+          <cell r="E112"/>
           <cell r="F112">
             <v>4085</v>
           </cell>
+          <cell r="G112"/>
+          <cell r="H112"/>
+          <cell r="I112"/>
+          <cell r="J112"/>
+          <cell r="K112"/>
+          <cell r="L112"/>
+          <cell r="M112"/>
         </row>
         <row r="113">
           <cell r="A113" t="str">
@@ -2883,18 +3752,276 @@
           <cell r="F113">
             <v>3791558.2399999993</v>
           </cell>
+          <cell r="G113"/>
+          <cell r="H113"/>
+          <cell r="I113"/>
+          <cell r="J113"/>
+          <cell r="K113"/>
+          <cell r="L113"/>
+          <cell r="M113"/>
+        </row>
+        <row r="114">
+          <cell r="A114"/>
+          <cell r="B114"/>
+          <cell r="C114"/>
+          <cell r="D114"/>
+          <cell r="E114"/>
+          <cell r="F114"/>
+          <cell r="G114"/>
+          <cell r="H114"/>
+          <cell r="I114"/>
+          <cell r="J114"/>
+          <cell r="K114"/>
+          <cell r="L114"/>
+          <cell r="M114"/>
+        </row>
+        <row r="115">
+          <cell r="A115"/>
+          <cell r="B115"/>
+          <cell r="C115"/>
+          <cell r="D115"/>
+          <cell r="E115"/>
+          <cell r="F115"/>
+          <cell r="G115"/>
+          <cell r="H115"/>
+          <cell r="I115"/>
+          <cell r="J115"/>
+          <cell r="K115"/>
+          <cell r="L115"/>
+          <cell r="M115"/>
+        </row>
+        <row r="116">
+          <cell r="A116"/>
+          <cell r="B116"/>
+          <cell r="C116"/>
+          <cell r="D116"/>
+          <cell r="E116"/>
+          <cell r="F116"/>
+          <cell r="G116"/>
+          <cell r="H116"/>
+          <cell r="I116"/>
+          <cell r="J116"/>
+          <cell r="K116"/>
+          <cell r="L116"/>
+          <cell r="M116"/>
+        </row>
+        <row r="117">
+          <cell r="A117"/>
+          <cell r="B117"/>
+          <cell r="C117"/>
+          <cell r="D117"/>
+          <cell r="E117"/>
+          <cell r="F117"/>
+          <cell r="G117"/>
+          <cell r="H117"/>
+          <cell r="I117"/>
+          <cell r="J117"/>
+          <cell r="K117"/>
+          <cell r="L117"/>
+          <cell r="M117"/>
+        </row>
+        <row r="118">
+          <cell r="A118"/>
+          <cell r="B118"/>
+          <cell r="C118"/>
+          <cell r="D118"/>
+          <cell r="E118"/>
+          <cell r="F118"/>
+          <cell r="G118"/>
+          <cell r="H118"/>
+          <cell r="I118"/>
+          <cell r="J118"/>
+          <cell r="K118"/>
+          <cell r="L118"/>
+          <cell r="M118"/>
+        </row>
+        <row r="119">
+          <cell r="A119"/>
+          <cell r="B119"/>
+          <cell r="C119"/>
+          <cell r="D119"/>
+          <cell r="E119"/>
+          <cell r="F119"/>
+          <cell r="G119"/>
+          <cell r="H119"/>
+          <cell r="I119"/>
+          <cell r="J119"/>
+          <cell r="K119"/>
+          <cell r="L119"/>
+          <cell r="M119"/>
+        </row>
+        <row r="120">
+          <cell r="A120"/>
+          <cell r="B120"/>
+          <cell r="C120"/>
+          <cell r="D120"/>
+          <cell r="E120"/>
+          <cell r="F120"/>
+          <cell r="G120"/>
+          <cell r="H120"/>
+          <cell r="I120"/>
+          <cell r="J120"/>
+          <cell r="K120"/>
+          <cell r="L120"/>
+          <cell r="M120"/>
+        </row>
+        <row r="121">
+          <cell r="A121"/>
+          <cell r="B121"/>
+          <cell r="C121"/>
+          <cell r="D121"/>
+          <cell r="E121"/>
+          <cell r="F121"/>
+          <cell r="G121"/>
+          <cell r="H121"/>
+          <cell r="I121"/>
+          <cell r="J121"/>
+          <cell r="K121"/>
+          <cell r="L121"/>
+          <cell r="M121"/>
+        </row>
+        <row r="122">
+          <cell r="A122"/>
+          <cell r="B122"/>
+          <cell r="C122"/>
+          <cell r="D122"/>
+          <cell r="E122"/>
+          <cell r="F122"/>
+          <cell r="G122"/>
+          <cell r="H122"/>
+          <cell r="I122"/>
+          <cell r="J122"/>
+          <cell r="K122"/>
+          <cell r="L122"/>
+          <cell r="M122"/>
+        </row>
+        <row r="123">
+          <cell r="A123"/>
+          <cell r="B123"/>
+          <cell r="C123"/>
+          <cell r="D123"/>
+          <cell r="E123"/>
+          <cell r="F123"/>
+          <cell r="G123"/>
+          <cell r="H123"/>
+          <cell r="I123"/>
+          <cell r="J123"/>
+          <cell r="K123"/>
+          <cell r="L123"/>
+          <cell r="M123"/>
+        </row>
+        <row r="124">
+          <cell r="A124"/>
+          <cell r="B124"/>
+          <cell r="C124"/>
+          <cell r="D124"/>
+          <cell r="E124"/>
+          <cell r="F124"/>
+          <cell r="G124"/>
+          <cell r="H124"/>
+          <cell r="I124"/>
+          <cell r="J124"/>
+          <cell r="K124"/>
+          <cell r="L124"/>
+          <cell r="M124"/>
+        </row>
+        <row r="125">
+          <cell r="A125"/>
+          <cell r="B125"/>
+          <cell r="C125"/>
+          <cell r="D125"/>
+          <cell r="E125"/>
+          <cell r="F125"/>
+          <cell r="G125"/>
+          <cell r="H125"/>
+          <cell r="I125"/>
+          <cell r="J125"/>
+          <cell r="K125"/>
+          <cell r="L125"/>
+          <cell r="M125"/>
+        </row>
+        <row r="126">
+          <cell r="A126"/>
+          <cell r="B126"/>
+          <cell r="C126"/>
+          <cell r="D126"/>
+          <cell r="E126"/>
+          <cell r="F126"/>
+          <cell r="G126"/>
+          <cell r="H126"/>
+          <cell r="I126"/>
+          <cell r="J126"/>
+          <cell r="K126"/>
+          <cell r="L126"/>
+          <cell r="M126"/>
+        </row>
+        <row r="127">
+          <cell r="A127"/>
+          <cell r="B127"/>
+          <cell r="C127"/>
+          <cell r="D127"/>
+          <cell r="E127"/>
+          <cell r="F127"/>
+          <cell r="G127"/>
+          <cell r="H127"/>
+          <cell r="I127"/>
+          <cell r="J127"/>
+          <cell r="K127"/>
+          <cell r="L127"/>
+          <cell r="M127"/>
+        </row>
+        <row r="128">
+          <cell r="A128"/>
+          <cell r="B128"/>
+          <cell r="C128"/>
+          <cell r="D128"/>
+          <cell r="E128"/>
+          <cell r="F128"/>
+          <cell r="G128"/>
+          <cell r="H128"/>
+          <cell r="I128"/>
+          <cell r="J128"/>
+          <cell r="K128"/>
+          <cell r="L128"/>
+          <cell r="M128"/>
+        </row>
+        <row r="129">
+          <cell r="A129"/>
+          <cell r="B129"/>
+          <cell r="C129"/>
+          <cell r="D129"/>
+          <cell r="E129"/>
+          <cell r="F129"/>
+          <cell r="G129"/>
+          <cell r="H129"/>
+          <cell r="I129"/>
+          <cell r="J129"/>
+          <cell r="K129"/>
+          <cell r="L129"/>
+          <cell r="M129"/>
+        </row>
+        <row r="130">
+          <cell r="A130"/>
+          <cell r="B130"/>
+          <cell r="C130"/>
+          <cell r="D130"/>
+          <cell r="E130"/>
+          <cell r="F130"/>
+          <cell r="G130"/>
+          <cell r="H130"/>
+          <cell r="I130"/>
+          <cell r="J130"/>
+          <cell r="K130"/>
+          <cell r="L130"/>
+          <cell r="M130"/>
         </row>
       </sheetData>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4070,8 +5197,9 @@
       <c r="M13" s="15">
         <v>-2.6200000000000001E-2</v>
       </c>
-      <c r="N13" s="6">
-        <v>-42534.310324259073</v>
+      <c r="N13" s="53">
+        <f>P$10*$F13</f>
+        <v>-39452.850276000012</v>
       </c>
       <c r="O13" s="15">
         <v>-2.6200000000000001E-2</v>
@@ -4082,10 +5210,11 @@
       </c>
       <c r="Q13" s="46">
         <f t="shared" si="0"/>
-        <v>0.23143550702235127</v>
-      </c>
-      <c r="R13" s="6">
-        <v>-58320.886017926772</v>
+        <v>0.32761662677291503</v>
+      </c>
+      <c r="R13" s="53">
+        <f>T$10*$F13</f>
+        <v>-53623.839466000005</v>
       </c>
       <c r="S13" s="15">
         <v>-2.6200000000000001E-2</v>
@@ -4096,10 +5225,11 @@
       </c>
       <c r="U13" s="46">
         <f t="shared" si="1"/>
-        <v>0.22974400591161581</v>
-      </c>
-      <c r="V13" s="6">
-        <v>-73371.232466442045</v>
+        <v>0.33746036677350677</v>
+      </c>
+      <c r="V13" s="53">
+        <f>X$10*$F13</f>
+        <v>-68807.577079999988</v>
       </c>
       <c r="W13" s="15">
         <v>-2.6200000000000005E-2</v>
@@ -4110,7 +5240,7 @@
       </c>
       <c r="Y13" s="46">
         <f t="shared" si="2"/>
-        <v>0.10621680012152424</v>
+        <v>0.1795865142240527</v>
       </c>
       <c r="Z13" s="6">
         <v>-64093.317628933997</v>
@@ -4210,8 +5340,9 @@
       <c r="M14" s="15">
         <v>-2.4649999999999998E-2</v>
       </c>
-      <c r="N14" s="6">
-        <v>-40017.967537900229</v>
+      <c r="N14" s="53">
+        <f>P$10*$F14</f>
+        <v>-37118.80760700001</v>
       </c>
       <c r="O14" s="15">
         <v>-2.4649999999999998E-2</v>
@@ -4222,10 +5353,11 @@
       </c>
       <c r="Q14" s="46">
         <f t="shared" si="0"/>
-        <v>0.51629414818561448</v>
-      </c>
-      <c r="R14" s="6">
-        <v>-54870.604593202093</v>
+        <v>0.63472411728433098</v>
+      </c>
+      <c r="R14" s="53">
+        <f>T$10*$F14</f>
+        <v>-50451.436749500004</v>
       </c>
       <c r="S14" s="15">
         <v>-2.4649999999999998E-2</v>
@@ -4236,10 +5368,11 @@
       </c>
       <c r="U14" s="46">
         <f t="shared" si="1"/>
-        <v>-0.65418059194574918</v>
-      </c>
-      <c r="V14" s="6">
-        <v>-69030.567950297554</v>
+        <v>-0.62388940290807371</v>
+      </c>
+      <c r="V14" s="53">
+        <f>X$10*$F14</f>
+        <v>-64736.899809999981</v>
       </c>
       <c r="W14" s="15">
         <v>-2.4649999999999998E-2</v>
@@ -4250,7 +5383,7 @@
       </c>
       <c r="Y14" s="46">
         <f t="shared" si="2"/>
-        <v>-0.43420630657245451</v>
+        <v>-0.39668009875927335</v>
       </c>
       <c r="Z14" s="6">
         <v>-60301.537387527591</v>
@@ -4350,8 +5483,9 @@
       <c r="M15" s="15">
         <v>-2.7499999999999998E-3</v>
       </c>
-      <c r="N15" s="6">
-        <v>-4464.4791370882613</v>
+      <c r="N15" s="53">
+        <f>P$10*$F15</f>
+        <v>-4141.0434450000012</v>
       </c>
       <c r="O15" s="15">
         <v>-2.7500000000000003E-3</v>
@@ -4364,8 +5498,9 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="R15" s="6">
-        <v>-6121.4670438663588</v>
+      <c r="R15" s="53">
+        <f>T$10*$F15</f>
+        <v>-5628.4564325000001</v>
       </c>
       <c r="S15" s="15">
         <v>-2.7499999999999998E-3</v>
@@ -4376,10 +5511,11 @@
       </c>
       <c r="U15" s="46">
         <f t="shared" si="1"/>
-        <v>-0.91881684628230609</v>
-      </c>
-      <c r="V15" s="6">
-        <v>-7701.1789802563198</v>
+        <v>-0.91170581029455278</v>
+      </c>
+      <c r="V15" s="53">
+        <f>X$10*$F15</f>
+        <v>-7222.1693499999983</v>
       </c>
       <c r="W15" s="15">
         <v>-2.7499999999999998E-3</v>
@@ -4390,7 +5526,7 @@
       </c>
       <c r="Y15" s="46">
         <f t="shared" si="2"/>
-        <v>-0.55444484425087404</v>
+        <v>-0.52489344493147327</v>
       </c>
       <c r="Z15" s="6">
         <v>-6727.3520412049038</v>
@@ -4490,8 +5626,9 @@
       <c r="M16" s="15">
         <v>-1.06E-2</v>
       </c>
-      <c r="N16" s="6">
-        <v>-17208.537764776571</v>
+      <c r="N16" s="53">
+        <f>P$10*$F16</f>
+        <v>-15961.840188000006</v>
       </c>
       <c r="O16" s="15">
         <v>-1.06E-2</v>
@@ -4502,10 +5639,11 @@
       </c>
       <c r="Q16" s="46">
         <f t="shared" si="0"/>
-        <v>-7.752824690935578E-2</v>
-      </c>
-      <c r="R16" s="6">
-        <v>-23595.472969084876</v>
+        <v>-5.4787033932184315E-3</v>
+      </c>
+      <c r="R16" s="53">
+        <f>T$10*$F16</f>
+        <v>-21695.141158000002</v>
       </c>
       <c r="S16" s="15">
         <v>-1.06E-2</v>
@@ -4516,10 +5654,11 @@
       </c>
       <c r="U16" s="46">
         <f t="shared" si="1"/>
-        <v>-0.37438295814875044</v>
-      </c>
-      <c r="V16" s="6">
-        <v>-29684.544432987997</v>
+        <v>-0.3195835928195071</v>
+      </c>
+      <c r="V16" s="53">
+        <f>X$10*$F16</f>
+        <v>-27838.180039999996</v>
       </c>
       <c r="W16" s="15">
         <v>-1.06E-2</v>
@@ -4530,7 +5669,7 @@
       </c>
       <c r="Y16" s="46">
         <f t="shared" si="2"/>
-        <v>-0.25221355341630158</v>
+        <v>-0.2026166951968601</v>
       </c>
       <c r="Z16" s="6">
         <v>-25930.884231553449</v>
@@ -4630,8 +5769,9 @@
       <c r="M17" s="15">
         <v>-1.2750000000000003E-2</v>
       </c>
-      <c r="N17" s="6">
-        <v>-20698.948726500123</v>
+      <c r="N17" s="53">
+        <f>P$10*$F17</f>
+        <v>-19199.383245000008</v>
       </c>
       <c r="O17" s="15">
         <v>-1.2750000000000003E-2</v>
@@ -4644,8 +5784,9 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="R17" s="6">
-        <v>-28381.347203380396</v>
+      <c r="R17" s="53">
+        <f>T$10*$F17</f>
+        <v>-26095.570732500004</v>
       </c>
       <c r="S17" s="15">
         <v>-1.2750000000000001E-2</v>
@@ -4656,10 +5797,11 @@
       </c>
       <c r="U17" s="46">
         <f t="shared" si="1"/>
-        <v>-0.91330186046605544</v>
-      </c>
-      <c r="V17" s="6">
-        <v>-35705.4661811884</v>
+        <v>-0.90570775304272222</v>
+      </c>
+      <c r="V17" s="53">
+        <f>X$10*$F17</f>
+        <v>-33484.603349999998</v>
       </c>
       <c r="W17" s="15">
         <v>-1.2750000000000003E-2</v>
@@ -4670,7 +5812,7 @@
       </c>
       <c r="Y17" s="46">
         <f t="shared" si="2"/>
-        <v>-0.55451498884559347</v>
+        <v>-0.52496824185913493</v>
       </c>
       <c r="Z17" s="6">
         <v>-31190.450372859104</v>
@@ -4770,8 +5912,9 @@
       <c r="M18" s="15">
         <v>-8.5000000000000006E-4</v>
       </c>
-      <c r="N18" s="6">
-        <v>-1379.929915100008</v>
+      <c r="N18" s="53">
+        <f>P$10*$F18</f>
+        <v>-1279.9588830000005</v>
       </c>
       <c r="O18" s="15">
         <v>-8.4999999999999995E-4</v>
@@ -4782,10 +5925,11 @@
       </c>
       <c r="Q18" s="46">
         <f t="shared" si="0"/>
-        <v>4.6154579448606237E-2</v>
-      </c>
-      <c r="R18" s="6">
-        <v>-1892.0898135586931</v>
+        <v>0.12786435499897175</v>
+      </c>
+      <c r="R18" s="53">
+        <f>T$10*$F18</f>
+        <v>-1739.7047155000002</v>
       </c>
       <c r="S18" s="15">
         <v>-8.5000000000000006E-4</v>
@@ -4796,10 +5940,11 @@
       </c>
       <c r="U18" s="46">
         <f t="shared" ref="U18" si="3">IFERROR((T18*-1)/R18-1,"")</f>
-        <v>-0.21246338872392168</v>
-      </c>
-      <c r="V18" s="6">
-        <v>-2380.3644120792264</v>
+        <v>-0.1434810823216397</v>
+      </c>
+      <c r="V18" s="53">
+        <f>X$10*$F18</f>
+        <v>-2232.3068899999998</v>
       </c>
       <c r="W18" s="15">
         <v>-8.5000000000000006E-4</v>
@@ -4810,7 +5955,7 @@
       </c>
       <c r="Y18" s="46">
         <f t="shared" ref="Y18" si="4">IFERROR((X18*-1)/V18-1,"")</f>
-        <v>-0.19288408520533074</v>
+        <v>-0.13935220618344279</v>
       </c>
       <c r="Z18" s="6">
         <v>-2079.363358190607</v>
@@ -4910,11 +6055,11 @@
       <c r="M19" s="15">
         <v>-8.5000000000000006E-4</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="53">
         <v>0</v>
       </c>
       <c r="O19" s="15">
-        <v>-8.4999999999999995E-4</v>
+        <v>0</v>
       </c>
       <c r="P19" s="6">
         <f>IFERROR(VLOOKUP($I19,[1]RESUMO!$A$5:$M$150,2,FALSE),"")</f>
@@ -4924,7 +6069,7 @@
         <f t="shared" ref="Q19" si="5">IFERROR((P19*-1)/N19-1,"")</f>
         <v/>
       </c>
-      <c r="R19" s="6">
+      <c r="R19" s="53">
         <v>0</v>
       </c>
       <c r="S19" s="15">
@@ -4938,7 +6083,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V19" s="6">
+      <c r="V19" s="53">
         <v>0</v>
       </c>
       <c r="W19" s="15">
@@ -5168,7 +6313,8 @@
         <v>-0.60739099063811108</v>
       </c>
       <c r="N23" s="7">
-        <v>-1069601.9562959964</v>
+        <f>N24+N32+N46</f>
+        <v>-1024256.2722652226</v>
       </c>
       <c r="O23" s="14">
         <v>-0.65884625943898545</v>
@@ -5179,10 +6325,11 @@
       </c>
       <c r="Q23" s="14">
         <f>IFERROR((P23*-1)/N23-1,"")</f>
-        <v>-0.10368428707819821</v>
+        <v>-6.4002763800745099E-2</v>
       </c>
       <c r="R23" s="7">
-        <v>-1301911.6608262858</v>
+        <f>R24+R32+R46</f>
+        <v>-1232791.5731127223</v>
       </c>
       <c r="S23" s="14">
         <v>-0.58486912395610513</v>
@@ -5193,10 +6340,11 @@
       </c>
       <c r="U23" s="14">
         <f>IFERROR((T23*-1)/R23-1,"")</f>
-        <v>-1.8055073576472069E-2</v>
+        <v>3.7000558636287151E-2</v>
       </c>
       <c r="V23" s="7">
-        <v>-1523387.2743081583</v>
+        <f>V24+V32+V46</f>
+        <v>-1456230.1241462221</v>
       </c>
       <c r="W23" s="14">
         <v>-0.54398359200424673</v>
@@ -5207,7 +6355,7 @@
       </c>
       <c r="Y23" s="14">
         <f>IFERROR((X23*-1)/V23-1,"")</f>
-        <v>-8.5296146619821323E-2</v>
+        <v>-4.3112632478352952E-2</v>
       </c>
       <c r="Z23" s="7">
         <v>-1386856.7374531499</v>
@@ -5293,8 +6441,9 @@
       <c r="M24" s="13">
         <v>-0.38555</v>
       </c>
-      <c r="N24" s="8">
-        <v>-625919.97501977417</v>
+      <c r="N24" s="54">
+        <f>SUM(N25:N31)</f>
+        <v>-580574.29098900023</v>
       </c>
       <c r="O24" s="13">
         <v>-0.38555</v>
@@ -5305,10 +6454,11 @@
       </c>
       <c r="Q24" s="45">
         <f>IFERROR((P24*-1)/N24-1,"")</f>
-        <v>-8.475049069667151E-2</v>
-      </c>
-      <c r="R24" s="8">
-        <v>-858229.67955006356</v>
+        <v>-1.3265039648726384E-2</v>
+      </c>
+      <c r="R24" s="54">
+        <f>SUM(R25:R31)</f>
+        <v>-789109.5918365001</v>
       </c>
       <c r="S24" s="13">
         <v>-0.38555</v>
@@ -5319,10 +6469,11 @@
       </c>
       <c r="U24" s="45">
         <f>IFERROR((T24*-1)/R24-1,"")</f>
-        <v>-6.3972962959539803E-3</v>
-      </c>
-      <c r="V24" s="8">
-        <v>-1079705.293031936</v>
+        <v>8.0634855819473827E-2</v>
+      </c>
+      <c r="V24" s="54">
+        <f>SUM(V25:V31)</f>
+        <v>-1012548.1428699999</v>
       </c>
       <c r="W24" s="13">
         <v>-0.38554999999999995</v>
@@ -5333,7 +6484,7 @@
       </c>
       <c r="Y24" s="45">
         <f>IFERROR((X24*-1)/V24-1,"")</f>
-        <v>-3.7421788420130775E-2</v>
+        <v>2.6421111251235141E-2</v>
       </c>
       <c r="Z24" s="8">
         <v>-943174.75617692748</v>
@@ -5434,8 +6585,9 @@
       <c r="M25" s="15">
         <v>-8.2750000000000004E-2</v>
       </c>
-      <c r="N25" s="6">
-        <v>-134340.23585238314</v>
+      <c r="N25" s="53">
+        <f>P$10*$F25</f>
+        <v>-124607.76184500004</v>
       </c>
       <c r="O25" s="15">
         <v>-8.2750000000000004E-2</v>
@@ -5445,10 +6597,11 @@
       </c>
       <c r="Q25" s="46">
         <f t="shared" ref="Q25:Q62" si="6">IFERROR((P25*-1)/N25-1,"")</f>
-        <v>3.1827834113485505</v>
-      </c>
-      <c r="R25" s="6">
-        <v>-184200.50831997863</v>
+        <v>3.5094791984063489</v>
+      </c>
+      <c r="R25" s="53">
+        <f>T$10*$F25</f>
+        <v>-169365.37083250002</v>
       </c>
       <c r="S25" s="15">
         <v>-8.2750000000000004E-2</v>
@@ -5458,10 +6611,11 @@
       </c>
       <c r="U25" s="46">
         <f t="shared" ref="U25:U31" si="7">IFERROR((T25*-1)/R25-1,"")</f>
-        <v>3.5067824598937918</v>
-      </c>
-      <c r="V25" s="6">
-        <v>-231735.47658771294</v>
+        <v>3.9015428355836006</v>
+      </c>
+      <c r="V25" s="53">
+        <f>X$10*$F25</f>
+        <v>-217321.64134999996</v>
       </c>
       <c r="W25" s="15">
         <v>-8.2750000000000004E-2</v>
@@ -5471,7 +6625,7 @@
       </c>
       <c r="Y25" s="46">
         <f t="shared" ref="Y25:Y31" si="8">IFERROR((X25*-1)/V25-1,"")</f>
-        <v>3.3576404220429241</v>
+        <v>3.6466604693716107</v>
       </c>
       <c r="Z25" s="6">
         <v>-202432.1386944385</v>
@@ -5551,7 +6705,7 @@
         <v>180</v>
       </c>
       <c r="F26" s="31">
-        <v>-8.2750000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="s">
         <v>160</v>
@@ -5571,7 +6725,8 @@
       <c r="M26" s="15">
         <v>-8.2750000000000004E-2</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="53">
+        <f>P$10*$F26</f>
         <v>0</v>
       </c>
       <c r="O26" s="15">
@@ -5585,7 +6740,8 @@
         <f t="shared" ref="Q26" si="9">IFERROR((P26*-1)/N26-1,"")</f>
         <v/>
       </c>
-      <c r="R26" s="6">
+      <c r="R26" s="53">
+        <f>T$10*$F26</f>
         <v>0</v>
       </c>
       <c r="S26" s="15">
@@ -5599,7 +6755,8 @@
         <f t="shared" ref="U26" si="10">IFERROR((T26*-1)/R26-1,"")</f>
         <v/>
       </c>
-      <c r="V26" s="6">
+      <c r="V26" s="53">
+        <f>X$10*$F26</f>
         <v>0</v>
       </c>
       <c r="W26" s="15">
@@ -5711,8 +6868,9 @@
       <c r="M27" s="15">
         <v>-0.10491250000000001</v>
       </c>
-      <c r="N27" s="6">
-        <v>-170319.87907991718</v>
+      <c r="N27" s="53">
+        <f>P$10*$F27</f>
+        <v>-157980.80742675005</v>
       </c>
       <c r="O27" s="15">
         <v>-0.10491250000000002</v>
@@ -5725,8 +6883,9 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="R27" s="6">
-        <v>-233533.96772350161</v>
+      <c r="R27" s="53">
+        <f>T$10*$F27</f>
+        <v>-214725.61289987504</v>
       </c>
       <c r="S27" s="15">
         <v>-0.10491250000000001</v>
@@ -5739,8 +6898,9 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="V27" s="6">
-        <v>-293799.97809677862</v>
+      <c r="V27" s="53">
+        <f>X$10*$F27</f>
+        <v>-275525.76070249995</v>
       </c>
       <c r="W27" s="15">
         <v>-0.10491249999999999</v>
@@ -5851,8 +7011,9 @@
       <c r="M28" s="15">
         <v>-7.4374999999999983E-2</v>
       </c>
-      <c r="N28" s="6">
-        <v>-120743.86757125067</v>
+      <c r="N28" s="53">
+        <f>P$10*$F28</f>
+        <v>-111996.40226250001</v>
       </c>
       <c r="O28" s="15">
         <v>-7.4374999999999983E-2</v>
@@ -5865,8 +7026,9 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="R28" s="6">
-        <v>-165557.85868638559</v>
+      <c r="R28" s="53">
+        <f>T$10*$F28</f>
+        <v>-152224.16260624997</v>
       </c>
       <c r="S28" s="15">
         <v>-7.4374999999999983E-2</v>
@@ -5879,8 +7041,9 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="V28" s="6">
-        <v>-208281.88605693224</v>
+      <c r="V28" s="53">
+        <f>X$10*$F28</f>
+        <v>-195326.85287499992</v>
       </c>
       <c r="W28" s="15">
         <v>-7.4374999999999983E-2</v>
@@ -5991,8 +7154,9 @@
       <c r="M29" s="15">
         <v>-5.6737499999999989E-2</v>
       </c>
-      <c r="N29" s="6">
-        <v>-92110.321832925532</v>
+      <c r="N29" s="53">
+        <f>P$10*$F29</f>
+        <v>-85437.255440250025</v>
       </c>
       <c r="O29" s="15">
         <v>-5.6737500000000003E-2</v>
@@ -6005,8 +7169,9 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="R29" s="6">
-        <v>-126296.99505504275</v>
+      <c r="R29" s="53">
+        <f>T$10*$F29</f>
+        <v>-116125.289759625</v>
       </c>
       <c r="S29" s="15">
         <v>-5.6737499999999996E-2</v>
@@ -6019,8 +7184,9 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="V29" s="6">
-        <v>-158889.32450628834</v>
+      <c r="V29" s="53">
+        <f>X$10*$F29</f>
+        <v>-149006.48490749995</v>
       </c>
       <c r="W29" s="15">
         <v>-5.6737499999999989E-2</v>
@@ -6131,8 +7297,9 @@
       <c r="M30" s="15">
         <v>-6.1650000000000003E-2</v>
       </c>
-      <c r="N30" s="6">
-        <v>-100085.50501872411</v>
+      <c r="N30" s="53">
+        <f>P$10*$F30</f>
+        <v>-92834.664867000029</v>
       </c>
       <c r="O30" s="15">
         <v>-6.1650000000000003E-2</v>
@@ -6143,10 +7310,11 @@
       </c>
       <c r="Q30" s="46">
         <f t="shared" si="6"/>
-        <v>-0.99999000854319697</v>
-      </c>
-      <c r="R30" s="6">
-        <v>-137232.16118340404</v>
+        <v>-0.99998922816168467</v>
+      </c>
+      <c r="R30" s="53">
+        <f>T$10*$F30</f>
+        <v>-126179.75965950002</v>
       </c>
       <c r="S30" s="15">
         <v>-6.165000000000001E-2</v>
@@ -6157,10 +7325,11 @@
       </c>
       <c r="U30" s="46">
         <f t="shared" si="7"/>
-        <v>-0.98166115013931332</v>
-      </c>
-      <c r="V30" s="6">
-        <v>-172646.43059374625</v>
+        <v>-0.98005480429831737</v>
+      </c>
+      <c r="V30" s="53">
+        <f>X$10*$F30</f>
+        <v>-161907.90560999999</v>
       </c>
       <c r="W30" s="15">
         <v>-6.1650000000000003E-2</v>
@@ -6171,7 +7340,7 @@
       </c>
       <c r="Y30" s="46">
         <f t="shared" si="8"/>
-        <v>-0.92923253635779157</v>
+        <v>-0.92453889169915004</v>
       </c>
       <c r="Z30" s="6">
         <v>-150815.00121464813</v>
@@ -6271,8 +7440,9 @@
       <c r="M31" s="15">
         <v>-5.1250000000000002E-3</v>
       </c>
-      <c r="N31" s="6">
-        <v>-8320.1656645735784</v>
+      <c r="N31" s="53">
+        <f>P$10*$F31</f>
+        <v>-7717.399147500003</v>
       </c>
       <c r="O31" s="15">
         <v>-5.1250000000000002E-3</v>
@@ -6283,10 +7453,11 @@
       </c>
       <c r="Q31" s="46">
         <f t="shared" si="6"/>
-        <v>0.24899436128386232</v>
-      </c>
-      <c r="R31" s="6">
-        <v>-11408.188581750943</v>
+        <v>0.34654691320020192</v>
+      </c>
+      <c r="R31" s="53">
+        <f>T$10*$F31</f>
+        <v>-10489.396078750002</v>
       </c>
       <c r="S31" s="15">
         <v>-5.1250000000000002E-3</v>
@@ -6297,10 +7468,11 @@
       </c>
       <c r="U31" s="46">
         <f t="shared" si="7"/>
-        <v>0.67277652041329339</v>
-      </c>
-      <c r="V31" s="6">
-        <v>-14352.197190477689</v>
+        <v>0.81929921005272277</v>
+      </c>
+      <c r="V31" s="53">
+        <f>X$10*$F31</f>
+        <v>-13459.497424999998</v>
       </c>
       <c r="W31" s="15">
         <v>-5.1250000000000002E-3</v>
@@ -6311,7 +7483,7 @@
       </c>
       <c r="Y31" s="46">
         <f t="shared" si="8"/>
-        <v>9.5920003832980161E-2</v>
+        <v>0.16860678399364515</v>
       </c>
       <c r="Z31" s="6">
         <v>-12537.337894972778</v>

--- a/orcamento.xlsx
+++ b/orcamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e87dc3a59766ad95/Documentos/Karams Estofados/Relatórios/Financeiro/Orçamento 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="629" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A65A51-856A-44A0-AC84-B62898BF0F30}"/>
+  <xr:revisionPtr revIDLastSave="873" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73BF3427-99EA-4D1E-BD1C-5E921793936A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="196">
   <si>
     <t>Faturamento</t>
   </si>
@@ -664,6 +664,30 @@
   <si>
     <t>Impostos a recolher</t>
   </si>
+  <si>
+    <t>Entrada de Compras</t>
+  </si>
+  <si>
+    <t>Investimentos</t>
+  </si>
+  <si>
+    <t>Computadores e Periféricos</t>
+  </si>
+  <si>
+    <t>Consórcios</t>
+  </si>
+  <si>
+    <t>Construções e Reformas</t>
+  </si>
+  <si>
+    <t>Maquinas e Equipamentos</t>
+  </si>
+  <si>
+    <t>Moveis e Utensilios</t>
+  </si>
+  <si>
+    <t>Lucro Líquido Depois dos Investimentos</t>
+  </si>
 </sst>
 </file>
 
@@ -934,14 +958,14 @@
     <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1334,13 +1358,13 @@
             <v>359850.92</v>
           </cell>
           <cell r="D17">
-            <v>259701.91999999998</v>
+            <v>340167.56</v>
           </cell>
           <cell r="E17">
-            <v>13734.57</v>
+            <v>17555.27</v>
           </cell>
           <cell r="F17">
-            <v>931726.25999999989</v>
+            <v>1016012.5999999999</v>
           </cell>
           <cell r="G17"/>
           <cell r="H17"/>
@@ -1462,10 +1486,12 @@
           <cell r="C22">
             <v>32736.5</v>
           </cell>
-          <cell r="D22"/>
+          <cell r="D22">
+            <v>35869.64</v>
+          </cell>
           <cell r="E22"/>
           <cell r="F22">
-            <v>67168.479999999996</v>
+            <v>103038.12</v>
           </cell>
           <cell r="G22"/>
           <cell r="H22"/>
@@ -1510,10 +1536,12 @@
           <cell r="C24">
             <v>42800.44</v>
           </cell>
-          <cell r="D24"/>
+          <cell r="D24">
+            <v>44596</v>
+          </cell>
           <cell r="E24"/>
           <cell r="F24">
-            <v>87169.52</v>
+            <v>131765.52000000002</v>
           </cell>
           <cell r="G24"/>
           <cell r="H24"/>
@@ -1586,9 +1614,11 @@
           <cell r="D27">
             <v>218151.71</v>
           </cell>
-          <cell r="E27"/>
+          <cell r="E27">
+            <v>3820.7</v>
+          </cell>
           <cell r="F27">
-            <v>609909.85</v>
+            <v>613730.54999999993</v>
           </cell>
           <cell r="G27"/>
           <cell r="H27"/>
@@ -1634,13 +1664,13 @@
             <v>65815.299999999988</v>
           </cell>
           <cell r="D29">
-            <v>94625.499999999985</v>
+            <v>108047.90999999999</v>
           </cell>
           <cell r="E29">
-            <v>2834.8199999999997</v>
+            <v>3454.82</v>
           </cell>
           <cell r="F29">
-            <v>250664.85999999996</v>
+            <v>264707.26999999996</v>
           </cell>
           <cell r="G29"/>
           <cell r="H29"/>
@@ -1729,10 +1759,12 @@
           <cell r="C33">
             <v>5251.66</v>
           </cell>
-          <cell r="D33"/>
+          <cell r="D33">
+            <v>5035.68</v>
+          </cell>
           <cell r="E33"/>
           <cell r="F33">
-            <v>11749.61</v>
+            <v>16785.29</v>
           </cell>
           <cell r="G33"/>
           <cell r="H33"/>
@@ -1798,10 +1830,12 @@
           <cell r="C36">
             <v>8297.76</v>
           </cell>
-          <cell r="D36"/>
+          <cell r="D36">
+            <v>8386.73</v>
+          </cell>
           <cell r="E36"/>
           <cell r="F36">
-            <v>16324.37</v>
+            <v>24711.1</v>
           </cell>
           <cell r="G36"/>
           <cell r="H36"/>
@@ -1825,10 +1859,10 @@
             <v>50727.39</v>
           </cell>
           <cell r="E37">
-            <v>92.5</v>
+            <v>712.5</v>
           </cell>
           <cell r="F37">
-            <v>62614.86</v>
+            <v>63234.86</v>
           </cell>
           <cell r="G37"/>
           <cell r="H37"/>
@@ -1999,13 +2033,13 @@
             <v>172282.52000000005</v>
           </cell>
           <cell r="D44">
-            <v>149071.4</v>
+            <v>178209.46000000002</v>
           </cell>
           <cell r="E44">
             <v>32097.289999999997</v>
           </cell>
           <cell r="F44">
-            <v>515908.87000000005</v>
+            <v>545046.93000000005</v>
           </cell>
           <cell r="G44"/>
           <cell r="H44"/>
@@ -2123,10 +2157,12 @@
           <cell r="C49">
             <v>9673.7099999999991</v>
           </cell>
-          <cell r="D49"/>
+          <cell r="D49">
+            <v>9088.76</v>
+          </cell>
           <cell r="E49"/>
           <cell r="F49">
-            <v>18448.259999999998</v>
+            <v>27537.019999999997</v>
           </cell>
           <cell r="G49"/>
           <cell r="H49"/>
@@ -2172,11 +2208,11 @@
             <v>17763.09</v>
           </cell>
           <cell r="D51">
-            <v>178.31</v>
+            <v>20227.61</v>
           </cell>
           <cell r="E51"/>
           <cell r="F51">
-            <v>40890.629999999997</v>
+            <v>60939.93</v>
           </cell>
           <cell r="G51"/>
           <cell r="H51"/>
@@ -2701,13 +2737,13 @@
             <v>315472.21000000002</v>
           </cell>
           <cell r="D72">
-            <v>322781.34999999998</v>
+            <v>386839.54</v>
           </cell>
           <cell r="E72">
-            <v>3833</v>
+            <v>58520.56</v>
           </cell>
           <cell r="F72">
-            <v>1043832.8499999999</v>
+            <v>1162578.6000000001</v>
           </cell>
           <cell r="G72"/>
           <cell r="H72"/>
@@ -2801,9 +2837,11 @@
           <cell r="D76">
             <v>88339.049999999988</v>
           </cell>
-          <cell r="E76"/>
+          <cell r="E76">
+            <v>54220.92</v>
+          </cell>
           <cell r="F76">
-            <v>284165.46999999991</v>
+            <v>338386.3899999999</v>
           </cell>
           <cell r="G76"/>
           <cell r="H76"/>
@@ -2904,10 +2942,10 @@
             <v>41728.47</v>
           </cell>
           <cell r="E80">
-            <v>77.13</v>
+            <v>543.77</v>
           </cell>
           <cell r="F80">
-            <v>199557.97999999998</v>
+            <v>200024.61999999997</v>
           </cell>
           <cell r="G80"/>
           <cell r="H80"/>
@@ -3131,10 +3169,12 @@
           <cell r="C89">
             <v>45445.030000000006</v>
           </cell>
-          <cell r="D89"/>
+          <cell r="D89">
+            <v>61558.19</v>
+          </cell>
           <cell r="E89"/>
           <cell r="F89">
-            <v>81144.87000000001</v>
+            <v>142703.06</v>
           </cell>
           <cell r="G89"/>
           <cell r="H89"/>
@@ -3154,10 +3194,12 @@
           <cell r="C90">
             <v>1807.69</v>
           </cell>
-          <cell r="D90"/>
+          <cell r="D90">
+            <v>2500</v>
+          </cell>
           <cell r="E90"/>
           <cell r="F90">
-            <v>2545.85</v>
+            <v>5045.8500000000004</v>
           </cell>
           <cell r="G90"/>
           <cell r="H90"/>
@@ -3206,10 +3248,10 @@
             <v>67412.58</v>
           </cell>
           <cell r="E92">
-            <v>6603.51</v>
+            <v>11003.51</v>
           </cell>
           <cell r="F92">
-            <v>211938.18</v>
+            <v>216338.18</v>
           </cell>
           <cell r="G92"/>
           <cell r="H92"/>
@@ -3336,9 +3378,11 @@
           <cell r="D97">
             <v>7769.93</v>
           </cell>
-          <cell r="E97"/>
+          <cell r="E97">
+            <v>4400</v>
+          </cell>
           <cell r="F97">
-            <v>23805.78</v>
+            <v>28205.78</v>
           </cell>
           <cell r="G97"/>
           <cell r="H97"/>
@@ -3416,10 +3460,10 @@
             <v>55657.97</v>
           </cell>
           <cell r="E100">
-            <v>19187.699999999997</v>
+            <v>25070.949999999997</v>
           </cell>
           <cell r="F100">
-            <v>192846.00999999998</v>
+            <v>198729.25999999998</v>
           </cell>
           <cell r="G100"/>
           <cell r="H100"/>
@@ -3443,10 +3487,10 @@
             <v>9300.989999999998</v>
           </cell>
           <cell r="E101">
-            <v>2596.56</v>
+            <v>4315.76</v>
           </cell>
           <cell r="F101">
-            <v>31326.189999999991</v>
+            <v>33045.389999999992</v>
           </cell>
           <cell r="G101"/>
           <cell r="H101"/>
@@ -3470,10 +3514,10 @@
             <v>251.57000000000002</v>
           </cell>
           <cell r="E102">
-            <v>26.55</v>
+            <v>91.179999999999993</v>
           </cell>
           <cell r="F102">
-            <v>517.65</v>
+            <v>582.28</v>
           </cell>
           <cell r="G102"/>
           <cell r="H102"/>
@@ -3570,10 +3614,10 @@
             <v>29003.100000000002</v>
           </cell>
           <cell r="E106">
-            <v>8875.0299999999988</v>
+            <v>12974.449999999999</v>
           </cell>
           <cell r="F106">
-            <v>96841.87999999999</v>
+            <v>100941.29999999999</v>
           </cell>
           <cell r="G106"/>
           <cell r="H106"/>
@@ -3744,13 +3788,13 @@
             <v>1221830.2699999996</v>
           </cell>
           <cell r="D113">
-            <v>1192889.1400000004</v>
+            <v>1379973.4400000002</v>
           </cell>
           <cell r="E113">
-            <v>79220.48000000001</v>
+            <v>148631.99</v>
           </cell>
           <cell r="F113">
-            <v>3791558.2399999993</v>
+            <v>4048054.0499999993</v>
           </cell>
           <cell r="G113"/>
           <cell r="H113"/>
@@ -4339,12 +4383,34 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FC32606B-92DD-4595-BB15-6B3BF7B8928E}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;18aa524d-4dbd-46e3-a26f-e5157eb200d8&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A350001F-DEBE-4485-B61A-2E77155FDFFC}">
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="B2:AW157"/>
+  <dimension ref="B2:AW166"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -4463,30 +4529,30 @@
         <v>157</v>
       </c>
       <c r="M4" s="43"/>
-      <c r="N4" s="51" t="s">
+      <c r="N4" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="O4" s="51"/>
-      <c r="P4" s="52" t="s">
+      <c r="O4" s="53"/>
+      <c r="P4" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="54"/>
       <c r="R4" s="44" t="s">
         <v>157</v>
       </c>
       <c r="S4" s="43"/>
-      <c r="T4" s="52" t="s">
+      <c r="T4" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="U4" s="52"/>
+      <c r="U4" s="54"/>
       <c r="V4" s="44" t="s">
         <v>157</v>
       </c>
       <c r="W4" s="43"/>
-      <c r="X4" s="52" t="s">
+      <c r="X4" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="Y4" s="52"/>
+      <c r="Y4" s="54"/>
       <c r="Z4" s="44" t="s">
         <v>157</v>
       </c>
@@ -5197,8 +5263,8 @@
       <c r="M13" s="15">
         <v>-2.6200000000000001E-2</v>
       </c>
-      <c r="N13" s="53">
-        <f>P$10*$F13</f>
+      <c r="N13" s="51">
+        <f t="shared" ref="N13:N18" si="3">P$10*$F13</f>
         <v>-39452.850276000012</v>
       </c>
       <c r="O13" s="15">
@@ -5212,8 +5278,8 @@
         <f t="shared" si="0"/>
         <v>0.32761662677291503</v>
       </c>
-      <c r="R13" s="53">
-        <f>T$10*$F13</f>
+      <c r="R13" s="51">
+        <f t="shared" ref="R13:R18" si="4">T$10*$F13</f>
         <v>-53623.839466000005</v>
       </c>
       <c r="S13" s="15">
@@ -5227,8 +5293,8 @@
         <f t="shared" si="1"/>
         <v>0.33746036677350677</v>
       </c>
-      <c r="V13" s="53">
-        <f>X$10*$F13</f>
+      <c r="V13" s="51">
+        <f t="shared" ref="V13:V18" si="5">X$10*$F13</f>
         <v>-68807.577079999988</v>
       </c>
       <c r="W13" s="15">
@@ -5340,8 +5406,8 @@
       <c r="M14" s="15">
         <v>-2.4649999999999998E-2</v>
       </c>
-      <c r="N14" s="53">
-        <f>P$10*$F14</f>
+      <c r="N14" s="51">
+        <f t="shared" si="3"/>
         <v>-37118.80760700001</v>
       </c>
       <c r="O14" s="15">
@@ -5355,8 +5421,8 @@
         <f t="shared" si="0"/>
         <v>0.63472411728433098</v>
       </c>
-      <c r="R14" s="53">
-        <f>T$10*$F14</f>
+      <c r="R14" s="51">
+        <f t="shared" si="4"/>
         <v>-50451.436749500004</v>
       </c>
       <c r="S14" s="15">
@@ -5370,8 +5436,8 @@
         <f t="shared" si="1"/>
         <v>-0.62388940290807371</v>
       </c>
-      <c r="V14" s="53">
-        <f>X$10*$F14</f>
+      <c r="V14" s="51">
+        <f t="shared" si="5"/>
         <v>-64736.899809999981</v>
       </c>
       <c r="W14" s="15">
@@ -5483,8 +5549,8 @@
       <c r="M15" s="15">
         <v>-2.7499999999999998E-3</v>
       </c>
-      <c r="N15" s="53">
-        <f>P$10*$F15</f>
+      <c r="N15" s="51">
+        <f t="shared" si="3"/>
         <v>-4141.0434450000012</v>
       </c>
       <c r="O15" s="15">
@@ -5498,8 +5564,8 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="R15" s="53">
-        <f>T$10*$F15</f>
+      <c r="R15" s="51">
+        <f t="shared" si="4"/>
         <v>-5628.4564325000001</v>
       </c>
       <c r="S15" s="15">
@@ -5513,8 +5579,8 @@
         <f t="shared" si="1"/>
         <v>-0.91170581029455278</v>
       </c>
-      <c r="V15" s="53">
-        <f>X$10*$F15</f>
+      <c r="V15" s="51">
+        <f t="shared" si="5"/>
         <v>-7222.1693499999983</v>
       </c>
       <c r="W15" s="15">
@@ -5626,8 +5692,8 @@
       <c r="M16" s="15">
         <v>-1.06E-2</v>
       </c>
-      <c r="N16" s="53">
-        <f>P$10*$F16</f>
+      <c r="N16" s="51">
+        <f t="shared" si="3"/>
         <v>-15961.840188000006</v>
       </c>
       <c r="O16" s="15">
@@ -5641,8 +5707,8 @@
         <f t="shared" si="0"/>
         <v>-5.4787033932184315E-3</v>
       </c>
-      <c r="R16" s="53">
-        <f>T$10*$F16</f>
+      <c r="R16" s="51">
+        <f t="shared" si="4"/>
         <v>-21695.141158000002</v>
       </c>
       <c r="S16" s="15">
@@ -5656,8 +5722,8 @@
         <f t="shared" si="1"/>
         <v>-0.3195835928195071</v>
       </c>
-      <c r="V16" s="53">
-        <f>X$10*$F16</f>
+      <c r="V16" s="51">
+        <f t="shared" si="5"/>
         <v>-27838.180039999996</v>
       </c>
       <c r="W16" s="15">
@@ -5769,8 +5835,8 @@
       <c r="M17" s="15">
         <v>-1.2750000000000003E-2</v>
       </c>
-      <c r="N17" s="53">
-        <f>P$10*$F17</f>
+      <c r="N17" s="51">
+        <f t="shared" si="3"/>
         <v>-19199.383245000008</v>
       </c>
       <c r="O17" s="15">
@@ -5784,8 +5850,8 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="R17" s="53">
-        <f>T$10*$F17</f>
+      <c r="R17" s="51">
+        <f t="shared" si="4"/>
         <v>-26095.570732500004</v>
       </c>
       <c r="S17" s="15">
@@ -5799,8 +5865,8 @@
         <f t="shared" si="1"/>
         <v>-0.90570775304272222</v>
       </c>
-      <c r="V17" s="53">
-        <f>X$10*$F17</f>
+      <c r="V17" s="51">
+        <f t="shared" si="5"/>
         <v>-33484.603349999998</v>
       </c>
       <c r="W17" s="15">
@@ -5912,8 +5978,8 @@
       <c r="M18" s="15">
         <v>-8.5000000000000006E-4</v>
       </c>
-      <c r="N18" s="53">
-        <f>P$10*$F18</f>
+      <c r="N18" s="51">
+        <f t="shared" si="3"/>
         <v>-1279.9588830000005</v>
       </c>
       <c r="O18" s="15">
@@ -5927,8 +5993,8 @@
         <f t="shared" si="0"/>
         <v>0.12786435499897175</v>
       </c>
-      <c r="R18" s="53">
-        <f>T$10*$F18</f>
+      <c r="R18" s="51">
+        <f t="shared" si="4"/>
         <v>-1739.7047155000002</v>
       </c>
       <c r="S18" s="15">
@@ -5939,11 +6005,11 @@
         <v>1490.09</v>
       </c>
       <c r="U18" s="46">
-        <f t="shared" ref="U18" si="3">IFERROR((T18*-1)/R18-1,"")</f>
+        <f t="shared" ref="U18" si="6">IFERROR((T18*-1)/R18-1,"")</f>
         <v>-0.1434810823216397</v>
       </c>
-      <c r="V18" s="53">
-        <f>X$10*$F18</f>
+      <c r="V18" s="51">
+        <f t="shared" si="5"/>
         <v>-2232.3068899999998</v>
       </c>
       <c r="W18" s="15">
@@ -5954,7 +6020,7 @@
         <v>1921.23</v>
       </c>
       <c r="Y18" s="46">
-        <f t="shared" ref="Y18" si="4">IFERROR((X18*-1)/V18-1,"")</f>
+        <f t="shared" ref="Y18" si="7">IFERROR((X18*-1)/V18-1,"")</f>
         <v>-0.13935220618344279</v>
       </c>
       <c r="Z18" s="6">
@@ -6055,7 +6121,7 @@
       <c r="M19" s="15">
         <v>-8.5000000000000006E-4</v>
       </c>
-      <c r="N19" s="53">
+      <c r="N19" s="51">
         <v>0</v>
       </c>
       <c r="O19" s="15">
@@ -6066,10 +6132,10 @@
         <v>5659.96</v>
       </c>
       <c r="Q19" s="46" t="str">
-        <f t="shared" ref="Q19" si="5">IFERROR((P19*-1)/N19-1,"")</f>
+        <f t="shared" ref="Q19" si="8">IFERROR((P19*-1)/N19-1,"")</f>
         <v/>
       </c>
-      <c r="R19" s="53">
+      <c r="R19" s="51">
         <v>0</v>
       </c>
       <c r="S19" s="15">
@@ -6083,7 +6149,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V19" s="53">
+      <c r="V19" s="51">
         <v>0</v>
       </c>
       <c r="W19" s="15">
@@ -6351,11 +6417,11 @@
       </c>
       <c r="X23" s="7">
         <f>X24+X32+X46</f>
-        <v>1393448.2099999997</v>
+        <v>1487336.2599999995</v>
       </c>
       <c r="Y23" s="14">
         <f>IFERROR((X23*-1)/V23-1,"")</f>
-        <v>-4.3112632478352952E-2</v>
+        <v>2.1360728182995503E-2</v>
       </c>
       <c r="Z23" s="7">
         <v>-1386856.7374531499</v>
@@ -6441,7 +6507,7 @@
       <c r="M24" s="13">
         <v>-0.38555</v>
       </c>
-      <c r="N24" s="54">
+      <c r="N24" s="52">
         <f>SUM(N25:N31)</f>
         <v>-580574.29098900023</v>
       </c>
@@ -6456,7 +6522,7 @@
         <f>IFERROR((P24*-1)/N24-1,"")</f>
         <v>-1.3265039648726384E-2</v>
       </c>
-      <c r="R24" s="54">
+      <c r="R24" s="52">
         <f>SUM(R25:R31)</f>
         <v>-789109.5918365001</v>
       </c>
@@ -6471,7 +6537,7 @@
         <f>IFERROR((T24*-1)/R24-1,"")</f>
         <v>8.0634855819473827E-2</v>
       </c>
-      <c r="V24" s="54">
+      <c r="V24" s="52">
         <f>SUM(V25:V31)</f>
         <v>-1012548.1428699999</v>
       </c>
@@ -6571,7 +6637,7 @@
         <v>160</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>10</v>
+        <v>188</v>
       </c>
       <c r="J25" s="6">
         <v>-206875</v>
@@ -6585,8 +6651,8 @@
       <c r="M25" s="15">
         <v>-8.2750000000000004E-2</v>
       </c>
-      <c r="N25" s="53">
-        <f>P$10*$F25</f>
+      <c r="N25" s="51">
+        <f t="shared" ref="N25:N31" si="9">P$10*$F25</f>
         <v>-124607.76184500004</v>
       </c>
       <c r="O25" s="15">
@@ -6596,11 +6662,11 @@
         <v>561916.11</v>
       </c>
       <c r="Q25" s="46">
-        <f t="shared" ref="Q25:Q62" si="6">IFERROR((P25*-1)/N25-1,"")</f>
+        <f t="shared" ref="Q25:Q62" si="10">IFERROR((P25*-1)/N25-1,"")</f>
         <v>3.5094791984063489</v>
       </c>
-      <c r="R25" s="53">
-        <f>T$10*$F25</f>
+      <c r="R25" s="51">
+        <f t="shared" ref="R25:R31" si="11">T$10*$F25</f>
         <v>-169365.37083250002</v>
       </c>
       <c r="S25" s="15">
@@ -6610,11 +6676,11 @@
         <v>830151.62000000011</v>
       </c>
       <c r="U25" s="46">
-        <f t="shared" ref="U25:U31" si="7">IFERROR((T25*-1)/R25-1,"")</f>
+        <f t="shared" ref="U25:U31" si="12">IFERROR((T25*-1)/R25-1,"")</f>
         <v>3.9015428355836006</v>
       </c>
-      <c r="V25" s="53">
-        <f>X$10*$F25</f>
+      <c r="V25" s="51">
+        <f t="shared" ref="V25:V31" si="13">X$10*$F25</f>
         <v>-217321.64134999996</v>
       </c>
       <c r="W25" s="15">
@@ -6624,7 +6690,7 @@
         <v>1009819.8799999997</v>
       </c>
       <c r="Y25" s="46">
-        <f t="shared" ref="Y25:Y31" si="8">IFERROR((X25*-1)/V25-1,"")</f>
+        <f t="shared" ref="Y25:Y31" si="14">IFERROR((X25*-1)/V25-1,"")</f>
         <v>3.6466604693716107</v>
       </c>
       <c r="Z25" s="6">
@@ -6725,8 +6791,8 @@
       <c r="M26" s="15">
         <v>-8.2750000000000004E-2</v>
       </c>
-      <c r="N26" s="53">
-        <f>P$10*$F26</f>
+      <c r="N26" s="51">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O26" s="15">
@@ -6737,11 +6803,11 @@
         <v>564</v>
       </c>
       <c r="Q26" s="46" t="str">
-        <f t="shared" ref="Q26" si="9">IFERROR((P26*-1)/N26-1,"")</f>
+        <f t="shared" ref="Q26" si="15">IFERROR((P26*-1)/N26-1,"")</f>
         <v/>
       </c>
-      <c r="R26" s="53">
-        <f>T$10*$F26</f>
+      <c r="R26" s="51">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S26" s="15">
@@ -6752,11 +6818,11 @@
         <v>987.68</v>
       </c>
       <c r="U26" s="46" t="str">
-        <f t="shared" ref="U26" si="10">IFERROR((T26*-1)/R26-1,"")</f>
+        <f t="shared" ref="U26" si="16">IFERROR((T26*-1)/R26-1,"")</f>
         <v/>
       </c>
-      <c r="V26" s="53">
-        <f>X$10*$F26</f>
+      <c r="V26" s="51">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="W26" s="15">
@@ -6767,7 +6833,7 @@
         <v>1534.3</v>
       </c>
       <c r="Y26" s="46" t="str">
-        <f t="shared" ref="Y26" si="11">IFERROR((X26*-1)/V26-1,"")</f>
+        <f t="shared" ref="Y26" si="17">IFERROR((X26*-1)/V26-1,"")</f>
         <v/>
       </c>
       <c r="Z26" s="6">
@@ -6868,8 +6934,8 @@
       <c r="M27" s="15">
         <v>-0.10491250000000001</v>
       </c>
-      <c r="N27" s="53">
-        <f>P$10*$F27</f>
+      <c r="N27" s="51">
+        <f t="shared" si="9"/>
         <v>-157980.80742675005</v>
       </c>
       <c r="O27" s="15">
@@ -6880,11 +6946,11 @@
         <v/>
       </c>
       <c r="Q27" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="R27" s="53">
-        <f>T$10*$F27</f>
+      <c r="R27" s="51">
+        <f t="shared" si="11"/>
         <v>-214725.61289987504</v>
       </c>
       <c r="S27" s="15">
@@ -6895,11 +6961,11 @@
         <v/>
       </c>
       <c r="U27" s="46" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="V27" s="53">
-        <f>X$10*$F27</f>
+      <c r="V27" s="51">
+        <f t="shared" si="13"/>
         <v>-275525.76070249995</v>
       </c>
       <c r="W27" s="15">
@@ -6910,7 +6976,7 @@
         <v/>
       </c>
       <c r="Y27" s="46" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Z27" s="6">
@@ -7011,8 +7077,8 @@
       <c r="M28" s="15">
         <v>-7.4374999999999983E-2</v>
       </c>
-      <c r="N28" s="53">
-        <f>P$10*$F28</f>
+      <c r="N28" s="51">
+        <f t="shared" si="9"/>
         <v>-111996.40226250001</v>
       </c>
       <c r="O28" s="15">
@@ -7023,11 +7089,11 @@
         <v/>
       </c>
       <c r="Q28" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="R28" s="53">
-        <f>T$10*$F28</f>
+      <c r="R28" s="51">
+        <f t="shared" si="11"/>
         <v>-152224.16260624997</v>
       </c>
       <c r="S28" s="15">
@@ -7038,11 +7104,11 @@
         <v/>
       </c>
       <c r="U28" s="46" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="V28" s="53">
-        <f>X$10*$F28</f>
+      <c r="V28" s="51">
+        <f t="shared" si="13"/>
         <v>-195326.85287499992</v>
       </c>
       <c r="W28" s="15">
@@ -7053,7 +7119,7 @@
         <v/>
       </c>
       <c r="Y28" s="46" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Z28" s="6">
@@ -7154,8 +7220,8 @@
       <c r="M29" s="15">
         <v>-5.6737499999999989E-2</v>
       </c>
-      <c r="N29" s="53">
-        <f>P$10*$F29</f>
+      <c r="N29" s="51">
+        <f t="shared" si="9"/>
         <v>-85437.255440250025</v>
       </c>
       <c r="O29" s="15">
@@ -7166,11 +7232,11 @@
         <v/>
       </c>
       <c r="Q29" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="R29" s="53">
-        <f>T$10*$F29</f>
+      <c r="R29" s="51">
+        <f t="shared" si="11"/>
         <v>-116125.289759625</v>
       </c>
       <c r="S29" s="15">
@@ -7181,11 +7247,11 @@
         <v/>
       </c>
       <c r="U29" s="46" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="V29" s="53">
-        <f>X$10*$F29</f>
+      <c r="V29" s="51">
+        <f t="shared" si="13"/>
         <v>-149006.48490749995</v>
       </c>
       <c r="W29" s="15">
@@ -7196,7 +7262,7 @@
         <v/>
       </c>
       <c r="Y29" s="46" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Z29" s="6">
@@ -7297,8 +7363,8 @@
       <c r="M30" s="15">
         <v>-6.1650000000000003E-2</v>
       </c>
-      <c r="N30" s="53">
-        <f>P$10*$F30</f>
+      <c r="N30" s="51">
+        <f t="shared" si="9"/>
         <v>-92834.664867000029</v>
       </c>
       <c r="O30" s="15">
@@ -7309,11 +7375,11 @@
         <v>1</v>
       </c>
       <c r="Q30" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.99998922816168467</v>
       </c>
-      <c r="R30" s="53">
-        <f>T$10*$F30</f>
+      <c r="R30" s="51">
+        <f t="shared" si="11"/>
         <v>-126179.75965950002</v>
       </c>
       <c r="S30" s="15">
@@ -7324,11 +7390,11 @@
         <v>2516.6800000000003</v>
       </c>
       <c r="U30" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>-0.98005480429831737</v>
       </c>
-      <c r="V30" s="53">
-        <f>X$10*$F30</f>
+      <c r="V30" s="51">
+        <f t="shared" si="13"/>
         <v>-161907.90560999999</v>
       </c>
       <c r="W30" s="15">
@@ -7339,7 +7405,7 @@
         <v>12217.75</v>
       </c>
       <c r="Y30" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>-0.92453889169915004</v>
       </c>
       <c r="Z30" s="6">
@@ -7440,8 +7506,8 @@
       <c r="M31" s="15">
         <v>-5.1250000000000002E-3</v>
       </c>
-      <c r="N31" s="53">
-        <f>P$10*$F31</f>
+      <c r="N31" s="51">
+        <f t="shared" si="9"/>
         <v>-7717.399147500003</v>
       </c>
       <c r="O31" s="15">
@@ -7452,11 +7518,11 @@
         <v>10391.839999999998</v>
       </c>
       <c r="Q31" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.34654691320020192</v>
       </c>
-      <c r="R31" s="53">
-        <f>T$10*$F31</f>
+      <c r="R31" s="51">
+        <f t="shared" si="11"/>
         <v>-10489.396078750002</v>
       </c>
       <c r="S31" s="15">
@@ -7467,11 +7533,11 @@
         <v>19083.350000000006</v>
       </c>
       <c r="U31" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>0.81929921005272277</v>
       </c>
-      <c r="V31" s="53">
-        <f>X$10*$F31</f>
+      <c r="V31" s="51">
+        <f t="shared" si="13"/>
         <v>-13459.497424999998</v>
       </c>
       <c r="W31" s="15">
@@ -7482,7 +7548,7 @@
         <v>15728.859999999995</v>
       </c>
       <c r="Y31" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.16860678399364515</v>
       </c>
       <c r="Z31" s="6">
@@ -7604,11 +7670,11 @@
       </c>
       <c r="X32" s="8">
         <f>SUM(X33:X45)</f>
-        <v>259701.91999999998</v>
+        <v>340167.56</v>
       </c>
       <c r="Y32" s="45">
         <f>(X32*-1)/V32-1</f>
-        <v>-0.25692370097751349</v>
+        <v>-2.6690093271895532E-2</v>
       </c>
       <c r="Z32" s="8">
         <v>-349495.63098922232</v>
@@ -7711,7 +7777,7 @@
         <v>4543.34</v>
       </c>
       <c r="Q33" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>5.1699074074074147E-2</v>
       </c>
       <c r="R33" s="6">
@@ -7725,7 +7791,7 @@
         <v>6905.72</v>
       </c>
       <c r="U33" s="46">
-        <f t="shared" ref="U33:U45" si="12">IFERROR((T33*-1)/R33-1,"")</f>
+        <f t="shared" ref="U33:U45" si="18">IFERROR((T33*-1)/R33-1,"")</f>
         <v>0.59854629629629641</v>
       </c>
       <c r="V33" s="6">
@@ -7739,7 +7805,7 @@
         <v>8155.15</v>
       </c>
       <c r="Y33" s="46">
-        <f t="shared" ref="Y33:Y45" si="13">IFERROR((X33*-1)/V33-1,"")</f>
+        <f t="shared" ref="Y33:Y45" si="19">IFERROR((X33*-1)/V33-1,"")</f>
         <v>0.88776620370370352</v>
       </c>
       <c r="Z33" s="6">
@@ -7851,7 +7917,7 @@
         <v>14950.47</v>
       </c>
       <c r="Q34" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.21507170128137343</v>
       </c>
       <c r="R34" s="6">
@@ -7865,7 +7931,7 @@
         <v>21105.59</v>
       </c>
       <c r="U34" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.10808388312560457</v>
       </c>
       <c r="V34" s="6">
@@ -7879,7 +7945,7 @@
         <v>9382.1299999999992</v>
       </c>
       <c r="Y34" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-0.50742021225707368</v>
       </c>
       <c r="Z34" s="6">
@@ -7982,7 +8048,7 @@
         <v>1899.2</v>
       </c>
       <c r="Q35" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.13437829017834746</v>
       </c>
       <c r="R35" s="6">
@@ -7996,7 +8062,7 @@
         <v>1694.1599999999999</v>
       </c>
       <c r="U35" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>-0.2278318892631368</v>
       </c>
       <c r="V35" s="6">
@@ -8010,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="Y35" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="Z35" s="6">
@@ -8113,7 +8179,7 @@
         <v>185861.81</v>
       </c>
       <c r="Q36" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.10713196036011785</v>
       </c>
       <c r="R36" s="6">
@@ -8127,7 +8193,7 @@
         <v>205896.33000000002</v>
       </c>
       <c r="U36" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>-1.0887430095799178E-2</v>
       </c>
       <c r="V36" s="6">
@@ -8141,7 +8207,7 @@
         <v>218151.71</v>
       </c>
       <c r="Y36" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>4.798661786295999E-2</v>
       </c>
       <c r="Z36" s="6">
@@ -8253,7 +8319,7 @@
         <v/>
       </c>
       <c r="Q37" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R37" s="6">
@@ -8267,7 +8333,7 @@
         <v/>
       </c>
       <c r="U37" s="46" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="V37" s="6">
@@ -8281,7 +8347,7 @@
         <v/>
       </c>
       <c r="Y37" s="46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z37" s="6">
@@ -8384,7 +8450,7 @@
         <v/>
       </c>
       <c r="Q38" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R38" s="6">
@@ -8398,7 +8464,7 @@
         <v/>
       </c>
       <c r="U38" s="46" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="V38" s="6">
@@ -8412,7 +8478,7 @@
         <v/>
       </c>
       <c r="Y38" s="46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z38" s="6">
@@ -8524,7 +8590,7 @@
         <v>6816.55</v>
       </c>
       <c r="Q39" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.1282180813648629</v>
       </c>
       <c r="R39" s="6">
@@ -8538,7 +8604,7 @@
         <v>9992.25</v>
       </c>
       <c r="U39" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.27792840608254155</v>
       </c>
       <c r="V39" s="6">
@@ -8552,7 +8618,7 @@
         <v>8223.1</v>
       </c>
       <c r="Y39" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>5.1668350577432243E-2</v>
       </c>
       <c r="Z39" s="6">
@@ -8655,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
       <c r="R40" s="6">
@@ -8669,7 +8735,7 @@
         <v>30936.210000000003</v>
       </c>
       <c r="U40" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>2.0936210000000002</v>
       </c>
       <c r="V40" s="6">
@@ -8683,7 +8749,7 @@
         <v>7839.08</v>
       </c>
       <c r="Y40" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-0.21609200000000006</v>
       </c>
       <c r="Z40" s="6">
@@ -8795,7 +8861,7 @@
         <v>808</v>
       </c>
       <c r="Q41" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.37442497551508647</v>
       </c>
       <c r="R41" s="6">
@@ -8809,7 +8875,7 @@
         <v>570</v>
       </c>
       <c r="U41" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>-0.55869088619257334</v>
       </c>
       <c r="V41" s="6">
@@ -8823,7 +8889,7 @@
         <v>349.9</v>
       </c>
       <c r="Y41" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-0.72909814224347613</v>
       </c>
       <c r="Z41" s="6">
@@ -8926,7 +8992,7 @@
         <v>1983.19</v>
       </c>
       <c r="Q42" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2156631484184786E-2</v>
       </c>
       <c r="R42" s="6">
@@ -8940,7 +9006,7 @@
         <v>1883.98</v>
       </c>
       <c r="U42" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>-2.8977228312176639E-2</v>
       </c>
       <c r="V42" s="6">
@@ -8954,7 +9020,7 @@
         <v>1980.53</v>
       </c>
       <c r="Y42" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>2.0785639980724246E-2</v>
       </c>
       <c r="Z42" s="6">
@@ -9057,7 +9123,7 @@
         <v>34431.979999999996</v>
       </c>
       <c r="Q43" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.0676123892476639</v>
       </c>
       <c r="R43" s="6">
@@ -9071,7 +9137,7 @@
         <v>32736.5</v>
       </c>
       <c r="U43" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.96580019448797749</v>
       </c>
       <c r="V43" s="6">
@@ -9082,11 +9148,11 @@
       </c>
       <c r="X43" s="6">
         <f>IFERROR(VLOOKUP($I43,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>35869.64</v>
       </c>
       <c r="Y43" s="46">
-        <f t="shared" si="13"/>
-        <v>-1</v>
+        <f t="shared" si="19"/>
+        <v>1.1539427027389531</v>
       </c>
       <c r="Z43" s="6">
         <v>-16653.014936000003</v>
@@ -9188,7 +9254,7 @@
         <v>44369.08</v>
       </c>
       <c r="Q44" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.1841454047147868</v>
       </c>
       <c r="R44" s="6">
@@ -9202,7 +9268,7 @@
         <v>42800.44</v>
       </c>
       <c r="U44" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.14228071318519442</v>
       </c>
       <c r="V44" s="6">
@@ -9213,11 +9279,11 @@
       </c>
       <c r="X44" s="6">
         <f>IFERROR(VLOOKUP($I44,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>44596</v>
       </c>
       <c r="Y44" s="46">
-        <f t="shared" si="13"/>
-        <v>-1</v>
+        <f t="shared" si="19"/>
+        <v>0.19020156533920995</v>
       </c>
       <c r="Z44" s="6">
         <v>-37469.283606000005</v>
@@ -9319,7 +9385,7 @@
         <v>2775.23</v>
       </c>
       <c r="Q45" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.8800117811892173</v>
       </c>
       <c r="R45" s="6">
@@ -9333,7 +9399,7 @@
         <v>5329.74</v>
       </c>
       <c r="U45" s="46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>-0.7695664830213782</v>
       </c>
       <c r="V45" s="6">
@@ -9347,7 +9413,7 @@
         <v>5620.32</v>
       </c>
       <c r="Y45" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-0.7570031363358648</v>
       </c>
       <c r="Z45" s="6">
@@ -9466,11 +9532,11 @@
       </c>
       <c r="X46" s="8">
         <f>SUM(X47:X62)</f>
-        <v>94445.5</v>
+        <v>107867.90999999999</v>
       </c>
       <c r="Y46" s="45">
         <f>(X46*-1)/V46-1</f>
-        <v>2.7514572144509142E-3</v>
+        <v>0.14526053585588761</v>
       </c>
       <c r="Z46" s="6">
         <v>-94186.350287000037</v>
@@ -9572,7 +9638,7 @@
         <v>2679.9199999999996</v>
       </c>
       <c r="Q47" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.7702925714285721</v>
       </c>
       <c r="R47" s="6">
@@ -9586,7 +9652,7 @@
         <v>9115.0500000000011</v>
       </c>
       <c r="U47" s="46">
-        <f t="shared" ref="U47:U62" si="14">IFERROR((T47*-1)/R47-1,"")</f>
+        <f t="shared" ref="U47:U62" si="20">IFERROR((T47*-1)/R47-1,"")</f>
         <v>-0.21871000000000218</v>
       </c>
       <c r="V47" s="6">
@@ -9600,7 +9666,7 @@
         <v>50727.39</v>
       </c>
       <c r="Y47" s="46">
-        <f t="shared" ref="Y47:Y62" si="15">IFERROR((X47*-1)/V47-1,"")</f>
+        <f t="shared" ref="Y47:Y62" si="21">IFERROR((X47*-1)/V47-1,"")</f>
         <v>3.3480619999999872</v>
       </c>
       <c r="Z47" s="6">
@@ -9703,7 +9769,7 @@
         <v>36962.579999999994</v>
       </c>
       <c r="Q48" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.11904269448182936</v>
       </c>
       <c r="R48" s="6">
@@ -9717,7 +9783,7 @@
         <v>30986.82</v>
       </c>
       <c r="U48" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-0.26146753138507739</v>
       </c>
       <c r="V48" s="6">
@@ -9731,7 +9797,7 @@
         <v>28474.9</v>
       </c>
       <c r="Y48" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-0.3213360328499969</v>
       </c>
       <c r="Z48" s="6">
@@ -9843,7 +9909,7 @@
         <v>230</v>
       </c>
       <c r="Q49" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.117647058823529</v>
       </c>
       <c r="R49" s="6">
@@ -9857,7 +9923,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="V49" s="6">
@@ -9871,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="Y49" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="Z49" s="6">
@@ -9974,7 +10040,7 @@
         <v/>
       </c>
       <c r="Q50" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R50" s="6">
@@ -9988,7 +10054,7 @@
         <v/>
       </c>
       <c r="U50" s="46" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V50" s="6">
@@ -10002,7 +10068,7 @@
         <v/>
       </c>
       <c r="Y50" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z50" s="6">
@@ -10114,7 +10180,7 @@
         <v>3000.69</v>
       </c>
       <c r="Q51" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.1389219371178767</v>
       </c>
       <c r="R51" s="6">
@@ -10128,7 +10194,7 @@
         <v>2925.69</v>
       </c>
       <c r="U51" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-0.16044393862958217</v>
       </c>
       <c r="V51" s="6">
@@ -10142,7 +10208,7 @@
         <v>1589.46</v>
       </c>
       <c r="Y51" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-0.54388852636273</v>
       </c>
       <c r="Z51" s="6">
@@ -10245,7 +10311,7 @@
         <v/>
       </c>
       <c r="Q52" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R52" s="6">
@@ -10259,7 +10325,7 @@
         <v/>
       </c>
       <c r="U52" s="46" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V52" s="6">
@@ -10273,7 +10339,7 @@
         <v/>
       </c>
       <c r="Y52" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z52" s="6">
@@ -10377,7 +10443,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
       <c r="R53" s="6">
@@ -10391,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="V53" s="6">
@@ -10405,7 +10471,7 @@
         <v>0</v>
       </c>
       <c r="Y53" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="Z53" s="6">
@@ -10508,7 +10574,7 @@
         <v>361.18</v>
       </c>
       <c r="Q54" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.27033532695817786</v>
       </c>
       <c r="R54" s="6">
@@ -10522,7 +10588,7 @@
         <v>243.78000000000003</v>
       </c>
       <c r="U54" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-0.50750967940047786</v>
       </c>
       <c r="V54" s="6">
@@ -10536,7 +10602,7 @@
         <v>272.03999999999996</v>
       </c>
       <c r="Y54" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-0.45041813595908609</v>
       </c>
       <c r="Z54" s="6">
@@ -10639,7 +10705,7 @@
         <v>6497.95</v>
       </c>
       <c r="Q55" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.93588235838508771</v>
       </c>
       <c r="R55" s="6">
@@ -10653,7 +10719,7 @@
         <v>5251.66</v>
       </c>
       <c r="U55" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.56458513011590261</v>
       </c>
       <c r="V55" s="6">
@@ -10664,11 +10730,11 @@
       </c>
       <c r="X55" s="6">
         <f>IFERROR(VLOOKUP($I55,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>5035.68</v>
       </c>
       <c r="Y55" s="46">
-        <f t="shared" si="15"/>
-        <v>-1</v>
+        <f t="shared" si="21"/>
+        <v>0.5002399332824381</v>
       </c>
       <c r="Z55" s="6">
         <v>-3356.5830960000003</v>
@@ -10770,7 +10836,7 @@
         <v>8026.6100000000006</v>
       </c>
       <c r="Q56" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6.2801700477318478E-2</v>
       </c>
       <c r="R56" s="6">
@@ -10784,7 +10850,7 @@
         <v>8297.76</v>
       </c>
       <c r="U56" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>9.8704613548269204E-2</v>
       </c>
       <c r="V56" s="6">
@@ -10795,11 +10861,11 @@
       </c>
       <c r="X56" s="6">
         <f>IFERROR(VLOOKUP($I56,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>8386.73</v>
       </c>
       <c r="Y56" s="46">
-        <f t="shared" si="15"/>
-        <v>-1</v>
+        <f t="shared" si="21"/>
+        <v>0.11048511207647316</v>
       </c>
       <c r="Z56" s="6">
         <v>-7552.3119660000002</v>
@@ -10901,7 +10967,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
       <c r="R57" s="6">
@@ -10915,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="V57" s="6">
@@ -10929,7 +10995,7 @@
         <v>1458.08</v>
       </c>
       <c r="Y57" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-0.68723622506141591</v>
       </c>
       <c r="Z57" s="6">
@@ -11041,7 +11107,7 @@
         <v>2316.15</v>
       </c>
       <c r="Q58" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-3.4835353408235736E-2</v>
       </c>
       <c r="R58" s="6">
@@ -11055,7 +11121,7 @@
         <v>2405.31</v>
       </c>
       <c r="U58" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>2.3185787162474103E-3</v>
       </c>
       <c r="V58" s="6">
@@ -11069,7 +11135,7 @@
         <v>2405.31</v>
       </c>
       <c r="Y58" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>2.3185787162474103E-3</v>
       </c>
       <c r="Z58" s="6">
@@ -11172,7 +11238,7 @@
         <v>2934.94</v>
       </c>
       <c r="Q59" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.17397600000000013</v>
       </c>
       <c r="R59" s="6">
@@ -11186,7 +11252,7 @@
         <v>1387.6999999999998</v>
       </c>
       <c r="U59" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-0.44492000000000009</v>
       </c>
       <c r="V59" s="6">
@@ -11200,7 +11266,7 @@
         <v>705.03</v>
       </c>
       <c r="Y59" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-0.71798800000000007</v>
       </c>
       <c r="Z59" s="6">
@@ -11303,7 +11369,7 @@
         <v>1649.3</v>
       </c>
       <c r="Q60" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-0.15420512820512822</v>
       </c>
       <c r="R60" s="6">
@@ -11317,7 +11383,7 @@
         <v>1675.48</v>
       </c>
       <c r="U60" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-0.14077948717948718</v>
       </c>
       <c r="V60" s="6">
@@ -11331,7 +11397,7 @@
         <v>2109.6999999999998</v>
       </c>
       <c r="Y60" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>8.1897435897435811E-2</v>
       </c>
       <c r="Z60" s="6">
@@ -11434,7 +11500,7 @@
         <v>22729.919999999998</v>
       </c>
       <c r="Q61" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.2471314285714281</v>
       </c>
       <c r="R61" s="6">
@@ -11448,7 +11514,7 @@
         <v>3526.05</v>
       </c>
       <c r="U61" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>-0.49627857142857146</v>
       </c>
       <c r="V61" s="6">
@@ -11462,7 +11528,7 @@
         <v>6703.59</v>
       </c>
       <c r="Y61" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>-4.2344285714285723E-2</v>
       </c>
       <c r="Z61" s="6">
@@ -11574,7 +11640,7 @@
         <v/>
       </c>
       <c r="Q62" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R62" s="6">
@@ -11588,7 +11654,7 @@
         <v/>
       </c>
       <c r="U62" s="46" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V62" s="6">
@@ -11602,7 +11668,7 @@
         <v/>
       </c>
       <c r="Y62" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Z62" s="6">
@@ -11727,11 +11793,11 @@
       </c>
       <c r="X64" s="48">
         <f>X21-X23</f>
-        <v>1063457.1999999995</v>
+        <v>969569.14999999967</v>
       </c>
       <c r="Y64" s="14">
         <f>X64/V64-1</f>
-        <v>4.0495070359296559E-3</v>
+        <v>-8.4593693949558513E-2</v>
       </c>
       <c r="Z64" s="7">
         <v>869130.19069200032</v>
@@ -11833,7 +11899,7 @@
         <v>655078.40999999992</v>
       </c>
       <c r="Q66" s="14">
-        <f t="shared" ref="Q66:Q130" si="16">IFERROR((P66*-1)/N66-1,"")</f>
+        <f t="shared" ref="Q66:Q130" si="22">IFERROR((P66*-1)/N66-1,"")</f>
         <v>5.1628124241417161E-2</v>
       </c>
       <c r="R66" s="7">
@@ -11847,7 +11913,7 @@
         <v>570118.07999999996</v>
       </c>
       <c r="U66" s="14">
-        <f t="shared" ref="U66" si="17">IFERROR((T66*-1)/R66-1,"")</f>
+        <f t="shared" ref="U66" si="23">IFERROR((T66*-1)/R66-1,"")</f>
         <v>-0.16281843283634978</v>
       </c>
       <c r="V66" s="7">
@@ -11858,11 +11924,11 @@
       </c>
       <c r="X66" s="7">
         <f>SUM(X67+X85+X101+X123)</f>
-        <v>557251.15</v>
+        <v>650447.4</v>
       </c>
       <c r="Y66" s="14">
-        <f t="shared" ref="Y66" si="18">IFERROR((X66*-1)/V66-1,"")</f>
-        <v>-0.24324261718761164</v>
+        <f t="shared" ref="Y66" si="24">IFERROR((X66*-1)/V66-1,"")</f>
+        <v>-0.11668038355574017</v>
       </c>
       <c r="Z66" s="7">
         <v>-702233.64180127438</v>
@@ -11984,11 +12050,11 @@
       </c>
       <c r="X67" s="8">
         <f>SUM(X68:X84)</f>
-        <v>149071.40000000002</v>
+        <v>178209.46000000002</v>
       </c>
       <c r="Y67" s="45">
         <f>(X67*-1)/V67-1</f>
-        <v>-0.14747148247323461</v>
+        <v>1.9166967929766354E-2</v>
       </c>
       <c r="Z67" s="8">
         <v>-174857.96303033334</v>
@@ -12091,7 +12157,7 @@
         <v>64498.680000000008</v>
       </c>
       <c r="Q68" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>9.3690140845070768E-3</v>
       </c>
       <c r="R68" s="6">
@@ -12105,7 +12171,7 @@
         <v>60318.180000000008</v>
       </c>
       <c r="U68" s="46">
-        <f t="shared" ref="U68:U84" si="19">IFERROR((T68*-1)/R68-1,"")</f>
+        <f t="shared" ref="U68:U84" si="25">IFERROR((T68*-1)/R68-1,"")</f>
         <v>-5.6053521126760431E-2</v>
       </c>
       <c r="V68" s="6">
@@ -12119,7 +12185,7 @@
         <v>59830.189999999995</v>
       </c>
       <c r="Y68" s="46">
-        <f t="shared" ref="Y68:Y84" si="20">IFERROR((X68*-1)/V68-1,"")</f>
+        <f t="shared" ref="Y68:Y84" si="26">IFERROR((X68*-1)/V68-1,"")</f>
         <v>-6.3690297339593194E-2</v>
       </c>
       <c r="Z68" s="6">
@@ -12222,7 +12288,7 @@
         <v>53990.009999999995</v>
       </c>
       <c r="Q69" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.10775179494599152</v>
       </c>
       <c r="R69" s="6">
@@ -12236,7 +12302,7 @@
         <v>71662.62000000001</v>
       </c>
       <c r="U69" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0.18430880202592115</v>
       </c>
       <c r="V69" s="6">
@@ -12250,7 +12316,7 @@
         <v>73572.070000000007</v>
       </c>
       <c r="Y69" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.21586470162920657</v>
       </c>
       <c r="Z69" s="6">
@@ -12351,7 +12417,7 @@
         <v/>
       </c>
       <c r="Q70" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R70" s="6">
@@ -12365,7 +12431,7 @@
         <v/>
       </c>
       <c r="U70" s="46" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="V70" s="6">
@@ -12379,7 +12445,7 @@
         <v/>
       </c>
       <c r="Y70" s="46" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z70" s="6">
@@ -12482,7 +12548,7 @@
         <v/>
       </c>
       <c r="Q71" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R71" s="6">
@@ -12496,7 +12562,7 @@
         <v/>
       </c>
       <c r="U71" s="46" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="V71" s="6">
@@ -12510,7 +12576,7 @@
         <v/>
       </c>
       <c r="Y71" s="46" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z71" s="6">
@@ -12613,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="R72" s="6">
@@ -12627,7 +12693,7 @@
         <v>297.89999999999998</v>
       </c>
       <c r="U72" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>-0.95569167957979073</v>
       </c>
       <c r="V72" s="6">
@@ -12641,7 +12707,7 @@
         <v>1372.31</v>
       </c>
       <c r="Y72" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-0.79588871703303998</v>
       </c>
       <c r="Z72" s="6">
@@ -12753,7 +12819,7 @@
         <v>2919.01</v>
       </c>
       <c r="Q73" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.36335814041405456</v>
       </c>
       <c r="R73" s="6">
@@ -12767,7 +12833,7 @@
         <v>4519.01</v>
       </c>
       <c r="U73" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>-1.4394972991705002E-2</v>
       </c>
       <c r="V73" s="6">
@@ -12781,7 +12847,7 @@
         <v>4955.24</v>
       </c>
       <c r="Y73" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>8.0747653586202173E-2</v>
       </c>
       <c r="Z73" s="6">
@@ -12884,7 +12950,7 @@
         <v/>
       </c>
       <c r="Q74" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R74" s="6">
@@ -12898,7 +12964,7 @@
         <v/>
       </c>
       <c r="U74" s="46" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="V74" s="6">
@@ -12912,7 +12978,7 @@
         <v/>
       </c>
       <c r="Y74" s="46" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z74" s="6">
@@ -13017,7 +13083,7 @@
         <v>879.73</v>
       </c>
       <c r="Q75" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.86804049999999999</v>
       </c>
       <c r="R75" s="6">
@@ -13031,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>-1</v>
       </c>
       <c r="V75" s="6">
@@ -13045,7 +13111,7 @@
         <v>4483.63</v>
       </c>
       <c r="Y75" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-0.32745550000000001</v>
       </c>
       <c r="Z75" s="6">
@@ -13146,7 +13212,7 @@
         <v/>
       </c>
       <c r="Q76" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R76" s="6">
@@ -13160,7 +13226,7 @@
         <v/>
       </c>
       <c r="U76" s="46" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="V76" s="6">
@@ -13174,7 +13240,7 @@
         <v/>
       </c>
       <c r="Y76" s="46" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z76" s="6">
@@ -13286,7 +13352,7 @@
         <v>0</v>
       </c>
       <c r="Q77" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="R77" s="6">
@@ -13300,7 +13366,7 @@
         <v>75</v>
       </c>
       <c r="U77" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>-0.75474968117458552</v>
       </c>
       <c r="V77" s="6">
@@ -13314,7 +13380,7 @@
         <v>0</v>
       </c>
       <c r="Y77" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="Z77" s="6">
@@ -13417,7 +13483,7 @@
         <v>650.30000000000007</v>
       </c>
       <c r="Q78" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>6.8045251088355352E-2</v>
       </c>
       <c r="R78" s="6">
@@ -13431,7 +13497,7 @@
         <v>721.42000000000007</v>
       </c>
       <c r="U78" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0.18485192225151659</v>
       </c>
       <c r="V78" s="6">
@@ -13445,7 +13511,7 @@
         <v>596.62</v>
       </c>
       <c r="Y78" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-2.0118164379002823E-2</v>
       </c>
       <c r="Z78" s="6">
@@ -13548,7 +13614,7 @@
         <v>22949.23</v>
       </c>
       <c r="Q79" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>1.1070162666175141</v>
       </c>
       <c r="R79" s="6">
@@ -13562,7 +13628,7 @@
         <v>17763.09</v>
       </c>
       <c r="U79" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0.63086602798398461</v>
       </c>
       <c r="V79" s="6">
@@ -13573,11 +13639,11 @@
       </c>
       <c r="X79" s="6">
         <f>IFERROR(VLOOKUP($I79,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>178.31</v>
+        <v>20227.61</v>
       </c>
       <c r="Y79" s="46">
-        <f t="shared" si="20"/>
-        <v>-0.98362899014474259</v>
+        <f t="shared" si="26"/>
+        <v>0.85713870595201214</v>
       </c>
       <c r="Z79" s="6">
         <v>-10891.814345999999</v>
@@ -13679,7 +13745,7 @@
         <v>8774.5499999999993</v>
       </c>
       <c r="Q80" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.81262155898300659</v>
       </c>
       <c r="R80" s="6">
@@ -13693,7 +13759,7 @@
         <v>9673.7099999999991</v>
       </c>
       <c r="U80" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0.99836747198995979</v>
       </c>
       <c r="V80" s="6">
@@ -13704,11 +13770,11 @@
       </c>
       <c r="X80" s="6">
         <f>IFERROR(VLOOKUP($I80,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>9088.76</v>
       </c>
       <c r="Y80" s="46">
-        <f t="shared" si="20"/>
-        <v>-1</v>
+        <f t="shared" si="26"/>
+        <v>0.87753016626748859</v>
       </c>
       <c r="Z80" s="6">
         <v>-4840.8063760000005</v>
@@ -13819,7 +13885,7 @@
         <v/>
       </c>
       <c r="Q81" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R81" s="6">
@@ -13833,7 +13899,7 @@
         <v/>
       </c>
       <c r="U81" s="46" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="V81" s="6">
@@ -13847,7 +13913,7 @@
         <v/>
       </c>
       <c r="Y81" s="46" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z81" s="6">
@@ -13959,7 +14025,7 @@
         <v>2233.96</v>
       </c>
       <c r="Q82" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>7.0558786742213053E-2</v>
       </c>
       <c r="R82" s="6">
@@ -13973,7 +14039,7 @@
         <v>2457.64</v>
       </c>
       <c r="U82" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0.17775076395688938</v>
       </c>
       <c r="V82" s="6">
@@ -13987,7 +14053,7 @@
         <v>1143.7600000000002</v>
       </c>
       <c r="Y82" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-0.45188708932824495</v>
       </c>
       <c r="Z82" s="6">
@@ -14090,7 +14156,7 @@
         <v>2231.33</v>
       </c>
       <c r="Q83" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.61748628571428577</v>
       </c>
       <c r="R83" s="6">
@@ -14104,7 +14170,7 @@
         <v>4424.49</v>
       </c>
       <c r="U83" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>-0.24151599999999995</v>
       </c>
       <c r="V83" s="6">
@@ -14118,7 +14184,7 @@
         <v>1873.7600000000002</v>
       </c>
       <c r="Y83" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-0.67878399999999994</v>
       </c>
       <c r="Z83" s="6">
@@ -14221,7 +14287,7 @@
         <v>3330.86</v>
       </c>
       <c r="Q84" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.33234399999999997</v>
       </c>
       <c r="R84" s="6">
@@ -14235,7 +14301,7 @@
         <v>369.46000000000004</v>
       </c>
       <c r="U84" s="46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>-0.85221599999999997</v>
       </c>
       <c r="V84" s="6">
@@ -14249,7 +14315,7 @@
         <v>1065.51</v>
       </c>
       <c r="Y84" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>-0.57379599999999997</v>
       </c>
       <c r="Z84" s="6">
@@ -14478,7 +14544,7 @@
         <v>800</v>
       </c>
       <c r="Q86" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-5.8823529411764719E-2</v>
       </c>
       <c r="R86" s="6">
@@ -14492,7 +14558,7 @@
         <v>900</v>
       </c>
       <c r="U86" s="46">
-        <f t="shared" ref="U86:U100" si="21">IFERROR((T86*-1)/R86-1,"")</f>
+        <f t="shared" ref="U86:U100" si="27">IFERROR((T86*-1)/R86-1,"")</f>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="V86" s="6">
@@ -14506,7 +14572,7 @@
         <v>900</v>
       </c>
       <c r="Y86" s="46">
-        <f t="shared" ref="Y86:Y100" si="22">IFERROR((X86*-1)/V86-1,"")</f>
+        <f t="shared" ref="Y86:Y100" si="28">IFERROR((X86*-1)/V86-1,"")</f>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="Z86" s="6">
@@ -14618,7 +14684,7 @@
         <v>32.229999999999997</v>
       </c>
       <c r="Q87" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>4.0348612007746754E-2</v>
       </c>
       <c r="R87" s="6">
@@ -14632,7 +14698,7 @@
         <v>32.229999999999997</v>
       </c>
       <c r="U87" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>4.0348612007746754E-2</v>
       </c>
       <c r="V87" s="6">
@@ -14646,7 +14712,7 @@
         <v>32.229999999999997</v>
       </c>
       <c r="Y87" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>4.0348612007746754E-2</v>
       </c>
       <c r="Z87" s="6">
@@ -14758,7 +14824,7 @@
         <v>98.41</v>
       </c>
       <c r="Q88" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.64419886865408005</v>
       </c>
       <c r="R88" s="6">
@@ -14772,7 +14838,7 @@
         <v>91.95</v>
       </c>
       <c r="U88" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.53626751318710175</v>
       </c>
       <c r="V88" s="6">
@@ -14786,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="Y88" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="Z88" s="6">
@@ -14898,7 +14964,7 @@
         <v>1996.0500000000002</v>
       </c>
       <c r="Q89" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.11781734503261687</v>
       </c>
       <c r="R89" s="6">
@@ -14912,7 +14978,7 @@
         <v>2146.02</v>
       </c>
       <c r="U89" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-5.1535972940004782E-2</v>
       </c>
       <c r="V89" s="6">
@@ -14926,7 +14992,7 @@
         <v>2146.02</v>
       </c>
       <c r="Y89" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-5.1535972940004782E-2</v>
       </c>
       <c r="Z89" s="6">
@@ -15038,7 +15104,7 @@
         <v>111.89</v>
       </c>
       <c r="Q90" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.72757264769974317</v>
       </c>
       <c r="R90" s="6">
@@ -15052,7 +15118,7 @@
         <v>373.27</v>
       </c>
       <c r="U90" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-9.1170276225606695E-2</v>
       </c>
       <c r="V90" s="6">
@@ -15066,7 +15132,7 @@
         <v>382.17</v>
       </c>
       <c r="Y90" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-6.9500748694350079E-2</v>
       </c>
       <c r="Z90" s="6">
@@ -15178,7 +15244,7 @@
         <v>367.37</v>
       </c>
       <c r="Q91" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.45998370453123238</v>
       </c>
       <c r="R91" s="6">
@@ -15192,7 +15258,7 @@
         <v>577.9</v>
       </c>
       <c r="U91" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-0.15051469322100119</v>
       </c>
       <c r="V91" s="6">
@@ -15206,7 +15272,7 @@
         <v>427.23</v>
       </c>
       <c r="Y91" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-0.37199237304863864</v>
       </c>
       <c r="Z91" s="6">
@@ -15318,7 +15384,7 @@
         <v>15.99</v>
       </c>
       <c r="Q92" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.92880888070998191</v>
       </c>
       <c r="R92" s="6">
@@ -15332,7 +15398,7 @@
         <v>368.6</v>
       </c>
       <c r="U92" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.64109109257665242</v>
       </c>
       <c r="V92" s="6">
@@ -15346,7 +15412,7 @@
         <v>150.63</v>
       </c>
       <c r="Y92" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-0.32936095693211842</v>
       </c>
       <c r="Z92" s="6">
@@ -15449,7 +15515,7 @@
         <v>351</v>
       </c>
       <c r="Q93" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.36181818181818182</v>
       </c>
       <c r="R93" s="6">
@@ -15463,7 +15529,7 @@
         <v>617.44000000000005</v>
       </c>
       <c r="U93" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.12261818181818196</v>
       </c>
       <c r="V93" s="6">
@@ -15477,7 +15543,7 @@
         <v>351</v>
       </c>
       <c r="Y93" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-0.36181818181818182</v>
       </c>
       <c r="Z93" s="6">
@@ -15580,7 +15646,7 @@
         <v>432.21</v>
       </c>
       <c r="Q94" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>3.7304000000000004E-2</v>
       </c>
       <c r="R94" s="6">
@@ -15594,7 +15660,7 @@
         <v>511.6699999999999</v>
       </c>
       <c r="U94" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.22800799999999977</v>
       </c>
       <c r="V94" s="6">
@@ -15608,7 +15674,7 @@
         <v>350.68</v>
       </c>
       <c r="Y94" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-0.15836800000000006</v>
       </c>
       <c r="Z94" s="6">
@@ -15720,7 +15786,7 @@
         <v>11212.419999999998</v>
       </c>
       <c r="Q95" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-4.2445277011776139E-2</v>
       </c>
       <c r="R95" s="6">
@@ -15734,7 +15800,7 @@
         <v>11212.419999999998</v>
       </c>
       <c r="U95" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-4.2445277011776139E-2</v>
       </c>
       <c r="V95" s="6">
@@ -15748,7 +15814,7 @@
         <v>11212.419999999998</v>
       </c>
       <c r="Y95" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-4.2445277011776139E-2</v>
       </c>
       <c r="Z95" s="6">
@@ -15860,7 +15926,7 @@
         <v>511.23</v>
       </c>
       <c r="Q96" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.38270665797290437</v>
       </c>
       <c r="R96" s="6">
@@ -15874,7 +15940,7 @@
         <v>981.08999999999992</v>
       </c>
       <c r="U96" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.18463377526624636</v>
       </c>
       <c r="V96" s="6">
@@ -15888,7 +15954,7 @@
         <v>780.64</v>
       </c>
       <c r="Y96" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-5.7402980028496198E-2</v>
       </c>
       <c r="Z96" s="6">
@@ -15991,7 +16057,7 @@
         <v>370</v>
       </c>
       <c r="Q97" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R97" s="6">
@@ -16005,7 +16071,7 @@
         <v>370</v>
       </c>
       <c r="U97" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V97" s="6">
@@ -16019,7 +16085,7 @@
         <v>370</v>
       </c>
       <c r="Y97" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z97" s="6">
@@ -16131,7 +16197,7 @@
         <v/>
       </c>
       <c r="Q98" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R98" s="6">
@@ -16145,7 +16211,7 @@
         <v/>
       </c>
       <c r="U98" s="46" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V98" s="6">
@@ -16159,7 +16225,7 @@
         <v/>
       </c>
       <c r="Y98" s="46" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Z98" s="6">
@@ -16271,7 +16337,7 @@
         <v>295.60000000000002</v>
       </c>
       <c r="Q99" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.79836900503243802</v>
       </c>
       <c r="R99" s="6">
@@ -16285,7 +16351,7 @@
         <v>338.73</v>
       </c>
       <c r="U99" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-0.76894970593585155</v>
       </c>
       <c r="V99" s="6">
@@ -16299,7 +16365,7 @@
         <v>782.8</v>
       </c>
       <c r="Y99" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-0.46604620141878372</v>
       </c>
       <c r="Z99" s="6">
@@ -16402,7 +16468,7 @@
         <v>100</v>
       </c>
       <c r="Q100" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.76</v>
       </c>
       <c r="R100" s="6">
@@ -16416,7 +16482,7 @@
         <v>100</v>
       </c>
       <c r="U100" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-0.76</v>
       </c>
       <c r="V100" s="6">
@@ -16430,7 +16496,7 @@
         <v>100</v>
       </c>
       <c r="Y100" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-0.76</v>
       </c>
       <c r="Z100" s="6">
@@ -16552,11 +16618,11 @@
       </c>
       <c r="X101" s="8">
         <f>SUM(X102:X122)</f>
-        <v>322781.34999999998</v>
+        <v>386839.54</v>
       </c>
       <c r="Y101" s="45">
         <f>(X101*-1)/V101-1</f>
-        <v>-0.31374263764198906</v>
+        <v>-0.17755012061202957</v>
       </c>
       <c r="Z101" s="8">
         <v>-436216.95079197281</v>
@@ -16668,7 +16734,7 @@
         <v>1955</v>
       </c>
       <c r="Q102" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.47881584115479836</v>
       </c>
       <c r="R102" s="6">
@@ -16682,7 +16748,7 @@
         <v>2415</v>
       </c>
       <c r="U102" s="46">
-        <f t="shared" ref="U102:U122" si="23">IFERROR((T102*-1)/R102-1,"")</f>
+        <f t="shared" ref="U102:U122" si="29">IFERROR((T102*-1)/R102-1,"")</f>
         <v>-0.35618427436769207</v>
       </c>
       <c r="V102" s="6">
@@ -16696,7 +16762,7 @@
         <v>3042.48</v>
       </c>
       <c r="Y102" s="46">
-        <f t="shared" ref="Y102:Y122" si="24">IFERROR((X102*-1)/V102-1,"")</f>
+        <f t="shared" ref="Y102:Y122" si="30">IFERROR((X102*-1)/V102-1,"")</f>
         <v>-0.18890415365557589</v>
       </c>
       <c r="Z102" s="6">
@@ -16799,7 +16865,7 @@
         <v>41074.299999999996</v>
       </c>
       <c r="Q103" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-2.6897207494167796E-2</v>
       </c>
       <c r="R103" s="6">
@@ -16813,7 +16879,7 @@
         <v>47569.919999999998</v>
       </c>
       <c r="U103" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.17806731456713698</v>
       </c>
       <c r="V103" s="6">
@@ -16827,7 +16893,7 @@
         <v>70184.260000000009</v>
       </c>
       <c r="Y103" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-3.6078084753119133E-2</v>
       </c>
       <c r="Z103" s="6">
@@ -16939,7 +17005,7 @@
         <v>4450.1000000000004</v>
       </c>
       <c r="Q104" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.58587464102187092</v>
       </c>
       <c r="R104" s="6">
@@ -16953,7 +17019,7 @@
         <v>10141.98</v>
       </c>
       <c r="U104" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-5.6189499505852614E-2</v>
       </c>
       <c r="V104" s="6">
@@ -16967,7 +17033,7 @@
         <v>9958.6499999999978</v>
       </c>
       <c r="Y104" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-7.3250150291556571E-2</v>
       </c>
       <c r="Z104" s="6">
@@ -17070,7 +17136,7 @@
         <v>4296.6099999999997</v>
       </c>
       <c r="Q105" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.78516950000000008</v>
       </c>
       <c r="R105" s="6">
@@ -17084,7 +17150,7 @@
         <v>4296.6099999999997</v>
       </c>
       <c r="U105" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.78516950000000008</v>
       </c>
       <c r="V105" s="6">
@@ -17098,7 +17164,7 @@
         <v>4296.6099999999997</v>
       </c>
       <c r="Y105" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.78516950000000008</v>
       </c>
       <c r="Z105" s="6">
@@ -17210,7 +17276,7 @@
         <v>260.32</v>
       </c>
       <c r="Q106" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.61253750257813611</v>
       </c>
       <c r="R106" s="6">
@@ -17224,7 +17290,7 @@
         <v>260.32</v>
       </c>
       <c r="U106" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.61253750257813611</v>
       </c>
       <c r="V106" s="6">
@@ -17238,7 +17304,7 @@
         <v>1564.33</v>
       </c>
       <c r="Y106" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.3283620489856491</v>
       </c>
       <c r="Z106" s="6">
@@ -17350,7 +17416,7 @@
         <v>11187.73</v>
       </c>
       <c r="Q107" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.29685421048834881</v>
       </c>
       <c r="R107" s="6">
@@ -17364,7 +17430,7 @@
         <v>18270.349999999999</v>
       </c>
       <c r="U107" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.14828653135213266</v>
       </c>
       <c r="V107" s="6">
@@ -17378,7 +17444,7 @@
         <v>21717.43</v>
       </c>
       <c r="Y107" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.36493457238546334</v>
       </c>
       <c r="Z107" s="6">
@@ -17490,7 +17556,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="R108" s="6">
@@ -17504,7 +17570,7 @@
         <v>2334.16</v>
       </c>
       <c r="U108" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.45597704529455263</v>
       </c>
       <c r="V108" s="6">
@@ -17518,7 +17584,7 @@
         <v>709</v>
       </c>
       <c r="Y108" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.55774765863786635</v>
       </c>
       <c r="Z108" s="6">
@@ -17630,7 +17696,7 @@
         <v>9673.85</v>
       </c>
       <c r="Q109" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.49116690482243508</v>
       </c>
       <c r="R109" s="6">
@@ -17644,7 +17710,7 @@
         <v>18654.349999999999</v>
       </c>
       <c r="U109" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-1.8803201514846046E-2</v>
       </c>
       <c r="V109" s="6">
@@ -17658,7 +17724,7 @@
         <v>19808.55</v>
       </c>
       <c r="Y109" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>4.1906356567400938E-2</v>
       </c>
       <c r="Z109" s="6">
@@ -17761,7 +17827,7 @@
         <v/>
       </c>
       <c r="Q110" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R110" s="6">
@@ -17775,7 +17841,7 @@
         <v/>
       </c>
       <c r="U110" s="46" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="V110" s="6">
@@ -17789,7 +17855,7 @@
         <v/>
       </c>
       <c r="Y110" s="46" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Z110" s="6">
@@ -17901,7 +17967,7 @@
         <v>673.06999999999994</v>
       </c>
       <c r="Q111" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.37521156744011908</v>
       </c>
       <c r="R111" s="6">
@@ -17915,7 +17981,7 @@
         <v>1644.02</v>
       </c>
       <c r="U111" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.52608893413329283</v>
       </c>
       <c r="V111" s="6">
@@ -17929,7 +17995,7 @@
         <v>420.81</v>
       </c>
       <c r="Y111" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.60937611198608832</v>
       </c>
       <c r="Z111" s="6">
@@ -18032,7 +18098,7 @@
         <v>119279.42999999996</v>
       </c>
       <c r="Q112" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.98799049999999933</v>
       </c>
       <c r="R112" s="6">
@@ -18046,7 +18112,7 @@
         <v>38472.950000000004</v>
       </c>
       <c r="U112" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.35878416666666657</v>
       </c>
       <c r="V112" s="6">
@@ -18060,7 +18126,7 @@
         <v>41728.47</v>
       </c>
       <c r="Y112" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.3045255</v>
       </c>
       <c r="Z112" s="6">
@@ -18172,7 +18238,7 @@
         <v>1368</v>
       </c>
       <c r="Q113" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.43055994938310649</v>
       </c>
       <c r="R113" s="6">
@@ -18186,7 +18252,7 @@
         <v>0</v>
       </c>
       <c r="U113" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="V113" s="6">
@@ -18200,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="Y113" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-1</v>
       </c>
       <c r="Z113" s="6">
@@ -18303,7 +18369,7 @@
         <v>738.16</v>
       </c>
       <c r="Q114" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.85236800000000001</v>
       </c>
       <c r="R114" s="6">
@@ -18317,7 +18383,7 @@
         <v>1807.69</v>
       </c>
       <c r="U114" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.63846199999999997</v>
       </c>
       <c r="V114" s="6">
@@ -18328,11 +18394,11 @@
       </c>
       <c r="X114" s="6">
         <f>IFERROR(VLOOKUP($I114,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="Y114" s="46">
-        <f t="shared" si="24"/>
-        <v>-1</v>
+        <f t="shared" si="30"/>
+        <v>-0.5</v>
       </c>
       <c r="Z114" s="6">
         <v>-5000</v>
@@ -18443,7 +18509,7 @@
         <v>13677.889999999998</v>
       </c>
       <c r="Q115" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.20938523571989009</v>
       </c>
       <c r="R115" s="6">
@@ -18457,7 +18523,7 @@
         <v>10422.07</v>
       </c>
       <c r="U115" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.39757942077609876</v>
       </c>
       <c r="V115" s="6">
@@ -18471,7 +18537,7 @@
         <v>13862.09</v>
       </c>
       <c r="Y115" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.19873803504928966</v>
       </c>
       <c r="Z115" s="6">
@@ -18574,7 +18640,7 @@
         <v>7224.44</v>
       </c>
       <c r="Q116" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-2.7927711668984778E-2</v>
       </c>
       <c r="R116" s="6">
@@ -18588,7 +18654,7 @@
         <v>5041.3999999999996</v>
       </c>
       <c r="U116" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.50527846763235718</v>
       </c>
       <c r="V116" s="6">
@@ -18602,7 +18668,7 @@
         <v>10515.810000000001</v>
       </c>
       <c r="Y116" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.17974160169837938</v>
       </c>
       <c r="Z116" s="6">
@@ -18705,7 +18771,7 @@
         <v>117100.21999999996</v>
       </c>
       <c r="Q117" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.76172809604733427</v>
       </c>
       <c r="R117" s="6">
@@ -18719,7 +18785,7 @@
         <v>78726.199999999983</v>
       </c>
       <c r="U117" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.13619494584498903</v>
       </c>
       <c r="V117" s="6">
@@ -18733,7 +18799,7 @@
         <v>88339.049999999988</v>
       </c>
       <c r="Y117" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.22954465025216664</v>
       </c>
       <c r="Z117" s="6">
@@ -18845,7 +18911,7 @@
         <v/>
       </c>
       <c r="Q118" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="R118" s="6">
@@ -18859,7 +18925,7 @@
         <v/>
       </c>
       <c r="U118" s="46" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="V118" s="6">
@@ -18873,7 +18939,7 @@
         <v/>
       </c>
       <c r="Y118" s="46" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Z118" s="6">
@@ -18976,7 +19042,7 @@
         <v>35699.840000000004</v>
       </c>
       <c r="Q119" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-4.6055582277741092E-2</v>
       </c>
       <c r="R119" s="6">
@@ -18990,7 +19056,7 @@
         <v>45445.030000000006</v>
       </c>
       <c r="U119" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.11435744165914097</v>
       </c>
       <c r="V119" s="6">
@@ -19001,11 +19067,11 @@
       </c>
       <c r="X119" s="6">
         <f>IFERROR(VLOOKUP($I119,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <v>61558.19</v>
       </c>
       <c r="Y119" s="46">
-        <f t="shared" si="24"/>
-        <v>-1</v>
+        <f t="shared" si="30"/>
+        <v>-4.6421997506404411E-2</v>
       </c>
       <c r="Z119" s="6">
         <v>-56391.877710522778</v>
@@ -19116,7 +19182,7 @@
         <v>7122.33</v>
       </c>
       <c r="Q120" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-2.7549662484435133E-2</v>
       </c>
       <c r="R120" s="6">
@@ -19130,7 +19196,7 @@
         <v>4005.16</v>
       </c>
       <c r="U120" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.45315378621829661</v>
       </c>
       <c r="V120" s="6">
@@ -19144,7 +19210,7 @@
         <v>4874.22</v>
       </c>
       <c r="Y120" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>-0.33449631172311345</v>
       </c>
       <c r="Z120" s="6">
@@ -19256,7 +19322,7 @@
         <v>1965</v>
       </c>
       <c r="Q121" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.33373161950899632</v>
       </c>
       <c r="R121" s="6">
@@ -19270,7 +19336,7 @@
         <v>1965</v>
       </c>
       <c r="U121" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-0.51408032370538925</v>
       </c>
       <c r="V121" s="6">
@@ -19284,7 +19350,7 @@
         <v>7759.59</v>
       </c>
       <c r="Y121" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.52524287238846901</v>
       </c>
       <c r="Z121" s="6">
@@ -19396,7 +19462,7 @@
         <v>24000</v>
       </c>
       <c r="Q122" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R122" s="6">
@@ -19410,7 +19476,7 @@
         <v>24000</v>
       </c>
       <c r="U122" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V122" s="6">
@@ -19424,7 +19490,7 @@
         <v>24000</v>
       </c>
       <c r="Y122" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z122" s="6">
@@ -19654,7 +19720,7 @@
         <v>11823</v>
       </c>
       <c r="Q124" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-8.3034509716628624E-2</v>
       </c>
       <c r="R124" s="6">
@@ -19668,7 +19734,7 @@
         <v>11880</v>
       </c>
       <c r="U124" s="46">
-        <f t="shared" ref="U124:U130" si="25">IFERROR((T124*-1)/R124-1,"")</f>
+        <f t="shared" ref="U124:U130" si="31">IFERROR((T124*-1)/R124-1,"")</f>
         <v>-7.861371694439212E-2</v>
       </c>
       <c r="V124" s="6">
@@ -19682,7 +19748,7 @@
         <v>12244</v>
       </c>
       <c r="Y124" s="46">
-        <f t="shared" ref="Y124:Y130" si="26">IFERROR((X124*-1)/V124-1,"")</f>
+        <f t="shared" ref="Y124:Y130" si="32">IFERROR((X124*-1)/V124-1,"")</f>
         <v>-5.0382689416425652E-2</v>
       </c>
       <c r="Z124" s="6">
@@ -19786,7 +19852,7 @@
         <v>16033.429999999998</v>
       </c>
       <c r="Q125" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.22904742528484257</v>
       </c>
       <c r="R125" s="6">
@@ -19800,7 +19866,7 @@
         <v>14452.9</v>
       </c>
       <c r="U125" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>-0.30504574086139402</v>
       </c>
       <c r="V125" s="6">
@@ -19814,7 +19880,7 @@
         <v>20130.41</v>
       </c>
       <c r="Y125" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>-3.204795108895897E-2</v>
       </c>
       <c r="Z125" s="6">
@@ -19918,7 +19984,7 @@
         <v>6035.41</v>
       </c>
       <c r="Q126" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>1.3527434414105421E-2</v>
       </c>
       <c r="R126" s="6">
@@ -19932,7 +19998,7 @@
         <v>6035.41</v>
       </c>
       <c r="U126" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>1.3527434414105421E-2</v>
       </c>
       <c r="V126" s="6">
@@ -19946,7 +20012,7 @@
         <v>6035.41</v>
       </c>
       <c r="Y126" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.3527434414105421E-2</v>
       </c>
       <c r="Z126" s="6">
@@ -20050,7 +20116,7 @@
         <v>8966</v>
       </c>
       <c r="Q127" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.12568709922475041</v>
       </c>
       <c r="R127" s="6">
@@ -20064,7 +20130,7 @@
         <v>9436</v>
       </c>
       <c r="U127" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>-7.9855394633587484E-2</v>
       </c>
       <c r="V127" s="6">
@@ -20078,7 +20144,7 @@
         <v>9436</v>
       </c>
       <c r="Y127" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>-7.9855394633587484E-2</v>
       </c>
       <c r="Z127" s="6">
@@ -20182,7 +20248,7 @@
         <v>23441.37</v>
       </c>
       <c r="Q128" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.99189061116624089</v>
       </c>
       <c r="R128" s="6">
@@ -20196,7 +20262,7 @@
         <v>11505.72</v>
       </c>
       <c r="U128" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>-2.2320980270878366E-2</v>
       </c>
       <c r="V128" s="6">
@@ -20210,7 +20276,7 @@
         <v>10818.33</v>
       </c>
       <c r="Y128" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>-8.073077829930253E-2</v>
       </c>
       <c r="Z128" s="6">
@@ -20314,7 +20380,7 @@
         <v>1195</v>
       </c>
       <c r="Q129" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.10765623483202291</v>
       </c>
       <c r="R129" s="6">
@@ -20328,7 +20394,7 @@
         <v>1082</v>
       </c>
       <c r="U129" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>-0.19203685865125419</v>
       </c>
       <c r="V129" s="6">
@@ -20342,7 +20408,7 @@
         <v>978.5</v>
       </c>
       <c r="Y129" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>-0.26932353622019611</v>
       </c>
       <c r="Z129" s="6">
@@ -20446,7 +20512,7 @@
         <v>6685.8499999999995</v>
       </c>
       <c r="Q130" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>-0.14231778898471237</v>
       </c>
       <c r="R130" s="6">
@@ -20460,7 +20526,7 @@
         <v>9350</v>
       </c>
       <c r="U130" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.1994478896464833</v>
       </c>
       <c r="V130" s="6">
@@ -20474,7 +20540,7 @@
         <v>7769.93</v>
       </c>
       <c r="Y130" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>-3.248541048032072E-3</v>
       </c>
       <c r="Z130" s="6">
@@ -20603,11 +20669,11 @@
       </c>
       <c r="X132" s="48">
         <f>X64-X66</f>
-        <v>506206.04999999946</v>
+        <v>319121.74999999965</v>
       </c>
       <c r="Y132" s="14">
         <f>X132/V132-1</f>
-        <v>0.56816700791058006</v>
+        <v>-1.1398224385725686E-2</v>
       </c>
       <c r="Z132" s="7">
         <v>166896.54889072594</v>
@@ -20709,7 +20775,7 @@
         <v>46089.81</v>
       </c>
       <c r="Q134" s="14">
-        <f t="shared" ref="Q134" si="27">IFERROR((P134*-1)/N134-1,"")</f>
+        <f t="shared" ref="Q134" si="33">IFERROR((P134*-1)/N134-1,"")</f>
         <v>-0.3443740875346758</v>
       </c>
       <c r="R134" s="7">
@@ -20723,7 +20789,7 @@
         <v>50627.689999999988</v>
       </c>
       <c r="U134" s="14">
-        <f t="shared" ref="U134" si="28">IFERROR((T134*-1)/R134-1,"")</f>
+        <f t="shared" ref="U134" si="34">IFERROR((T134*-1)/R134-1,"")</f>
         <v>-0.27982290549122324</v>
       </c>
       <c r="V134" s="7">
@@ -20737,7 +20803,7 @@
         <v>52086.069999999992</v>
       </c>
       <c r="Y134" s="14">
-        <f t="shared" ref="Y134" si="29">IFERROR((X134*-1)/V134-1,"")</f>
+        <f t="shared" ref="Y134" si="35">IFERROR((X134*-1)/V134-1,"")</f>
         <v>-0.25907750171930088</v>
       </c>
       <c r="Z134" s="7">
@@ -22630,7 +22696,7 @@
         <v>-290070.51999999938</v>
       </c>
       <c r="Q151" s="14">
-        <f t="shared" ref="Q151" si="30">IFERROR((P151*-1)/N151-1,"")</f>
+        <f t="shared" ref="Q151" si="36">IFERROR((P151*-1)/N151-1,"")</f>
         <v>-2.0918188286927273</v>
       </c>
       <c r="R151" s="7">
@@ -22655,11 +22721,11 @@
       </c>
       <c r="X151" s="48">
         <f>X132-X134</f>
-        <v>454119.97999999946</v>
+        <v>267035.67999999964</v>
       </c>
       <c r="Y151" s="14">
-        <f t="shared" ref="Y151" si="31">IFERROR((X151*-1)/V151-1,"")</f>
-        <v>-2.7984795538138778</v>
+        <f t="shared" ref="Y151" si="37">IFERROR((X151*-1)/V151-1,"")</f>
+        <v>-2.0575579841670599</v>
       </c>
       <c r="Z151" s="7">
         <v>96597.603831202126</v>
@@ -23120,11 +23186,11 @@
       </c>
       <c r="X157" s="48">
         <f>X151-X153</f>
-        <v>454119.97999999946</v>
+        <v>267035.67999999964</v>
       </c>
       <c r="Y157" s="50">
         <f>X157/V157-1</f>
-        <v>0.79847955381387803</v>
+        <v>5.7557984167059706E-2</v>
       </c>
       <c r="Z157" s="7">
         <v>96597.603831202126</v>
@@ -23188,6 +23254,629 @@
         <v>4.0263006817170405E-2</v>
       </c>
       <c r="AU157" s="7">
+        <v>100657.51704292603</v>
+      </c>
+    </row>
+    <row r="159" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="I159" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="J159" s="7">
+        <v>0</v>
+      </c>
+      <c r="K159" s="41">
+        <v>0</v>
+      </c>
+      <c r="L159" s="7">
+        <v>0</v>
+      </c>
+      <c r="M159" s="14">
+        <v>0</v>
+      </c>
+      <c r="N159" s="7">
+        <f>SUM(N160:N164)</f>
+        <v>-49588</v>
+      </c>
+      <c r="O159" s="14">
+        <f>N159/N10</f>
+        <v>-3.0544884590711457E-2</v>
+      </c>
+      <c r="P159" s="48">
+        <f>SUM(P160:P164)</f>
+        <v>53166.43</v>
+      </c>
+      <c r="Q159" s="14"/>
+      <c r="R159" s="7">
+        <f>SUM(R160:R164)</f>
+        <v>-49588</v>
+      </c>
+      <c r="S159" s="14">
+        <f>R159/R10</f>
+        <v>-2.2276849490946486E-2</v>
+      </c>
+      <c r="T159" s="48">
+        <f>SUM(T160:T164)</f>
+        <v>26446.83</v>
+      </c>
+      <c r="U159" s="14"/>
+      <c r="V159" s="7">
+        <f>SUM(V160:V164)</f>
+        <v>-49588</v>
+      </c>
+      <c r="W159" s="14">
+        <f>V159/V10</f>
+        <v>-1.7707288760540046E-2</v>
+      </c>
+      <c r="X159" s="48">
+        <f>SUM(X160:X164)</f>
+        <v>26833.7</v>
+      </c>
+      <c r="Y159" s="14"/>
+      <c r="Z159" s="7">
+        <f>SUM(Z160:Z164)</f>
+        <v>-40588</v>
+      </c>
+      <c r="AA159" s="14">
+        <f>Z159/Z10</f>
+        <v>-1.6591520603700831E-2</v>
+      </c>
+      <c r="AB159" s="7">
+        <f>SUM(AB160:AB164)</f>
+        <v>-40588</v>
+      </c>
+      <c r="AC159" s="14">
+        <f>AB159/AB10</f>
+        <v>-1.5836962823106898E-2</v>
+      </c>
+      <c r="AD159" s="7">
+        <f>SUM(AD160:AD164)</f>
+        <v>-40588</v>
+      </c>
+      <c r="AE159" s="14">
+        <f>AD159/AD10</f>
+        <v>-1.8301914658308122E-2</v>
+      </c>
+      <c r="AF159" s="7">
+        <f>SUM(AF160:AF164)</f>
+        <v>-39509</v>
+      </c>
+      <c r="AG159" s="14">
+        <f>AF159/AF10</f>
+        <v>-1.7589501093920212E-2</v>
+      </c>
+      <c r="AH159" s="7">
+        <f>SUM(AH160:AH164)</f>
+        <v>-39509</v>
+      </c>
+      <c r="AI159" s="14">
+        <f>AH159/AH10</f>
+        <v>-1.4681435746880482E-2</v>
+      </c>
+      <c r="AJ159" s="7">
+        <f>SUM(AJ160:AJ164)</f>
+        <v>-39509</v>
+      </c>
+      <c r="AK159" s="14">
+        <f>AJ159/AJ10</f>
+        <v>-1.3260688717751866E-2</v>
+      </c>
+      <c r="AL159" s="7">
+        <f>SUM(AL160:AL164)</f>
+        <v>-39509</v>
+      </c>
+      <c r="AM159" s="14">
+        <f>AL159/AL10</f>
+        <v>-1.311909473119041E-2</v>
+      </c>
+      <c r="AN159" s="7">
+        <f>SUM(AN160:AN164)</f>
+        <v>-39509</v>
+      </c>
+      <c r="AO159" s="14">
+        <f>AN159/AN10</f>
+        <v>-1.4426864003362933E-2</v>
+      </c>
+      <c r="AP159" s="7">
+        <f>SUM(AP160:AP164)</f>
+        <v>-39509</v>
+      </c>
+      <c r="AQ159" s="14">
+        <f>AP159/AP10</f>
+        <v>-1.6083642686052581E-2</v>
+      </c>
+      <c r="AR159" s="16"/>
+      <c r="AS159" s="7">
+        <f t="shared" ref="AS159:AS164" si="38">N159+R159+V159+Z159+AB159+AD159+AF159+AH159+AJ159+AL159+AN159+AP159</f>
+        <v>-507582</v>
+      </c>
+      <c r="AT159" s="14">
+        <v>0</v>
+      </c>
+      <c r="AU159" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="I160" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J160" s="6">
+        <v>0</v>
+      </c>
+      <c r="K160" s="37">
+        <v>0</v>
+      </c>
+      <c r="L160" s="6">
+        <v>0</v>
+      </c>
+      <c r="M160" s="15">
+        <v>0</v>
+      </c>
+      <c r="N160" s="6">
+        <v>-2167</v>
+      </c>
+      <c r="O160" s="15">
+        <v>0</v>
+      </c>
+      <c r="P160" s="6">
+        <f>IFERROR(VLOOKUP($I160,[1]RESUMO!$A$5:$M$150,2,FALSE),"")</f>
+        <v>9551.4999999999982</v>
+      </c>
+      <c r="R160" s="6">
+        <v>-2167</v>
+      </c>
+      <c r="S160" s="15">
+        <v>0</v>
+      </c>
+      <c r="T160" s="6">
+        <f>IFERROR(VLOOKUP($I160,[1]RESUMO!$A$5:$M$150,3,FALSE),"")</f>
+        <v>4960.7299999999996</v>
+      </c>
+      <c r="V160" s="6">
+        <v>-2167</v>
+      </c>
+      <c r="W160" s="15">
+        <v>0</v>
+      </c>
+      <c r="X160" s="6">
+        <f>IFERROR(VLOOKUP($I160,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <v>2407.11</v>
+      </c>
+      <c r="Z160" s="6">
+        <v>-2167</v>
+      </c>
+      <c r="AA160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB160" s="6">
+        <v>-2167</v>
+      </c>
+      <c r="AC160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD160" s="6">
+        <v>-2167</v>
+      </c>
+      <c r="AE160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF160" s="6">
+        <v>-1088</v>
+      </c>
+      <c r="AG160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AH160" s="6">
+        <v>-1088</v>
+      </c>
+      <c r="AI160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AJ160" s="6">
+        <v>-1088</v>
+      </c>
+      <c r="AK160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AL160" s="6">
+        <v>-1088</v>
+      </c>
+      <c r="AM160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN160" s="6">
+        <v>-1088</v>
+      </c>
+      <c r="AO160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP160" s="6">
+        <v>-1088</v>
+      </c>
+      <c r="AQ160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AR160" s="6"/>
+      <c r="AS160" s="6">
+        <f t="shared" si="38"/>
+        <v>-19530</v>
+      </c>
+      <c r="AT160" s="15">
+        <v>0</v>
+      </c>
+      <c r="AU160" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="9:47" x14ac:dyDescent="0.25">
+      <c r="I161" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J161" s="6">
+        <v>0</v>
+      </c>
+      <c r="K161" s="37">
+        <v>0</v>
+      </c>
+      <c r="L161" s="6">
+        <v>0</v>
+      </c>
+      <c r="M161" s="15">
+        <v>0</v>
+      </c>
+      <c r="N161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="O161" s="15">
+        <v>0</v>
+      </c>
+      <c r="P161" s="6">
+        <f>IFERROR(VLOOKUP($I161,[1]RESUMO!$A$5:$M$150,2,FALSE),"")</f>
+        <v>3037.44</v>
+      </c>
+      <c r="R161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="S161" s="15">
+        <v>0</v>
+      </c>
+      <c r="T161" s="6">
+        <f>IFERROR(VLOOKUP($I161,[1]RESUMO!$A$5:$M$150,3,FALSE),"")</f>
+        <v>3037.44</v>
+      </c>
+      <c r="V161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="W161" s="15">
+        <v>0</v>
+      </c>
+      <c r="X161" s="6">
+        <f>IFERROR(VLOOKUP($I161,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <v>3037.44</v>
+      </c>
+      <c r="Z161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AA161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AC161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AE161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AG161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AH161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AI161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AJ161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AK161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AL161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AM161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AO161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AP161" s="6">
+        <v>-1508</v>
+      </c>
+      <c r="AQ161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AR161" s="6"/>
+      <c r="AS161" s="6">
+        <f t="shared" si="38"/>
+        <v>-18096</v>
+      </c>
+      <c r="AT161" s="15">
+        <v>0</v>
+      </c>
+      <c r="AU161" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="9:47" x14ac:dyDescent="0.25">
+      <c r="I162" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="N162" s="6">
+        <v>-9000</v>
+      </c>
+      <c r="O162" s="15">
+        <v>0</v>
+      </c>
+      <c r="P162" s="6">
+        <f>IFERROR(VLOOKUP($I162,[1]RESUMO!$A$5:$M$150,2,FALSE),"")</f>
+        <v>14634.46</v>
+      </c>
+      <c r="R162" s="6">
+        <v>-9000</v>
+      </c>
+      <c r="T162" s="6">
+        <f>IFERROR(VLOOKUP($I162,[1]RESUMO!$A$5:$M$150,3,FALSE),"")</f>
+        <v>5089.95</v>
+      </c>
+      <c r="V162" s="6">
+        <v>-9000</v>
+      </c>
+      <c r="X162" s="6">
+        <f>IFERROR(VLOOKUP($I162,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <v>2570</v>
+      </c>
+      <c r="Y162" s="6"/>
+      <c r="AS162" s="6">
+        <f t="shared" si="38"/>
+        <v>-27000</v>
+      </c>
+    </row>
+    <row r="163" spans="9:47" x14ac:dyDescent="0.25">
+      <c r="I163" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="N163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="O163" s="15">
+        <v>0</v>
+      </c>
+      <c r="P163" s="6">
+        <f>IFERROR(VLOOKUP($I163,[1]RESUMO!$A$5:$M$150,2,FALSE),"")</f>
+        <v>25943.030000000002</v>
+      </c>
+      <c r="R163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="T163" s="6">
+        <f>IFERROR(VLOOKUP($I163,[1]RESUMO!$A$5:$M$150,3,FALSE),"")</f>
+        <v>13358.710000000001</v>
+      </c>
+      <c r="V163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="X163" s="6">
+        <f>IFERROR(VLOOKUP($I163,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <v>14734.15</v>
+      </c>
+      <c r="Z163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AB163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AD163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AF163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AH163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AJ163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AL163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AN163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AP163" s="6">
+        <v>-36540</v>
+      </c>
+      <c r="AS163" s="6">
+        <f t="shared" si="38"/>
+        <v>-438480</v>
+      </c>
+    </row>
+    <row r="164" spans="9:47" x14ac:dyDescent="0.25">
+      <c r="I164" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="N164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="O164" s="15">
+        <v>0</v>
+      </c>
+      <c r="P164" s="6">
+        <f>IFERROR(VLOOKUP($I164,[1]RESUMO!$A$5:$M$150,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="T164" s="6">
+        <f>IFERROR(VLOOKUP($I164,[1]RESUMO!$A$5:$M$150,3,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="V164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="X164" s="6">
+        <f>IFERROR(VLOOKUP($I164,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <v>4085</v>
+      </c>
+      <c r="Z164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AB164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AD164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AF164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AH164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AJ164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AL164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AN164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AP164" s="6">
+        <v>-373</v>
+      </c>
+      <c r="AS164" s="6">
+        <f t="shared" si="38"/>
+        <v>-4476</v>
+      </c>
+    </row>
+    <row r="166" spans="9:47" x14ac:dyDescent="0.25">
+      <c r="I166" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="J166" s="7">
+        <v>120235.26388602481</v>
+      </c>
+      <c r="K166" s="41">
+        <v>4.8094105554409926E-2</v>
+      </c>
+      <c r="L166" s="7">
+        <v>-99894.989458602286</v>
+      </c>
+      <c r="M166" s="14">
+        <v>-4.9947494729301142E-2</v>
+      </c>
+      <c r="N166" s="7">
+        <f>N157+N159</f>
+        <v>-315264.42211053544</v>
+      </c>
+      <c r="O166" s="14">
+        <f>N166/N10</f>
+        <v>-0.19419447021302827</v>
+      </c>
+      <c r="P166" s="7">
+        <f>P157+P159</f>
+        <v>-236904.08999999939</v>
+      </c>
+      <c r="Q166" s="14"/>
+      <c r="R166" s="7">
+        <f>R157+R159</f>
+        <v>-49989.39105013806</v>
+      </c>
+      <c r="S166" s="14"/>
+      <c r="T166" s="7">
+        <f>T157+T159</f>
+        <v>58442.510000000009</v>
+      </c>
+      <c r="U166" s="50"/>
+      <c r="V166" s="7">
+        <f>V157+V159</f>
+        <v>202914.16441826487</v>
+      </c>
+      <c r="W166" s="14"/>
+      <c r="X166" s="7">
+        <f>X157+X159</f>
+        <v>293869.37999999966</v>
+      </c>
+      <c r="Y166" s="50"/>
+      <c r="Z166" s="7">
+        <f>Z157+Z159</f>
+        <v>56009.603831202126</v>
+      </c>
+      <c r="AA166" s="14"/>
+      <c r="AB166" s="7">
+        <f>AB157+AB159</f>
+        <v>77957.683600538978</v>
+      </c>
+      <c r="AC166" s="14"/>
+      <c r="AD166" s="7">
+        <f>AD157+AD159</f>
+        <v>-74008.653377912837</v>
+      </c>
+      <c r="AE166" s="14"/>
+      <c r="AF166" s="7">
+        <f>AF157+AF159</f>
+        <v>-60391.92288240233</v>
+      </c>
+      <c r="AG166" s="14"/>
+      <c r="AH166" s="7">
+        <f>AH157+AH159</f>
+        <v>135487.07692978822</v>
+      </c>
+      <c r="AI166" s="14"/>
+      <c r="AJ166" s="7">
+        <f>AJ157+AJ159</f>
+        <v>262423.98451222153</v>
+      </c>
+      <c r="AK166" s="14"/>
+      <c r="AL166" s="7">
+        <f>AL157+AL159</f>
+        <v>276581.29078392463</v>
+      </c>
+      <c r="AM166" s="14"/>
+      <c r="AN166" s="7">
+        <f>AN157+AN159</f>
+        <v>156393.29599993315</v>
+      </c>
+      <c r="AO166" s="14"/>
+      <c r="AP166" s="7">
+        <f>AP157+AP159</f>
+        <v>32195.493860227623</v>
+      </c>
+      <c r="AQ166" s="14"/>
+      <c r="AR166" s="7"/>
+      <c r="AS166" s="7">
+        <f>N166+R166+V166+Z166+AB166+AD166+AF166+AH166+AJ166+AL166+AN166+AP166</f>
+        <v>700308.20451511245</v>
+      </c>
+      <c r="AT166" s="14">
+        <v>4.0263006817170405E-2</v>
+      </c>
+      <c r="AU166" s="7">
         <v>100657.51704292603</v>
       </c>
     </row>
@@ -23213,7 +23902,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y1:Y1048576">
+  <conditionalFormatting sqref="Y1:Y161 Y163:Y1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/orcamento.xlsx
+++ b/orcamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e87dc3a59766ad95/Documentos/Karams Estofados/Relatórios/Financeiro/Orçamento 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="890" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D92305-79FD-41D6-BA26-A50BC11A0F3D}"/>
+  <xr:revisionPtr revIDLastSave="912" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5134468F-250C-42FC-B3A1-D3BF6784E194}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Acompanhamento Orçamento" sheetId="21" r:id="rId1"/>
@@ -1069,23 +1069,40 @@
           <cell r="D5">
             <v>169337.99</v>
           </cell>
+          <cell r="E5"/>
           <cell r="F5">
             <v>420937.66000000003</v>
           </cell>
+          <cell r="G5"/>
+          <cell r="H5"/>
+          <cell r="I5"/>
+          <cell r="J5"/>
+          <cell r="K5"/>
+          <cell r="L5"/>
+          <cell r="M5"/>
         </row>
         <row r="6">
           <cell r="A6" t="str">
             <v>COFINS</v>
           </cell>
+          <cell r="B6"/>
           <cell r="C6">
             <v>2460.61</v>
           </cell>
           <cell r="D6">
             <v>15906.25</v>
           </cell>
+          <cell r="E6"/>
           <cell r="F6">
             <v>18366.86</v>
           </cell>
+          <cell r="G6"/>
+          <cell r="H6"/>
+          <cell r="I6"/>
+          <cell r="J6"/>
+          <cell r="K6"/>
+          <cell r="L6"/>
+          <cell r="M6"/>
         </row>
         <row r="7">
           <cell r="A7" t="str">
@@ -1100,9 +1117,17 @@
           <cell r="D7">
             <v>39057.060000000005</v>
           </cell>
+          <cell r="E7"/>
           <cell r="F7">
             <v>118711.39000000001</v>
           </cell>
+          <cell r="G7"/>
+          <cell r="H7"/>
+          <cell r="I7"/>
+          <cell r="J7"/>
+          <cell r="K7"/>
+          <cell r="L7"/>
+          <cell r="M7"/>
         </row>
         <row r="8">
           <cell r="A8" t="str">
@@ -1117,9 +1142,17 @@
           <cell r="D8">
             <v>5659.96</v>
           </cell>
+          <cell r="E8"/>
           <cell r="F8">
             <v>16979.88</v>
           </cell>
+          <cell r="G8"/>
+          <cell r="H8"/>
+          <cell r="I8"/>
+          <cell r="J8"/>
+          <cell r="K8"/>
+          <cell r="L8"/>
+          <cell r="M8"/>
         </row>
         <row r="9">
           <cell r="A9" t="str">
@@ -1134,9 +1167,17 @@
           <cell r="D9">
             <v>22197.7</v>
           </cell>
+          <cell r="E9"/>
           <cell r="F9">
             <v>52833.82</v>
           </cell>
+          <cell r="G9"/>
+          <cell r="H9"/>
+          <cell r="I9"/>
+          <cell r="J9"/>
+          <cell r="K9"/>
+          <cell r="L9"/>
+          <cell r="M9"/>
         </row>
         <row r="10">
           <cell r="A10" t="str">
@@ -1151,23 +1192,40 @@
           <cell r="D10">
             <v>1921.23</v>
           </cell>
+          <cell r="E10"/>
           <cell r="F10">
             <v>4854.9400000000005</v>
           </cell>
+          <cell r="G10"/>
+          <cell r="H10"/>
+          <cell r="I10"/>
+          <cell r="J10"/>
+          <cell r="K10"/>
+          <cell r="L10"/>
+          <cell r="M10"/>
         </row>
         <row r="11">
           <cell r="A11" t="str">
             <v>PIS</v>
           </cell>
+          <cell r="B11"/>
           <cell r="C11">
             <v>496.96</v>
           </cell>
           <cell r="D11">
             <v>3431.3</v>
           </cell>
+          <cell r="E11"/>
           <cell r="F11">
             <v>3928.26</v>
           </cell>
+          <cell r="G11"/>
+          <cell r="H11"/>
+          <cell r="I11"/>
+          <cell r="J11"/>
+          <cell r="K11"/>
+          <cell r="L11"/>
+          <cell r="M11"/>
         </row>
         <row r="12">
           <cell r="A12" t="str">
@@ -1182,9 +1240,17 @@
           <cell r="D12">
             <v>81164.490000000005</v>
           </cell>
+          <cell r="E12"/>
           <cell r="F12">
             <v>205262.51</v>
           </cell>
+          <cell r="G12"/>
+          <cell r="H12"/>
+          <cell r="I12"/>
+          <cell r="J12"/>
+          <cell r="K12"/>
+          <cell r="L12"/>
+          <cell r="M12"/>
         </row>
         <row r="13">
           <cell r="A13" t="str">
@@ -1205,6 +1271,13 @@
           <cell r="F13">
             <v>63618.049999999988</v>
           </cell>
+          <cell r="G13"/>
+          <cell r="H13"/>
+          <cell r="I13"/>
+          <cell r="J13"/>
+          <cell r="K13"/>
+          <cell r="L13"/>
+          <cell r="M13"/>
         </row>
         <row r="14">
           <cell r="A14" t="str">
@@ -1219,9 +1292,17 @@
           <cell r="D14">
             <v>1534.3</v>
           </cell>
+          <cell r="E14"/>
           <cell r="F14">
             <v>3085.9799999999996</v>
           </cell>
+          <cell r="G14"/>
+          <cell r="H14"/>
+          <cell r="I14"/>
+          <cell r="J14"/>
+          <cell r="K14"/>
+          <cell r="L14"/>
+          <cell r="M14"/>
         </row>
         <row r="15">
           <cell r="A15" t="str">
@@ -1236,9 +1317,17 @@
           <cell r="D15">
             <v>12217.75</v>
           </cell>
+          <cell r="E15"/>
           <cell r="F15">
             <v>14735.43</v>
           </cell>
+          <cell r="G15"/>
+          <cell r="H15"/>
+          <cell r="I15"/>
+          <cell r="J15"/>
+          <cell r="K15"/>
+          <cell r="L15"/>
+          <cell r="M15"/>
         </row>
         <row r="16">
           <cell r="A16" t="str">
@@ -1259,6 +1348,13 @@
           <cell r="F16">
             <v>45796.639999999992</v>
           </cell>
+          <cell r="G16"/>
+          <cell r="H16"/>
+          <cell r="I16"/>
+          <cell r="J16"/>
+          <cell r="K16"/>
+          <cell r="L16"/>
+          <cell r="M16"/>
         </row>
         <row r="17">
           <cell r="A17" t="str">
@@ -1279,6 +1375,13 @@
           <cell r="F17">
             <v>1021223.9</v>
           </cell>
+          <cell r="G17"/>
+          <cell r="H17"/>
+          <cell r="I17"/>
+          <cell r="J17"/>
+          <cell r="K17"/>
+          <cell r="L17"/>
+          <cell r="M17"/>
         </row>
         <row r="18">
           <cell r="A18" t="str">
@@ -1299,6 +1402,13 @@
           <cell r="F18">
             <v>2147.9</v>
           </cell>
+          <cell r="G18"/>
+          <cell r="H18"/>
+          <cell r="I18"/>
+          <cell r="J18"/>
+          <cell r="K18"/>
+          <cell r="L18"/>
+          <cell r="M18"/>
         </row>
         <row r="19">
           <cell r="A19" t="str">
@@ -1313,9 +1423,17 @@
           <cell r="D19">
             <v>8155.15</v>
           </cell>
+          <cell r="E19"/>
           <cell r="F19">
             <v>19604.21</v>
           </cell>
+          <cell r="G19"/>
+          <cell r="H19"/>
+          <cell r="I19"/>
+          <cell r="J19"/>
+          <cell r="K19"/>
+          <cell r="L19"/>
+          <cell r="M19"/>
         </row>
         <row r="20">
           <cell r="A20" t="str">
@@ -1327,12 +1445,20 @@
           <cell r="C20">
             <v>1694.1599999999999</v>
           </cell>
+          <cell r="D20"/>
           <cell r="E20">
             <v>1307.92</v>
           </cell>
           <cell r="F20">
             <v>4901.28</v>
           </cell>
+          <cell r="G20"/>
+          <cell r="H20"/>
+          <cell r="I20"/>
+          <cell r="J20"/>
+          <cell r="K20"/>
+          <cell r="L20"/>
+          <cell r="M20"/>
         </row>
         <row r="21">
           <cell r="A21" t="str">
@@ -1353,6 +1479,13 @@
           <cell r="F21">
             <v>29649.43</v>
           </cell>
+          <cell r="G21"/>
+          <cell r="H21"/>
+          <cell r="I21"/>
+          <cell r="J21"/>
+          <cell r="K21"/>
+          <cell r="L21"/>
+          <cell r="M21"/>
         </row>
         <row r="22">
           <cell r="A22" t="str">
@@ -1367,9 +1500,17 @@
           <cell r="D22">
             <v>35869.64</v>
           </cell>
+          <cell r="E22"/>
           <cell r="F22">
             <v>103038.12</v>
           </cell>
+          <cell r="G22"/>
+          <cell r="H22"/>
+          <cell r="I22"/>
+          <cell r="J22"/>
+          <cell r="K22"/>
+          <cell r="L22"/>
+          <cell r="M22"/>
         </row>
         <row r="23">
           <cell r="A23" t="str">
@@ -1390,6 +1531,13 @@
           <cell r="F23">
             <v>26620</v>
           </cell>
+          <cell r="G23"/>
+          <cell r="H23"/>
+          <cell r="I23"/>
+          <cell r="J23"/>
+          <cell r="K23"/>
+          <cell r="L23"/>
+          <cell r="M23"/>
         </row>
         <row r="24">
           <cell r="A24" t="str">
@@ -1404,9 +1552,17 @@
           <cell r="D24">
             <v>44918.66</v>
           </cell>
+          <cell r="E24"/>
           <cell r="F24">
             <v>132088.18</v>
           </cell>
+          <cell r="G24"/>
+          <cell r="H24"/>
+          <cell r="I24"/>
+          <cell r="J24"/>
+          <cell r="K24"/>
+          <cell r="L24"/>
+          <cell r="M24"/>
         </row>
         <row r="25">
           <cell r="A25" t="str">
@@ -1427,20 +1583,36 @@
           <cell r="F25">
             <v>49320.149999999994</v>
           </cell>
+          <cell r="G25"/>
+          <cell r="H25"/>
+          <cell r="I25"/>
+          <cell r="J25"/>
+          <cell r="K25"/>
+          <cell r="L25"/>
+          <cell r="M25"/>
         </row>
         <row r="26">
           <cell r="A26" t="str">
             <v>Rescisões MOD</v>
           </cell>
+          <cell r="B26"/>
           <cell r="C26">
             <v>30936.210000000003</v>
           </cell>
           <cell r="D26">
             <v>394.44</v>
           </cell>
+          <cell r="E26"/>
           <cell r="F26">
             <v>31330.65</v>
           </cell>
+          <cell r="G26"/>
+          <cell r="H26"/>
+          <cell r="I26"/>
+          <cell r="J26"/>
+          <cell r="K26"/>
+          <cell r="L26"/>
+          <cell r="M26"/>
         </row>
         <row r="27">
           <cell r="A27" t="str">
@@ -1461,6 +1633,13 @@
           <cell r="F27">
             <v>616676.28</v>
           </cell>
+          <cell r="G27"/>
+          <cell r="H27"/>
+          <cell r="I27"/>
+          <cell r="J27"/>
+          <cell r="K27"/>
+          <cell r="L27"/>
+          <cell r="M27"/>
         </row>
         <row r="28">
           <cell r="A28" t="str">
@@ -1475,9 +1654,17 @@
           <cell r="D28">
             <v>1980.53</v>
           </cell>
+          <cell r="E28"/>
           <cell r="F28">
             <v>5847.7</v>
           </cell>
+          <cell r="G28"/>
+          <cell r="H28"/>
+          <cell r="I28"/>
+          <cell r="J28"/>
+          <cell r="K28"/>
+          <cell r="L28"/>
+          <cell r="M28"/>
         </row>
         <row r="29">
           <cell r="A29" t="str">
@@ -1498,17 +1685,34 @@
           <cell r="F29">
             <v>279047.74999999994</v>
           </cell>
+          <cell r="G29"/>
+          <cell r="H29"/>
+          <cell r="I29"/>
+          <cell r="J29"/>
+          <cell r="K29"/>
+          <cell r="L29"/>
+          <cell r="M29"/>
         </row>
         <row r="30">
           <cell r="A30" t="str">
             <v>Assistência Médica CIF</v>
           </cell>
+          <cell r="B30"/>
+          <cell r="C30"/>
+          <cell r="D30"/>
           <cell r="E30">
             <v>225</v>
           </cell>
           <cell r="F30">
             <v>225</v>
           </cell>
+          <cell r="G30"/>
+          <cell r="H30"/>
+          <cell r="I30"/>
+          <cell r="J30"/>
+          <cell r="K30"/>
+          <cell r="L30"/>
+          <cell r="M30"/>
         </row>
         <row r="31">
           <cell r="A31" t="str">
@@ -1523,14 +1727,24 @@
           <cell r="D31">
             <v>705.03</v>
           </cell>
+          <cell r="E31"/>
           <cell r="F31">
             <v>5027.6699999999992</v>
           </cell>
+          <cell r="G31"/>
+          <cell r="H31"/>
+          <cell r="I31"/>
+          <cell r="J31"/>
+          <cell r="K31"/>
+          <cell r="L31"/>
+          <cell r="M31"/>
         </row>
         <row r="32">
           <cell r="A32" t="str">
             <v>Férias CIF</v>
           </cell>
+          <cell r="B32"/>
+          <cell r="C32"/>
           <cell r="D32">
             <v>1458.08</v>
           </cell>
@@ -1540,6 +1754,13 @@
           <cell r="F32">
             <v>2774.3</v>
           </cell>
+          <cell r="G32"/>
+          <cell r="H32"/>
+          <cell r="I32"/>
+          <cell r="J32"/>
+          <cell r="K32"/>
+          <cell r="L32"/>
+          <cell r="M32"/>
         </row>
         <row r="33">
           <cell r="A33" t="str">
@@ -1554,9 +1775,17 @@
           <cell r="D33">
             <v>5035.68</v>
           </cell>
+          <cell r="E33"/>
           <cell r="F33">
             <v>16785.29</v>
           </cell>
+          <cell r="G33"/>
+          <cell r="H33"/>
+          <cell r="I33"/>
+          <cell r="J33"/>
+          <cell r="K33"/>
+          <cell r="L33"/>
+          <cell r="M33"/>
         </row>
         <row r="34">
           <cell r="A34" t="str">
@@ -1577,6 +1806,13 @@
           <cell r="F34">
             <v>7945.3</v>
           </cell>
+          <cell r="G34"/>
+          <cell r="H34"/>
+          <cell r="I34"/>
+          <cell r="J34"/>
+          <cell r="K34"/>
+          <cell r="L34"/>
+          <cell r="M34"/>
         </row>
         <row r="35">
           <cell r="A35" t="str">
@@ -1585,9 +1821,19 @@
           <cell r="B35">
             <v>230</v>
           </cell>
+          <cell r="C35"/>
+          <cell r="D35"/>
+          <cell r="E35"/>
           <cell r="F35">
             <v>230</v>
           </cell>
+          <cell r="G35"/>
+          <cell r="H35"/>
+          <cell r="I35"/>
+          <cell r="J35"/>
+          <cell r="K35"/>
+          <cell r="L35"/>
+          <cell r="M35"/>
         </row>
         <row r="36">
           <cell r="A36" t="str">
@@ -1602,20 +1848,38 @@
           <cell r="D36">
             <v>8006.02</v>
           </cell>
+          <cell r="E36"/>
           <cell r="F36">
             <v>24330.39</v>
           </cell>
+          <cell r="G36"/>
+          <cell r="H36"/>
+          <cell r="I36"/>
+          <cell r="J36"/>
+          <cell r="K36"/>
+          <cell r="L36"/>
+          <cell r="M36"/>
         </row>
         <row r="37">
           <cell r="A37" t="str">
             <v>IPTU e Taxas Municipais CIF</v>
           </cell>
+          <cell r="B37"/>
+          <cell r="C37"/>
+          <cell r="D37"/>
           <cell r="E37">
             <v>2430.6600000000003</v>
           </cell>
           <cell r="F37">
             <v>2430.6600000000003</v>
           </cell>
+          <cell r="G37"/>
+          <cell r="H37"/>
+          <cell r="I37"/>
+          <cell r="J37"/>
+          <cell r="K37"/>
+          <cell r="L37"/>
+          <cell r="M37"/>
         </row>
         <row r="38">
           <cell r="A38" t="str">
@@ -1636,6 +1900,13 @@
           <cell r="F38">
             <v>68290.62</v>
           </cell>
+          <cell r="G38"/>
+          <cell r="H38"/>
+          <cell r="I38"/>
+          <cell r="J38"/>
+          <cell r="K38"/>
+          <cell r="L38"/>
+          <cell r="M38"/>
         </row>
         <row r="39">
           <cell r="A39" t="str">
@@ -1656,6 +1927,13 @@
           <cell r="F39">
             <v>39131.61</v>
           </cell>
+          <cell r="G39"/>
+          <cell r="H39"/>
+          <cell r="I39"/>
+          <cell r="J39"/>
+          <cell r="K39"/>
+          <cell r="L39"/>
+          <cell r="M39"/>
         </row>
         <row r="40">
           <cell r="A40" t="str">
@@ -1676,6 +1954,13 @@
           <cell r="F40">
             <v>6673.58</v>
           </cell>
+          <cell r="G40"/>
+          <cell r="H40"/>
+          <cell r="I40"/>
+          <cell r="J40"/>
+          <cell r="K40"/>
+          <cell r="L40"/>
+          <cell r="M40"/>
         </row>
         <row r="41">
           <cell r="A41" t="str">
@@ -1690,20 +1975,38 @@
           <cell r="D41">
             <v>2405.31</v>
           </cell>
+          <cell r="E41"/>
           <cell r="F41">
             <v>7126.77</v>
           </cell>
+          <cell r="G41"/>
+          <cell r="H41"/>
+          <cell r="I41"/>
+          <cell r="J41"/>
+          <cell r="K41"/>
+          <cell r="L41"/>
+          <cell r="M41"/>
         </row>
         <row r="42">
           <cell r="A42" t="str">
             <v>Medicina e Segurança do Trabalho MOD</v>
           </cell>
+          <cell r="B42"/>
+          <cell r="C42"/>
           <cell r="D42">
             <v>180</v>
           </cell>
+          <cell r="E42"/>
           <cell r="F42">
             <v>180</v>
           </cell>
+          <cell r="G42"/>
+          <cell r="H42"/>
+          <cell r="I42"/>
+          <cell r="J42"/>
+          <cell r="K42"/>
+          <cell r="L42"/>
+          <cell r="M42"/>
         </row>
         <row r="43">
           <cell r="A43" t="str">
@@ -1724,6 +2027,13 @@
           <cell r="F43">
             <v>97019.559999999983</v>
           </cell>
+          <cell r="G43"/>
+          <cell r="H43"/>
+          <cell r="I43"/>
+          <cell r="J43"/>
+          <cell r="K43"/>
+          <cell r="L43"/>
+          <cell r="M43"/>
         </row>
         <row r="44">
           <cell r="A44" t="str">
@@ -1738,9 +2048,17 @@
           <cell r="D44">
             <v>272.03999999999996</v>
           </cell>
+          <cell r="E44"/>
           <cell r="F44">
             <v>877</v>
           </cell>
+          <cell r="G44"/>
+          <cell r="H44"/>
+          <cell r="I44"/>
+          <cell r="J44"/>
+          <cell r="K44"/>
+          <cell r="L44"/>
+          <cell r="M44"/>
         </row>
         <row r="45">
           <cell r="A45" t="str">
@@ -1761,17 +2079,34 @@
           <cell r="F45">
             <v>563079.43000000005</v>
           </cell>
+          <cell r="G45"/>
+          <cell r="H45"/>
+          <cell r="I45"/>
+          <cell r="J45"/>
+          <cell r="K45"/>
+          <cell r="L45"/>
+          <cell r="M45"/>
         </row>
         <row r="46">
           <cell r="A46" t="str">
             <v>Assistência Médica (Adm)</v>
           </cell>
+          <cell r="B46"/>
           <cell r="C46">
             <v>75</v>
           </cell>
+          <cell r="D46"/>
+          <cell r="E46"/>
           <cell r="F46">
             <v>75</v>
           </cell>
+          <cell r="G46"/>
+          <cell r="H46"/>
+          <cell r="I46"/>
+          <cell r="J46"/>
+          <cell r="K46"/>
+          <cell r="L46"/>
+          <cell r="M46"/>
         </row>
         <row r="47">
           <cell r="A47" t="str">
@@ -1792,6 +2127,13 @@
           <cell r="F47">
             <v>4935.9799999999996</v>
           </cell>
+          <cell r="G47"/>
+          <cell r="H47"/>
+          <cell r="I47"/>
+          <cell r="J47"/>
+          <cell r="K47"/>
+          <cell r="L47"/>
+          <cell r="M47"/>
         </row>
         <row r="48">
           <cell r="A48" t="str">
@@ -1812,11 +2154,19 @@
           <cell r="F48">
             <v>9726.68</v>
           </cell>
+          <cell r="G48"/>
+          <cell r="H48"/>
+          <cell r="I48"/>
+          <cell r="J48"/>
+          <cell r="K48"/>
+          <cell r="L48"/>
+          <cell r="M48"/>
         </row>
         <row r="49">
           <cell r="A49" t="str">
             <v>Ferias (Adm)</v>
           </cell>
+          <cell r="B49"/>
           <cell r="C49">
             <v>297.89999999999998</v>
           </cell>
@@ -1829,6 +2179,13 @@
           <cell r="F49">
             <v>3200.04</v>
           </cell>
+          <cell r="G49"/>
+          <cell r="H49"/>
+          <cell r="I49"/>
+          <cell r="J49"/>
+          <cell r="K49"/>
+          <cell r="L49"/>
+          <cell r="M49"/>
         </row>
         <row r="50">
           <cell r="A50" t="str">
@@ -1843,9 +2200,17 @@
           <cell r="D50">
             <v>9088.76</v>
           </cell>
+          <cell r="E50"/>
           <cell r="F50">
             <v>27537.019999999997</v>
           </cell>
+          <cell r="G50"/>
+          <cell r="H50"/>
+          <cell r="I50"/>
+          <cell r="J50"/>
+          <cell r="K50"/>
+          <cell r="L50"/>
+          <cell r="M50"/>
         </row>
         <row r="51">
           <cell r="A51" t="str">
@@ -1866,6 +2231,13 @@
           <cell r="F51">
             <v>14373.5</v>
           </cell>
+          <cell r="G51"/>
+          <cell r="H51"/>
+          <cell r="I51"/>
+          <cell r="J51"/>
+          <cell r="K51"/>
+          <cell r="L51"/>
+          <cell r="M51"/>
         </row>
         <row r="52">
           <cell r="A52" t="str">
@@ -1880,9 +2252,17 @@
           <cell r="D52">
             <v>20718.489999999998</v>
           </cell>
+          <cell r="E52"/>
           <cell r="F52">
             <v>61430.81</v>
           </cell>
+          <cell r="G52"/>
+          <cell r="H52"/>
+          <cell r="I52"/>
+          <cell r="J52"/>
+          <cell r="K52"/>
+          <cell r="L52"/>
+          <cell r="M52"/>
         </row>
         <row r="53">
           <cell r="A53" t="str">
@@ -1903,6 +2283,13 @@
           <cell r="F53">
             <v>5933.3600000000006</v>
           </cell>
+          <cell r="G53"/>
+          <cell r="H53"/>
+          <cell r="I53"/>
+          <cell r="J53"/>
+          <cell r="K53"/>
+          <cell r="L53"/>
+          <cell r="M53"/>
         </row>
         <row r="54">
           <cell r="A54" t="str">
@@ -1923,6 +2310,13 @@
           <cell r="F54">
             <v>215577.69</v>
           </cell>
+          <cell r="G54"/>
+          <cell r="H54"/>
+          <cell r="I54"/>
+          <cell r="J54"/>
+          <cell r="K54"/>
+          <cell r="L54"/>
+          <cell r="M54"/>
         </row>
         <row r="55">
           <cell r="A55" t="str">
@@ -1931,12 +2325,21 @@
           <cell r="B55">
             <v>879.73</v>
           </cell>
+          <cell r="C55"/>
           <cell r="D55">
             <v>11928.27</v>
           </cell>
+          <cell r="E55"/>
           <cell r="F55">
             <v>12808</v>
           </cell>
+          <cell r="G55"/>
+          <cell r="H55"/>
+          <cell r="I55"/>
+          <cell r="J55"/>
+          <cell r="K55"/>
+          <cell r="L55"/>
+          <cell r="M55"/>
         </row>
         <row r="56">
           <cell r="A56" t="str">
@@ -1957,6 +2360,13 @@
           <cell r="F56">
             <v>205513.01</v>
           </cell>
+          <cell r="G56"/>
+          <cell r="H56"/>
+          <cell r="I56"/>
+          <cell r="J56"/>
+          <cell r="K56"/>
+          <cell r="L56"/>
+          <cell r="M56"/>
         </row>
         <row r="57">
           <cell r="A57" t="str">
@@ -1971,9 +2381,17 @@
           <cell r="D57">
             <v>596.62</v>
           </cell>
+          <cell r="E57"/>
           <cell r="F57">
             <v>1968.3400000000001</v>
           </cell>
+          <cell r="G57"/>
+          <cell r="H57"/>
+          <cell r="I57"/>
+          <cell r="J57"/>
+          <cell r="K57"/>
+          <cell r="L57"/>
+          <cell r="M57"/>
         </row>
         <row r="58">
           <cell r="A58" t="str">
@@ -1994,6 +2412,13 @@
           <cell r="F58">
             <v>58178.34</v>
           </cell>
+          <cell r="G58"/>
+          <cell r="H58"/>
+          <cell r="I58"/>
+          <cell r="J58"/>
+          <cell r="K58"/>
+          <cell r="L58"/>
+          <cell r="M58"/>
         </row>
         <row r="59">
           <cell r="A59" t="str">
@@ -2008,9 +2433,17 @@
           <cell r="D59">
             <v>32.229999999999997</v>
           </cell>
+          <cell r="E59"/>
           <cell r="F59">
             <v>96.69</v>
           </cell>
+          <cell r="G59"/>
+          <cell r="H59"/>
+          <cell r="I59"/>
+          <cell r="J59"/>
+          <cell r="K59"/>
+          <cell r="L59"/>
+          <cell r="M59"/>
         </row>
         <row r="60">
           <cell r="A60" t="str">
@@ -2031,6 +2464,13 @@
           <cell r="F60">
             <v>2024.63</v>
           </cell>
+          <cell r="G60"/>
+          <cell r="H60"/>
+          <cell r="I60"/>
+          <cell r="J60"/>
+          <cell r="K60"/>
+          <cell r="L60"/>
+          <cell r="M60"/>
         </row>
         <row r="61">
           <cell r="A61" t="str">
@@ -2051,6 +2491,13 @@
           <cell r="F61">
             <v>3500</v>
           </cell>
+          <cell r="G61"/>
+          <cell r="H61"/>
+          <cell r="I61"/>
+          <cell r="J61"/>
+          <cell r="K61"/>
+          <cell r="L61"/>
+          <cell r="M61"/>
         </row>
         <row r="62">
           <cell r="A62" t="str">
@@ -2065,9 +2512,17 @@
           <cell r="D62">
             <v>780.64</v>
           </cell>
+          <cell r="E62"/>
           <cell r="F62">
             <v>2272.96</v>
           </cell>
+          <cell r="G62"/>
+          <cell r="H62"/>
+          <cell r="I62"/>
+          <cell r="J62"/>
+          <cell r="K62"/>
+          <cell r="L62"/>
+          <cell r="M62"/>
         </row>
         <row r="63">
           <cell r="A63" t="str">
@@ -2082,9 +2537,17 @@
           <cell r="D63">
             <v>150.63</v>
           </cell>
+          <cell r="E63"/>
           <cell r="F63">
             <v>535.22</v>
           </cell>
+          <cell r="G63"/>
+          <cell r="H63"/>
+          <cell r="I63"/>
+          <cell r="J63"/>
+          <cell r="K63"/>
+          <cell r="L63"/>
+          <cell r="M63"/>
         </row>
         <row r="64">
           <cell r="A64" t="str">
@@ -2099,9 +2562,17 @@
           <cell r="D64">
             <v>350.68</v>
           </cell>
+          <cell r="E64"/>
           <cell r="F64">
             <v>1294.56</v>
           </cell>
+          <cell r="G64"/>
+          <cell r="H64"/>
+          <cell r="I64"/>
+          <cell r="J64"/>
+          <cell r="K64"/>
+          <cell r="L64"/>
+          <cell r="M64"/>
         </row>
         <row r="65">
           <cell r="A65" t="str">
@@ -2116,9 +2587,17 @@
           <cell r="D65">
             <v>100</v>
           </cell>
+          <cell r="E65"/>
           <cell r="F65">
             <v>300</v>
           </cell>
+          <cell r="G65"/>
+          <cell r="H65"/>
+          <cell r="I65"/>
+          <cell r="J65"/>
+          <cell r="K65"/>
+          <cell r="L65"/>
+          <cell r="M65"/>
         </row>
         <row r="66">
           <cell r="A66" t="str">
@@ -2130,9 +2609,18 @@
           <cell r="C66">
             <v>91.95</v>
           </cell>
+          <cell r="D66"/>
+          <cell r="E66"/>
           <cell r="F66">
             <v>190.36</v>
           </cell>
+          <cell r="G66"/>
+          <cell r="H66"/>
+          <cell r="I66"/>
+          <cell r="J66"/>
+          <cell r="K66"/>
+          <cell r="L66"/>
+          <cell r="M66"/>
         </row>
         <row r="67">
           <cell r="A67" t="str">
@@ -2153,6 +2641,13 @@
           <cell r="F67">
             <v>1256.1499999999999</v>
           </cell>
+          <cell r="G67"/>
+          <cell r="H67"/>
+          <cell r="I67"/>
+          <cell r="J67"/>
+          <cell r="K67"/>
+          <cell r="L67"/>
+          <cell r="M67"/>
         </row>
         <row r="68">
           <cell r="A68" t="str">
@@ -2173,6 +2668,13 @@
           <cell r="F68">
             <v>1820.6</v>
           </cell>
+          <cell r="G68"/>
+          <cell r="H68"/>
+          <cell r="I68"/>
+          <cell r="J68"/>
+          <cell r="K68"/>
+          <cell r="L68"/>
+          <cell r="M68"/>
         </row>
         <row r="69">
           <cell r="A69" t="str">
@@ -2193,6 +2695,13 @@
           <cell r="F69">
             <v>1480</v>
           </cell>
+          <cell r="G69"/>
+          <cell r="H69"/>
+          <cell r="I69"/>
+          <cell r="J69"/>
+          <cell r="K69"/>
+          <cell r="L69"/>
+          <cell r="M69"/>
         </row>
         <row r="70">
           <cell r="A70" t="str">
@@ -2213,6 +2722,13 @@
           <cell r="F70">
             <v>35334.74</v>
           </cell>
+          <cell r="G70"/>
+          <cell r="H70"/>
+          <cell r="I70"/>
+          <cell r="J70"/>
+          <cell r="K70"/>
+          <cell r="L70"/>
+          <cell r="M70"/>
         </row>
         <row r="71">
           <cell r="A71" t="str">
@@ -2227,9 +2743,17 @@
           <cell r="D71">
             <v>351</v>
           </cell>
+          <cell r="E71"/>
           <cell r="F71">
             <v>1319.44</v>
           </cell>
+          <cell r="G71"/>
+          <cell r="H71"/>
+          <cell r="I71"/>
+          <cell r="J71"/>
+          <cell r="K71"/>
+          <cell r="L71"/>
+          <cell r="M71"/>
         </row>
         <row r="72">
           <cell r="A72" t="str">
@@ -2250,6 +2774,13 @@
           <cell r="F72">
             <v>6752.99</v>
           </cell>
+          <cell r="G72"/>
+          <cell r="H72"/>
+          <cell r="I72"/>
+          <cell r="J72"/>
+          <cell r="K72"/>
+          <cell r="L72"/>
+          <cell r="M72"/>
         </row>
         <row r="73">
           <cell r="A73" t="str">
@@ -2270,6 +2801,13 @@
           <cell r="F73">
             <v>1236528.47</v>
           </cell>
+          <cell r="G73"/>
+          <cell r="H73"/>
+          <cell r="I73"/>
+          <cell r="J73"/>
+          <cell r="K73"/>
+          <cell r="L73"/>
+          <cell r="M73"/>
         </row>
         <row r="74">
           <cell r="A74" t="str">
@@ -2278,9 +2816,19 @@
           <cell r="B74">
             <v>1368</v>
           </cell>
+          <cell r="C74"/>
+          <cell r="D74"/>
+          <cell r="E74"/>
           <cell r="F74">
             <v>1368</v>
           </cell>
+          <cell r="G74"/>
+          <cell r="H74"/>
+          <cell r="I74"/>
+          <cell r="J74"/>
+          <cell r="K74"/>
+          <cell r="L74"/>
+          <cell r="M74"/>
         </row>
         <row r="75">
           <cell r="A75" t="str">
@@ -2295,9 +2843,17 @@
           <cell r="D75">
             <v>3042.48</v>
           </cell>
+          <cell r="E75"/>
           <cell r="F75">
             <v>7412.48</v>
           </cell>
+          <cell r="G75"/>
+          <cell r="H75"/>
+          <cell r="I75"/>
+          <cell r="J75"/>
+          <cell r="K75"/>
+          <cell r="L75"/>
+          <cell r="M75"/>
         </row>
         <row r="76">
           <cell r="A76" t="str">
@@ -2318,6 +2874,13 @@
           <cell r="F76">
             <v>183897.01</v>
           </cell>
+          <cell r="G76"/>
+          <cell r="H76"/>
+          <cell r="I76"/>
+          <cell r="J76"/>
+          <cell r="K76"/>
+          <cell r="L76"/>
+          <cell r="M76"/>
         </row>
         <row r="77">
           <cell r="A77" t="str">
@@ -2338,6 +2901,13 @@
           <cell r="F77">
             <v>338386.3899999999</v>
           </cell>
+          <cell r="G77"/>
+          <cell r="H77"/>
+          <cell r="I77"/>
+          <cell r="J77"/>
+          <cell r="K77"/>
+          <cell r="L77"/>
+          <cell r="M77"/>
         </row>
         <row r="78">
           <cell r="A78" t="str">
@@ -2358,6 +2928,13 @@
           <cell r="F78">
             <v>31329.660000000003</v>
           </cell>
+          <cell r="G78"/>
+          <cell r="H78"/>
+          <cell r="I78"/>
+          <cell r="J78"/>
+          <cell r="K78"/>
+          <cell r="L78"/>
+          <cell r="M78"/>
         </row>
         <row r="79">
           <cell r="A79" t="str">
@@ -2378,6 +2955,13 @@
           <cell r="F79">
             <v>63215.880000000005</v>
           </cell>
+          <cell r="G79"/>
+          <cell r="H79"/>
+          <cell r="I79"/>
+          <cell r="J79"/>
+          <cell r="K79"/>
+          <cell r="L79"/>
+          <cell r="M79"/>
         </row>
         <row r="80">
           <cell r="A80" t="str">
@@ -2392,9 +2976,17 @@
           <cell r="D80">
             <v>24000</v>
           </cell>
+          <cell r="E80"/>
           <cell r="F80">
             <v>72000</v>
           </cell>
+          <cell r="G80"/>
+          <cell r="H80"/>
+          <cell r="I80"/>
+          <cell r="J80"/>
+          <cell r="K80"/>
+          <cell r="L80"/>
+          <cell r="M80"/>
         </row>
         <row r="81">
           <cell r="A81" t="str">
@@ -2415,20 +3007,36 @@
           <cell r="F81">
             <v>200814.61999999997</v>
           </cell>
+          <cell r="G81"/>
+          <cell r="H81"/>
+          <cell r="I81"/>
+          <cell r="J81"/>
+          <cell r="K81"/>
+          <cell r="L81"/>
+          <cell r="M81"/>
         </row>
         <row r="82">
           <cell r="A82" t="str">
             <v>Fretes</v>
           </cell>
+          <cell r="B82"/>
           <cell r="C82">
             <v>2334.16</v>
           </cell>
           <cell r="D82">
             <v>709</v>
           </cell>
+          <cell r="E82"/>
           <cell r="F82">
             <v>3043.16</v>
           </cell>
+          <cell r="G82"/>
+          <cell r="H82"/>
+          <cell r="I82"/>
+          <cell r="J82"/>
+          <cell r="K82"/>
+          <cell r="L82"/>
+          <cell r="M82"/>
         </row>
         <row r="83">
           <cell r="A83" t="str">
@@ -2443,9 +3051,17 @@
           <cell r="D83">
             <v>420.81</v>
           </cell>
+          <cell r="E83"/>
           <cell r="F83">
             <v>2737.9</v>
           </cell>
+          <cell r="G83"/>
+          <cell r="H83"/>
+          <cell r="I83"/>
+          <cell r="J83"/>
+          <cell r="K83"/>
+          <cell r="L83"/>
+          <cell r="M83"/>
         </row>
         <row r="84">
           <cell r="A84" t="str">
@@ -2466,6 +3082,13 @@
           <cell r="F84">
             <v>54139.75</v>
           </cell>
+          <cell r="G84"/>
+          <cell r="H84"/>
+          <cell r="I84"/>
+          <cell r="J84"/>
+          <cell r="K84"/>
+          <cell r="L84"/>
+          <cell r="M84"/>
         </row>
         <row r="85">
           <cell r="A85" t="str">
@@ -2486,6 +3109,13 @@
           <cell r="F85">
             <v>13500.389999999998</v>
           </cell>
+          <cell r="G85"/>
+          <cell r="H85"/>
+          <cell r="I85"/>
+          <cell r="J85"/>
+          <cell r="K85"/>
+          <cell r="L85"/>
+          <cell r="M85"/>
         </row>
         <row r="86">
           <cell r="A86" t="str">
@@ -2506,6 +3136,13 @@
           <cell r="F86">
             <v>18256</v>
           </cell>
+          <cell r="G86"/>
+          <cell r="H86"/>
+          <cell r="I86"/>
+          <cell r="J86"/>
+          <cell r="K86"/>
+          <cell r="L86"/>
+          <cell r="M86"/>
         </row>
         <row r="87">
           <cell r="A87" t="str">
@@ -2526,6 +3163,13 @@
           <cell r="F87">
             <v>2751.99</v>
           </cell>
+          <cell r="G87"/>
+          <cell r="H87"/>
+          <cell r="I87"/>
+          <cell r="J87"/>
+          <cell r="K87"/>
+          <cell r="L87"/>
+          <cell r="M87"/>
         </row>
         <row r="88">
           <cell r="A88" t="str">
@@ -2540,9 +3184,17 @@
           <cell r="D88">
             <v>9958.6499999999978</v>
           </cell>
+          <cell r="E88"/>
           <cell r="F88">
             <v>24550.729999999996</v>
           </cell>
+          <cell r="G88"/>
+          <cell r="H88"/>
+          <cell r="I88"/>
+          <cell r="J88"/>
+          <cell r="K88"/>
+          <cell r="L88"/>
+          <cell r="M88"/>
         </row>
         <row r="89">
           <cell r="A89" t="str">
@@ -2563,6 +3215,13 @@
           <cell r="F89">
             <v>13970.310000000001</v>
           </cell>
+          <cell r="G89"/>
+          <cell r="H89"/>
+          <cell r="I89"/>
+          <cell r="J89"/>
+          <cell r="K89"/>
+          <cell r="L89"/>
+          <cell r="M89"/>
         </row>
         <row r="90">
           <cell r="A90" t="str">
@@ -2577,9 +3236,17 @@
           <cell r="D90">
             <v>61558.19</v>
           </cell>
+          <cell r="E90"/>
           <cell r="F90">
             <v>142703.06</v>
           </cell>
+          <cell r="G90"/>
+          <cell r="H90"/>
+          <cell r="I90"/>
+          <cell r="J90"/>
+          <cell r="K90"/>
+          <cell r="L90"/>
+          <cell r="M90"/>
         </row>
         <row r="91">
           <cell r="A91" t="str">
@@ -2600,6 +3267,13 @@
           <cell r="F91">
             <v>5164.5</v>
           </cell>
+          <cell r="G91"/>
+          <cell r="H91"/>
+          <cell r="I91"/>
+          <cell r="J91"/>
+          <cell r="K91"/>
+          <cell r="L91"/>
+          <cell r="M91"/>
         </row>
         <row r="92">
           <cell r="A92" t="str">
@@ -2620,6 +3294,13 @@
           <cell r="F92">
             <v>57286.639999999992</v>
           </cell>
+          <cell r="G92"/>
+          <cell r="H92"/>
+          <cell r="I92"/>
+          <cell r="J92"/>
+          <cell r="K92"/>
+          <cell r="L92"/>
+          <cell r="M92"/>
         </row>
         <row r="93">
           <cell r="A93" t="str">
@@ -2640,6 +3321,13 @@
           <cell r="F93">
             <v>241075.47</v>
           </cell>
+          <cell r="G93"/>
+          <cell r="H93"/>
+          <cell r="I93"/>
+          <cell r="J93"/>
+          <cell r="K93"/>
+          <cell r="L93"/>
+          <cell r="M93"/>
         </row>
         <row r="94">
           <cell r="A94" t="str">
@@ -2660,6 +3348,13 @@
           <cell r="F94">
             <v>55625.149999999994</v>
           </cell>
+          <cell r="G94"/>
+          <cell r="H94"/>
+          <cell r="I94"/>
+          <cell r="J94"/>
+          <cell r="K94"/>
+          <cell r="L94"/>
+          <cell r="M94"/>
         </row>
         <row r="95">
           <cell r="A95" t="str">
@@ -2674,9 +3369,17 @@
           <cell r="D95">
             <v>6035.41</v>
           </cell>
+          <cell r="E95"/>
           <cell r="F95">
             <v>18106.23</v>
           </cell>
+          <cell r="G95"/>
+          <cell r="H95"/>
+          <cell r="I95"/>
+          <cell r="J95"/>
+          <cell r="K95"/>
+          <cell r="L95"/>
+          <cell r="M95"/>
         </row>
         <row r="96">
           <cell r="A96" t="str">
@@ -2697,6 +3400,13 @@
           <cell r="F96">
             <v>42695</v>
           </cell>
+          <cell r="G96"/>
+          <cell r="H96"/>
+          <cell r="I96"/>
+          <cell r="J96"/>
+          <cell r="K96"/>
+          <cell r="L96"/>
+          <cell r="M96"/>
         </row>
         <row r="97">
           <cell r="A97" t="str">
@@ -2717,6 +3427,13 @@
           <cell r="F97">
             <v>32556</v>
           </cell>
+          <cell r="G97"/>
+          <cell r="H97"/>
+          <cell r="I97"/>
+          <cell r="J97"/>
+          <cell r="K97"/>
+          <cell r="L97"/>
+          <cell r="M97"/>
         </row>
         <row r="98">
           <cell r="A98" t="str">
@@ -2737,6 +3454,13 @@
           <cell r="F98">
             <v>29005.78</v>
           </cell>
+          <cell r="G98"/>
+          <cell r="H98"/>
+          <cell r="I98"/>
+          <cell r="J98"/>
+          <cell r="K98"/>
+          <cell r="L98"/>
+          <cell r="M98"/>
         </row>
         <row r="99">
           <cell r="A99" t="str">
@@ -2757,6 +3481,13 @@
           <cell r="F99">
             <v>52413.81</v>
           </cell>
+          <cell r="G99"/>
+          <cell r="H99"/>
+          <cell r="I99"/>
+          <cell r="J99"/>
+          <cell r="K99"/>
+          <cell r="L99"/>
+          <cell r="M99"/>
         </row>
         <row r="100">
           <cell r="A100" t="str">
@@ -2777,17 +3508,34 @@
           <cell r="F100">
             <v>3673.5</v>
           </cell>
+          <cell r="G100"/>
+          <cell r="H100"/>
+          <cell r="I100"/>
+          <cell r="J100"/>
+          <cell r="K100"/>
+          <cell r="L100"/>
+          <cell r="M100"/>
         </row>
         <row r="101">
           <cell r="A101" t="str">
             <v>Consultoria Tributaria</v>
           </cell>
+          <cell r="B101"/>
+          <cell r="C101"/>
+          <cell r="D101"/>
           <cell r="E101">
             <v>7000</v>
           </cell>
           <cell r="F101">
             <v>7000</v>
           </cell>
+          <cell r="G101"/>
+          <cell r="H101"/>
+          <cell r="I101"/>
+          <cell r="J101"/>
+          <cell r="K101"/>
+          <cell r="L101"/>
+          <cell r="M101"/>
         </row>
         <row r="102">
           <cell r="A102" t="str">
@@ -2808,6 +3556,13 @@
           <cell r="F102">
             <v>211752.66999999998</v>
           </cell>
+          <cell r="G102"/>
+          <cell r="H102"/>
+          <cell r="I102"/>
+          <cell r="J102"/>
+          <cell r="K102"/>
+          <cell r="L102"/>
+          <cell r="M102"/>
         </row>
         <row r="103">
           <cell r="A103" t="str">
@@ -2828,6 +3583,13 @@
           <cell r="F103">
             <v>34519.19999999999</v>
           </cell>
+          <cell r="G103"/>
+          <cell r="H103"/>
+          <cell r="I103"/>
+          <cell r="J103"/>
+          <cell r="K103"/>
+          <cell r="L103"/>
+          <cell r="M103"/>
         </row>
         <row r="104">
           <cell r="A104" t="str">
@@ -2848,6 +3610,13 @@
           <cell r="F104">
             <v>614.20000000000005</v>
           </cell>
+          <cell r="G104"/>
+          <cell r="H104"/>
+          <cell r="I104"/>
+          <cell r="J104"/>
+          <cell r="K104"/>
+          <cell r="L104"/>
+          <cell r="M104"/>
         </row>
         <row r="105">
           <cell r="A105" t="str">
@@ -2868,6 +3637,13 @@
           <cell r="F105">
             <v>31529.140000000003</v>
           </cell>
+          <cell r="G105"/>
+          <cell r="H105"/>
+          <cell r="I105"/>
+          <cell r="J105"/>
+          <cell r="K105"/>
+          <cell r="L105"/>
+          <cell r="M105"/>
         </row>
         <row r="106">
           <cell r="A106" t="str">
@@ -2888,17 +3664,34 @@
           <cell r="F106">
             <v>40004.299999999996</v>
           </cell>
+          <cell r="G106"/>
+          <cell r="H106"/>
+          <cell r="I106"/>
+          <cell r="J106"/>
+          <cell r="K106"/>
+          <cell r="L106"/>
+          <cell r="M106"/>
         </row>
         <row r="107">
           <cell r="A107" t="str">
             <v>Juros Pagos</v>
           </cell>
+          <cell r="B107"/>
           <cell r="C107">
             <v>95.75</v>
           </cell>
+          <cell r="D107"/>
+          <cell r="E107"/>
           <cell r="F107">
             <v>95.75</v>
           </cell>
+          <cell r="G107"/>
+          <cell r="H107"/>
+          <cell r="I107"/>
+          <cell r="J107"/>
+          <cell r="K107"/>
+          <cell r="L107"/>
+          <cell r="M107"/>
         </row>
         <row r="108">
           <cell r="A108" t="str">
@@ -2919,6 +3712,13 @@
           <cell r="F108">
             <v>104990.07999999999</v>
           </cell>
+          <cell r="G108"/>
+          <cell r="H108"/>
+          <cell r="I108"/>
+          <cell r="J108"/>
+          <cell r="K108"/>
+          <cell r="L108"/>
+          <cell r="M108"/>
         </row>
         <row r="109">
           <cell r="A109" t="str">
@@ -2939,6 +3739,13 @@
           <cell r="F109">
             <v>112628.33</v>
           </cell>
+          <cell r="G109"/>
+          <cell r="H109"/>
+          <cell r="I109"/>
+          <cell r="J109"/>
+          <cell r="K109"/>
+          <cell r="L109"/>
+          <cell r="M109"/>
         </row>
         <row r="110">
           <cell r="A110" t="str">
@@ -2959,6 +3766,13 @@
           <cell r="F110">
             <v>18141.399999999998</v>
           </cell>
+          <cell r="G110"/>
+          <cell r="H110"/>
+          <cell r="I110"/>
+          <cell r="J110"/>
+          <cell r="K110"/>
+          <cell r="L110"/>
+          <cell r="M110"/>
         </row>
         <row r="111">
           <cell r="A111" t="str">
@@ -2979,6 +3793,13 @@
           <cell r="F111">
             <v>12149.76</v>
           </cell>
+          <cell r="G111"/>
+          <cell r="H111"/>
+          <cell r="I111"/>
+          <cell r="J111"/>
+          <cell r="K111"/>
+          <cell r="L111"/>
+          <cell r="M111"/>
         </row>
         <row r="112">
           <cell r="A112" t="str">
@@ -2993,9 +3814,17 @@
           <cell r="D112">
             <v>2570</v>
           </cell>
+          <cell r="E112"/>
           <cell r="F112">
             <v>22294.41</v>
           </cell>
+          <cell r="G112"/>
+          <cell r="H112"/>
+          <cell r="I112"/>
+          <cell r="J112"/>
+          <cell r="K112"/>
+          <cell r="L112"/>
+          <cell r="M112"/>
         </row>
         <row r="113">
           <cell r="A113" t="str">
@@ -3016,17 +3845,34 @@
           <cell r="F113">
             <v>55957.760000000009</v>
           </cell>
+          <cell r="G113"/>
+          <cell r="H113"/>
+          <cell r="I113"/>
+          <cell r="J113"/>
+          <cell r="K113"/>
+          <cell r="L113"/>
+          <cell r="M113"/>
         </row>
         <row r="114">
           <cell r="A114" t="str">
             <v>Moveis e Utensilios</v>
           </cell>
+          <cell r="B114"/>
+          <cell r="C114"/>
           <cell r="D114">
             <v>4085</v>
           </cell>
+          <cell r="E114"/>
           <cell r="F114">
             <v>4085</v>
           </cell>
+          <cell r="G114"/>
+          <cell r="H114"/>
+          <cell r="I114"/>
+          <cell r="J114"/>
+          <cell r="K114"/>
+          <cell r="L114"/>
+          <cell r="M114"/>
         </row>
         <row r="115">
           <cell r="A115" t="str">
@@ -3047,6 +3893,238 @@
           <cell r="F115">
             <v>4208070.07</v>
           </cell>
+          <cell r="G115"/>
+          <cell r="H115"/>
+          <cell r="I115"/>
+          <cell r="J115"/>
+          <cell r="K115"/>
+          <cell r="L115"/>
+          <cell r="M115"/>
+        </row>
+        <row r="116">
+          <cell r="A116"/>
+          <cell r="B116"/>
+          <cell r="C116"/>
+          <cell r="D116"/>
+          <cell r="E116"/>
+          <cell r="F116"/>
+          <cell r="G116"/>
+          <cell r="H116"/>
+          <cell r="I116"/>
+          <cell r="J116"/>
+          <cell r="K116"/>
+          <cell r="L116"/>
+          <cell r="M116"/>
+        </row>
+        <row r="117">
+          <cell r="A117"/>
+          <cell r="B117"/>
+          <cell r="C117"/>
+          <cell r="D117"/>
+          <cell r="E117"/>
+          <cell r="F117"/>
+          <cell r="G117"/>
+          <cell r="H117"/>
+          <cell r="I117"/>
+          <cell r="J117"/>
+          <cell r="K117"/>
+          <cell r="L117"/>
+          <cell r="M117"/>
+        </row>
+        <row r="118">
+          <cell r="A118"/>
+          <cell r="B118"/>
+          <cell r="C118"/>
+          <cell r="D118"/>
+          <cell r="E118"/>
+          <cell r="F118"/>
+          <cell r="G118"/>
+          <cell r="H118"/>
+          <cell r="I118"/>
+          <cell r="J118"/>
+          <cell r="K118"/>
+          <cell r="L118"/>
+          <cell r="M118"/>
+        </row>
+        <row r="119">
+          <cell r="A119"/>
+          <cell r="B119"/>
+          <cell r="C119"/>
+          <cell r="D119"/>
+          <cell r="E119"/>
+          <cell r="F119"/>
+          <cell r="G119"/>
+          <cell r="H119"/>
+          <cell r="I119"/>
+          <cell r="J119"/>
+          <cell r="K119"/>
+          <cell r="L119"/>
+          <cell r="M119"/>
+        </row>
+        <row r="120">
+          <cell r="A120"/>
+          <cell r="B120"/>
+          <cell r="C120"/>
+          <cell r="D120"/>
+          <cell r="E120"/>
+          <cell r="F120"/>
+          <cell r="G120"/>
+          <cell r="H120"/>
+          <cell r="I120"/>
+          <cell r="J120"/>
+          <cell r="K120"/>
+          <cell r="L120"/>
+          <cell r="M120"/>
+        </row>
+        <row r="121">
+          <cell r="A121"/>
+          <cell r="B121"/>
+          <cell r="C121"/>
+          <cell r="D121"/>
+          <cell r="E121"/>
+          <cell r="F121"/>
+          <cell r="G121"/>
+          <cell r="H121"/>
+          <cell r="I121"/>
+          <cell r="J121"/>
+          <cell r="K121"/>
+          <cell r="L121"/>
+          <cell r="M121"/>
+        </row>
+        <row r="122">
+          <cell r="A122"/>
+          <cell r="B122"/>
+          <cell r="C122"/>
+          <cell r="D122"/>
+          <cell r="E122"/>
+          <cell r="F122"/>
+          <cell r="G122"/>
+          <cell r="H122"/>
+          <cell r="I122"/>
+          <cell r="J122"/>
+          <cell r="K122"/>
+          <cell r="L122"/>
+          <cell r="M122"/>
+        </row>
+        <row r="123">
+          <cell r="A123"/>
+          <cell r="B123"/>
+          <cell r="C123"/>
+          <cell r="D123"/>
+          <cell r="E123"/>
+          <cell r="F123"/>
+          <cell r="G123"/>
+          <cell r="H123"/>
+          <cell r="I123"/>
+          <cell r="J123"/>
+          <cell r="K123"/>
+          <cell r="L123"/>
+          <cell r="M123"/>
+        </row>
+        <row r="124">
+          <cell r="A124"/>
+          <cell r="B124"/>
+          <cell r="C124"/>
+          <cell r="D124"/>
+          <cell r="E124"/>
+          <cell r="F124"/>
+          <cell r="G124"/>
+          <cell r="H124"/>
+          <cell r="I124"/>
+          <cell r="J124"/>
+          <cell r="K124"/>
+          <cell r="L124"/>
+          <cell r="M124"/>
+        </row>
+        <row r="125">
+          <cell r="A125"/>
+          <cell r="B125"/>
+          <cell r="C125"/>
+          <cell r="D125"/>
+          <cell r="E125"/>
+          <cell r="F125"/>
+          <cell r="G125"/>
+          <cell r="H125"/>
+          <cell r="I125"/>
+          <cell r="J125"/>
+          <cell r="K125"/>
+          <cell r="L125"/>
+          <cell r="M125"/>
+        </row>
+        <row r="126">
+          <cell r="A126"/>
+          <cell r="B126"/>
+          <cell r="C126"/>
+          <cell r="D126"/>
+          <cell r="E126"/>
+          <cell r="F126"/>
+          <cell r="G126"/>
+          <cell r="H126"/>
+          <cell r="I126"/>
+          <cell r="J126"/>
+          <cell r="K126"/>
+          <cell r="L126"/>
+          <cell r="M126"/>
+        </row>
+        <row r="127">
+          <cell r="A127"/>
+          <cell r="B127"/>
+          <cell r="C127"/>
+          <cell r="D127"/>
+          <cell r="E127"/>
+          <cell r="F127"/>
+          <cell r="G127"/>
+          <cell r="H127"/>
+          <cell r="I127"/>
+          <cell r="J127"/>
+          <cell r="K127"/>
+          <cell r="L127"/>
+          <cell r="M127"/>
+        </row>
+        <row r="128">
+          <cell r="A128"/>
+          <cell r="B128"/>
+          <cell r="C128"/>
+          <cell r="D128"/>
+          <cell r="E128"/>
+          <cell r="F128"/>
+          <cell r="G128"/>
+          <cell r="H128"/>
+          <cell r="I128"/>
+          <cell r="J128"/>
+          <cell r="K128"/>
+          <cell r="L128"/>
+          <cell r="M128"/>
+        </row>
+        <row r="129">
+          <cell r="A129"/>
+          <cell r="B129"/>
+          <cell r="C129"/>
+          <cell r="D129"/>
+          <cell r="E129"/>
+          <cell r="F129"/>
+          <cell r="G129"/>
+          <cell r="H129"/>
+          <cell r="I129"/>
+          <cell r="J129"/>
+          <cell r="K129"/>
+          <cell r="L129"/>
+          <cell r="M129"/>
+        </row>
+        <row r="130">
+          <cell r="A130"/>
+          <cell r="B130"/>
+          <cell r="C130"/>
+          <cell r="D130"/>
+          <cell r="E130"/>
+          <cell r="F130"/>
+          <cell r="G130"/>
+          <cell r="H130"/>
+          <cell r="I130"/>
+          <cell r="J130"/>
+          <cell r="K130"/>
+          <cell r="L130"/>
+          <cell r="M130"/>
         </row>
       </sheetData>
       <sheetData sheetId="9"/>
@@ -4192,11 +5270,11 @@
       </c>
       <c r="AB12" s="7">
         <f>SUM(AB13:AB19)</f>
-        <v>169337.99000000002</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="14">
         <f t="shared" ref="AC12:AC19" si="3">IFERROR((AB12*-1)/Z12-1,"")</f>
-        <v>-0.11025953506770358</v>
+        <v>-1</v>
       </c>
       <c r="AD12" s="7">
         <v>-199390.90817291645</v>
@@ -4336,19 +5414,20 @@
         <f t="shared" si="2"/>
         <v>0.1795865142240527</v>
       </c>
-      <c r="Z13" s="6">
-        <v>-64093.317628933997</v>
+      <c r="Z13" s="51">
+        <f t="shared" ref="Z13:Z18" si="7">AB$10*$F13</f>
+        <v>-19181.695960000001</v>
       </c>
       <c r="AA13" s="15">
         <v>-2.6200000000000001E-2</v>
       </c>
       <c r="AB13" s="6">
-        <f>IFERROR(VLOOKUP($I13,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>81164.490000000005</v>
+        <f>IFERROR(VLOOKUP($I13,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC13" s="46">
         <f t="shared" si="3"/>
-        <v>0.26634870845505243</v>
+        <v>-1</v>
       </c>
       <c r="AD13" s="6">
         <v>-67147.066762601695</v>
@@ -4487,19 +5566,20 @@
         <f t="shared" si="2"/>
         <v>-0.39668009875927335</v>
       </c>
-      <c r="Z14" s="6">
-        <v>-60301.537387527591</v>
+      <c r="Z14" s="51">
+        <f t="shared" si="7"/>
+        <v>-18046.900969999999</v>
       </c>
       <c r="AA14" s="15">
         <v>-2.4649999999999998E-2</v>
       </c>
       <c r="AB14" s="6">
-        <f>IFERROR(VLOOKUP($I14,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>39057.060000000005</v>
+        <f>IFERROR(VLOOKUP($I14,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC14" s="46">
         <f t="shared" si="3"/>
-        <v>-0.35230407561585098</v>
+        <v>-1</v>
       </c>
       <c r="AD14" s="6">
         <v>-63174.625790005026</v>
@@ -4638,19 +5718,20 @@
         <f t="shared" si="2"/>
         <v>-0.52489344493147327</v>
       </c>
-      <c r="Z15" s="6">
-        <v>-6727.3520412049038</v>
+      <c r="Z15" s="51">
+        <f t="shared" si="7"/>
+        <v>-2013.3459499999999</v>
       </c>
       <c r="AA15" s="15">
         <v>-2.7499999999999998E-3</v>
       </c>
       <c r="AB15" s="6">
-        <f>IFERROR(VLOOKUP($I15,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>3431.3</v>
+        <f>IFERROR(VLOOKUP($I15,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC15" s="46">
         <f t="shared" si="3"/>
-        <v>-0.48994790535958987</v>
+        <v>-1</v>
       </c>
       <c r="AD15" s="6">
         <v>-7047.8791449295668</v>
@@ -4789,19 +5870,20 @@
         <f t="shared" si="2"/>
         <v>-0.2026166951968601</v>
       </c>
-      <c r="Z16" s="6">
-        <v>-25930.884231553449</v>
+      <c r="Z16" s="51">
+        <f t="shared" si="7"/>
+        <v>-7760.533480000001</v>
       </c>
       <c r="AA16" s="15">
         <v>-1.06E-2</v>
       </c>
       <c r="AB16" s="6">
-        <f>IFERROR(VLOOKUP($I16,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>22197.7</v>
+        <f>IFERROR(VLOOKUP($I16,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC16" s="46">
         <f t="shared" si="3"/>
-        <v>-0.1439667154508677</v>
+        <v>-1</v>
       </c>
       <c r="AD16" s="6">
         <v>-27166.37052227397</v>
@@ -4940,19 +6022,20 @@
         <f t="shared" si="2"/>
         <v>-0.52496824185913493</v>
       </c>
-      <c r="Z17" s="6">
-        <v>-31190.450372859104</v>
+      <c r="Z17" s="51">
+        <f t="shared" si="7"/>
+        <v>-9334.6039500000006</v>
       </c>
       <c r="AA17" s="15">
         <v>-1.2750000000000001E-2</v>
       </c>
       <c r="AB17" s="6">
-        <f>IFERROR(VLOOKUP($I17,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>15906.25</v>
+        <f>IFERROR(VLOOKUP($I17,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC17" s="46">
         <f t="shared" si="3"/>
-        <v>-0.49002820382994239</v>
+        <v>-1</v>
       </c>
       <c r="AD17" s="6">
         <v>-32676.530581037088</v>
@@ -5073,7 +6156,7 @@
         <v>1490.09</v>
       </c>
       <c r="U18" s="46">
-        <f t="shared" ref="U18" si="7">IFERROR((T18*-1)/R18-1,"")</f>
+        <f t="shared" ref="U18" si="8">IFERROR((T18*-1)/R18-1,"")</f>
         <v>-0.1434810823216397</v>
       </c>
       <c r="V18" s="51">
@@ -5088,22 +6171,23 @@
         <v>1921.23</v>
       </c>
       <c r="Y18" s="46">
-        <f t="shared" ref="Y18" si="8">IFERROR((X18*-1)/V18-1,"")</f>
+        <f t="shared" ref="Y18" si="9">IFERROR((X18*-1)/V18-1,"")</f>
         <v>-0.13935220618344279</v>
       </c>
-      <c r="Z18" s="6">
-        <v>-2079.363358190607</v>
+      <c r="Z18" s="51">
+        <f t="shared" si="7"/>
+        <v>-622.30693000000008</v>
       </c>
       <c r="AA18" s="15">
         <v>-8.5000000000000006E-4</v>
       </c>
       <c r="AB18" s="6">
-        <f>IFERROR(VLOOKUP($I18,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>1921.23</v>
+        <f>IFERROR(VLOOKUP($I18,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC18" s="46">
         <f t="shared" si="3"/>
-        <v>-7.6048929864864667E-2</v>
+        <v>-1</v>
       </c>
       <c r="AD18" s="6">
         <v>-2178.4353720691392</v>
@@ -5208,7 +6292,7 @@
         <v>5659.96</v>
       </c>
       <c r="Q19" s="46" t="str">
-        <f t="shared" ref="Q19" si="9">IFERROR((P19*-1)/N19-1,"")</f>
+        <f t="shared" ref="Q19" si="10">IFERROR((P19*-1)/N19-1,"")</f>
         <v/>
       </c>
       <c r="R19" s="51">
@@ -5239,15 +6323,15 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Z19" s="6">
+      <c r="Z19" s="51">
         <v>0</v>
       </c>
       <c r="AA19" s="15">
         <v>-8.5000000000000006E-4</v>
       </c>
       <c r="AB19" s="6">
-        <f>IFERROR(VLOOKUP($I19,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>5659.96</v>
+        <f>IFERROR(VLOOKUP($I19,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC19" s="46" t="str">
         <f t="shared" si="3"/>
@@ -5383,11 +6467,11 @@
       </c>
       <c r="AB21" s="48">
         <f>AB10-AB12</f>
-        <v>562787.81000000006</v>
+        <v>732125.8</v>
       </c>
       <c r="AC21" s="14">
         <f>AB21/Z21-1</f>
-        <v>-0.75053587280192335</v>
+        <v>-0.67547427209520827</v>
       </c>
       <c r="AD21" s="7">
         <v>2363474.2354378351</v>
@@ -5523,11 +6607,11 @@
       </c>
       <c r="AB23" s="7">
         <f>AB24+AB32+AB46</f>
-        <v>777827.44</v>
+        <v>366735.60000000003</v>
       </c>
       <c r="AC23" s="14">
         <f>IFERROR((AB23*-1)/Z23-1,"")</f>
-        <v>-0.43914362673940133</v>
+        <v>-0.73556345792898536</v>
       </c>
       <c r="AD23" s="7">
         <v>-1455440.7019585797</v>
@@ -5652,19 +6736,20 @@
         <f>IFERROR((X24*-1)/V24-1,"")</f>
         <v>2.6421111251235141E-2</v>
       </c>
-      <c r="Z24" s="8">
-        <v>-943174.75617692748</v>
+      <c r="Z24" s="52">
+        <f>SUM(Z25:Z31)</f>
+        <v>-282271.10219000006</v>
       </c>
       <c r="AA24" s="13">
         <v>-0.38554999999999995</v>
       </c>
       <c r="AB24" s="8">
         <f>SUM(AB25:AB31)</f>
-        <v>347524.36</v>
+        <v>318636.04000000004</v>
       </c>
       <c r="AC24" s="45">
         <f>IFERROR((AB24*-1)/Z24-1,"")</f>
-        <v>-0.63153767875567601</v>
+        <v>0.12882982894055628</v>
       </c>
       <c r="AD24" s="8">
         <v>-988112.6561191252</v>
@@ -5760,7 +6845,7 @@
         <v>-8.2750000000000004E-2</v>
       </c>
       <c r="N25" s="51">
-        <f t="shared" ref="N25:N31" si="10">P$10*$F25</f>
+        <f t="shared" ref="N25:N31" si="11">P$10*$F25</f>
         <v>-124607.76184500004</v>
       </c>
       <c r="O25" s="15">
@@ -5770,11 +6855,11 @@
         <v>561916.11</v>
       </c>
       <c r="Q25" s="46">
-        <f t="shared" ref="Q25:Q62" si="11">IFERROR((P25*-1)/N25-1,"")</f>
+        <f t="shared" ref="Q25:Q62" si="12">IFERROR((P25*-1)/N25-1,"")</f>
         <v>3.5094791984063489</v>
       </c>
       <c r="R25" s="51">
-        <f t="shared" ref="R25:R31" si="12">T$10*$F25</f>
+        <f t="shared" ref="R25:R31" si="13">T$10*$F25</f>
         <v>-169365.37083250002</v>
       </c>
       <c r="S25" s="15">
@@ -5784,11 +6869,11 @@
         <v>830151.62000000011</v>
       </c>
       <c r="U25" s="46">
-        <f t="shared" ref="U25:U31" si="13">IFERROR((T25*-1)/R25-1,"")</f>
+        <f t="shared" ref="U25:U31" si="14">IFERROR((T25*-1)/R25-1,"")</f>
         <v>3.9015428355836006</v>
       </c>
       <c r="V25" s="51">
-        <f t="shared" ref="V25:V31" si="14">X$10*$F25</f>
+        <f t="shared" ref="V25:V31" si="15">X$10*$F25</f>
         <v>-217321.64134999996</v>
       </c>
       <c r="W25" s="15">
@@ -5798,11 +6883,12 @@
         <v>1009819.8799999997</v>
       </c>
       <c r="Y25" s="46">
-        <f t="shared" ref="Y25:Y31" si="15">IFERROR((X25*-1)/V25-1,"")</f>
+        <f t="shared" ref="Y25:Y31" si="16">IFERROR((X25*-1)/V25-1,"")</f>
         <v>3.6466604693716107</v>
       </c>
-      <c r="Z25" s="6">
-        <v>-202432.1386944385</v>
+      <c r="Z25" s="51">
+        <f t="shared" ref="Z25:Z31" si="17">AB$10*$F25</f>
+        <v>-60583.409950000008</v>
       </c>
       <c r="AA25" s="15">
         <v>-8.2750000000000004E-2</v>
@@ -5811,8 +6897,8 @@
         <v>318043.45</v>
       </c>
       <c r="AC25" s="46">
-        <f t="shared" ref="AC25:AC31" si="16">IFERROR((AB25*-1)/Z25-1,"")</f>
-        <v>0.57111144530301683</v>
+        <f t="shared" ref="AC25:AC31" si="18">IFERROR((AB25*-1)/Z25-1,"")</f>
+        <v>4.2496789180814334</v>
       </c>
       <c r="AD25" s="6">
         <v>-212077.09063378972</v>
@@ -5907,7 +6993,7 @@
         <v>-8.2750000000000004E-2</v>
       </c>
       <c r="N26" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O26" s="15">
@@ -5918,11 +7004,11 @@
         <v>564</v>
       </c>
       <c r="Q26" s="46" t="str">
-        <f t="shared" ref="Q26" si="17">IFERROR((P26*-1)/N26-1,"")</f>
+        <f t="shared" ref="Q26" si="19">IFERROR((P26*-1)/N26-1,"")</f>
         <v/>
       </c>
       <c r="R26" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S26" s="15">
@@ -5933,11 +7019,11 @@
         <v>987.68</v>
       </c>
       <c r="U26" s="46" t="str">
-        <f t="shared" ref="U26" si="18">IFERROR((T26*-1)/R26-1,"")</f>
+        <f t="shared" ref="U26" si="20">IFERROR((T26*-1)/R26-1,"")</f>
         <v/>
       </c>
       <c r="V26" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="W26" s="15">
@@ -5948,21 +7034,22 @@
         <v>1534.3</v>
       </c>
       <c r="Y26" s="46" t="str">
-        <f t="shared" ref="Y26" si="19">IFERROR((X26*-1)/V26-1,"")</f>
+        <f t="shared" ref="Y26" si="21">IFERROR((X26*-1)/V26-1,"")</f>
         <v/>
       </c>
-      <c r="Z26" s="6">
+      <c r="Z26" s="51">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA26" s="15">
         <v>0</v>
       </c>
       <c r="AB26" s="6">
-        <f>IFERROR(VLOOKUP($I26,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>1534.3</v>
+        <f>IFERROR(VLOOKUP($I26,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC26" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD26" s="6">
@@ -6058,7 +7145,7 @@
         <v>-0.10491250000000001</v>
       </c>
       <c r="N27" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-157980.80742675005</v>
       </c>
       <c r="O27" s="15">
@@ -6069,11 +7156,11 @@
         <v/>
       </c>
       <c r="Q27" s="46" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R27" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-214725.61289987504</v>
       </c>
       <c r="S27" s="15">
@@ -6084,11 +7171,11 @@
         <v/>
       </c>
       <c r="U27" s="46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="V27" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-275525.76070249995</v>
       </c>
       <c r="W27" s="15">
@@ -6099,21 +7186,22 @@
         <v/>
       </c>
       <c r="Y27" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Z27" s="6">
-        <v>-256648.4803719671</v>
+      <c r="Z27" s="51">
+        <f t="shared" si="17"/>
+        <v>-76809.147992500002</v>
       </c>
       <c r="AA27" s="15">
         <v>-0.10491250000000001</v>
       </c>
       <c r="AB27" s="6" t="str">
-        <f>IFERROR(VLOOKUP($I27,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I27,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC27" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD27" s="6">
@@ -6209,7 +7297,7 @@
         <v>-7.4374999999999983E-2</v>
       </c>
       <c r="N28" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-111996.40226250001</v>
       </c>
       <c r="O28" s="15">
@@ -6220,11 +7308,11 @@
         <v/>
       </c>
       <c r="Q28" s="46" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R28" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-152224.16260624997</v>
       </c>
       <c r="S28" s="15">
@@ -6235,11 +7323,11 @@
         <v/>
       </c>
       <c r="U28" s="46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="V28" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-195326.85287499992</v>
       </c>
       <c r="W28" s="15">
@@ -6250,21 +7338,22 @@
         <v/>
       </c>
       <c r="Y28" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Z28" s="6">
-        <v>-181944.29384167804</v>
+      <c r="Z28" s="51">
+        <f t="shared" si="17"/>
+        <v>-54451.856374999988</v>
       </c>
       <c r="AA28" s="15">
         <v>-7.4374999999999983E-2</v>
       </c>
       <c r="AB28" s="6" t="str">
-        <f>IFERROR(VLOOKUP($I28,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I28,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC28" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD28" s="6">
@@ -6360,7 +7449,7 @@
         <v>-5.6737499999999989E-2</v>
       </c>
       <c r="N29" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-85437.255440250025</v>
       </c>
       <c r="O29" s="15">
@@ -6371,11 +7460,11 @@
         <v/>
       </c>
       <c r="Q29" s="46" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R29" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-116125.289759625</v>
       </c>
       <c r="S29" s="15">
@@ -6386,11 +7475,11 @@
         <v/>
       </c>
       <c r="U29" s="46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="V29" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-149006.48490749995</v>
       </c>
       <c r="W29" s="15">
@@ -6401,21 +7490,22 @@
         <v/>
       </c>
       <c r="Y29" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Z29" s="6">
-        <v>-138797.504159223</v>
+      <c r="Z29" s="51">
+        <f t="shared" si="17"/>
+        <v>-41538.987577499996</v>
       </c>
       <c r="AA29" s="15">
         <v>-5.6737499999999996E-2</v>
       </c>
       <c r="AB29" s="6" t="str">
-        <f>IFERROR(VLOOKUP($I29,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I29,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC29" s="46" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD29" s="6">
@@ -6511,7 +7601,7 @@
         <v>-6.1650000000000003E-2</v>
       </c>
       <c r="N30" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-92834.664867000029</v>
       </c>
       <c r="O30" s="15">
@@ -6522,11 +7612,11 @@
         <v>1</v>
       </c>
       <c r="Q30" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.99998922816168467</v>
       </c>
       <c r="R30" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-126179.75965950002</v>
       </c>
       <c r="S30" s="15">
@@ -6537,11 +7627,11 @@
         <v>2516.6800000000003</v>
       </c>
       <c r="U30" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.98005480429831737</v>
       </c>
       <c r="V30" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-161907.90560999999</v>
       </c>
       <c r="W30" s="15">
@@ -6552,22 +7642,23 @@
         <v>12217.75</v>
       </c>
       <c r="Y30" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.92453889169915004</v>
       </c>
-      <c r="Z30" s="6">
-        <v>-150815.00121464813</v>
+      <c r="Z30" s="51">
+        <f t="shared" si="17"/>
+        <v>-45135.555570000004</v>
       </c>
       <c r="AA30" s="15">
         <v>-6.1650000000000003E-2</v>
       </c>
       <c r="AB30" s="6">
-        <f>IFERROR(VLOOKUP($I30,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>12217.75</v>
+        <f>IFERROR(VLOOKUP($I30,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC30" s="46">
-        <f t="shared" si="16"/>
-        <v>-0.91898849649173142</v>
+        <f t="shared" si="18"/>
+        <v>-1</v>
       </c>
       <c r="AD30" s="6">
         <v>-158000.63610360285</v>
@@ -6662,7 +7753,7 @@
         <v>-5.1250000000000002E-3</v>
       </c>
       <c r="N31" s="51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7717.399147500003</v>
       </c>
       <c r="O31" s="15">
@@ -6673,11 +7764,11 @@
         <v>10391.839999999998</v>
       </c>
       <c r="Q31" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.34654691320020192</v>
       </c>
       <c r="R31" s="51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-10489.396078750002</v>
       </c>
       <c r="S31" s="15">
@@ -6688,11 +7779,11 @@
         <v>19083.350000000006</v>
       </c>
       <c r="U31" s="46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.81929921005272277</v>
       </c>
       <c r="V31" s="51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-13459.497424999998</v>
       </c>
       <c r="W31" s="15">
@@ -6703,22 +7794,23 @@
         <v>15728.859999999995</v>
       </c>
       <c r="Y31" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.16860678399364515</v>
       </c>
-      <c r="Z31" s="6">
-        <v>-12537.337894972778</v>
+      <c r="Z31" s="51">
+        <f t="shared" si="17"/>
+        <v>-3752.1447250000006</v>
       </c>
       <c r="AA31" s="15">
         <v>-5.1250000000000002E-3</v>
       </c>
       <c r="AB31" s="6">
-        <f>IFERROR(VLOOKUP($I31,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>15728.859999999995</v>
+        <f>IFERROR(VLOOKUP($I31,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>592.58999999999992</v>
       </c>
       <c r="AC31" s="46">
-        <f t="shared" si="16"/>
-        <v>0.25456138550010321</v>
+        <f t="shared" si="18"/>
+        <v>-0.84206632647945101</v>
       </c>
       <c r="AD31" s="6">
         <v>-13134.683861005104</v>
@@ -6847,11 +7939,11 @@
       </c>
       <c r="AB32" s="8">
         <f>SUM(AB33:AB45)</f>
-        <v>333045.58</v>
+        <v>29888.550000000003</v>
       </c>
       <c r="AC32" s="45">
         <f>(AB32*-1)/Z32-1</f>
-        <v>-4.7067973189426238E-2</v>
+        <v>-0.91448090519643233</v>
       </c>
       <c r="AD32" s="8">
         <v>-369175.10009796615</v>
@@ -6948,7 +8040,7 @@
         <v>4543.34</v>
       </c>
       <c r="Q33" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.1699074074074147E-2</v>
       </c>
       <c r="R33" s="6">
@@ -6962,7 +8054,7 @@
         <v>6905.72</v>
       </c>
       <c r="U33" s="46">
-        <f t="shared" ref="U33:U45" si="20">IFERROR((T33*-1)/R33-1,"")</f>
+        <f t="shared" ref="U33:U45" si="22">IFERROR((T33*-1)/R33-1,"")</f>
         <v>0.59854629629629641</v>
       </c>
       <c r="V33" s="6">
@@ -6976,7 +8068,7 @@
         <v>8155.15</v>
       </c>
       <c r="Y33" s="46">
-        <f t="shared" ref="Y33:Y45" si="21">IFERROR((X33*-1)/V33-1,"")</f>
+        <f t="shared" ref="Y33:Y45" si="23">IFERROR((X33*-1)/V33-1,"")</f>
         <v>0.88776620370370352</v>
       </c>
       <c r="Z33" s="6">
@@ -6986,12 +8078,12 @@
         <v>-1.7659251258496989E-3</v>
       </c>
       <c r="AB33" s="6">
-        <f>IFERROR(VLOOKUP($I33,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>8155.15</v>
+        <f>IFERROR(VLOOKUP($I33,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC33" s="46">
-        <f t="shared" ref="AC33:AC45" si="22">IFERROR((AB33*-1)/Z33-1,"")</f>
-        <v>0.88776620370370352</v>
+        <f t="shared" ref="AC33:AC45" si="24">IFERROR((AB33*-1)/Z33-1,"")</f>
+        <v>-1</v>
       </c>
       <c r="AD33" s="6">
         <v>-4320</v>
@@ -7068,7 +8160,7 @@
         <v>-19046.924444444445</v>
       </c>
       <c r="H34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>18</v>
@@ -7096,7 +8188,7 @@
         <v>14950.47</v>
       </c>
       <c r="Q34" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.21507170128137343</v>
       </c>
       <c r="R34" s="6">
@@ -7110,7 +8202,7 @@
         <v>21105.59</v>
       </c>
       <c r="U34" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.10808388312560457</v>
       </c>
       <c r="V34" s="6">
@@ -7124,7 +8216,7 @@
         <v>9382.1299999999992</v>
       </c>
       <c r="Y34" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.50742021225707368</v>
       </c>
       <c r="Z34" s="6">
@@ -7134,12 +8226,12 @@
         <v>-7.7859820478252927E-3</v>
       </c>
       <c r="AB34" s="6">
-        <f>IFERROR(VLOOKUP($I34,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>9382.1299999999992</v>
+        <f>IFERROR(VLOOKUP($I34,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>3881.96</v>
       </c>
       <c r="AC34" s="46">
-        <f t="shared" si="22"/>
-        <v>-0.50742021225707368</v>
+        <f t="shared" si="24"/>
+        <v>-0.79618966771654942</v>
       </c>
       <c r="AD34" s="6">
         <v>-19046.924444444445</v>
@@ -7235,7 +8327,7 @@
         <v>1899.2</v>
       </c>
       <c r="Q35" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.13437829017834746</v>
       </c>
       <c r="R35" s="6">
@@ -7249,7 +8341,7 @@
         <v>1694.1599999999999</v>
       </c>
       <c r="U35" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.2278318892631368</v>
       </c>
       <c r="V35" s="6">
@@ -7263,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="Y35" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="Z35" s="6">
@@ -7273,12 +8365,12 @@
         <v>-8.9687331108055895E-4</v>
       </c>
       <c r="AB35" s="6">
-        <f>IFERROR(VLOOKUP($I35,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($I35,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>1307.92</v>
       </c>
       <c r="AC35" s="46">
-        <f t="shared" si="22"/>
-        <v>-1</v>
+        <f t="shared" si="24"/>
+        <v>-0.40387323783175244</v>
       </c>
       <c r="AD35" s="6">
         <v>-2194.0299999999997</v>
@@ -7374,7 +8466,7 @@
         <v>185861.81</v>
       </c>
       <c r="Q36" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.10713196036011785</v>
       </c>
       <c r="R36" s="6">
@@ -7388,7 +8480,7 @@
         <v>205896.33000000002</v>
       </c>
       <c r="U36" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-1.0887430095799178E-2</v>
       </c>
       <c r="V36" s="6">
@@ -7402,7 +8494,7 @@
         <v>218151.71</v>
       </c>
       <c r="Y36" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>4.798661786295999E-2</v>
       </c>
       <c r="Z36" s="6">
@@ -7412,12 +8504,12 @@
         <v>-8.5092527478682636E-2</v>
       </c>
       <c r="AB36" s="6">
-        <f>IFERROR(VLOOKUP($I36,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>218151.71</v>
+        <f>IFERROR(VLOOKUP($I36,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>6766.4299999999994</v>
       </c>
       <c r="AC36" s="46">
-        <f t="shared" si="22"/>
-        <v>4.798661786295999E-2</v>
+        <f t="shared" si="24"/>
+        <v>-0.96749451062883496</v>
       </c>
       <c r="AD36" s="6">
         <v>-221693.26133550002</v>
@@ -7522,7 +8614,7 @@
         <v/>
       </c>
       <c r="Q37" s="46" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R37" s="6">
@@ -7536,7 +8628,7 @@
         <v/>
       </c>
       <c r="U37" s="46" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="V37" s="6">
@@ -7550,7 +8642,7 @@
         <v/>
       </c>
       <c r="Y37" s="46" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Z37" s="6">
@@ -7560,11 +8652,11 @@
         <v>-5.015717892170326E-5</v>
       </c>
       <c r="AB37" s="6" t="str">
-        <f>IFERROR(VLOOKUP($I37,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I37,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC37" s="46" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AD37" s="6">
@@ -7661,7 +8753,7 @@
         <v/>
       </c>
       <c r="Q38" s="46" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R38" s="6">
@@ -7675,7 +8767,7 @@
         <v/>
       </c>
       <c r="U38" s="46" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="V38" s="6">
@@ -7689,7 +8781,7 @@
         <v/>
       </c>
       <c r="Y38" s="46" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Z38" s="6">
@@ -7699,11 +8791,11 @@
         <v>-7.0910439565568858E-3</v>
       </c>
       <c r="AB38" s="6" t="str">
-        <f>IFERROR(VLOOKUP($I38,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I38,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC38" s="46" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AD38" s="6">
@@ -7809,7 +8901,7 @@
         <v>6816.55</v>
       </c>
       <c r="Q39" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.1282180813648629</v>
       </c>
       <c r="R39" s="6">
@@ -7823,7 +8915,7 @@
         <v>9992.25</v>
       </c>
       <c r="U39" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.27792840608254155</v>
       </c>
       <c r="V39" s="6">
@@ -7837,7 +8929,7 @@
         <v>8223.1</v>
       </c>
       <c r="Y39" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>5.1668350577432243E-2</v>
       </c>
       <c r="Z39" s="6">
@@ -7847,12 +8939,12 @@
         <v>-3.196283599891523E-3</v>
       </c>
       <c r="AB39" s="6">
-        <f>IFERROR(VLOOKUP($I39,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>8223.1</v>
+        <f>IFERROR(VLOOKUP($I39,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>1588.1</v>
       </c>
       <c r="AC39" s="46">
-        <f t="shared" si="22"/>
-        <v>5.1668350577432243E-2</v>
+        <f t="shared" si="24"/>
+        <v>-0.79689478328707908</v>
       </c>
       <c r="AD39" s="6">
         <v>-7819.0999999999995</v>
@@ -7948,7 +9040,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="R40" s="6">
@@ -7962,7 +9054,7 @@
         <v>30936.210000000003</v>
       </c>
       <c r="U40" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2.0936210000000002</v>
       </c>
       <c r="V40" s="6">
@@ -7976,7 +9068,7 @@
         <v>394.44</v>
       </c>
       <c r="Y40" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.96055599999999997</v>
       </c>
       <c r="Z40" s="6">
@@ -7986,12 +9078,12 @@
         <v>-4.0877896431705998E-3</v>
       </c>
       <c r="AB40" s="6">
-        <f>IFERROR(VLOOKUP($I40,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>394.44</v>
+        <f>IFERROR(VLOOKUP($I40,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC40" s="46">
-        <f t="shared" si="22"/>
-        <v>-0.96055599999999997</v>
+        <f t="shared" si="24"/>
+        <v>-1</v>
       </c>
       <c r="AD40" s="6">
         <v>-10000</v>
@@ -8096,7 +9188,7 @@
         <v>808</v>
       </c>
       <c r="Q41" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.37442497551508647</v>
       </c>
       <c r="R41" s="6">
@@ -8110,7 +9202,7 @@
         <v>570</v>
       </c>
       <c r="U41" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.55869088619257334</v>
       </c>
       <c r="V41" s="6">
@@ -8124,7 +9216,7 @@
         <v>349.9</v>
       </c>
       <c r="Y41" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.72909814224347613</v>
       </c>
       <c r="Z41" s="6">
@@ -8134,12 +9226,12 @@
         <v>-5.2798367939983163E-4</v>
       </c>
       <c r="AB41" s="6">
-        <f>IFERROR(VLOOKUP($I41,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>349.9</v>
+        <f>IFERROR(VLOOKUP($I41,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>420</v>
       </c>
       <c r="AC41" s="46">
-        <f t="shared" si="22"/>
-        <v>-0.72909814224347613</v>
+        <f t="shared" si="24"/>
+        <v>-0.67482486351031723</v>
       </c>
       <c r="AD41" s="6">
         <v>-1291.6116666666667</v>
@@ -8235,7 +9327,7 @@
         <v>1983.19</v>
       </c>
       <c r="Q42" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.2156631484184786E-2</v>
       </c>
       <c r="R42" s="6">
@@ -8249,7 +9341,7 @@
         <v>1883.98</v>
       </c>
       <c r="U42" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-2.8977228312176639E-2</v>
       </c>
       <c r="V42" s="6">
@@ -8263,7 +9355,7 @@
         <v>1980.53</v>
       </c>
       <c r="Y42" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2.0785639980724246E-2</v>
       </c>
       <c r="Z42" s="6">
@@ -8273,12 +9365,12 @@
         <v>-7.931136278662332E-4</v>
       </c>
       <c r="AB42" s="6">
-        <f>IFERROR(VLOOKUP($I42,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>1980.53</v>
+        <f>IFERROR(VLOOKUP($I42,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC42" s="46">
-        <f t="shared" si="22"/>
-        <v>2.0785639980724246E-2</v>
+        <f t="shared" si="24"/>
+        <v>-1</v>
       </c>
       <c r="AD42" s="6">
         <v>-1940.2016666666657</v>
@@ -8374,7 +9466,7 @@
         <v>34431.979999999996</v>
       </c>
       <c r="Q43" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.0676123892476639</v>
       </c>
       <c r="R43" s="6">
@@ -8388,7 +9480,7 @@
         <v>32736.5</v>
       </c>
       <c r="U43" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.96580019448797749</v>
       </c>
       <c r="V43" s="6">
@@ -8402,7 +9494,7 @@
         <v>35869.64</v>
       </c>
       <c r="Y43" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1.1539427027389531</v>
       </c>
       <c r="Z43" s="6">
@@ -8412,12 +9504,12 @@
         <v>-6.8074021982946114E-3</v>
       </c>
       <c r="AB43" s="6">
-        <f>IFERROR(VLOOKUP($I43,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>35869.64</v>
+        <f>IFERROR(VLOOKUP($I43,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC43" s="46">
-        <f t="shared" si="22"/>
-        <v>1.1539427027389531</v>
+        <f t="shared" si="24"/>
+        <v>-1</v>
       </c>
       <c r="AD43" s="6">
         <v>-17735.460906840002</v>
@@ -8513,7 +9605,7 @@
         <v>44369.08</v>
       </c>
       <c r="Q44" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.1841454047147868</v>
       </c>
       <c r="R44" s="6">
@@ -8527,7 +9619,7 @@
         <v>42800.44</v>
       </c>
       <c r="U44" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.14228071318519442</v>
       </c>
       <c r="V44" s="6">
@@ -8541,7 +9633,7 @@
         <v>44918.66</v>
       </c>
       <c r="Y44" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.19881288557134624</v>
       </c>
       <c r="Z44" s="6">
@@ -8551,12 +9643,12 @@
         <v>-1.5316654946162874E-2</v>
       </c>
       <c r="AB44" s="6">
-        <f>IFERROR(VLOOKUP($I44,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>44918.66</v>
+        <f>IFERROR(VLOOKUP($I44,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC44" s="46">
-        <f t="shared" si="22"/>
-        <v>0.19881288557134624</v>
+        <f t="shared" si="24"/>
+        <v>-1</v>
       </c>
       <c r="AD44" s="6">
         <v>-39904.787040390001</v>
@@ -8652,7 +9744,7 @@
         <v>2775.23</v>
       </c>
       <c r="Q45" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.8800117811892173</v>
       </c>
       <c r="R45" s="6">
@@ -8666,7 +9758,7 @@
         <v>5329.74</v>
       </c>
       <c r="U45" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.7695664830213782</v>
       </c>
       <c r="V45" s="6">
@@ -8680,7 +9772,7 @@
         <v>5620.32</v>
       </c>
       <c r="Y45" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-0.7570031363358648</v>
       </c>
       <c r="Z45" s="6">
@@ -8690,12 +9782,12 @@
         <v>-9.4547252754091822E-3</v>
       </c>
       <c r="AB45" s="6">
-        <f>IFERROR(VLOOKUP($I45,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>5620.32</v>
+        <f>IFERROR(VLOOKUP($I45,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>15924.140000000001</v>
       </c>
       <c r="AC45" s="46">
-        <f t="shared" si="22"/>
-        <v>-0.7570031363358648</v>
+        <f t="shared" si="24"/>
+        <v>-0.31151320982637953</v>
       </c>
       <c r="AD45" s="6">
         <v>-24632.584592833333</v>
@@ -8821,11 +9913,11 @@
       </c>
       <c r="AB46" s="8">
         <f>SUM(AB47:AB62)</f>
-        <v>97257.500000000015</v>
+        <v>18211.010000000002</v>
       </c>
       <c r="AC46" s="45">
         <f>(AB46*-1)/Z46-1</f>
-        <v>3.2607163390891758E-2</v>
+        <v>-0.80664915941101545</v>
       </c>
       <c r="AD46" s="6">
         <v>-98152.945741488365</v>
@@ -8921,7 +10013,7 @@
         <v>2679.9199999999996</v>
       </c>
       <c r="Q47" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.7702925714285721</v>
       </c>
       <c r="R47" s="6">
@@ -8935,7 +10027,7 @@
         <v>9080.0500000000011</v>
       </c>
       <c r="U47" s="46">
-        <f t="shared" ref="U47:U62" si="23">IFERROR((T47*-1)/R47-1,"")</f>
+        <f t="shared" ref="U47:U62" si="25">IFERROR((T47*-1)/R47-1,"")</f>
         <v>-0.22171000000000218</v>
       </c>
       <c r="V47" s="6">
@@ -8949,7 +10041,7 @@
         <v>50727.39</v>
       </c>
       <c r="Y47" s="46">
-        <f t="shared" ref="Y47:Y62" si="24">IFERROR((X47*-1)/V47-1,"")</f>
+        <f t="shared" ref="Y47:Y62" si="26">IFERROR((X47*-1)/V47-1,"")</f>
         <v>3.3480619999999872</v>
       </c>
       <c r="Z47" s="6">
@@ -8959,12 +10051,12 @@
         <v>-4.7690879170323797E-3</v>
       </c>
       <c r="AB47" s="6">
-        <f>IFERROR(VLOOKUP($I47,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>50727.39</v>
+        <f>IFERROR(VLOOKUP($I47,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>5803.26</v>
       </c>
       <c r="AC47" s="46">
-        <f t="shared" ref="AC47:AC62" si="25">IFERROR((AB47*-1)/Z47-1,"")</f>
-        <v>3.3480619999999872</v>
+        <f t="shared" ref="AC47:AC62" si="27">IFERROR((AB47*-1)/Z47-1,"")</f>
+        <v>-0.50257771428571574</v>
       </c>
       <c r="AD47" s="6">
         <v>-11666.666666666701</v>
@@ -9060,7 +10152,7 @@
         <v>36962.579999999994</v>
       </c>
       <c r="Q48" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.11904269448182936</v>
       </c>
       <c r="R48" s="6">
@@ -9074,7 +10166,7 @@
         <v>30986.82</v>
       </c>
       <c r="U48" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.26146753138507739</v>
       </c>
       <c r="V48" s="6">
@@ -9088,7 +10180,7 @@
         <v>28474.9</v>
       </c>
       <c r="Y48" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-0.3213360328499969</v>
       </c>
       <c r="Z48" s="6">
@@ -9098,12 +10190,12 @@
         <v>-1.7151257020337884E-2</v>
       </c>
       <c r="AB48" s="6">
-        <f>IFERROR(VLOOKUP($I48,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>28474.9</v>
+        <f>IFERROR(VLOOKUP($I48,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>595.26</v>
       </c>
       <c r="AC48" s="46">
-        <f t="shared" si="25"/>
-        <v>-0.3213360328499969</v>
+        <f t="shared" si="27"/>
+        <v>-0.98581271530064329</v>
       </c>
       <c r="AD48" s="6">
         <v>-44684.512465500004</v>
@@ -9208,7 +10300,7 @@
         <v>230</v>
       </c>
       <c r="Q49" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.117647058823529</v>
       </c>
       <c r="R49" s="6">
@@ -9222,7 +10314,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-1</v>
       </c>
       <c r="V49" s="6">
@@ -9236,7 +10328,7 @@
         <v>0</v>
       </c>
       <c r="Y49" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="Z49" s="6">
@@ -9246,11 +10338,11 @@
         <v>-1.1582070655650032E-5</v>
       </c>
       <c r="AB49" s="6">
-        <f>IFERROR(VLOOKUP($I49,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I49,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v>0</v>
       </c>
       <c r="AC49" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="AD49" s="6">
@@ -9347,7 +10439,7 @@
         <v/>
       </c>
       <c r="Q50" s="46" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R50" s="6">
@@ -9361,7 +10453,7 @@
         <v/>
       </c>
       <c r="U50" s="46" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="V50" s="6">
@@ -9375,7 +10467,7 @@
         <v/>
       </c>
       <c r="Y50" s="46" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z50" s="6">
@@ -9385,11 +10477,11 @@
         <v>-1.4292714183614904E-3</v>
       </c>
       <c r="AB50" s="6" t="str">
-        <f>IFERROR(VLOOKUP($I50,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I50,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC50" s="46" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD50" s="6">
@@ -9495,7 +10587,7 @@
         <v>3000.69</v>
       </c>
       <c r="Q51" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.1389219371178767</v>
       </c>
       <c r="R51" s="6">
@@ -9509,7 +10601,7 @@
         <v>2925.69</v>
       </c>
       <c r="U51" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.16044393862958217</v>
       </c>
       <c r="V51" s="6">
@@ -9523,7 +10615,7 @@
         <v>1589.46</v>
       </c>
       <c r="Y51" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-0.54388852636273</v>
       </c>
       <c r="Z51" s="6">
@@ -9533,12 +10625,12 @@
         <v>-1.4245153875258763E-3</v>
       </c>
       <c r="AB51" s="6">
-        <f>IFERROR(VLOOKUP($I51,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>1589.46</v>
+        <f>IFERROR(VLOOKUP($I51,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>429.46</v>
       </c>
       <c r="AC51" s="46">
-        <f t="shared" si="25"/>
-        <v>-0.54388852636273</v>
+        <f t="shared" si="27"/>
+        <v>-0.87676214974377342</v>
       </c>
       <c r="AD51" s="6">
         <v>-3484.8059999999996</v>
@@ -9634,7 +10726,7 @@
         <v/>
       </c>
       <c r="Q52" s="46" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R52" s="6">
@@ -9648,7 +10740,7 @@
         <v/>
       </c>
       <c r="U52" s="46" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="V52" s="6">
@@ -9662,7 +10754,7 @@
         <v/>
       </c>
       <c r="Y52" s="46" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z52" s="6">
@@ -9672,11 +10764,11 @@
         <v>-1.1616712401881651E-3</v>
       </c>
       <c r="AB52" s="6" t="str">
-        <f>IFERROR(VLOOKUP($I52,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($I52,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="AC52" s="46" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD52" s="6">
@@ -9774,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="R53" s="6">
@@ -9788,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-1</v>
       </c>
       <c r="V53" s="6">
@@ -9802,7 +10894,7 @@
         <v>0</v>
       </c>
       <c r="Y53" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="Z53" s="6">
@@ -9812,12 +10904,12 @@
         <v>-3.9878658963375403E-5</v>
       </c>
       <c r="AB53" s="6">
-        <f>IFERROR(VLOOKUP($I53,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($I53,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>225</v>
       </c>
       <c r="AC53" s="46">
-        <f t="shared" si="25"/>
-        <v>-1</v>
+        <f t="shared" si="27"/>
+        <v>1.3063781321184509</v>
       </c>
       <c r="AD53" s="6">
         <v>-97.555555555555557</v>
@@ -9913,7 +11005,7 @@
         <v>361.18</v>
       </c>
       <c r="Q54" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.27033532695817786</v>
       </c>
       <c r="R54" s="6">
@@ -9927,7 +11019,7 @@
         <v>243.78000000000003</v>
       </c>
       <c r="U54" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.50750967940047786</v>
       </c>
       <c r="V54" s="6">
@@ -9941,7 +11033,7 @@
         <v>272.03999999999996</v>
       </c>
       <c r="Y54" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-0.45041813595908609</v>
       </c>
       <c r="Z54" s="6">
@@ -9951,12 +11043,12 @@
         <v>-2.0234333905264079E-4</v>
       </c>
       <c r="AB54" s="6">
-        <f>IFERROR(VLOOKUP($I54,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>272.03999999999996</v>
+        <f>IFERROR(VLOOKUP($I54,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC54" s="46">
-        <f t="shared" si="25"/>
-        <v>-0.45041813595908609</v>
+        <f t="shared" si="27"/>
+        <v>-1</v>
       </c>
       <c r="AD54" s="6">
         <v>-494.99449999999968</v>
@@ -10052,7 +11144,7 @@
         <v>6497.95</v>
       </c>
       <c r="Q55" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.93588235838508771</v>
       </c>
       <c r="R55" s="6">
@@ -10066,7 +11158,7 @@
         <v>5251.66</v>
       </c>
       <c r="U55" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.56458513011590261</v>
       </c>
       <c r="V55" s="6">
@@ -10080,7 +11172,7 @@
         <v>5035.68</v>
       </c>
       <c r="Y55" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.5002399332824381</v>
       </c>
       <c r="Z55" s="6">
@@ -10090,12 +11182,12 @@
         <v>-1.3721005616270307E-3</v>
       </c>
       <c r="AB55" s="6">
-        <f>IFERROR(VLOOKUP($I55,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>5035.68</v>
+        <f>IFERROR(VLOOKUP($I55,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v>0</v>
       </c>
       <c r="AC55" s="46">
-        <f t="shared" si="25"/>
-        <v>0.5002399332824381</v>
+        <f t="shared" si="27"/>
+        <v>-1</v>
       </c>
       <c r="AD55" s="6">
         <v>-3574.7609972400005</v>
@@ -10191,7 +11283,7 @@
         <v>8026.6100000000006</v>
       </c>
       <c r="Q56" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.2801700477318478E-2</v>
       </c>
       <c r="R56" s="6">
@@ -10205,7 +11297,7 @@
         <v>8297.76</v>
       </c>
       <c r="U56" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9.8704613548269204E-2</v>
       </c>
       <c r="V56" s="6">
@@ -10219,7 +11311,7 @@
         <v>8006.02</v>
       </c>
       <c r="Y56" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>6.0075383014176698E-2</v>
       </c>
       <c r="Z56" s="6">
@@ -10233,7 +11325,7 @@
         <v>0</v>
       </c>
       <c r="AC56" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="AD56" s="6">
@@ -10330,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="R57" s="6">
@@ -10344,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-1</v>
       </c>
       <c r="V57" s="6">
@@ -10358,7 +11450,7 @@
         <v>1458.08</v>
       </c>
       <c r="Y57" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-0.68723622506141591</v>
       </c>
       <c r="Z57" s="6">
@@ -10372,7 +11464,7 @@
         <v>1316.22</v>
       </c>
       <c r="AC57" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-0.71766574135187144</v>
       </c>
       <c r="AD57" s="6">
@@ -10478,7 +11570,7 @@
         <v>2316.15</v>
       </c>
       <c r="Q58" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3.4835353408235736E-2</v>
       </c>
       <c r="R58" s="6">
@@ -10492,7 +11584,7 @@
         <v>2405.31</v>
       </c>
       <c r="U58" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>2.3185787162474103E-3</v>
       </c>
       <c r="V58" s="6">
@@ -10506,7 +11598,7 @@
         <v>2405.31</v>
       </c>
       <c r="Y58" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>2.3185787162474103E-3</v>
       </c>
       <c r="Z58" s="6">
@@ -10520,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="AC58" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="AD58" s="6">
@@ -10617,7 +11709,7 @@
         <v>2934.94</v>
       </c>
       <c r="Q59" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.17397600000000013</v>
       </c>
       <c r="R59" s="6">
@@ -10631,7 +11723,7 @@
         <v>1387.6999999999998</v>
       </c>
       <c r="U59" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.44492000000000009</v>
       </c>
       <c r="V59" s="6">
@@ -10645,7 +11737,7 @@
         <v>705.03</v>
       </c>
       <c r="Y59" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-0.71798800000000007</v>
       </c>
       <c r="Z59" s="6">
@@ -10659,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="AC59" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="AD59" s="6">
@@ -10756,7 +11848,7 @@
         <v>1649.3</v>
       </c>
       <c r="Q60" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.15420512820512822</v>
       </c>
       <c r="R60" s="6">
@@ -10770,7 +11862,7 @@
         <v>1675.48</v>
       </c>
       <c r="U60" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.14077948717948718</v>
       </c>
       <c r="V60" s="6">
@@ -10784,7 +11876,7 @@
         <v>2109.6999999999998</v>
       </c>
       <c r="Y60" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>8.1897435897435811E-2</v>
       </c>
       <c r="Z60" s="6">
@@ -10798,7 +11890,7 @@
         <v>1239.0999999999999</v>
       </c>
       <c r="AC60" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-0.36456410256410265</v>
       </c>
       <c r="AD60" s="6">
@@ -10895,7 +11987,7 @@
         <v>22729.919999999998</v>
       </c>
       <c r="Q61" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.2471314285714281</v>
       </c>
       <c r="R61" s="6">
@@ -10909,7 +12001,7 @@
         <v>3526.05</v>
       </c>
       <c r="U61" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.49627857142857146</v>
       </c>
       <c r="V61" s="6">
@@ -10923,7 +12015,7 @@
         <v>6703.59</v>
       </c>
       <c r="Y61" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-4.2344285714285723E-2</v>
       </c>
       <c r="Z61" s="6">
@@ -10937,7 +12029,7 @@
         <v>6172.05</v>
       </c>
       <c r="AC61" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-0.11827857142857146</v>
       </c>
       <c r="AD61" s="6">
@@ -11043,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="R62" s="6">
@@ -11057,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-1</v>
       </c>
       <c r="V62" s="6">
@@ -11071,7 +12163,7 @@
         <v>0</v>
       </c>
       <c r="Y62" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="Z62" s="6">
@@ -11085,7 +12177,7 @@
         <v>2430.6600000000003</v>
       </c>
       <c r="AC62" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2.4828448405562442</v>
       </c>
       <c r="AD62" s="6">
@@ -11218,11 +12310,11 @@
       </c>
       <c r="AB64" s="48">
         <f>AB21-AB23</f>
-        <v>-215039.62999999989</v>
+        <v>365390.2</v>
       </c>
       <c r="AC64" s="14">
         <f>AB64/Z64-1</f>
-        <v>-1.2474193536284657</v>
+        <v>-0.57959094746314488</v>
       </c>
       <c r="AD64" s="7">
         <v>908033.53347925539</v>
@@ -11318,7 +12410,7 @@
         <v>655078.40999999992</v>
       </c>
       <c r="Q66" s="14">
-        <f t="shared" ref="Q66:Q130" si="26">IFERROR((P66*-1)/N66-1,"")</f>
+        <f t="shared" ref="Q66:Q130" si="28">IFERROR((P66*-1)/N66-1,"")</f>
         <v>5.1628124241417161E-2</v>
       </c>
       <c r="R66" s="7">
@@ -11332,7 +12424,7 @@
         <v>570118.07999999996</v>
       </c>
       <c r="U66" s="14">
-        <f t="shared" ref="U66" si="27">IFERROR((T66*-1)/R66-1,"")</f>
+        <f t="shared" ref="U66" si="29">IFERROR((T66*-1)/R66-1,"")</f>
         <v>-0.16281843283634978</v>
       </c>
       <c r="V66" s="7">
@@ -11346,7 +12438,7 @@
         <v>659011.41999999993</v>
       </c>
       <c r="Y66" s="14">
-        <f t="shared" ref="Y66" si="28">IFERROR((X66*-1)/V66-1,"")</f>
+        <f t="shared" ref="Y66" si="30">IFERROR((X66*-1)/V66-1,"")</f>
         <v>-0.10505028577747111</v>
       </c>
       <c r="Z66" s="7">
@@ -11360,7 +12452,7 @@
         <v>207653.8</v>
       </c>
       <c r="AC66" s="14">
-        <f t="shared" ref="AC66" si="29">IFERROR((AB66*-1)/Z66-1,"")</f>
+        <f t="shared" ref="AC66" si="31">IFERROR((AB66*-1)/Z66-1,"")</f>
         <v>-0.70429528345102543</v>
       </c>
       <c r="AD66" s="7">
@@ -11592,7 +12684,7 @@
         <v>64498.680000000008</v>
       </c>
       <c r="Q68" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>9.3690140845070768E-3</v>
       </c>
       <c r="R68" s="6">
@@ -11606,7 +12698,7 @@
         <v>60318.180000000008</v>
       </c>
       <c r="U68" s="46">
-        <f t="shared" ref="U68:U84" si="30">IFERROR((T68*-1)/R68-1,"")</f>
+        <f t="shared" ref="U68:U84" si="32">IFERROR((T68*-1)/R68-1,"")</f>
         <v>-5.6053521126760431E-2</v>
       </c>
       <c r="V68" s="6">
@@ -11620,7 +12712,7 @@
         <v>59830.189999999995</v>
       </c>
       <c r="Y68" s="46">
-        <f t="shared" ref="Y68:Y84" si="31">IFERROR((X68*-1)/V68-1,"")</f>
+        <f t="shared" ref="Y68:Y84" si="33">IFERROR((X68*-1)/V68-1,"")</f>
         <v>-6.3690297339593194E-2</v>
       </c>
       <c r="Z68" s="6">
@@ -11634,7 +12726,7 @@
         <v>30930.639999999999</v>
       </c>
       <c r="AC68" s="46">
-        <f t="shared" ref="AC68:AC84" si="32">IFERROR((AB68*-1)/Z68-1,"")</f>
+        <f t="shared" ref="AC68:AC84" si="34">IFERROR((AB68*-1)/Z68-1,"")</f>
         <v>-0.5159524256651018</v>
       </c>
       <c r="AD68" s="6">
@@ -11731,7 +12823,7 @@
         <v>53990.009999999995</v>
       </c>
       <c r="Q69" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.10775179494599152</v>
       </c>
       <c r="R69" s="6">
@@ -11745,7 +12837,7 @@
         <v>71662.62000000001</v>
       </c>
       <c r="U69" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.18430880202592115</v>
       </c>
       <c r="V69" s="6">
@@ -11759,7 +12851,7 @@
         <v>74200.570000000007</v>
       </c>
       <c r="Y69" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.22625140088850371</v>
       </c>
       <c r="Z69" s="6">
@@ -11773,7 +12865,7 @@
         <v>5659.81</v>
       </c>
       <c r="AC69" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.90646500503617744</v>
       </c>
       <c r="AD69" s="6">
@@ -11868,7 +12960,7 @@
         <v/>
       </c>
       <c r="Q70" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R70" s="6">
@@ -11882,7 +12974,7 @@
         <v/>
       </c>
       <c r="U70" s="46" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V70" s="6">
@@ -11896,7 +12988,7 @@
         <v/>
       </c>
       <c r="Y70" s="46" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z70" s="6">
@@ -11910,7 +13002,7 @@
         <v/>
       </c>
       <c r="AC70" s="46" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AD70" s="6">
@@ -12007,7 +13099,7 @@
         <v/>
       </c>
       <c r="Q71" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R71" s="6">
@@ -12021,7 +13113,7 @@
         <v/>
       </c>
       <c r="U71" s="46" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V71" s="6">
@@ -12035,7 +13127,7 @@
         <v/>
       </c>
       <c r="Y71" s="46" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z71" s="6">
@@ -12049,7 +13141,7 @@
         <v/>
       </c>
       <c r="AC71" s="46" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AD71" s="6">
@@ -12146,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="R72" s="6">
@@ -12160,7 +13252,7 @@
         <v>297.89999999999998</v>
       </c>
       <c r="U72" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-0.95569167957979073</v>
       </c>
       <c r="V72" s="6">
@@ -12174,7 +13266,7 @@
         <v>1372.31</v>
       </c>
       <c r="Y72" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-0.79588871703303998</v>
       </c>
       <c r="Z72" s="6">
@@ -12188,7 +13280,7 @@
         <v>1529.83</v>
       </c>
       <c r="AC72" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.77245989315727182</v>
       </c>
       <c r="AD72" s="6">
@@ -12294,7 +13386,7 @@
         <v>2919.01</v>
       </c>
       <c r="Q73" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.36335814041405456</v>
       </c>
       <c r="R73" s="6">
@@ -12308,7 +13400,7 @@
         <v>4519.01</v>
       </c>
       <c r="U73" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-1.4394972991705002E-2</v>
       </c>
       <c r="V73" s="6">
@@ -12322,7 +13414,7 @@
         <v>4955.24</v>
       </c>
       <c r="Y73" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8.0747653586202173E-2</v>
       </c>
       <c r="Z73" s="6">
@@ -12336,7 +13428,7 @@
         <v>1980.24</v>
       </c>
       <c r="AC73" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.56810573583972901</v>
       </c>
       <c r="AD73" s="6">
@@ -12433,7 +13525,7 @@
         <v/>
       </c>
       <c r="Q74" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R74" s="6">
@@ -12447,7 +13539,7 @@
         <v/>
       </c>
       <c r="U74" s="46" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V74" s="6">
@@ -12461,7 +13553,7 @@
         <v/>
       </c>
       <c r="Y74" s="46" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z74" s="6">
@@ -12475,7 +13567,7 @@
         <v/>
       </c>
       <c r="AC74" s="46" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AD74" s="6">
@@ -12574,7 +13666,7 @@
         <v>879.73</v>
       </c>
       <c r="Q75" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.86804049999999999</v>
       </c>
       <c r="R75" s="6">
@@ -12588,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="V75" s="6">
@@ -12602,7 +13694,7 @@
         <v>11928.27</v>
       </c>
       <c r="Y75" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.78924050000000001</v>
       </c>
       <c r="Z75" s="6">
@@ -12616,7 +13708,7 @@
         <v>0</v>
       </c>
       <c r="AC75" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="AD75" s="6">
@@ -12711,7 +13803,7 @@
         <v/>
       </c>
       <c r="Q76" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R76" s="6">
@@ -12725,7 +13817,7 @@
         <v/>
       </c>
       <c r="U76" s="46" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V76" s="6">
@@ -12739,7 +13831,7 @@
         <v/>
       </c>
       <c r="Y76" s="46" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z76" s="6">
@@ -12753,7 +13845,7 @@
         <v/>
       </c>
       <c r="AC76" s="46" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AD76" s="6">
@@ -12859,7 +13951,7 @@
         <v>0</v>
       </c>
       <c r="Q77" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="R77" s="6">
@@ -12873,7 +13965,7 @@
         <v>75</v>
       </c>
       <c r="U77" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-0.75474968117458552</v>
       </c>
       <c r="V77" s="6">
@@ -12887,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="Y77" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-1</v>
       </c>
       <c r="Z77" s="6">
@@ -12901,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="AC77" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="AD77" s="6">
@@ -12998,7 +14090,7 @@
         <v>650.30000000000007</v>
       </c>
       <c r="Q78" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>6.8045251088355352E-2</v>
       </c>
       <c r="R78" s="6">
@@ -13012,7 +14104,7 @@
         <v>721.42000000000007</v>
       </c>
       <c r="U78" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.18485192225151659</v>
       </c>
       <c r="V78" s="6">
@@ -13026,7 +14118,7 @@
         <v>596.62</v>
       </c>
       <c r="Y78" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-2.0118164379002823E-2</v>
       </c>
       <c r="Z78" s="6">
@@ -13040,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="AC78" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="AD78" s="6">
@@ -13137,7 +14229,7 @@
         <v>22949.23</v>
       </c>
       <c r="Q79" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.1070162666175141</v>
       </c>
       <c r="R79" s="6">
@@ -13151,7 +14243,7 @@
         <v>17763.09</v>
       </c>
       <c r="U79" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.63086602798398461</v>
       </c>
       <c r="V79" s="6">
@@ -13165,7 +14257,7 @@
         <v>20718.489999999998</v>
       </c>
       <c r="Y79" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.90220741391986992</v>
       </c>
       <c r="Z79" s="6">
@@ -13179,7 +14271,7 @@
         <v>0</v>
       </c>
       <c r="AC79" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="AD79" s="6">
@@ -13276,7 +14368,7 @@
         <v>8774.5499999999993</v>
       </c>
       <c r="Q80" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.81262155898300659</v>
       </c>
       <c r="R80" s="6">
@@ -13290,7 +14382,7 @@
         <v>9673.7099999999991</v>
       </c>
       <c r="U80" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.99836747198995979</v>
       </c>
       <c r="V80" s="6">
@@ -13304,7 +14396,7 @@
         <v>9088.76</v>
       </c>
       <c r="Y80" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.87753016626748859</v>
       </c>
       <c r="Z80" s="6">
@@ -13318,7 +14410,7 @@
         <v>0</v>
       </c>
       <c r="AC80" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="AD80" s="6">
@@ -13424,7 +14516,7 @@
         <v/>
       </c>
       <c r="Q81" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R81" s="6">
@@ -13438,7 +14530,7 @@
         <v/>
       </c>
       <c r="U81" s="46" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V81" s="6">
@@ -13452,7 +14544,7 @@
         <v/>
       </c>
       <c r="Y81" s="46" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z81" s="6">
@@ -13466,7 +14558,7 @@
         <v/>
       </c>
       <c r="AC81" s="46" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="AD81" s="6">
@@ -13572,7 +14664,7 @@
         <v>2233.96</v>
       </c>
       <c r="Q82" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>7.0558786742213053E-2</v>
       </c>
       <c r="R82" s="6">
@@ -13586,7 +14678,7 @@
         <v>2457.64</v>
       </c>
       <c r="U82" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.17775076395688938</v>
       </c>
       <c r="V82" s="6">
@@ -13600,7 +14692,7 @@
         <v>1143.7600000000002</v>
       </c>
       <c r="Y82" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-0.45188708932824495</v>
       </c>
       <c r="Z82" s="6">
@@ -13614,7 +14706,7 @@
         <v>98</v>
       </c>
       <c r="AC82" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.95303641913877735</v>
       </c>
       <c r="AD82" s="6">
@@ -13711,7 +14803,7 @@
         <v>2231.33</v>
       </c>
       <c r="Q83" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.61748628571428577</v>
       </c>
       <c r="R83" s="6">
@@ -13725,7 +14817,7 @@
         <v>4424.49</v>
       </c>
       <c r="U83" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-0.24151599999999995</v>
       </c>
       <c r="V83" s="6">
@@ -13739,7 +14831,7 @@
         <v>1873.7600000000002</v>
       </c>
       <c r="Y83" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-0.67878399999999994</v>
       </c>
       <c r="Z83" s="6">
@@ -13753,7 +14845,7 @@
         <v>1197.0999999999999</v>
       </c>
       <c r="AC83" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.79478285714285712</v>
       </c>
       <c r="AD83" s="6">
@@ -13850,7 +14942,7 @@
         <v>3330.86</v>
       </c>
       <c r="Q84" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.33234399999999997</v>
       </c>
       <c r="R84" s="6">
@@ -13864,7 +14956,7 @@
         <v>369.46000000000004</v>
       </c>
       <c r="U84" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-0.85221599999999997</v>
       </c>
       <c r="V84" s="6">
@@ -13878,7 +14970,7 @@
         <v>1065.51</v>
       </c>
       <c r="Y84" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-0.57379599999999997</v>
       </c>
       <c r="Z84" s="6">
@@ -13892,7 +14984,7 @@
         <v>170.15</v>
       </c>
       <c r="AC84" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.93193999999999999</v>
       </c>
       <c r="AD84" s="6">
@@ -14123,7 +15215,7 @@
         <v>800</v>
       </c>
       <c r="Q86" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-5.8823529411764719E-2</v>
       </c>
       <c r="R86" s="6">
@@ -14137,7 +15229,7 @@
         <v>900</v>
       </c>
       <c r="U86" s="46">
-        <f t="shared" ref="U86:U100" si="33">IFERROR((T86*-1)/R86-1,"")</f>
+        <f t="shared" ref="U86:U100" si="35">IFERROR((T86*-1)/R86-1,"")</f>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="V86" s="6">
@@ -14151,7 +15243,7 @@
         <v>900</v>
       </c>
       <c r="Y86" s="46">
-        <f t="shared" ref="Y86:Y100" si="34">IFERROR((X86*-1)/V86-1,"")</f>
+        <f t="shared" ref="Y86:Y100" si="36">IFERROR((X86*-1)/V86-1,"")</f>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="Z86" s="6">
@@ -14165,7 +15257,7 @@
         <v>900</v>
       </c>
       <c r="AC86" s="46">
-        <f t="shared" ref="AC86:AC100" si="35">IFERROR((AB86*-1)/Z86-1,"")</f>
+        <f t="shared" ref="AC86:AC100" si="37">IFERROR((AB86*-1)/Z86-1,"")</f>
         <v>5.8823529411764719E-2</v>
       </c>
       <c r="AD86" s="6">
@@ -14271,7 +15363,7 @@
         <v>32.229999999999997</v>
       </c>
       <c r="Q87" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.0348612007746754E-2</v>
       </c>
       <c r="R87" s="6">
@@ -14285,7 +15377,7 @@
         <v>32.229999999999997</v>
       </c>
       <c r="U87" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>4.0348612007746754E-2</v>
       </c>
       <c r="V87" s="6">
@@ -14299,7 +15391,7 @@
         <v>32.229999999999997</v>
       </c>
       <c r="Y87" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>4.0348612007746754E-2</v>
       </c>
       <c r="Z87" s="6">
@@ -14313,7 +15405,7 @@
         <v>0</v>
       </c>
       <c r="AC87" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="AD87" s="6">
@@ -14419,7 +15511,7 @@
         <v>98.41</v>
       </c>
       <c r="Q88" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.64419886865408005</v>
       </c>
       <c r="R88" s="6">
@@ -14433,7 +15525,7 @@
         <v>91.95</v>
       </c>
       <c r="U88" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.53626751318710175</v>
       </c>
       <c r="V88" s="6">
@@ -14447,7 +15539,7 @@
         <v>0</v>
       </c>
       <c r="Y88" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-1</v>
       </c>
       <c r="Z88" s="6">
@@ -14461,7 +15553,7 @@
         <v>0</v>
       </c>
       <c r="AC88" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="AD88" s="6">
@@ -14567,7 +15659,7 @@
         <v>1996.0500000000002</v>
       </c>
       <c r="Q89" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.11781734503261687</v>
       </c>
       <c r="R89" s="6">
@@ -14581,7 +15673,7 @@
         <v>2146.02</v>
       </c>
       <c r="U89" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-5.1535972940004782E-2</v>
       </c>
       <c r="V89" s="6">
@@ -14595,7 +15687,7 @@
         <v>2146.02</v>
       </c>
       <c r="Y89" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-5.1535972940004782E-2</v>
       </c>
       <c r="Z89" s="6">
@@ -14609,7 +15701,7 @@
         <v>464.9</v>
       </c>
       <c r="AC89" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-0.79453084026234999</v>
       </c>
       <c r="AD89" s="6">
@@ -14715,7 +15807,7 @@
         <v>111.89</v>
       </c>
       <c r="Q90" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.72757264769974317</v>
       </c>
       <c r="R90" s="6">
@@ -14729,7 +15821,7 @@
         <v>373.27</v>
       </c>
       <c r="U90" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-9.1170276225606695E-2</v>
       </c>
       <c r="V90" s="6">
@@ -14743,7 +15835,7 @@
         <v>382.17</v>
       </c>
       <c r="Y90" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-6.9500748694350079E-2</v>
       </c>
       <c r="Z90" s="6">
@@ -14757,7 +15849,7 @@
         <v>388.82</v>
       </c>
       <c r="AC90" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-5.3309472505265298E-2</v>
       </c>
       <c r="AD90" s="6">
@@ -14863,7 +15955,7 @@
         <v>367.37</v>
       </c>
       <c r="Q91" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.45998370453123238</v>
       </c>
       <c r="R91" s="6">
@@ -14877,7 +15969,7 @@
         <v>577.9</v>
       </c>
       <c r="U91" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-0.15051469322100119</v>
       </c>
       <c r="V91" s="6">
@@ -14891,7 +15983,7 @@
         <v>427.23</v>
       </c>
       <c r="Y91" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.37199237304863864</v>
       </c>
       <c r="Z91" s="6">
@@ -14905,7 +15997,7 @@
         <v>448.1</v>
       </c>
       <c r="AC91" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-0.34131447314817542</v>
       </c>
       <c r="AD91" s="6">
@@ -15011,7 +16103,7 @@
         <v>15.99</v>
       </c>
       <c r="Q92" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.92880888070998191</v>
       </c>
       <c r="R92" s="6">
@@ -15025,7 +16117,7 @@
         <v>368.6</v>
       </c>
       <c r="U92" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.64109109257665242</v>
       </c>
       <c r="V92" s="6">
@@ -15039,7 +16131,7 @@
         <v>150.63</v>
       </c>
       <c r="Y92" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.32936095693211842</v>
       </c>
       <c r="Z92" s="6">
@@ -15053,7 +16145,7 @@
         <v>0</v>
       </c>
       <c r="AC92" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="AD92" s="6">
@@ -15150,7 +16242,7 @@
         <v>351</v>
       </c>
       <c r="Q93" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.36181818181818182</v>
       </c>
       <c r="R93" s="6">
@@ -15164,7 +16256,7 @@
         <v>617.44000000000005</v>
       </c>
       <c r="U93" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.12261818181818196</v>
       </c>
       <c r="V93" s="6">
@@ -15178,7 +16270,7 @@
         <v>351</v>
       </c>
       <c r="Y93" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.36181818181818182</v>
       </c>
       <c r="Z93" s="6">
@@ -15192,7 +16284,7 @@
         <v>0</v>
       </c>
       <c r="AC93" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="AD93" s="6">
@@ -15289,7 +16381,7 @@
         <v>432.21</v>
       </c>
       <c r="Q94" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3.7304000000000004E-2</v>
       </c>
       <c r="R94" s="6">
@@ -15303,7 +16395,7 @@
         <v>511.6699999999999</v>
       </c>
       <c r="U94" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.22800799999999977</v>
       </c>
       <c r="V94" s="6">
@@ -15317,7 +16409,7 @@
         <v>350.68</v>
       </c>
       <c r="Y94" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.15836800000000006</v>
       </c>
       <c r="Z94" s="6">
@@ -15331,7 +16423,7 @@
         <v>0</v>
       </c>
       <c r="AC94" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="AD94" s="6">
@@ -15437,7 +16529,7 @@
         <v>11212.419999999998</v>
       </c>
       <c r="Q95" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4.2445277011776139E-2</v>
       </c>
       <c r="R95" s="6">
@@ -15451,7 +16543,7 @@
         <v>11212.419999999998</v>
       </c>
       <c r="U95" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-4.2445277011776139E-2</v>
       </c>
       <c r="V95" s="6">
@@ -15465,7 +16557,7 @@
         <v>11212.419999999998</v>
       </c>
       <c r="Y95" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-4.2445277011776139E-2</v>
       </c>
       <c r="Z95" s="6">
@@ -15479,7 +16571,7 @@
         <v>1697.48</v>
       </c>
       <c r="AC95" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-0.8550330801755508</v>
       </c>
       <c r="AD95" s="6">
@@ -15585,7 +16677,7 @@
         <v>511.23</v>
       </c>
       <c r="Q96" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.38270665797290437</v>
       </c>
       <c r="R96" s="6">
@@ -15599,7 +16691,7 @@
         <v>981.08999999999992</v>
       </c>
       <c r="U96" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.18463377526624636</v>
       </c>
       <c r="V96" s="6">
@@ -15613,7 +16705,7 @@
         <v>780.64</v>
       </c>
       <c r="Y96" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-5.7402980028496198E-2</v>
       </c>
       <c r="Z96" s="6">
@@ -15627,7 +16719,7 @@
         <v>0</v>
       </c>
       <c r="AC96" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="AD96" s="6">
@@ -15724,7 +16816,7 @@
         <v>370</v>
       </c>
       <c r="Q97" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="R97" s="6">
@@ -15738,7 +16830,7 @@
         <v>370</v>
       </c>
       <c r="U97" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="V97" s="6">
@@ -15752,7 +16844,7 @@
         <v>370</v>
       </c>
       <c r="Y97" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Z97" s="6">
@@ -15766,7 +16858,7 @@
         <v>370</v>
       </c>
       <c r="AC97" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AD97" s="6">
@@ -15872,7 +16964,7 @@
         <v/>
       </c>
       <c r="Q98" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R98" s="6">
@@ -15886,7 +16978,7 @@
         <v/>
       </c>
       <c r="U98" s="46" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V98" s="6">
@@ -15900,7 +16992,7 @@
         <v/>
       </c>
       <c r="Y98" s="46" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Z98" s="6">
@@ -15914,7 +17006,7 @@
         <v/>
       </c>
       <c r="AC98" s="46" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD98" s="6">
@@ -16020,7 +17112,7 @@
         <v>295.60000000000002</v>
       </c>
       <c r="Q99" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.79836900503243802</v>
       </c>
       <c r="R99" s="6">
@@ -16034,7 +17126,7 @@
         <v>338.73</v>
       </c>
       <c r="U99" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-0.76894970593585155</v>
       </c>
       <c r="V99" s="6">
@@ -16048,7 +17140,7 @@
         <v>782.8</v>
       </c>
       <c r="Y99" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.46604620141878372</v>
       </c>
       <c r="Z99" s="6">
@@ -16062,7 +17154,7 @@
         <v>607.5</v>
       </c>
       <c r="AC99" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-0.58561965682410722</v>
       </c>
       <c r="AD99" s="6">
@@ -16159,7 +17251,7 @@
         <v>100</v>
       </c>
       <c r="Q100" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.76</v>
       </c>
       <c r="R100" s="6">
@@ -16173,7 +17265,7 @@
         <v>100</v>
       </c>
       <c r="U100" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-0.76</v>
       </c>
       <c r="V100" s="6">
@@ -16187,7 +17279,7 @@
         <v>100</v>
       </c>
       <c r="Y100" s="46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.76</v>
       </c>
       <c r="Z100" s="6">
@@ -16201,7 +17293,7 @@
         <v>0</v>
       </c>
       <c r="AC100" s="46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1</v>
       </c>
       <c r="AD100" s="6">
@@ -16441,7 +17533,7 @@
         <v>1955</v>
       </c>
       <c r="Q102" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.47881584115479836</v>
       </c>
       <c r="R102" s="6">
@@ -16455,7 +17547,7 @@
         <v>2415</v>
       </c>
       <c r="U102" s="46">
-        <f t="shared" ref="U102:U122" si="36">IFERROR((T102*-1)/R102-1,"")</f>
+        <f t="shared" ref="U102:U122" si="38">IFERROR((T102*-1)/R102-1,"")</f>
         <v>-0.35618427436769207</v>
       </c>
       <c r="V102" s="6">
@@ -16469,7 +17561,7 @@
         <v>3042.48</v>
       </c>
       <c r="Y102" s="46">
-        <f t="shared" ref="Y102:Y122" si="37">IFERROR((X102*-1)/V102-1,"")</f>
+        <f t="shared" ref="Y102:Y122" si="39">IFERROR((X102*-1)/V102-1,"")</f>
         <v>-0.18890415365557589</v>
       </c>
       <c r="Z102" s="6">
@@ -16483,7 +17575,7 @@
         <v>0</v>
       </c>
       <c r="AC102" s="46">
-        <f t="shared" ref="AC102:AC122" si="38">IFERROR((AB102*-1)/Z102-1,"")</f>
+        <f t="shared" ref="AC102:AC122" si="40">IFERROR((AB102*-1)/Z102-1,"")</f>
         <v>-1</v>
       </c>
       <c r="AD102" s="6">
@@ -16580,7 +17672,7 @@
         <v>41074.299999999996</v>
       </c>
       <c r="Q103" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-2.6897207494167796E-2</v>
       </c>
       <c r="R103" s="6">
@@ -16594,7 +17686,7 @@
         <v>47569.919999999998</v>
       </c>
       <c r="U103" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.17806731456713698</v>
       </c>
       <c r="V103" s="6">
@@ -16608,7 +17700,7 @@
         <v>69230.98000000001</v>
       </c>
       <c r="Y103" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-4.9170585598273697E-2</v>
       </c>
       <c r="Z103" s="6">
@@ -16622,7 +17714,7 @@
         <v>26021.809999999998</v>
       </c>
       <c r="AC103" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.59087813302094949</v>
       </c>
       <c r="AD103" s="6">
@@ -16728,7 +17820,7 @@
         <v>4450.1000000000004</v>
       </c>
       <c r="Q104" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.58587464102187092</v>
       </c>
       <c r="R104" s="6">
@@ -16742,7 +17834,7 @@
         <v>10141.98</v>
       </c>
       <c r="U104" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-5.6189499505852614E-2</v>
       </c>
       <c r="V104" s="6">
@@ -16756,7 +17848,7 @@
         <v>9958.6499999999978</v>
       </c>
       <c r="Y104" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-7.3250150291556571E-2</v>
       </c>
       <c r="Z104" s="6">
@@ -16770,7 +17862,7 @@
         <v>0</v>
       </c>
       <c r="AC104" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-1</v>
       </c>
       <c r="AD104" s="6">
@@ -16867,7 +17959,7 @@
         <v>4296.6099999999997</v>
       </c>
       <c r="Q105" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.78516950000000008</v>
       </c>
       <c r="R105" s="6">
@@ -16881,7 +17973,7 @@
         <v>4296.6099999999997</v>
       </c>
       <c r="U105" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.78516950000000008</v>
       </c>
       <c r="V105" s="6">
@@ -16895,7 +17987,7 @@
         <v>4296.6099999999997</v>
       </c>
       <c r="Y105" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.78516950000000008</v>
       </c>
       <c r="Z105" s="6">
@@ -16909,7 +18001,7 @@
         <v>610.55999999999995</v>
       </c>
       <c r="AC105" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.969472</v>
       </c>
       <c r="AD105" s="6">
@@ -17015,7 +18107,7 @@
         <v>260.32</v>
       </c>
       <c r="Q106" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.61253750257813611</v>
       </c>
       <c r="R106" s="6">
@@ -17029,7 +18121,7 @@
         <v>260.32</v>
       </c>
       <c r="U106" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.61253750257813611</v>
       </c>
       <c r="V106" s="6">
@@ -17043,7 +18135,7 @@
         <v>1564.33</v>
       </c>
       <c r="Y106" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1.3283620489856491</v>
       </c>
       <c r="Z106" s="6">
@@ -17057,7 +18149,7 @@
         <v>667.02</v>
       </c>
       <c r="AC106" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-7.2017707808404996E-3</v>
       </c>
       <c r="AD106" s="6">
@@ -17163,7 +18255,7 @@
         <v>11187.73</v>
       </c>
       <c r="Q107" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.29685421048834881</v>
       </c>
       <c r="R107" s="6">
@@ -17177,7 +18269,7 @@
         <v>18270.349999999999</v>
       </c>
       <c r="U107" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.14828653135213266</v>
       </c>
       <c r="V107" s="6">
@@ -17191,7 +18283,7 @@
         <v>22670.71</v>
       </c>
       <c r="Y107" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.42484796127004198</v>
       </c>
       <c r="Z107" s="6">
@@ -17205,7 +18297,7 @@
         <v>5157.8499999999995</v>
       </c>
       <c r="AC107" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.67583052947893185</v>
       </c>
       <c r="AD107" s="6">
@@ -17311,7 +18403,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-1</v>
       </c>
       <c r="R108" s="6">
@@ -17325,7 +18417,7 @@
         <v>2334.16</v>
       </c>
       <c r="U108" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.45597704529455263</v>
       </c>
       <c r="V108" s="6">
@@ -17339,7 +18431,7 @@
         <v>709</v>
       </c>
       <c r="Y108" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.55774765863786635</v>
       </c>
       <c r="Z108" s="6">
@@ -17353,7 +18445,7 @@
         <v>0</v>
       </c>
       <c r="AC108" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-1</v>
       </c>
       <c r="AD108" s="6">
@@ -17459,7 +18551,7 @@
         <v>9673.85</v>
       </c>
       <c r="Q109" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.49116690482243508</v>
       </c>
       <c r="R109" s="6">
@@ -17473,7 +18565,7 @@
         <v>18654.349999999999</v>
       </c>
       <c r="U109" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1.8803201514846046E-2</v>
       </c>
       <c r="V109" s="6">
@@ -17487,7 +18579,7 @@
         <v>19808.55</v>
       </c>
       <c r="Y109" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>4.1906356567400938E-2</v>
       </c>
       <c r="Z109" s="6">
@@ -17501,7 +18593,7 @@
         <v>6003</v>
       </c>
       <c r="AC109" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.68424928334107704</v>
       </c>
       <c r="AD109" s="6">
@@ -17598,7 +18690,7 @@
         <v/>
       </c>
       <c r="Q110" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R110" s="6">
@@ -17612,7 +18704,7 @@
         <v/>
       </c>
       <c r="U110" s="46" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="V110" s="6">
@@ -17626,7 +18718,7 @@
         <v/>
       </c>
       <c r="Y110" s="46" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z110" s="6">
@@ -17640,7 +18732,7 @@
         <v/>
       </c>
       <c r="AC110" s="46" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD110" s="6">
@@ -17746,7 +18838,7 @@
         <v>673.06999999999994</v>
       </c>
       <c r="Q111" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.37521156744011908</v>
       </c>
       <c r="R111" s="6">
@@ -17760,7 +18852,7 @@
         <v>1644.02</v>
       </c>
       <c r="U111" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.52608893413329283</v>
       </c>
       <c r="V111" s="6">
@@ -17774,7 +18866,7 @@
         <v>420.81</v>
       </c>
       <c r="Y111" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.60937611198608832</v>
       </c>
       <c r="Z111" s="6">
@@ -17788,7 +18880,7 @@
         <v>0</v>
       </c>
       <c r="AC111" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-1</v>
       </c>
       <c r="AD111" s="6">
@@ -17885,7 +18977,7 @@
         <v>119279.42999999996</v>
       </c>
       <c r="Q112" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.98799049999999933</v>
       </c>
       <c r="R112" s="6">
@@ -17899,7 +18991,7 @@
         <v>38472.950000000004</v>
       </c>
       <c r="U112" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.35878416666666657</v>
       </c>
       <c r="V112" s="6">
@@ -17913,7 +19005,7 @@
         <v>41728.47</v>
       </c>
       <c r="Y112" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.3045255</v>
       </c>
       <c r="Z112" s="6">
@@ -17927,7 +19019,7 @@
         <v>1333.77</v>
       </c>
       <c r="AC112" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.97777049999999999</v>
       </c>
       <c r="AD112" s="6">
@@ -18033,7 +19125,7 @@
         <v>1368</v>
       </c>
       <c r="Q113" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.43055994938310649</v>
       </c>
       <c r="R113" s="6">
@@ -18047,7 +19139,7 @@
         <v>0</v>
       </c>
       <c r="U113" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1</v>
       </c>
       <c r="V113" s="6">
@@ -18061,7 +19153,7 @@
         <v>0</v>
       </c>
       <c r="Y113" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-1</v>
       </c>
       <c r="Z113" s="6">
@@ -18075,7 +19167,7 @@
         <v>0</v>
       </c>
       <c r="AC113" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-1</v>
       </c>
       <c r="AD113" s="6">
@@ -18172,7 +19264,7 @@
         <v>738.16</v>
       </c>
       <c r="Q114" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.85236800000000001</v>
       </c>
       <c r="R114" s="6">
@@ -18186,7 +19278,7 @@
         <v>1807.69</v>
       </c>
       <c r="U114" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.63846199999999997</v>
       </c>
       <c r="V114" s="6">
@@ -18200,7 +19292,7 @@
         <v>2500</v>
       </c>
       <c r="Y114" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.5</v>
       </c>
       <c r="Z114" s="6">
@@ -18214,7 +19306,7 @@
         <v>118.65</v>
       </c>
       <c r="AC114" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.97626999999999997</v>
       </c>
       <c r="AD114" s="6">
@@ -18320,7 +19412,7 @@
         <v>13677.889999999998</v>
       </c>
       <c r="Q115" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.20938523571989009</v>
       </c>
       <c r="R115" s="6">
@@ -18334,7 +19426,7 @@
         <v>10422.07</v>
       </c>
       <c r="U115" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.39757942077609876</v>
       </c>
       <c r="V115" s="6">
@@ -18348,7 +19440,7 @@
         <v>13862.09</v>
       </c>
       <c r="Y115" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.19873803504928966</v>
       </c>
       <c r="Z115" s="6">
@@ -18362,7 +19454,7 @@
         <v>25253.83</v>
       </c>
       <c r="AC115" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.45973178996321606</v>
       </c>
       <c r="AD115" s="6">
@@ -18459,7 +19551,7 @@
         <v>7224.44</v>
       </c>
       <c r="Q116" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-2.7927711668984778E-2</v>
       </c>
       <c r="R116" s="6">
@@ -18473,7 +19565,7 @@
         <v>5041.3999999999996</v>
       </c>
       <c r="U116" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.50527846763235718</v>
       </c>
       <c r="V116" s="6">
@@ -18487,7 +19579,7 @@
         <v>10515.810000000001</v>
       </c>
       <c r="Y116" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.17974160169837938</v>
       </c>
       <c r="Z116" s="6">
@@ -18501,7 +19593,7 @@
         <v>8548.01</v>
       </c>
       <c r="AC116" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.23671621138158483</v>
       </c>
       <c r="AD116" s="6">
@@ -18598,7 +19690,7 @@
         <v>117100.21999999996</v>
       </c>
       <c r="Q117" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.76172809604733427</v>
       </c>
       <c r="R117" s="6">
@@ -18612,7 +19704,7 @@
         <v>78726.199999999983</v>
       </c>
       <c r="U117" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.13619494584498903</v>
       </c>
       <c r="V117" s="6">
@@ -18626,7 +19718,7 @@
         <v>88339.049999999988</v>
       </c>
       <c r="Y117" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.22954465025216664</v>
       </c>
       <c r="Z117" s="6">
@@ -18640,7 +19732,7 @@
         <v>54220.92</v>
       </c>
       <c r="AC117" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.4586542958897426</v>
       </c>
       <c r="AD117" s="6">
@@ -18746,7 +19838,7 @@
         <v/>
       </c>
       <c r="Q118" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R118" s="6">
@@ -18760,7 +19852,7 @@
         <v/>
       </c>
       <c r="U118" s="46" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="V118" s="6">
@@ -18774,7 +19866,7 @@
         <v/>
       </c>
       <c r="Y118" s="46" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z118" s="6">
@@ -18788,7 +19880,7 @@
         <v/>
       </c>
       <c r="AC118" s="46" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD118" s="6">
@@ -18885,7 +19977,7 @@
         <v>35699.840000000004</v>
       </c>
       <c r="Q119" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4.6055582277741092E-2</v>
       </c>
       <c r="R119" s="6">
@@ -18899,7 +19991,7 @@
         <v>45445.030000000006</v>
       </c>
       <c r="U119" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.11435744165914097</v>
       </c>
       <c r="V119" s="6">
@@ -18913,7 +20005,7 @@
         <v>61558.19</v>
       </c>
       <c r="Y119" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-4.6421997506404411E-2</v>
       </c>
       <c r="Z119" s="6">
@@ -18927,7 +20019,7 @@
         <v>0</v>
       </c>
       <c r="AC119" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-1</v>
       </c>
       <c r="AD119" s="6">
@@ -19033,7 +20125,7 @@
         <v>7122.33</v>
       </c>
       <c r="Q120" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-2.7549662484435133E-2</v>
       </c>
       <c r="R120" s="6">
@@ -19047,7 +20139,7 @@
         <v>4005.16</v>
       </c>
       <c r="U120" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.45315378621829661</v>
       </c>
       <c r="V120" s="6">
@@ -19061,7 +20153,7 @@
         <v>4874.22</v>
       </c>
       <c r="Y120" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.33449631172311345</v>
       </c>
       <c r="Z120" s="6">
@@ -19075,7 +20167,7 @@
         <v>2254.29</v>
       </c>
       <c r="AC120" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.69220956184872606</v>
       </c>
       <c r="AD120" s="6">
@@ -19181,7 +20273,7 @@
         <v>1965</v>
       </c>
       <c r="Q121" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.33373161950899632</v>
       </c>
       <c r="R121" s="6">
@@ -19195,7 +20287,7 @@
         <v>1965</v>
       </c>
       <c r="U121" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.51408032370538925</v>
       </c>
       <c r="V121" s="6">
@@ -19209,7 +20301,7 @@
         <v>7759.59</v>
       </c>
       <c r="Y121" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.52524287238846901</v>
       </c>
       <c r="Z121" s="6">
@@ -19223,7 +20315,7 @@
         <v>2280.7200000000003</v>
       </c>
       <c r="AC121" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.48680163697401568</v>
       </c>
       <c r="AD121" s="6">
@@ -19329,7 +20421,7 @@
         <v>24000</v>
       </c>
       <c r="Q122" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="R122" s="6">
@@ -19343,7 +20435,7 @@
         <v>24000</v>
       </c>
       <c r="U122" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="V122" s="6">
@@ -19357,7 +20449,7 @@
         <v>24000</v>
       </c>
       <c r="Y122" s="46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Z122" s="6">
@@ -19371,7 +20463,7 @@
         <v>0</v>
       </c>
       <c r="AC122" s="46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-1</v>
       </c>
       <c r="AD122" s="6">
@@ -19603,7 +20695,7 @@
         <v>11823</v>
       </c>
       <c r="Q124" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-8.3034509716628624E-2</v>
       </c>
       <c r="R124" s="6">
@@ -19617,7 +20709,7 @@
         <v>11880</v>
       </c>
       <c r="U124" s="46">
-        <f t="shared" ref="U124:U130" si="39">IFERROR((T124*-1)/R124-1,"")</f>
+        <f t="shared" ref="U124:U130" si="41">IFERROR((T124*-1)/R124-1,"")</f>
         <v>-7.861371694439212E-2</v>
       </c>
       <c r="V124" s="6">
@@ -19631,7 +20723,7 @@
         <v>12244</v>
       </c>
       <c r="Y124" s="46">
-        <f t="shared" ref="Y124:Y130" si="40">IFERROR((X124*-1)/V124-1,"")</f>
+        <f t="shared" ref="Y124:Y130" si="42">IFERROR((X124*-1)/V124-1,"")</f>
         <v>-5.0382689416425652E-2</v>
       </c>
       <c r="Z124" s="6">
@@ -19645,7 +20737,7 @@
         <v>6748</v>
       </c>
       <c r="AC124" s="46">
-        <f t="shared" ref="AC124:AC130" si="41">IFERROR((AB124*-1)/Z124-1,"")</f>
+        <f t="shared" ref="AC124:AC130" si="43">IFERROR((AB124*-1)/Z124-1,"")</f>
         <v>-0.47664018198154523</v>
       </c>
       <c r="AD124" s="6">
@@ -19743,7 +20835,7 @@
         <v>16033.429999999998</v>
       </c>
       <c r="Q125" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.22904742528484257</v>
       </c>
       <c r="R125" s="6">
@@ -19757,7 +20849,7 @@
         <v>14452.9</v>
       </c>
       <c r="U125" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-0.30504574086139402</v>
       </c>
       <c r="V125" s="6">
@@ -19771,7 +20863,7 @@
         <v>20130.41</v>
       </c>
       <c r="Y125" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>-3.204795108895897E-2</v>
       </c>
       <c r="Z125" s="6">
@@ -19785,7 +20877,7 @@
         <v>5008.41</v>
       </c>
       <c r="AC125" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.75917526164213511</v>
       </c>
       <c r="AD125" s="6">
@@ -19883,7 +20975,7 @@
         <v>6035.41</v>
       </c>
       <c r="Q126" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.3527434414105421E-2</v>
       </c>
       <c r="R126" s="6">
@@ -19897,7 +20989,7 @@
         <v>6035.41</v>
       </c>
       <c r="U126" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>1.3527434414105421E-2</v>
       </c>
       <c r="V126" s="6">
@@ -19911,7 +21003,7 @@
         <v>6035.41</v>
       </c>
       <c r="Y126" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1.3527434414105421E-2</v>
       </c>
       <c r="Z126" s="6">
@@ -19925,7 +21017,7 @@
         <v>0</v>
       </c>
       <c r="AC126" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-1</v>
       </c>
       <c r="AD126" s="6">
@@ -20023,7 +21115,7 @@
         <v>8966</v>
       </c>
       <c r="Q127" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.12568709922475041</v>
       </c>
       <c r="R127" s="6">
@@ -20037,7 +21129,7 @@
         <v>9436</v>
       </c>
       <c r="U127" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-7.9855394633587484E-2</v>
       </c>
       <c r="V127" s="6">
@@ -20051,7 +21143,7 @@
         <v>9436</v>
       </c>
       <c r="Y127" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>-7.9855394633587484E-2</v>
       </c>
       <c r="Z127" s="6">
@@ -20065,7 +21157,7 @@
         <v>4718</v>
       </c>
       <c r="AC127" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.53992769731679369</v>
       </c>
       <c r="AD127" s="6">
@@ -20163,7 +21255,7 @@
         <v>23441.37</v>
       </c>
       <c r="Q128" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.99189061116624089</v>
       </c>
       <c r="R128" s="6">
@@ -20177,7 +21269,7 @@
         <v>11505.72</v>
       </c>
       <c r="U128" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-2.2320980270878366E-2</v>
       </c>
       <c r="V128" s="6">
@@ -20191,7 +21283,7 @@
         <v>10818.33</v>
       </c>
       <c r="Y128" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>-8.073077829930253E-2</v>
       </c>
       <c r="Z128" s="6">
@@ -20205,7 +21297,7 @@
         <v>6648.3899999999994</v>
       </c>
       <c r="AC128" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.43506434903883506</v>
       </c>
       <c r="AD128" s="6">
@@ -20303,7 +21395,7 @@
         <v>1195</v>
       </c>
       <c r="Q129" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.10765623483202291</v>
       </c>
       <c r="R129" s="6">
@@ -20317,7 +21409,7 @@
         <v>1082</v>
       </c>
       <c r="U129" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-0.19203685865125419</v>
       </c>
       <c r="V129" s="6">
@@ -20331,7 +21423,7 @@
         <v>978.5</v>
       </c>
       <c r="Y129" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>-0.26932353622019611</v>
       </c>
       <c r="Z129" s="6">
@@ -20345,7 +21437,7 @@
         <v>418</v>
       </c>
       <c r="AC129" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.68786636498726828</v>
       </c>
       <c r="AD129" s="6">
@@ -20443,7 +21535,7 @@
         <v>6685.8499999999995</v>
       </c>
       <c r="Q130" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-0.14231778898471237</v>
       </c>
       <c r="R130" s="6">
@@ -20457,7 +21549,7 @@
         <v>9350</v>
       </c>
       <c r="U130" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.1994478896464833</v>
       </c>
       <c r="V130" s="6">
@@ -20471,7 +21563,7 @@
         <v>7769.93</v>
       </c>
       <c r="Y130" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>-3.248541048032072E-3</v>
       </c>
       <c r="Z130" s="6">
@@ -20485,7 +21577,7 @@
         <v>5200</v>
       </c>
       <c r="AC130" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.33292737688110019</v>
       </c>
       <c r="AD130" s="6">
@@ -20626,11 +21718,11 @@
       </c>
       <c r="AB132" s="48">
         <f>AB64-AB66</f>
-        <v>-422693.42999999988</v>
+        <v>157736.40000000002</v>
       </c>
       <c r="AC132" s="14">
         <f>AB132/Z132-1</f>
-        <v>-3.5326672888650004</v>
+        <v>-5.4885190566303699E-2</v>
       </c>
       <c r="AD132" s="7">
         <v>188844.62866006279</v>
@@ -20726,7 +21818,7 @@
         <v>46089.81</v>
       </c>
       <c r="Q134" s="14">
-        <f t="shared" ref="Q134" si="42">IFERROR((P134*-1)/N134-1,"")</f>
+        <f t="shared" ref="Q134" si="44">IFERROR((P134*-1)/N134-1,"")</f>
         <v>-0.3443740875346758</v>
       </c>
       <c r="R134" s="7">
@@ -20740,7 +21832,7 @@
         <v>50627.689999999988</v>
       </c>
       <c r="U134" s="14">
-        <f t="shared" ref="U134" si="43">IFERROR((T134*-1)/R134-1,"")</f>
+        <f t="shared" ref="U134" si="45">IFERROR((T134*-1)/R134-1,"")</f>
         <v>-0.27982290549122324</v>
       </c>
       <c r="V134" s="7">
@@ -20754,7 +21846,7 @@
         <v>52086.069999999992</v>
       </c>
       <c r="Y134" s="14">
-        <f t="shared" ref="Y134" si="44">IFERROR((X134*-1)/V134-1,"")</f>
+        <f t="shared" ref="Y134" si="46">IFERROR((X134*-1)/V134-1,"")</f>
         <v>-0.25907750171930088</v>
       </c>
       <c r="Z134" s="7">
@@ -20768,7 +21860,7 @@
         <v>22944.799999999996</v>
       </c>
       <c r="AC134" s="14">
-        <f t="shared" ref="AC134" si="45">IFERROR((AB134*-1)/Z134-1,"")</f>
+        <f t="shared" ref="AC134" si="47">IFERROR((AB134*-1)/Z134-1,"")</f>
         <v>-0.67361103384165899</v>
       </c>
       <c r="AD134" s="7">
@@ -22718,7 +23810,7 @@
         <v>-290070.51999999938</v>
       </c>
       <c r="Q151" s="14">
-        <f t="shared" ref="Q151" si="46">IFERROR((P151*-1)/N151-1,"")</f>
+        <f t="shared" ref="Q151" si="48">IFERROR((P151*-1)/N151-1,"")</f>
         <v>-2.0918188286927273</v>
       </c>
       <c r="R151" s="7">
@@ -22746,7 +23838,7 @@
         <v>265974.34999999969</v>
       </c>
       <c r="Y151" s="14">
-        <f t="shared" ref="Y151" si="47">IFERROR((X151*-1)/V151-1,"")</f>
+        <f t="shared" ref="Y151" si="49">IFERROR((X151*-1)/V151-1,"")</f>
         <v>-2.0533547330684199</v>
       </c>
       <c r="Z151" s="7">
@@ -22757,11 +23849,11 @@
       </c>
       <c r="AB151" s="48">
         <f>AB132-AB134</f>
-        <v>-445638.22999999986</v>
+        <v>134791.60000000003</v>
       </c>
       <c r="AC151" s="14">
-        <f t="shared" ref="AC151" si="48">IFERROR((AB151*-1)/Z151-1,"")</f>
-        <v>3.6133466289569975</v>
+        <f t="shared" ref="AC151" si="50">IFERROR((AB151*-1)/Z151-1,"")</f>
+        <v>-2.3953927908557584</v>
       </c>
       <c r="AD151" s="7">
         <v>118545.68360053898</v>
@@ -23240,11 +24332,11 @@
       </c>
       <c r="AB157" s="48">
         <f>AB151-AB153</f>
-        <v>-445638.22999999986</v>
+        <v>134791.60000000003</v>
       </c>
       <c r="AC157" s="50">
         <f>AB157/Z157-1</f>
-        <v>-5.6133466289569975</v>
+        <v>0.3953927908557584</v>
       </c>
       <c r="AD157" s="7">
         <v>118545.68360053898</v>
@@ -23439,7 +24531,7 @@
       </c>
       <c r="AT159" s="16"/>
       <c r="AU159" s="7">
-        <f t="shared" ref="AU159:AU164" si="49">N159+R159+V159+Z159+AD159+AF159+AH159+AJ159+AL159+AN159+AP159+AR159</f>
+        <f t="shared" ref="AU159:AU164" si="51">N159+R159+V159+Z159+AD159+AF159+AH159+AJ159+AL159+AN159+AP159+AR159</f>
         <v>-507582</v>
       </c>
       <c r="AV159" s="14">
@@ -23555,7 +24647,7 @@
       </c>
       <c r="AT160" s="6"/>
       <c r="AU160" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-19530</v>
       </c>
       <c r="AV160" s="15">
@@ -23671,7 +24763,7 @@
       </c>
       <c r="AT161" s="6"/>
       <c r="AU161" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-18096</v>
       </c>
       <c r="AV161" s="15">
@@ -23716,7 +24808,7 @@
       </c>
       <c r="AC162" s="6"/>
       <c r="AU162" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-27000</v>
       </c>
     </row>
@@ -23780,7 +24872,7 @@
         <v>-36540</v>
       </c>
       <c r="AU163" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-438480</v>
       </c>
     </row>
@@ -23844,8 +24936,14 @@
         <v>-373</v>
       </c>
       <c r="AU164" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-4476</v>
+      </c>
+    </row>
+    <row r="165" spans="9:49" x14ac:dyDescent="0.25">
+      <c r="AB165" s="15" t="str">
+        <f>IFERROR(VLOOKUP($I165,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="166" spans="9:49" x14ac:dyDescent="0.25">
@@ -23904,7 +25002,7 @@
       <c r="AA166" s="14"/>
       <c r="AB166" s="7">
         <f>AB157+AB159</f>
-        <v>-439421.85999999987</v>
+        <v>141007.97000000003</v>
       </c>
       <c r="AC166" s="50"/>
       <c r="AD166" s="7">

--- a/orcamento.xlsx
+++ b/orcamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e87dc3a59766ad95/Documentos/Karams Estofados/Relatórios/Financeiro/Orçamento 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="912" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5134468F-250C-42FC-B3A1-D3BF6784E194}"/>
+  <xr:revisionPtr revIDLastSave="914" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75149217-7FBE-40ED-8486-D8EF6A60CE9F}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Acompanhamento Orçamento" sheetId="21" r:id="rId1"/>
@@ -1069,40 +1069,23 @@
           <cell r="D5">
             <v>169337.99</v>
           </cell>
-          <cell r="E5"/>
           <cell r="F5">
             <v>420937.66000000003</v>
           </cell>
-          <cell r="G5"/>
-          <cell r="H5"/>
-          <cell r="I5"/>
-          <cell r="J5"/>
-          <cell r="K5"/>
-          <cell r="L5"/>
-          <cell r="M5"/>
         </row>
         <row r="6">
           <cell r="A6" t="str">
             <v>COFINS</v>
           </cell>
-          <cell r="B6"/>
           <cell r="C6">
             <v>2460.61</v>
           </cell>
           <cell r="D6">
             <v>15906.25</v>
           </cell>
-          <cell r="E6"/>
           <cell r="F6">
             <v>18366.86</v>
           </cell>
-          <cell r="G6"/>
-          <cell r="H6"/>
-          <cell r="I6"/>
-          <cell r="J6"/>
-          <cell r="K6"/>
-          <cell r="L6"/>
-          <cell r="M6"/>
         </row>
         <row r="7">
           <cell r="A7" t="str">
@@ -1117,17 +1100,9 @@
           <cell r="D7">
             <v>39057.060000000005</v>
           </cell>
-          <cell r="E7"/>
           <cell r="F7">
             <v>118711.39000000001</v>
           </cell>
-          <cell r="G7"/>
-          <cell r="H7"/>
-          <cell r="I7"/>
-          <cell r="J7"/>
-          <cell r="K7"/>
-          <cell r="L7"/>
-          <cell r="M7"/>
         </row>
         <row r="8">
           <cell r="A8" t="str">
@@ -1142,17 +1117,9 @@
           <cell r="D8">
             <v>5659.96</v>
           </cell>
-          <cell r="E8"/>
           <cell r="F8">
             <v>16979.88</v>
           </cell>
-          <cell r="G8"/>
-          <cell r="H8"/>
-          <cell r="I8"/>
-          <cell r="J8"/>
-          <cell r="K8"/>
-          <cell r="L8"/>
-          <cell r="M8"/>
         </row>
         <row r="9">
           <cell r="A9" t="str">
@@ -1167,17 +1134,9 @@
           <cell r="D9">
             <v>22197.7</v>
           </cell>
-          <cell r="E9"/>
           <cell r="F9">
             <v>52833.82</v>
           </cell>
-          <cell r="G9"/>
-          <cell r="H9"/>
-          <cell r="I9"/>
-          <cell r="J9"/>
-          <cell r="K9"/>
-          <cell r="L9"/>
-          <cell r="M9"/>
         </row>
         <row r="10">
           <cell r="A10" t="str">
@@ -1192,40 +1151,23 @@
           <cell r="D10">
             <v>1921.23</v>
           </cell>
-          <cell r="E10"/>
           <cell r="F10">
             <v>4854.9400000000005</v>
           </cell>
-          <cell r="G10"/>
-          <cell r="H10"/>
-          <cell r="I10"/>
-          <cell r="J10"/>
-          <cell r="K10"/>
-          <cell r="L10"/>
-          <cell r="M10"/>
         </row>
         <row r="11">
           <cell r="A11" t="str">
             <v>PIS</v>
           </cell>
-          <cell r="B11"/>
           <cell r="C11">
             <v>496.96</v>
           </cell>
           <cell r="D11">
             <v>3431.3</v>
           </cell>
-          <cell r="E11"/>
           <cell r="F11">
             <v>3928.26</v>
           </cell>
-          <cell r="G11"/>
-          <cell r="H11"/>
-          <cell r="I11"/>
-          <cell r="J11"/>
-          <cell r="K11"/>
-          <cell r="L11"/>
-          <cell r="M11"/>
         </row>
         <row r="12">
           <cell r="A12" t="str">
@@ -1240,17 +1182,9 @@
           <cell r="D12">
             <v>81164.490000000005</v>
           </cell>
-          <cell r="E12"/>
           <cell r="F12">
             <v>205262.51</v>
           </cell>
-          <cell r="G12"/>
-          <cell r="H12"/>
-          <cell r="I12"/>
-          <cell r="J12"/>
-          <cell r="K12"/>
-          <cell r="L12"/>
-          <cell r="M12"/>
         </row>
         <row r="13">
           <cell r="A13" t="str">
@@ -1266,18 +1200,11 @@
             <v>29480.909999999996</v>
           </cell>
           <cell r="E13">
-            <v>592.58999999999992</v>
+            <v>5007.66</v>
           </cell>
           <cell r="F13">
-            <v>63618.049999999988</v>
-          </cell>
-          <cell r="G13"/>
-          <cell r="H13"/>
-          <cell r="I13"/>
-          <cell r="J13"/>
-          <cell r="K13"/>
-          <cell r="L13"/>
-          <cell r="M13"/>
+            <v>68033.119999999995</v>
+          </cell>
         </row>
         <row r="14">
           <cell r="A14" t="str">
@@ -1292,17 +1219,9 @@
           <cell r="D14">
             <v>1534.3</v>
           </cell>
-          <cell r="E14"/>
           <cell r="F14">
             <v>3085.9799999999996</v>
           </cell>
-          <cell r="G14"/>
-          <cell r="H14"/>
-          <cell r="I14"/>
-          <cell r="J14"/>
-          <cell r="K14"/>
-          <cell r="L14"/>
-          <cell r="M14"/>
         </row>
         <row r="15">
           <cell r="A15" t="str">
@@ -1317,17 +1236,9 @@
           <cell r="D15">
             <v>12217.75</v>
           </cell>
-          <cell r="E15"/>
           <cell r="F15">
             <v>14735.43</v>
           </cell>
-          <cell r="G15"/>
-          <cell r="H15"/>
-          <cell r="I15"/>
-          <cell r="J15"/>
-          <cell r="K15"/>
-          <cell r="L15"/>
-          <cell r="M15"/>
         </row>
         <row r="16">
           <cell r="A16" t="str">
@@ -1343,18 +1254,11 @@
             <v>15728.859999999995</v>
           </cell>
           <cell r="E16">
-            <v>592.58999999999992</v>
+            <v>5007.66</v>
           </cell>
           <cell r="F16">
-            <v>45796.639999999992</v>
-          </cell>
-          <cell r="G16"/>
-          <cell r="H16"/>
-          <cell r="I16"/>
-          <cell r="J16"/>
-          <cell r="K16"/>
-          <cell r="L16"/>
-          <cell r="M16"/>
+            <v>50211.709999999992</v>
+          </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
@@ -1370,18 +1274,11 @@
             <v>333045.58</v>
           </cell>
           <cell r="E17">
-            <v>29888.55</v>
+            <v>35596.559999999998</v>
           </cell>
           <cell r="F17">
-            <v>1021223.9</v>
-          </cell>
-          <cell r="G17"/>
-          <cell r="H17"/>
-          <cell r="I17"/>
-          <cell r="J17"/>
-          <cell r="K17"/>
-          <cell r="L17"/>
-          <cell r="M17"/>
+            <v>1026931.9100000001</v>
+          </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
@@ -1402,13 +1299,6 @@
           <cell r="F18">
             <v>2147.9</v>
           </cell>
-          <cell r="G18"/>
-          <cell r="H18"/>
-          <cell r="I18"/>
-          <cell r="J18"/>
-          <cell r="K18"/>
-          <cell r="L18"/>
-          <cell r="M18"/>
         </row>
         <row r="19">
           <cell r="A19" t="str">
@@ -1423,17 +1313,9 @@
           <cell r="D19">
             <v>8155.15</v>
           </cell>
-          <cell r="E19"/>
           <cell r="F19">
             <v>19604.21</v>
           </cell>
-          <cell r="G19"/>
-          <cell r="H19"/>
-          <cell r="I19"/>
-          <cell r="J19"/>
-          <cell r="K19"/>
-          <cell r="L19"/>
-          <cell r="M19"/>
         </row>
         <row r="20">
           <cell r="A20" t="str">
@@ -1445,20 +1327,12 @@
           <cell r="C20">
             <v>1694.1599999999999</v>
           </cell>
-          <cell r="D20"/>
           <cell r="E20">
             <v>1307.92</v>
           </cell>
           <cell r="F20">
             <v>4901.28</v>
           </cell>
-          <cell r="G20"/>
-          <cell r="H20"/>
-          <cell r="I20"/>
-          <cell r="J20"/>
-          <cell r="K20"/>
-          <cell r="L20"/>
-          <cell r="M20"/>
         </row>
         <row r="21">
           <cell r="A21" t="str">
@@ -1479,13 +1353,6 @@
           <cell r="F21">
             <v>29649.43</v>
           </cell>
-          <cell r="G21"/>
-          <cell r="H21"/>
-          <cell r="I21"/>
-          <cell r="J21"/>
-          <cell r="K21"/>
-          <cell r="L21"/>
-          <cell r="M21"/>
         </row>
         <row r="22">
           <cell r="A22" t="str">
@@ -1500,17 +1367,9 @@
           <cell r="D22">
             <v>35869.64</v>
           </cell>
-          <cell r="E22"/>
           <cell r="F22">
             <v>103038.12</v>
           </cell>
-          <cell r="G22"/>
-          <cell r="H22"/>
-          <cell r="I22"/>
-          <cell r="J22"/>
-          <cell r="K22"/>
-          <cell r="L22"/>
-          <cell r="M22"/>
         </row>
         <row r="23">
           <cell r="A23" t="str">
@@ -1531,13 +1390,6 @@
           <cell r="F23">
             <v>26620</v>
           </cell>
-          <cell r="G23"/>
-          <cell r="H23"/>
-          <cell r="I23"/>
-          <cell r="J23"/>
-          <cell r="K23"/>
-          <cell r="L23"/>
-          <cell r="M23"/>
         </row>
         <row r="24">
           <cell r="A24" t="str">
@@ -1552,17 +1404,9 @@
           <cell r="D24">
             <v>44918.66</v>
           </cell>
-          <cell r="E24"/>
           <cell r="F24">
             <v>132088.18</v>
           </cell>
-          <cell r="G24"/>
-          <cell r="H24"/>
-          <cell r="I24"/>
-          <cell r="J24"/>
-          <cell r="K24"/>
-          <cell r="L24"/>
-          <cell r="M24"/>
         </row>
         <row r="25">
           <cell r="A25" t="str">
@@ -1578,41 +1422,25 @@
             <v>9382.1299999999992</v>
           </cell>
           <cell r="E25">
-            <v>3881.96</v>
+            <v>7049.37</v>
           </cell>
           <cell r="F25">
-            <v>49320.149999999994</v>
-          </cell>
-          <cell r="G25"/>
-          <cell r="H25"/>
-          <cell r="I25"/>
-          <cell r="J25"/>
-          <cell r="K25"/>
-          <cell r="L25"/>
-          <cell r="M25"/>
+            <v>52487.56</v>
+          </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
             <v>Rescisões MOD</v>
           </cell>
-          <cell r="B26"/>
           <cell r="C26">
             <v>30936.210000000003</v>
           </cell>
           <cell r="D26">
             <v>394.44</v>
           </cell>
-          <cell r="E26"/>
           <cell r="F26">
             <v>31330.65</v>
           </cell>
-          <cell r="G26"/>
-          <cell r="H26"/>
-          <cell r="I26"/>
-          <cell r="J26"/>
-          <cell r="K26"/>
-          <cell r="L26"/>
-          <cell r="M26"/>
         </row>
         <row r="27">
           <cell r="A27" t="str">
@@ -1628,18 +1456,11 @@
             <v>218151.71</v>
           </cell>
           <cell r="E27">
-            <v>6766.4299999999994</v>
+            <v>7266.4299999999994</v>
           </cell>
           <cell r="F27">
-            <v>616676.28</v>
-          </cell>
-          <cell r="G27"/>
-          <cell r="H27"/>
-          <cell r="I27"/>
-          <cell r="J27"/>
-          <cell r="K27"/>
-          <cell r="L27"/>
-          <cell r="M27"/>
+            <v>617176.28</v>
+          </cell>
         </row>
         <row r="28">
           <cell r="A28" t="str">
@@ -1654,17 +1475,12 @@
           <cell r="D28">
             <v>1980.53</v>
           </cell>
-          <cell r="E28"/>
+          <cell r="E28">
+            <v>2040.6</v>
+          </cell>
           <cell r="F28">
-            <v>5847.7</v>
-          </cell>
-          <cell r="G28"/>
-          <cell r="H28"/>
-          <cell r="I28"/>
-          <cell r="J28"/>
-          <cell r="K28"/>
-          <cell r="L28"/>
-          <cell r="M28"/>
+            <v>7888.2999999999993</v>
+          </cell>
         </row>
         <row r="29">
           <cell r="A29" t="str">
@@ -1680,39 +1496,22 @@
             <v>107667.2</v>
           </cell>
           <cell r="E29">
-            <v>18211.009999999998</v>
+            <v>19725.309999999998</v>
           </cell>
           <cell r="F29">
-            <v>279047.74999999994</v>
-          </cell>
-          <cell r="G29"/>
-          <cell r="H29"/>
-          <cell r="I29"/>
-          <cell r="J29"/>
-          <cell r="K29"/>
-          <cell r="L29"/>
-          <cell r="M29"/>
+            <v>280562.05</v>
+          </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
             <v>Assistência Médica CIF</v>
           </cell>
-          <cell r="B30"/>
-          <cell r="C30"/>
-          <cell r="D30"/>
           <cell r="E30">
             <v>225</v>
           </cell>
           <cell r="F30">
             <v>225</v>
           </cell>
-          <cell r="G30"/>
-          <cell r="H30"/>
-          <cell r="I30"/>
-          <cell r="J30"/>
-          <cell r="K30"/>
-          <cell r="L30"/>
-          <cell r="M30"/>
         </row>
         <row r="31">
           <cell r="A31" t="str">
@@ -1727,24 +1526,14 @@
           <cell r="D31">
             <v>705.03</v>
           </cell>
-          <cell r="E31"/>
           <cell r="F31">
             <v>5027.6699999999992</v>
           </cell>
-          <cell r="G31"/>
-          <cell r="H31"/>
-          <cell r="I31"/>
-          <cell r="J31"/>
-          <cell r="K31"/>
-          <cell r="L31"/>
-          <cell r="M31"/>
         </row>
         <row r="32">
           <cell r="A32" t="str">
             <v>Férias CIF</v>
           </cell>
-          <cell r="B32"/>
-          <cell r="C32"/>
           <cell r="D32">
             <v>1458.08</v>
           </cell>
@@ -1754,13 +1543,6 @@
           <cell r="F32">
             <v>2774.3</v>
           </cell>
-          <cell r="G32"/>
-          <cell r="H32"/>
-          <cell r="I32"/>
-          <cell r="J32"/>
-          <cell r="K32"/>
-          <cell r="L32"/>
-          <cell r="M32"/>
         </row>
         <row r="33">
           <cell r="A33" t="str">
@@ -1775,17 +1557,9 @@
           <cell r="D33">
             <v>5035.68</v>
           </cell>
-          <cell r="E33"/>
           <cell r="F33">
             <v>16785.29</v>
           </cell>
-          <cell r="G33"/>
-          <cell r="H33"/>
-          <cell r="I33"/>
-          <cell r="J33"/>
-          <cell r="K33"/>
-          <cell r="L33"/>
-          <cell r="M33"/>
         </row>
         <row r="34">
           <cell r="A34" t="str">
@@ -1806,13 +1580,6 @@
           <cell r="F34">
             <v>7945.3</v>
           </cell>
-          <cell r="G34"/>
-          <cell r="H34"/>
-          <cell r="I34"/>
-          <cell r="J34"/>
-          <cell r="K34"/>
-          <cell r="L34"/>
-          <cell r="M34"/>
         </row>
         <row r="35">
           <cell r="A35" t="str">
@@ -1821,19 +1588,9 @@
           <cell r="B35">
             <v>230</v>
           </cell>
-          <cell r="C35"/>
-          <cell r="D35"/>
-          <cell r="E35"/>
           <cell r="F35">
             <v>230</v>
           </cell>
-          <cell r="G35"/>
-          <cell r="H35"/>
-          <cell r="I35"/>
-          <cell r="J35"/>
-          <cell r="K35"/>
-          <cell r="L35"/>
-          <cell r="M35"/>
         </row>
         <row r="36">
           <cell r="A36" t="str">
@@ -1848,38 +1605,20 @@
           <cell r="D36">
             <v>8006.02</v>
           </cell>
-          <cell r="E36"/>
           <cell r="F36">
             <v>24330.39</v>
           </cell>
-          <cell r="G36"/>
-          <cell r="H36"/>
-          <cell r="I36"/>
-          <cell r="J36"/>
-          <cell r="K36"/>
-          <cell r="L36"/>
-          <cell r="M36"/>
         </row>
         <row r="37">
           <cell r="A37" t="str">
             <v>IPTU e Taxas Municipais CIF</v>
           </cell>
-          <cell r="B37"/>
-          <cell r="C37"/>
-          <cell r="D37"/>
           <cell r="E37">
             <v>2430.6600000000003</v>
           </cell>
           <cell r="F37">
             <v>2430.6600000000003</v>
           </cell>
-          <cell r="G37"/>
-          <cell r="H37"/>
-          <cell r="I37"/>
-          <cell r="J37"/>
-          <cell r="K37"/>
-          <cell r="L37"/>
-          <cell r="M37"/>
         </row>
         <row r="38">
           <cell r="A38" t="str">
@@ -1900,13 +1639,6 @@
           <cell r="F38">
             <v>68290.62</v>
           </cell>
-          <cell r="G38"/>
-          <cell r="H38"/>
-          <cell r="I38"/>
-          <cell r="J38"/>
-          <cell r="K38"/>
-          <cell r="L38"/>
-          <cell r="M38"/>
         </row>
         <row r="39">
           <cell r="A39" t="str">
@@ -1922,18 +1654,11 @@
             <v>6703.59</v>
           </cell>
           <cell r="E39">
-            <v>6172.05</v>
+            <v>6555.5700000000006</v>
           </cell>
           <cell r="F39">
-            <v>39131.61</v>
-          </cell>
-          <cell r="G39"/>
-          <cell r="H39"/>
-          <cell r="I39"/>
-          <cell r="J39"/>
-          <cell r="K39"/>
-          <cell r="L39"/>
-          <cell r="M39"/>
+            <v>39515.129999999997</v>
+          </cell>
         </row>
         <row r="40">
           <cell r="A40" t="str">
@@ -1949,18 +1674,11 @@
             <v>2109.6999999999998</v>
           </cell>
           <cell r="E40">
-            <v>1239.0999999999999</v>
+            <v>2093.6</v>
           </cell>
           <cell r="F40">
-            <v>6673.58</v>
-          </cell>
-          <cell r="G40"/>
-          <cell r="H40"/>
-          <cell r="I40"/>
-          <cell r="J40"/>
-          <cell r="K40"/>
-          <cell r="L40"/>
-          <cell r="M40"/>
+            <v>7528.08</v>
+          </cell>
         </row>
         <row r="41">
           <cell r="A41" t="str">
@@ -1975,38 +1693,20 @@
           <cell r="D41">
             <v>2405.31</v>
           </cell>
-          <cell r="E41"/>
           <cell r="F41">
             <v>7126.77</v>
           </cell>
-          <cell r="G41"/>
-          <cell r="H41"/>
-          <cell r="I41"/>
-          <cell r="J41"/>
-          <cell r="K41"/>
-          <cell r="L41"/>
-          <cell r="M41"/>
         </row>
         <row r="42">
           <cell r="A42" t="str">
             <v>Medicina e Segurança do Trabalho MOD</v>
           </cell>
-          <cell r="B42"/>
-          <cell r="C42"/>
           <cell r="D42">
             <v>180</v>
           </cell>
-          <cell r="E42"/>
           <cell r="F42">
             <v>180</v>
           </cell>
-          <cell r="G42"/>
-          <cell r="H42"/>
-          <cell r="I42"/>
-          <cell r="J42"/>
-          <cell r="K42"/>
-          <cell r="L42"/>
-          <cell r="M42"/>
         </row>
         <row r="43">
           <cell r="A43" t="str">
@@ -2027,13 +1727,6 @@
           <cell r="F43">
             <v>97019.559999999983</v>
           </cell>
-          <cell r="G43"/>
-          <cell r="H43"/>
-          <cell r="I43"/>
-          <cell r="J43"/>
-          <cell r="K43"/>
-          <cell r="L43"/>
-          <cell r="M43"/>
         </row>
         <row r="44">
           <cell r="A44" t="str">
@@ -2048,17 +1741,12 @@
           <cell r="D44">
             <v>272.03999999999996</v>
           </cell>
-          <cell r="E44"/>
+          <cell r="E44">
+            <v>276.27999999999997</v>
+          </cell>
           <cell r="F44">
-            <v>877</v>
-          </cell>
-          <cell r="G44"/>
-          <cell r="H44"/>
-          <cell r="I44"/>
-          <cell r="J44"/>
-          <cell r="K44"/>
-          <cell r="L44"/>
-          <cell r="M44"/>
+            <v>1153.28</v>
+          </cell>
         </row>
         <row r="45">
           <cell r="A45" t="str">
@@ -2074,39 +1762,22 @@
             <v>186773.47999999998</v>
           </cell>
           <cell r="E45">
-            <v>41565.769999999997</v>
+            <v>76539.610000000015</v>
           </cell>
           <cell r="F45">
-            <v>563079.43000000005</v>
-          </cell>
-          <cell r="G45"/>
-          <cell r="H45"/>
-          <cell r="I45"/>
-          <cell r="J45"/>
-          <cell r="K45"/>
-          <cell r="L45"/>
-          <cell r="M45"/>
+            <v>598053.27</v>
+          </cell>
         </row>
         <row r="46">
           <cell r="A46" t="str">
             <v>Assistência Médica (Adm)</v>
           </cell>
-          <cell r="B46"/>
           <cell r="C46">
             <v>75</v>
           </cell>
-          <cell r="D46"/>
-          <cell r="E46"/>
           <cell r="F46">
             <v>75</v>
           </cell>
-          <cell r="G46"/>
-          <cell r="H46"/>
-          <cell r="I46"/>
-          <cell r="J46"/>
-          <cell r="K46"/>
-          <cell r="L46"/>
-          <cell r="M46"/>
         </row>
         <row r="47">
           <cell r="A47" t="str">
@@ -2127,13 +1798,6 @@
           <cell r="F47">
             <v>4935.9799999999996</v>
           </cell>
-          <cell r="G47"/>
-          <cell r="H47"/>
-          <cell r="I47"/>
-          <cell r="J47"/>
-          <cell r="K47"/>
-          <cell r="L47"/>
-          <cell r="M47"/>
         </row>
         <row r="48">
           <cell r="A48" t="str">
@@ -2154,19 +1818,11 @@
           <cell r="F48">
             <v>9726.68</v>
           </cell>
-          <cell r="G48"/>
-          <cell r="H48"/>
-          <cell r="I48"/>
-          <cell r="J48"/>
-          <cell r="K48"/>
-          <cell r="L48"/>
-          <cell r="M48"/>
         </row>
         <row r="49">
           <cell r="A49" t="str">
             <v>Ferias (Adm)</v>
           </cell>
-          <cell r="B49"/>
           <cell r="C49">
             <v>297.89999999999998</v>
           </cell>
@@ -2174,18 +1830,11 @@
             <v>1372.31</v>
           </cell>
           <cell r="E49">
-            <v>1529.83</v>
+            <v>2681.09</v>
           </cell>
           <cell r="F49">
-            <v>3200.04</v>
-          </cell>
-          <cell r="G49"/>
-          <cell r="H49"/>
-          <cell r="I49"/>
-          <cell r="J49"/>
-          <cell r="K49"/>
-          <cell r="L49"/>
-          <cell r="M49"/>
+            <v>4351.3</v>
+          </cell>
         </row>
         <row r="50">
           <cell r="A50" t="str">
@@ -2200,17 +1849,9 @@
           <cell r="D50">
             <v>9088.76</v>
           </cell>
-          <cell r="E50"/>
           <cell r="F50">
             <v>27537.019999999997</v>
           </cell>
-          <cell r="G50"/>
-          <cell r="H50"/>
-          <cell r="I50"/>
-          <cell r="J50"/>
-          <cell r="K50"/>
-          <cell r="L50"/>
-          <cell r="M50"/>
         </row>
         <row r="51">
           <cell r="A51" t="str">
@@ -2231,13 +1872,6 @@
           <cell r="F51">
             <v>14373.5</v>
           </cell>
-          <cell r="G51"/>
-          <cell r="H51"/>
-          <cell r="I51"/>
-          <cell r="J51"/>
-          <cell r="K51"/>
-          <cell r="L51"/>
-          <cell r="M51"/>
         </row>
         <row r="52">
           <cell r="A52" t="str">
@@ -2252,17 +1886,9 @@
           <cell r="D52">
             <v>20718.489999999998</v>
           </cell>
-          <cell r="E52"/>
           <cell r="F52">
             <v>61430.81</v>
           </cell>
-          <cell r="G52"/>
-          <cell r="H52"/>
-          <cell r="I52"/>
-          <cell r="J52"/>
-          <cell r="K52"/>
-          <cell r="L52"/>
-          <cell r="M52"/>
         </row>
         <row r="53">
           <cell r="A53" t="str">
@@ -2278,18 +1904,11 @@
             <v>1143.7600000000002</v>
           </cell>
           <cell r="E53">
-            <v>98</v>
+            <v>116</v>
           </cell>
           <cell r="F53">
-            <v>5933.3600000000006</v>
-          </cell>
-          <cell r="G53"/>
-          <cell r="H53"/>
-          <cell r="I53"/>
-          <cell r="J53"/>
-          <cell r="K53"/>
-          <cell r="L53"/>
-          <cell r="M53"/>
+            <v>5951.3600000000006</v>
+          </cell>
         </row>
         <row r="54">
           <cell r="A54" t="str">
@@ -2305,18 +1924,11 @@
             <v>59830.189999999995</v>
           </cell>
           <cell r="E54">
-            <v>30930.639999999999</v>
+            <v>51717.240000000005</v>
           </cell>
           <cell r="F54">
-            <v>215577.69</v>
-          </cell>
-          <cell r="G54"/>
-          <cell r="H54"/>
-          <cell r="I54"/>
-          <cell r="J54"/>
-          <cell r="K54"/>
-          <cell r="L54"/>
-          <cell r="M54"/>
+            <v>236364.29000000004</v>
+          </cell>
         </row>
         <row r="55">
           <cell r="A55" t="str">
@@ -2325,21 +1937,15 @@
           <cell r="B55">
             <v>879.73</v>
           </cell>
-          <cell r="C55"/>
           <cell r="D55">
             <v>11928.27</v>
           </cell>
-          <cell r="E55"/>
+          <cell r="E55">
+            <v>12417.35</v>
+          </cell>
           <cell r="F55">
-            <v>12808</v>
-          </cell>
-          <cell r="G55"/>
-          <cell r="H55"/>
-          <cell r="I55"/>
-          <cell r="J55"/>
-          <cell r="K55"/>
-          <cell r="L55"/>
-          <cell r="M55"/>
+            <v>25225.35</v>
+          </cell>
         </row>
         <row r="56">
           <cell r="A56" t="str">
@@ -2360,13 +1966,6 @@
           <cell r="F56">
             <v>205513.01</v>
           </cell>
-          <cell r="G56"/>
-          <cell r="H56"/>
-          <cell r="I56"/>
-          <cell r="J56"/>
-          <cell r="K56"/>
-          <cell r="L56"/>
-          <cell r="M56"/>
         </row>
         <row r="57">
           <cell r="A57" t="str">
@@ -2381,17 +1980,12 @@
           <cell r="D57">
             <v>596.62</v>
           </cell>
-          <cell r="E57"/>
+          <cell r="E57">
+            <v>600.63</v>
+          </cell>
           <cell r="F57">
-            <v>1968.3400000000001</v>
-          </cell>
-          <cell r="G57"/>
-          <cell r="H57"/>
-          <cell r="I57"/>
-          <cell r="J57"/>
-          <cell r="K57"/>
-          <cell r="L57"/>
-          <cell r="M57"/>
+            <v>2568.9700000000003</v>
+          </cell>
         </row>
         <row r="58">
           <cell r="A58" t="str">
@@ -2407,18 +2001,11 @@
             <v>17985.82</v>
           </cell>
           <cell r="E58">
-            <v>4876.7999999999993</v>
+            <v>5156.7999999999993</v>
           </cell>
           <cell r="F58">
-            <v>58178.34</v>
-          </cell>
-          <cell r="G58"/>
-          <cell r="H58"/>
-          <cell r="I58"/>
-          <cell r="J58"/>
-          <cell r="K58"/>
-          <cell r="L58"/>
-          <cell r="M58"/>
+            <v>58458.34</v>
+          </cell>
         </row>
         <row r="59">
           <cell r="A59" t="str">
@@ -2433,17 +2020,9 @@
           <cell r="D59">
             <v>32.229999999999997</v>
           </cell>
-          <cell r="E59"/>
           <cell r="F59">
             <v>96.69</v>
           </cell>
-          <cell r="G59"/>
-          <cell r="H59"/>
-          <cell r="I59"/>
-          <cell r="J59"/>
-          <cell r="K59"/>
-          <cell r="L59"/>
-          <cell r="M59"/>
         </row>
         <row r="60">
           <cell r="A60" t="str">
@@ -2464,13 +2043,6 @@
           <cell r="F60">
             <v>2024.63</v>
           </cell>
-          <cell r="G60"/>
-          <cell r="H60"/>
-          <cell r="I60"/>
-          <cell r="J60"/>
-          <cell r="K60"/>
-          <cell r="L60"/>
-          <cell r="M60"/>
         </row>
         <row r="61">
           <cell r="A61" t="str">
@@ -2491,13 +2063,6 @@
           <cell r="F61">
             <v>3500</v>
           </cell>
-          <cell r="G61"/>
-          <cell r="H61"/>
-          <cell r="I61"/>
-          <cell r="J61"/>
-          <cell r="K61"/>
-          <cell r="L61"/>
-          <cell r="M61"/>
         </row>
         <row r="62">
           <cell r="A62" t="str">
@@ -2512,17 +2077,12 @@
           <cell r="D62">
             <v>780.64</v>
           </cell>
-          <cell r="E62"/>
+          <cell r="E62">
+            <v>120</v>
+          </cell>
           <cell r="F62">
-            <v>2272.96</v>
-          </cell>
-          <cell r="G62"/>
-          <cell r="H62"/>
-          <cell r="I62"/>
-          <cell r="J62"/>
-          <cell r="K62"/>
-          <cell r="L62"/>
-          <cell r="M62"/>
+            <v>2392.96</v>
+          </cell>
         </row>
         <row r="63">
           <cell r="A63" t="str">
@@ -2537,17 +2097,9 @@
           <cell r="D63">
             <v>150.63</v>
           </cell>
-          <cell r="E63"/>
           <cell r="F63">
             <v>535.22</v>
           </cell>
-          <cell r="G63"/>
-          <cell r="H63"/>
-          <cell r="I63"/>
-          <cell r="J63"/>
-          <cell r="K63"/>
-          <cell r="L63"/>
-          <cell r="M63"/>
         </row>
         <row r="64">
           <cell r="A64" t="str">
@@ -2562,17 +2114,9 @@
           <cell r="D64">
             <v>350.68</v>
           </cell>
-          <cell r="E64"/>
           <cell r="F64">
             <v>1294.56</v>
           </cell>
-          <cell r="G64"/>
-          <cell r="H64"/>
-          <cell r="I64"/>
-          <cell r="J64"/>
-          <cell r="K64"/>
-          <cell r="L64"/>
-          <cell r="M64"/>
         </row>
         <row r="65">
           <cell r="A65" t="str">
@@ -2587,17 +2131,12 @@
           <cell r="D65">
             <v>100</v>
           </cell>
-          <cell r="E65"/>
+          <cell r="E65">
+            <v>100</v>
+          </cell>
           <cell r="F65">
-            <v>300</v>
-          </cell>
-          <cell r="G65"/>
-          <cell r="H65"/>
-          <cell r="I65"/>
-          <cell r="J65"/>
-          <cell r="K65"/>
-          <cell r="L65"/>
-          <cell r="M65"/>
+            <v>400</v>
+          </cell>
         </row>
         <row r="66">
           <cell r="A66" t="str">
@@ -2609,18 +2148,12 @@
           <cell r="C66">
             <v>91.95</v>
           </cell>
-          <cell r="D66"/>
-          <cell r="E66"/>
+          <cell r="E66">
+            <v>60</v>
+          </cell>
           <cell r="F66">
-            <v>190.36</v>
-          </cell>
-          <cell r="G66"/>
-          <cell r="H66"/>
-          <cell r="I66"/>
-          <cell r="J66"/>
-          <cell r="K66"/>
-          <cell r="L66"/>
-          <cell r="M66"/>
+            <v>250.36</v>
+          </cell>
         </row>
         <row r="67">
           <cell r="A67" t="str">
@@ -2641,13 +2174,6 @@
           <cell r="F67">
             <v>1256.1499999999999</v>
           </cell>
-          <cell r="G67"/>
-          <cell r="H67"/>
-          <cell r="I67"/>
-          <cell r="J67"/>
-          <cell r="K67"/>
-          <cell r="L67"/>
-          <cell r="M67"/>
         </row>
         <row r="68">
           <cell r="A68" t="str">
@@ -2668,13 +2194,6 @@
           <cell r="F68">
             <v>1820.6</v>
           </cell>
-          <cell r="G68"/>
-          <cell r="H68"/>
-          <cell r="I68"/>
-          <cell r="J68"/>
-          <cell r="K68"/>
-          <cell r="L68"/>
-          <cell r="M68"/>
         </row>
         <row r="69">
           <cell r="A69" t="str">
@@ -2695,13 +2214,6 @@
           <cell r="F69">
             <v>1480</v>
           </cell>
-          <cell r="G69"/>
-          <cell r="H69"/>
-          <cell r="I69"/>
-          <cell r="J69"/>
-          <cell r="K69"/>
-          <cell r="L69"/>
-          <cell r="M69"/>
         </row>
         <row r="70">
           <cell r="A70" t="str">
@@ -2722,13 +2234,6 @@
           <cell r="F70">
             <v>35334.74</v>
           </cell>
-          <cell r="G70"/>
-          <cell r="H70"/>
-          <cell r="I70"/>
-          <cell r="J70"/>
-          <cell r="K70"/>
-          <cell r="L70"/>
-          <cell r="M70"/>
         </row>
         <row r="71">
           <cell r="A71" t="str">
@@ -2743,17 +2248,9 @@
           <cell r="D71">
             <v>351</v>
           </cell>
-          <cell r="E71"/>
           <cell r="F71">
             <v>1319.44</v>
           </cell>
-          <cell r="G71"/>
-          <cell r="H71"/>
-          <cell r="I71"/>
-          <cell r="J71"/>
-          <cell r="K71"/>
-          <cell r="L71"/>
-          <cell r="M71"/>
         </row>
         <row r="72">
           <cell r="A72" t="str">
@@ -2774,13 +2271,6 @@
           <cell r="F72">
             <v>6752.99</v>
           </cell>
-          <cell r="G72"/>
-          <cell r="H72"/>
-          <cell r="I72"/>
-          <cell r="J72"/>
-          <cell r="K72"/>
-          <cell r="L72"/>
-          <cell r="M72"/>
         </row>
         <row r="73">
           <cell r="A73" t="str">
@@ -2793,21 +2283,14 @@
             <v>315472.21000000002</v>
           </cell>
           <cell r="D73">
-            <v>386839.54000000004</v>
+            <v>386595.21</v>
           </cell>
           <cell r="E73">
-            <v>132470.43</v>
+            <v>181507.31</v>
           </cell>
           <cell r="F73">
-            <v>1236528.47</v>
-          </cell>
-          <cell r="G73"/>
-          <cell r="H73"/>
-          <cell r="I73"/>
-          <cell r="J73"/>
-          <cell r="K73"/>
-          <cell r="L73"/>
-          <cell r="M73"/>
+            <v>1285321.02</v>
+          </cell>
         </row>
         <row r="74">
           <cell r="A74" t="str">
@@ -2816,19 +2299,9 @@
           <cell r="B74">
             <v>1368</v>
           </cell>
-          <cell r="C74"/>
-          <cell r="D74"/>
-          <cell r="E74"/>
           <cell r="F74">
             <v>1368</v>
           </cell>
-          <cell r="G74"/>
-          <cell r="H74"/>
-          <cell r="I74"/>
-          <cell r="J74"/>
-          <cell r="K74"/>
-          <cell r="L74"/>
-          <cell r="M74"/>
         </row>
         <row r="75">
           <cell r="A75" t="str">
@@ -2843,17 +2316,12 @@
           <cell r="D75">
             <v>3042.48</v>
           </cell>
-          <cell r="E75"/>
+          <cell r="E75">
+            <v>86</v>
+          </cell>
           <cell r="F75">
-            <v>7412.48</v>
-          </cell>
-          <cell r="G75"/>
-          <cell r="H75"/>
-          <cell r="I75"/>
-          <cell r="J75"/>
-          <cell r="K75"/>
-          <cell r="L75"/>
-          <cell r="M75"/>
+            <v>7498.48</v>
+          </cell>
         </row>
         <row r="76">
           <cell r="A76" t="str">
@@ -2869,18 +2337,11 @@
             <v>69230.98000000001</v>
           </cell>
           <cell r="E76">
-            <v>26021.809999999998</v>
+            <v>28146.19</v>
           </cell>
           <cell r="F76">
-            <v>183897.01</v>
-          </cell>
-          <cell r="G76"/>
-          <cell r="H76"/>
-          <cell r="I76"/>
-          <cell r="J76"/>
-          <cell r="K76"/>
-          <cell r="L76"/>
-          <cell r="M76"/>
+            <v>186021.39</v>
+          </cell>
         </row>
         <row r="77">
           <cell r="A77" t="str">
@@ -2896,18 +2357,11 @@
             <v>88339.049999999988</v>
           </cell>
           <cell r="E77">
-            <v>54220.92</v>
+            <v>54479.799999999996</v>
           </cell>
           <cell r="F77">
-            <v>338386.3899999999</v>
-          </cell>
-          <cell r="G77"/>
-          <cell r="H77"/>
-          <cell r="I77"/>
-          <cell r="J77"/>
-          <cell r="K77"/>
-          <cell r="L77"/>
-          <cell r="M77"/>
+            <v>338645.2699999999</v>
+          </cell>
         </row>
         <row r="78">
           <cell r="A78" t="str">
@@ -2928,13 +2382,6 @@
           <cell r="F78">
             <v>31329.660000000003</v>
           </cell>
-          <cell r="G78"/>
-          <cell r="H78"/>
-          <cell r="I78"/>
-          <cell r="J78"/>
-          <cell r="K78"/>
-          <cell r="L78"/>
-          <cell r="M78"/>
         </row>
         <row r="79">
           <cell r="A79" t="str">
@@ -2955,13 +2402,6 @@
           <cell r="F79">
             <v>63215.880000000005</v>
           </cell>
-          <cell r="G79"/>
-          <cell r="H79"/>
-          <cell r="I79"/>
-          <cell r="J79"/>
-          <cell r="K79"/>
-          <cell r="L79"/>
-          <cell r="M79"/>
         </row>
         <row r="80">
           <cell r="A80" t="str">
@@ -2976,17 +2416,12 @@
           <cell r="D80">
             <v>24000</v>
           </cell>
-          <cell r="E80"/>
+          <cell r="E80">
+            <v>510</v>
+          </cell>
           <cell r="F80">
-            <v>72000</v>
-          </cell>
-          <cell r="G80"/>
-          <cell r="H80"/>
-          <cell r="I80"/>
-          <cell r="J80"/>
-          <cell r="K80"/>
-          <cell r="L80"/>
-          <cell r="M80"/>
+            <v>72510</v>
+          </cell>
         </row>
         <row r="81">
           <cell r="A81" t="str">
@@ -3002,41 +2437,25 @@
             <v>41728.47</v>
           </cell>
           <cell r="E81">
-            <v>1333.77</v>
+            <v>39467.100000000006</v>
           </cell>
           <cell r="F81">
-            <v>200814.61999999997</v>
-          </cell>
-          <cell r="G81"/>
-          <cell r="H81"/>
-          <cell r="I81"/>
-          <cell r="J81"/>
-          <cell r="K81"/>
-          <cell r="L81"/>
-          <cell r="M81"/>
+            <v>238947.94999999998</v>
+          </cell>
         </row>
         <row r="82">
           <cell r="A82" t="str">
             <v>Fretes</v>
           </cell>
-          <cell r="B82"/>
           <cell r="C82">
             <v>2334.16</v>
           </cell>
           <cell r="D82">
             <v>709</v>
           </cell>
-          <cell r="E82"/>
           <cell r="F82">
             <v>3043.16</v>
           </cell>
-          <cell r="G82"/>
-          <cell r="H82"/>
-          <cell r="I82"/>
-          <cell r="J82"/>
-          <cell r="K82"/>
-          <cell r="L82"/>
-          <cell r="M82"/>
         </row>
         <row r="83">
           <cell r="A83" t="str">
@@ -3051,17 +2470,9 @@
           <cell r="D83">
             <v>420.81</v>
           </cell>
-          <cell r="E83"/>
           <cell r="F83">
             <v>2737.9</v>
           </cell>
-          <cell r="G83"/>
-          <cell r="H83"/>
-          <cell r="I83"/>
-          <cell r="J83"/>
-          <cell r="K83"/>
-          <cell r="L83"/>
-          <cell r="M83"/>
         </row>
         <row r="84">
           <cell r="A84" t="str">
@@ -3077,18 +2488,11 @@
             <v>19808.55</v>
           </cell>
           <cell r="E84">
-            <v>6003</v>
+            <v>7301</v>
           </cell>
           <cell r="F84">
-            <v>54139.75</v>
-          </cell>
-          <cell r="G84"/>
-          <cell r="H84"/>
-          <cell r="I84"/>
-          <cell r="J84"/>
-          <cell r="K84"/>
-          <cell r="L84"/>
-          <cell r="M84"/>
+            <v>55437.75</v>
+          </cell>
         </row>
         <row r="85">
           <cell r="A85" t="str">
@@ -3104,18 +2508,11 @@
             <v>4296.6099999999997</v>
           </cell>
           <cell r="E85">
-            <v>610.55999999999995</v>
+            <v>4715.6899999999996</v>
           </cell>
           <cell r="F85">
-            <v>13500.389999999998</v>
-          </cell>
-          <cell r="G85"/>
-          <cell r="H85"/>
-          <cell r="I85"/>
-          <cell r="J85"/>
-          <cell r="K85"/>
-          <cell r="L85"/>
-          <cell r="M85"/>
+            <v>17605.519999999997</v>
+          </cell>
         </row>
         <row r="86">
           <cell r="A86" t="str">
@@ -3136,13 +2533,6 @@
           <cell r="F86">
             <v>18256</v>
           </cell>
-          <cell r="G86"/>
-          <cell r="H86"/>
-          <cell r="I86"/>
-          <cell r="J86"/>
-          <cell r="K86"/>
-          <cell r="L86"/>
-          <cell r="M86"/>
         </row>
         <row r="87">
           <cell r="A87" t="str">
@@ -3163,13 +2553,6 @@
           <cell r="F87">
             <v>2751.99</v>
           </cell>
-          <cell r="G87"/>
-          <cell r="H87"/>
-          <cell r="I87"/>
-          <cell r="J87"/>
-          <cell r="K87"/>
-          <cell r="L87"/>
-          <cell r="M87"/>
         </row>
         <row r="88">
           <cell r="A88" t="str">
@@ -3184,17 +2567,9 @@
           <cell r="D88">
             <v>9958.6499999999978</v>
           </cell>
-          <cell r="E88"/>
           <cell r="F88">
             <v>24550.729999999996</v>
           </cell>
-          <cell r="G88"/>
-          <cell r="H88"/>
-          <cell r="I88"/>
-          <cell r="J88"/>
-          <cell r="K88"/>
-          <cell r="L88"/>
-          <cell r="M88"/>
         </row>
         <row r="89">
           <cell r="A89" t="str">
@@ -3210,18 +2585,11 @@
             <v>7759.59</v>
           </cell>
           <cell r="E89">
-            <v>2280.7200000000003</v>
+            <v>2492.92</v>
           </cell>
           <cell r="F89">
-            <v>13970.310000000001</v>
-          </cell>
-          <cell r="G89"/>
-          <cell r="H89"/>
-          <cell r="I89"/>
-          <cell r="J89"/>
-          <cell r="K89"/>
-          <cell r="L89"/>
-          <cell r="M89"/>
+            <v>14182.51</v>
+          </cell>
         </row>
         <row r="90">
           <cell r="A90" t="str">
@@ -3234,19 +2602,11 @@
             <v>45445.030000000006</v>
           </cell>
           <cell r="D90">
-            <v>61558.19</v>
-          </cell>
-          <cell r="E90"/>
+            <v>61484.200000000004</v>
+          </cell>
           <cell r="F90">
-            <v>142703.06</v>
-          </cell>
-          <cell r="G90"/>
-          <cell r="H90"/>
-          <cell r="I90"/>
-          <cell r="J90"/>
-          <cell r="K90"/>
-          <cell r="L90"/>
-          <cell r="M90"/>
+            <v>142629.07</v>
+          </cell>
         </row>
         <row r="91">
           <cell r="A91" t="str">
@@ -3259,21 +2619,14 @@
             <v>1807.69</v>
           </cell>
           <cell r="D91">
-            <v>2500</v>
+            <v>2581.66</v>
           </cell>
           <cell r="E91">
-            <v>118.65</v>
+            <v>2175.61</v>
           </cell>
           <cell r="F91">
-            <v>5164.5</v>
-          </cell>
-          <cell r="G91"/>
-          <cell r="H91"/>
-          <cell r="I91"/>
-          <cell r="J91"/>
-          <cell r="K91"/>
-          <cell r="L91"/>
-          <cell r="M91"/>
+            <v>7303.1200000000008</v>
+          </cell>
         </row>
         <row r="92">
           <cell r="A92" t="str">
@@ -3286,21 +2639,14 @@
             <v>18270.349999999999</v>
           </cell>
           <cell r="D92">
-            <v>22670.71</v>
+            <v>22418.71</v>
           </cell>
           <cell r="E92">
-            <v>5157.8499999999995</v>
+            <v>5409.8499999999995</v>
           </cell>
           <cell r="F92">
             <v>57286.639999999992</v>
           </cell>
-          <cell r="G92"/>
-          <cell r="H92"/>
-          <cell r="I92"/>
-          <cell r="J92"/>
-          <cell r="K92"/>
-          <cell r="L92"/>
-          <cell r="M92"/>
         </row>
         <row r="93">
           <cell r="A93" t="str">
@@ -3316,18 +2662,11 @@
             <v>67412.58</v>
           </cell>
           <cell r="E93">
-            <v>35740.800000000003</v>
+            <v>41946.38</v>
           </cell>
           <cell r="F93">
-            <v>241075.47</v>
-          </cell>
-          <cell r="G93"/>
-          <cell r="H93"/>
-          <cell r="I93"/>
-          <cell r="J93"/>
-          <cell r="K93"/>
-          <cell r="L93"/>
-          <cell r="M93"/>
+            <v>247281.05</v>
+          </cell>
         </row>
         <row r="94">
           <cell r="A94" t="str">
@@ -3343,18 +2682,11 @@
             <v>20130.41</v>
           </cell>
           <cell r="E94">
-            <v>5008.41</v>
+            <v>10016.82</v>
           </cell>
           <cell r="F94">
-            <v>55625.149999999994</v>
-          </cell>
-          <cell r="G94"/>
-          <cell r="H94"/>
-          <cell r="I94"/>
-          <cell r="J94"/>
-          <cell r="K94"/>
-          <cell r="L94"/>
-          <cell r="M94"/>
+            <v>60633.56</v>
+          </cell>
         </row>
         <row r="95">
           <cell r="A95" t="str">
@@ -3369,17 +2701,9 @@
           <cell r="D95">
             <v>6035.41</v>
           </cell>
-          <cell r="E95"/>
           <cell r="F95">
             <v>18106.23</v>
           </cell>
-          <cell r="G95"/>
-          <cell r="H95"/>
-          <cell r="I95"/>
-          <cell r="J95"/>
-          <cell r="K95"/>
-          <cell r="L95"/>
-          <cell r="M95"/>
         </row>
         <row r="96">
           <cell r="A96" t="str">
@@ -3400,13 +2724,6 @@
           <cell r="F96">
             <v>42695</v>
           </cell>
-          <cell r="G96"/>
-          <cell r="H96"/>
-          <cell r="I96"/>
-          <cell r="J96"/>
-          <cell r="K96"/>
-          <cell r="L96"/>
-          <cell r="M96"/>
         </row>
         <row r="97">
           <cell r="A97" t="str">
@@ -3427,13 +2744,6 @@
           <cell r="F97">
             <v>32556</v>
           </cell>
-          <cell r="G97"/>
-          <cell r="H97"/>
-          <cell r="I97"/>
-          <cell r="J97"/>
-          <cell r="K97"/>
-          <cell r="L97"/>
-          <cell r="M97"/>
         </row>
         <row r="98">
           <cell r="A98" t="str">
@@ -3454,13 +2764,6 @@
           <cell r="F98">
             <v>29005.78</v>
           </cell>
-          <cell r="G98"/>
-          <cell r="H98"/>
-          <cell r="I98"/>
-          <cell r="J98"/>
-          <cell r="K98"/>
-          <cell r="L98"/>
-          <cell r="M98"/>
         </row>
         <row r="99">
           <cell r="A99" t="str">
@@ -3476,18 +2779,11 @@
             <v>10818.33</v>
           </cell>
           <cell r="E99">
-            <v>6648.3899999999994</v>
+            <v>7845.5599999999995</v>
           </cell>
           <cell r="F99">
-            <v>52413.81</v>
-          </cell>
-          <cell r="G99"/>
-          <cell r="H99"/>
-          <cell r="I99"/>
-          <cell r="J99"/>
-          <cell r="K99"/>
-          <cell r="L99"/>
-          <cell r="M99"/>
+            <v>53610.979999999996</v>
+          </cell>
         </row>
         <row r="100">
           <cell r="A100" t="str">
@@ -3508,34 +2804,17 @@
           <cell r="F100">
             <v>3673.5</v>
           </cell>
-          <cell r="G100"/>
-          <cell r="H100"/>
-          <cell r="I100"/>
-          <cell r="J100"/>
-          <cell r="K100"/>
-          <cell r="L100"/>
-          <cell r="M100"/>
         </row>
         <row r="101">
           <cell r="A101" t="str">
             <v>Consultoria Tributaria</v>
           </cell>
-          <cell r="B101"/>
-          <cell r="C101"/>
-          <cell r="D101"/>
           <cell r="E101">
             <v>7000</v>
           </cell>
           <cell r="F101">
             <v>7000</v>
           </cell>
-          <cell r="G101"/>
-          <cell r="H101"/>
-          <cell r="I101"/>
-          <cell r="J101"/>
-          <cell r="K101"/>
-          <cell r="L101"/>
-          <cell r="M101"/>
         </row>
         <row r="102">
           <cell r="A102" t="str">
@@ -3551,18 +2830,11 @@
             <v>55657.97</v>
           </cell>
           <cell r="E102">
-            <v>38094.359999999993</v>
+            <v>45281.599999999991</v>
           </cell>
           <cell r="F102">
-            <v>211752.66999999998</v>
-          </cell>
-          <cell r="G102"/>
-          <cell r="H102"/>
-          <cell r="I102"/>
-          <cell r="J102"/>
-          <cell r="K102"/>
-          <cell r="L102"/>
-          <cell r="M102"/>
+            <v>218939.90999999997</v>
+          </cell>
         </row>
         <row r="103">
           <cell r="A103" t="str">
@@ -3578,18 +2850,11 @@
             <v>9300.989999999998</v>
           </cell>
           <cell r="E103">
-            <v>5789.5699999999988</v>
+            <v>6360.23</v>
           </cell>
           <cell r="F103">
-            <v>34519.19999999999</v>
-          </cell>
-          <cell r="G103"/>
-          <cell r="H103"/>
-          <cell r="I103"/>
-          <cell r="J103"/>
-          <cell r="K103"/>
-          <cell r="L103"/>
-          <cell r="M103"/>
+            <v>35089.859999999986</v>
+          </cell>
         </row>
         <row r="104">
           <cell r="A104" t="str">
@@ -3605,18 +2870,11 @@
             <v>251.57000000000002</v>
           </cell>
           <cell r="E104">
-            <v>123.10000000000001</v>
+            <v>183.16000000000003</v>
           </cell>
           <cell r="F104">
-            <v>614.20000000000005</v>
-          </cell>
-          <cell r="G104"/>
-          <cell r="H104"/>
-          <cell r="I104"/>
-          <cell r="J104"/>
-          <cell r="K104"/>
-          <cell r="L104"/>
-          <cell r="M104"/>
+            <v>674.26</v>
+          </cell>
         </row>
         <row r="105">
           <cell r="A105" t="str">
@@ -3632,18 +2890,11 @@
             <v>13530.41</v>
           </cell>
           <cell r="E105">
-            <v>8.9</v>
+            <v>4872.24</v>
           </cell>
           <cell r="F105">
-            <v>31529.140000000003</v>
-          </cell>
-          <cell r="G105"/>
-          <cell r="H105"/>
-          <cell r="I105"/>
-          <cell r="J105"/>
-          <cell r="K105"/>
-          <cell r="L105"/>
-          <cell r="M105"/>
+            <v>36392.480000000003</v>
+          </cell>
         </row>
         <row r="106">
           <cell r="A106" t="str">
@@ -3664,34 +2915,17 @@
           <cell r="F106">
             <v>40004.299999999996</v>
           </cell>
-          <cell r="G106"/>
-          <cell r="H106"/>
-          <cell r="I106"/>
-          <cell r="J106"/>
-          <cell r="K106"/>
-          <cell r="L106"/>
-          <cell r="M106"/>
         </row>
         <row r="107">
           <cell r="A107" t="str">
             <v>Juros Pagos</v>
           </cell>
-          <cell r="B107"/>
           <cell r="C107">
             <v>95.75</v>
           </cell>
-          <cell r="D107"/>
-          <cell r="E107"/>
           <cell r="F107">
             <v>95.75</v>
           </cell>
-          <cell r="G107"/>
-          <cell r="H107"/>
-          <cell r="I107"/>
-          <cell r="J107"/>
-          <cell r="K107"/>
-          <cell r="L107"/>
-          <cell r="M107"/>
         </row>
         <row r="108">
           <cell r="A108" t="str">
@@ -3707,18 +2941,11 @@
             <v>29003.100000000002</v>
           </cell>
           <cell r="E108">
-            <v>17023.229999999996</v>
+            <v>18716.409999999996</v>
           </cell>
           <cell r="F108">
-            <v>104990.07999999999</v>
-          </cell>
-          <cell r="G108"/>
-          <cell r="H108"/>
-          <cell r="I108"/>
-          <cell r="J108"/>
-          <cell r="K108"/>
-          <cell r="L108"/>
-          <cell r="M108"/>
+            <v>106683.25999999998</v>
+          </cell>
         </row>
         <row r="109">
           <cell r="A109" t="str">
@@ -3734,18 +2961,11 @@
             <v>26833.7</v>
           </cell>
           <cell r="E109">
-            <v>6216.37</v>
+            <v>6236.2699999999995</v>
           </cell>
           <cell r="F109">
-            <v>112628.33</v>
-          </cell>
-          <cell r="G109"/>
-          <cell r="H109"/>
-          <cell r="I109"/>
-          <cell r="J109"/>
-          <cell r="K109"/>
-          <cell r="L109"/>
-          <cell r="M109"/>
+            <v>112648.23000000001</v>
+          </cell>
         </row>
         <row r="110">
           <cell r="A110" t="str">
@@ -3761,18 +2981,11 @@
             <v>2407.11</v>
           </cell>
           <cell r="E110">
-            <v>1222.06</v>
+            <v>1241.96</v>
           </cell>
           <cell r="F110">
-            <v>18141.399999999998</v>
-          </cell>
-          <cell r="G110"/>
-          <cell r="H110"/>
-          <cell r="I110"/>
-          <cell r="J110"/>
-          <cell r="K110"/>
-          <cell r="L110"/>
-          <cell r="M110"/>
+            <v>18161.299999999996</v>
+          </cell>
         </row>
         <row r="111">
           <cell r="A111" t="str">
@@ -3793,13 +3006,6 @@
           <cell r="F111">
             <v>12149.76</v>
           </cell>
-          <cell r="G111"/>
-          <cell r="H111"/>
-          <cell r="I111"/>
-          <cell r="J111"/>
-          <cell r="K111"/>
-          <cell r="L111"/>
-          <cell r="M111"/>
         </row>
         <row r="112">
           <cell r="A112" t="str">
@@ -3814,17 +3020,9 @@
           <cell r="D112">
             <v>2570</v>
           </cell>
-          <cell r="E112"/>
           <cell r="F112">
             <v>22294.41</v>
           </cell>
-          <cell r="G112"/>
-          <cell r="H112"/>
-          <cell r="I112"/>
-          <cell r="J112"/>
-          <cell r="K112"/>
-          <cell r="L112"/>
-          <cell r="M112"/>
         </row>
         <row r="113">
           <cell r="A113" t="str">
@@ -3845,34 +3043,17 @@
           <cell r="F113">
             <v>55957.760000000009</v>
           </cell>
-          <cell r="G113"/>
-          <cell r="H113"/>
-          <cell r="I113"/>
-          <cell r="J113"/>
-          <cell r="K113"/>
-          <cell r="L113"/>
-          <cell r="M113"/>
         </row>
         <row r="114">
           <cell r="A114" t="str">
             <v>Moveis e Utensilios</v>
           </cell>
-          <cell r="B114"/>
-          <cell r="C114"/>
           <cell r="D114">
             <v>4085</v>
           </cell>
-          <cell r="E114"/>
           <cell r="F114">
             <v>4085</v>
           </cell>
-          <cell r="G114"/>
-          <cell r="H114"/>
-          <cell r="I114"/>
-          <cell r="J114"/>
-          <cell r="K114"/>
-          <cell r="L114"/>
-          <cell r="M114"/>
         </row>
         <row r="115">
           <cell r="A115" t="str">
@@ -3885,246 +3066,14 @@
             <v>1221760.2699999996</v>
           </cell>
           <cell r="D115">
-            <v>1381034.77</v>
+            <v>1380790.44</v>
           </cell>
           <cell r="E115">
-            <v>307656.68</v>
+            <v>416997.49999999988</v>
           </cell>
           <cell r="F115">
-            <v>4208070.07</v>
-          </cell>
-          <cell r="G115"/>
-          <cell r="H115"/>
-          <cell r="I115"/>
-          <cell r="J115"/>
-          <cell r="K115"/>
-          <cell r="L115"/>
-          <cell r="M115"/>
-        </row>
-        <row r="116">
-          <cell r="A116"/>
-          <cell r="B116"/>
-          <cell r="C116"/>
-          <cell r="D116"/>
-          <cell r="E116"/>
-          <cell r="F116"/>
-          <cell r="G116"/>
-          <cell r="H116"/>
-          <cell r="I116"/>
-          <cell r="J116"/>
-          <cell r="K116"/>
-          <cell r="L116"/>
-          <cell r="M116"/>
-        </row>
-        <row r="117">
-          <cell r="A117"/>
-          <cell r="B117"/>
-          <cell r="C117"/>
-          <cell r="D117"/>
-          <cell r="E117"/>
-          <cell r="F117"/>
-          <cell r="G117"/>
-          <cell r="H117"/>
-          <cell r="I117"/>
-          <cell r="J117"/>
-          <cell r="K117"/>
-          <cell r="L117"/>
-          <cell r="M117"/>
-        </row>
-        <row r="118">
-          <cell r="A118"/>
-          <cell r="B118"/>
-          <cell r="C118"/>
-          <cell r="D118"/>
-          <cell r="E118"/>
-          <cell r="F118"/>
-          <cell r="G118"/>
-          <cell r="H118"/>
-          <cell r="I118"/>
-          <cell r="J118"/>
-          <cell r="K118"/>
-          <cell r="L118"/>
-          <cell r="M118"/>
-        </row>
-        <row r="119">
-          <cell r="A119"/>
-          <cell r="B119"/>
-          <cell r="C119"/>
-          <cell r="D119"/>
-          <cell r="E119"/>
-          <cell r="F119"/>
-          <cell r="G119"/>
-          <cell r="H119"/>
-          <cell r="I119"/>
-          <cell r="J119"/>
-          <cell r="K119"/>
-          <cell r="L119"/>
-          <cell r="M119"/>
-        </row>
-        <row r="120">
-          <cell r="A120"/>
-          <cell r="B120"/>
-          <cell r="C120"/>
-          <cell r="D120"/>
-          <cell r="E120"/>
-          <cell r="F120"/>
-          <cell r="G120"/>
-          <cell r="H120"/>
-          <cell r="I120"/>
-          <cell r="J120"/>
-          <cell r="K120"/>
-          <cell r="L120"/>
-          <cell r="M120"/>
-        </row>
-        <row r="121">
-          <cell r="A121"/>
-          <cell r="B121"/>
-          <cell r="C121"/>
-          <cell r="D121"/>
-          <cell r="E121"/>
-          <cell r="F121"/>
-          <cell r="G121"/>
-          <cell r="H121"/>
-          <cell r="I121"/>
-          <cell r="J121"/>
-          <cell r="K121"/>
-          <cell r="L121"/>
-          <cell r="M121"/>
-        </row>
-        <row r="122">
-          <cell r="A122"/>
-          <cell r="B122"/>
-          <cell r="C122"/>
-          <cell r="D122"/>
-          <cell r="E122"/>
-          <cell r="F122"/>
-          <cell r="G122"/>
-          <cell r="H122"/>
-          <cell r="I122"/>
-          <cell r="J122"/>
-          <cell r="K122"/>
-          <cell r="L122"/>
-          <cell r="M122"/>
-        </row>
-        <row r="123">
-          <cell r="A123"/>
-          <cell r="B123"/>
-          <cell r="C123"/>
-          <cell r="D123"/>
-          <cell r="E123"/>
-          <cell r="F123"/>
-          <cell r="G123"/>
-          <cell r="H123"/>
-          <cell r="I123"/>
-          <cell r="J123"/>
-          <cell r="K123"/>
-          <cell r="L123"/>
-          <cell r="M123"/>
-        </row>
-        <row r="124">
-          <cell r="A124"/>
-          <cell r="B124"/>
-          <cell r="C124"/>
-          <cell r="D124"/>
-          <cell r="E124"/>
-          <cell r="F124"/>
-          <cell r="G124"/>
-          <cell r="H124"/>
-          <cell r="I124"/>
-          <cell r="J124"/>
-          <cell r="K124"/>
-          <cell r="L124"/>
-          <cell r="M124"/>
-        </row>
-        <row r="125">
-          <cell r="A125"/>
-          <cell r="B125"/>
-          <cell r="C125"/>
-          <cell r="D125"/>
-          <cell r="E125"/>
-          <cell r="F125"/>
-          <cell r="G125"/>
-          <cell r="H125"/>
-          <cell r="I125"/>
-          <cell r="J125"/>
-          <cell r="K125"/>
-          <cell r="L125"/>
-          <cell r="M125"/>
-        </row>
-        <row r="126">
-          <cell r="A126"/>
-          <cell r="B126"/>
-          <cell r="C126"/>
-          <cell r="D126"/>
-          <cell r="E126"/>
-          <cell r="F126"/>
-          <cell r="G126"/>
-          <cell r="H126"/>
-          <cell r="I126"/>
-          <cell r="J126"/>
-          <cell r="K126"/>
-          <cell r="L126"/>
-          <cell r="M126"/>
-        </row>
-        <row r="127">
-          <cell r="A127"/>
-          <cell r="B127"/>
-          <cell r="C127"/>
-          <cell r="D127"/>
-          <cell r="E127"/>
-          <cell r="F127"/>
-          <cell r="G127"/>
-          <cell r="H127"/>
-          <cell r="I127"/>
-          <cell r="J127"/>
-          <cell r="K127"/>
-          <cell r="L127"/>
-          <cell r="M127"/>
-        </row>
-        <row r="128">
-          <cell r="A128"/>
-          <cell r="B128"/>
-          <cell r="C128"/>
-          <cell r="D128"/>
-          <cell r="E128"/>
-          <cell r="F128"/>
-          <cell r="G128"/>
-          <cell r="H128"/>
-          <cell r="I128"/>
-          <cell r="J128"/>
-          <cell r="K128"/>
-          <cell r="L128"/>
-          <cell r="M128"/>
-        </row>
-        <row r="129">
-          <cell r="A129"/>
-          <cell r="B129"/>
-          <cell r="C129"/>
-          <cell r="D129"/>
-          <cell r="E129"/>
-          <cell r="F129"/>
-          <cell r="G129"/>
-          <cell r="H129"/>
-          <cell r="I129"/>
-          <cell r="J129"/>
-          <cell r="K129"/>
-          <cell r="L129"/>
-          <cell r="M129"/>
-        </row>
-        <row r="130">
-          <cell r="A130"/>
-          <cell r="B130"/>
-          <cell r="C130"/>
-          <cell r="D130"/>
-          <cell r="E130"/>
-          <cell r="F130"/>
-          <cell r="G130"/>
-          <cell r="H130"/>
-          <cell r="I130"/>
-          <cell r="J130"/>
-          <cell r="K130"/>
-          <cell r="L130"/>
-          <cell r="M130"/>
+            <v>4317166.5599999996</v>
+          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="9"/>
@@ -6607,11 +5556,11 @@
       </c>
       <c r="AB23" s="7">
         <f>AB24+AB32+AB46</f>
-        <v>366735.60000000003</v>
+        <v>573381.71</v>
       </c>
       <c r="AC23" s="14">
         <f>IFERROR((AB23*-1)/Z23-1,"")</f>
-        <v>-0.73556345792898536</v>
+        <v>-0.58656024482170444</v>
       </c>
       <c r="AD23" s="7">
         <v>-1455440.7019585797</v>
@@ -6745,11 +5694,11 @@
       </c>
       <c r="AB24" s="8">
         <f>SUM(AB25:AB31)</f>
-        <v>318636.04000000004</v>
+        <v>518059.83999999997</v>
       </c>
       <c r="AC24" s="45">
         <f>IFERROR((AB24*-1)/Z24-1,"")</f>
-        <v>0.12882982894055628</v>
+        <v>0.83532722967612782</v>
       </c>
       <c r="AD24" s="8">
         <v>-988112.6561191252</v>
@@ -6894,11 +5843,11 @@
         <v>-8.2750000000000004E-2</v>
       </c>
       <c r="AB25" s="47">
-        <v>318043.45</v>
+        <v>513052.18</v>
       </c>
       <c r="AC25" s="46">
         <f t="shared" ref="AC25:AC31" si="18">IFERROR((AB25*-1)/Z25-1,"")</f>
-        <v>4.2496789180814334</v>
+        <v>7.4685259615367681</v>
       </c>
       <c r="AD25" s="6">
         <v>-212077.09063378972</v>
@@ -7806,11 +6755,11 @@
       </c>
       <c r="AB31" s="6">
         <f>IFERROR(VLOOKUP($I31,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>592.58999999999992</v>
+        <v>5007.66</v>
       </c>
       <c r="AC31" s="46">
         <f t="shared" si="18"/>
-        <v>-0.84206632647945101</v>
+        <v>0.33461269940753668</v>
       </c>
       <c r="AD31" s="6">
         <v>-13134.683861005104</v>
@@ -7939,11 +6888,11 @@
       </c>
       <c r="AB32" s="8">
         <f>SUM(AB33:AB45)</f>
-        <v>29888.550000000003</v>
+        <v>35596.559999999998</v>
       </c>
       <c r="AC32" s="45">
         <f>(AB32*-1)/Z32-1</f>
-        <v>-0.91448090519643233</v>
+        <v>-0.89814876970208046</v>
       </c>
       <c r="AD32" s="8">
         <v>-369175.10009796615</v>
@@ -8227,11 +7176,11 @@
       </c>
       <c r="AB34" s="6">
         <f>IFERROR(VLOOKUP($I34,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>3881.96</v>
+        <v>7049.37</v>
       </c>
       <c r="AC34" s="46">
         <f t="shared" si="24"/>
-        <v>-0.79618966771654942</v>
+        <v>-0.62989457848896224</v>
       </c>
       <c r="AD34" s="6">
         <v>-19046.924444444445</v>
@@ -8505,11 +7454,11 @@
       </c>
       <c r="AB36" s="6">
         <f>IFERROR(VLOOKUP($I36,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>6766.4299999999994</v>
+        <v>7266.4299999999994</v>
       </c>
       <c r="AC36" s="46">
         <f t="shared" si="24"/>
-        <v>-0.96749451062883496</v>
+        <v>-0.96509254316806437</v>
       </c>
       <c r="AD36" s="6">
         <v>-221693.26133550002</v>
@@ -9366,11 +8315,11 @@
       </c>
       <c r="AB42" s="6">
         <f>IFERROR(VLOOKUP($I42,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>2040.6</v>
       </c>
       <c r="AC42" s="46">
         <f t="shared" si="24"/>
-        <v>-1</v>
+        <v>5.1746339083308834E-2</v>
       </c>
       <c r="AD42" s="6">
         <v>-1940.2016666666657</v>
@@ -9913,11 +8862,11 @@
       </c>
       <c r="AB46" s="8">
         <f>SUM(AB47:AB62)</f>
-        <v>18211.010000000002</v>
+        <v>19725.310000000001</v>
       </c>
       <c r="AC46" s="45">
         <f>(AB46*-1)/Z46-1</f>
-        <v>-0.80664915941101545</v>
+        <v>-0.79057145817951324</v>
       </c>
       <c r="AD46" s="6">
         <v>-98152.945741488365</v>
@@ -11044,11 +9993,11 @@
       </c>
       <c r="AB54" s="6">
         <f>IFERROR(VLOOKUP($I54,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>276.27999999999997</v>
       </c>
       <c r="AC54" s="46">
         <f t="shared" si="27"/>
-        <v>-1</v>
+        <v>-0.44185238421841022</v>
       </c>
       <c r="AD54" s="6">
         <v>-494.99449999999968</v>
@@ -11887,11 +10836,11 @@
       </c>
       <c r="AB60" s="6">
         <f>IFERROR(VLOOKUP($I60,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>1239.0999999999999</v>
+        <v>2093.6</v>
       </c>
       <c r="AC60" s="46">
         <f t="shared" si="27"/>
-        <v>-0.36456410256410265</v>
+        <v>7.3641025641025593E-2</v>
       </c>
       <c r="AD60" s="6">
         <v>-1950</v>
@@ -12026,11 +10975,11 @@
       </c>
       <c r="AB61" s="6">
         <f>IFERROR(VLOOKUP($I61,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>6172.05</v>
+        <v>6555.5700000000006</v>
       </c>
       <c r="AC61" s="46">
         <f t="shared" si="27"/>
-        <v>-0.11827857142857146</v>
+        <v>-6.3489999999999935E-2</v>
       </c>
       <c r="AD61" s="6">
         <v>-7000</v>
@@ -12310,11 +11259,11 @@
       </c>
       <c r="AB64" s="48">
         <f>AB21-AB23</f>
-        <v>365390.2</v>
+        <v>158744.09000000008</v>
       </c>
       <c r="AC64" s="14">
         <f>AB64/Z64-1</f>
-        <v>-0.57959094746314488</v>
+        <v>-0.81735292169104345</v>
       </c>
       <c r="AD64" s="7">
         <v>908033.53347925539</v>
@@ -12435,11 +11384,11 @@
       </c>
       <c r="X66" s="7">
         <f>SUM(X67+X85+X101+X123)</f>
-        <v>659011.41999999993</v>
+        <v>658767.09</v>
       </c>
       <c r="Y66" s="14">
         <f t="shared" ref="Y66" si="30">IFERROR((X66*-1)/V66-1,"")</f>
-        <v>-0.10505028577747111</v>
+        <v>-0.10538209044282265</v>
       </c>
       <c r="Z66" s="7">
         <v>-702233.64180127438</v>
@@ -12449,11 +11398,11 @@
       </c>
       <c r="AB66" s="7">
         <f>SUM(AB67+AB85+AB101+AB123)</f>
-        <v>207653.8</v>
+        <v>298150.10000000003</v>
       </c>
       <c r="AC66" s="14">
         <f t="shared" ref="AC66" si="31">IFERROR((AB66*-1)/Z66-1,"")</f>
-        <v>-0.70429528345102543</v>
+        <v>-0.57542606583867739</v>
       </c>
       <c r="AD66" s="7">
         <v>-719188.9048191926</v>
@@ -12583,11 +11532,11 @@
       </c>
       <c r="AB67" s="8">
         <f>SUM(AB68:AB84)</f>
-        <v>41565.769999999997</v>
+        <v>76539.61</v>
       </c>
       <c r="AC67" s="45">
         <f>(AB67*-1)/Z67-1</f>
-        <v>-0.76228837806609118</v>
+        <v>-0.56227552538329428</v>
       </c>
       <c r="AD67" s="8">
         <v>-180578.51873174944</v>
@@ -12723,11 +11672,11 @@
       </c>
       <c r="AB68" s="6">
         <f>IFERROR(VLOOKUP($I68,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>30930.639999999999</v>
+        <v>51717.240000000005</v>
       </c>
       <c r="AC68" s="46">
         <f t="shared" ref="AC68:AC84" si="34">IFERROR((AB68*-1)/Z68-1,"")</f>
-        <v>-0.5159524256651018</v>
+        <v>-0.19065352112676048</v>
       </c>
       <c r="AD68" s="6">
         <v>-63900</v>
@@ -13277,11 +12226,11 @@
       </c>
       <c r="AB72" s="6">
         <f>IFERROR(VLOOKUP($I72,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>1529.83</v>
+        <v>2681.09</v>
       </c>
       <c r="AC72" s="46">
         <f t="shared" si="34"/>
-        <v>-0.77245989315727182</v>
+        <v>-0.60122660357361912</v>
       </c>
       <c r="AD72" s="6">
         <v>-7160.3594311666666</v>
@@ -13705,11 +12654,11 @@
       </c>
       <c r="AB75" s="6">
         <f>IFERROR(VLOOKUP($I75,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>12417.35</v>
       </c>
       <c r="AC75" s="46">
         <f t="shared" si="34"/>
-        <v>-1</v>
+        <v>0.86260249999999994</v>
       </c>
       <c r="AD75" s="6">
         <v>-6666.666666666667</v>
@@ -14129,11 +13078,11 @@
       </c>
       <c r="AB78" s="6">
         <f>IFERROR(VLOOKUP($I78,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>600.63</v>
       </c>
       <c r="AC78" s="46">
         <f t="shared" si="34"/>
-        <v>-1</v>
+        <v>-1.3532186435185722E-2</v>
       </c>
       <c r="AD78" s="6">
         <v>-608.86933333333388</v>
@@ -14703,11 +13652,11 @@
       </c>
       <c r="AB82" s="6">
         <f>IFERROR(VLOOKUP($I82,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AC82" s="46">
         <f t="shared" si="34"/>
-        <v>-0.95303641913877735</v>
+        <v>-0.9444104553071242</v>
       </c>
       <c r="AD82" s="6">
         <v>-2086.7233333333334</v>
@@ -15114,11 +14063,11 @@
       </c>
       <c r="AB85" s="8">
         <f>SUM(AB86:AB100)</f>
-        <v>4876.8</v>
+        <v>5156.8</v>
       </c>
       <c r="AC85" s="45">
         <f>(AB85*-1)/Z85-1</f>
-        <v>-0.76041989307056201</v>
+        <v>-0.74666447354541376</v>
       </c>
       <c r="AD85" s="8">
         <v>-20355.613253968255</v>
@@ -15550,11 +14499,11 @@
       </c>
       <c r="AB88" s="6">
         <f>IFERROR(VLOOKUP($I88,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC88" s="46">
         <f t="shared" si="37"/>
-        <v>-1</v>
+        <v>2.458409910017334E-3</v>
       </c>
       <c r="AD88" s="6">
         <v>-59.852857142857147</v>
@@ -16716,11 +15665,11 @@
       </c>
       <c r="AB96" s="6">
         <f>IFERROR(VLOOKUP($I96,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AC96" s="46">
         <f t="shared" si="37"/>
-        <v>-1</v>
+        <v>-0.8551039629066145</v>
       </c>
       <c r="AD96" s="6">
         <v>-828.18</v>
@@ -17290,11 +16239,11 @@
       </c>
       <c r="AB100" s="6">
         <f>IFERROR(VLOOKUP($I100,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC100" s="46">
         <f t="shared" si="37"/>
-        <v>-1</v>
+        <v>-0.76</v>
       </c>
       <c r="AD100" s="6">
         <v>-416.66666666666669</v>
@@ -17409,11 +16358,11 @@
       </c>
       <c r="X101" s="8">
         <f>SUM(X102:X122)</f>
-        <v>386839.54</v>
+        <v>386595.21</v>
       </c>
       <c r="Y101" s="45">
         <f>(X101*-1)/V101-1</f>
-        <v>-0.17755012061202957</v>
+        <v>-0.17806958451954746</v>
       </c>
       <c r="Z101" s="8">
         <v>-436216.95079197281</v>
@@ -17423,11 +16372,11 @@
       </c>
       <c r="AB101" s="8">
         <f>SUM(AB102:AB122)</f>
-        <v>132470.43</v>
+        <v>181507.31000000003</v>
       </c>
       <c r="AC101" s="45">
         <f>(AB101*-1)/Z101-1</f>
-        <v>-0.69631984782000433</v>
+        <v>-0.58390587603149124</v>
       </c>
       <c r="AD101" s="8">
         <v>-447451.65810847498</v>
@@ -17572,11 +16521,11 @@
       </c>
       <c r="AB102" s="6">
         <f>IFERROR(VLOOKUP($I102,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AC102" s="46">
         <f t="shared" ref="AC102:AC122" si="40">IFERROR((AB102*-1)/Z102-1,"")</f>
-        <v>-1</v>
+        <v>-0.97707322881806269</v>
       </c>
       <c r="AD102" s="6">
         <v>-3751.0733333333333</v>
@@ -17711,11 +16660,11 @@
       </c>
       <c r="AB103" s="6">
         <f>IFERROR(VLOOKUP($I103,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>26021.809999999998</v>
+        <v>28146.19</v>
       </c>
       <c r="AC103" s="46">
         <f t="shared" si="40"/>
-        <v>-0.59087813302094949</v>
+        <v>-0.55747806162803115</v>
       </c>
       <c r="AD103" s="6">
         <v>-66634.493733879543</v>
@@ -17998,11 +16947,11 @@
       </c>
       <c r="AB105" s="6">
         <f>IFERROR(VLOOKUP($I105,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>610.55999999999995</v>
+        <v>4715.6899999999996</v>
       </c>
       <c r="AC105" s="46">
         <f t="shared" si="40"/>
-        <v>-0.969472</v>
+        <v>-0.76421550000000005</v>
       </c>
       <c r="AD105" s="6">
         <v>-20000</v>
@@ -18280,11 +17229,11 @@
       </c>
       <c r="X107" s="6">
         <f>IFERROR(VLOOKUP($I107,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>22670.71</v>
+        <v>22418.71</v>
       </c>
       <c r="Y107" s="46">
         <f t="shared" si="39"/>
-        <v>0.42484796127004198</v>
+        <v>0.40900982976732103</v>
       </c>
       <c r="Z107" s="6">
         <v>-15910.96777777778</v>
@@ -18294,11 +17243,11 @@
       </c>
       <c r="AB107" s="6">
         <f>IFERROR(VLOOKUP($I107,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>5157.8499999999995</v>
+        <v>5409.8499999999995</v>
       </c>
       <c r="AC107" s="46">
         <f t="shared" si="40"/>
-        <v>-0.67583052947893185</v>
+        <v>-0.6599923979762109</v>
       </c>
       <c r="AD107" s="6">
         <v>-15910.96777777778</v>
@@ -18590,11 +17539,11 @@
       </c>
       <c r="AB109" s="6">
         <f>IFERROR(VLOOKUP($I109,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>6003</v>
+        <v>7301</v>
       </c>
       <c r="AC109" s="46">
         <f t="shared" si="40"/>
-        <v>-0.68424928334107704</v>
+        <v>-0.61597601493806486</v>
       </c>
       <c r="AD109" s="6">
         <v>-19011.833333333332</v>
@@ -19016,11 +17965,11 @@
       </c>
       <c r="AB112" s="6">
         <f>IFERROR(VLOOKUP($I112,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>1333.77</v>
+        <v>39467.100000000006</v>
       </c>
       <c r="AC112" s="46">
         <f t="shared" si="40"/>
-        <v>-0.97777049999999999</v>
+        <v>-0.34221499999999994</v>
       </c>
       <c r="AD112" s="6">
         <v>-60000</v>
@@ -19289,11 +18238,11 @@
       </c>
       <c r="X114" s="6">
         <f>IFERROR(VLOOKUP($I114,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>2500</v>
+        <v>2581.66</v>
       </c>
       <c r="Y114" s="46">
         <f t="shared" si="39"/>
-        <v>-0.5</v>
+        <v>-0.48366799999999999</v>
       </c>
       <c r="Z114" s="6">
         <v>-5000</v>
@@ -19303,11 +18252,11 @@
       </c>
       <c r="AB114" s="6">
         <f>IFERROR(VLOOKUP($I114,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>118.65</v>
+        <v>2175.61</v>
       </c>
       <c r="AC114" s="46">
         <f t="shared" si="40"/>
-        <v>-0.97626999999999997</v>
+        <v>-0.56487799999999999</v>
       </c>
       <c r="AD114" s="6">
         <v>-5000</v>
@@ -19729,11 +18678,11 @@
       </c>
       <c r="AB117" s="6">
         <f>IFERROR(VLOOKUP($I117,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>54220.92</v>
+        <v>54479.799999999996</v>
       </c>
       <c r="AC117" s="46">
         <f t="shared" si="40"/>
-        <v>-0.4586542958897426</v>
+        <v>-0.45606961868618245</v>
       </c>
       <c r="AD117" s="6">
         <v>-104931.64492165871</v>
@@ -20002,11 +18951,11 @@
       </c>
       <c r="X119" s="6">
         <f>IFERROR(VLOOKUP($I119,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>61558.19</v>
+        <v>61484.200000000004</v>
       </c>
       <c r="Y119" s="46">
         <f t="shared" si="39"/>
-        <v>-4.6421997506404411E-2</v>
+        <v>-4.7568152654963836E-2</v>
       </c>
       <c r="Z119" s="6">
         <v>-56391.877710522778</v>
@@ -20312,11 +19261,11 @@
       </c>
       <c r="AB121" s="6">
         <f>IFERROR(VLOOKUP($I121,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>2280.7200000000003</v>
+        <v>2492.92</v>
       </c>
       <c r="AC121" s="46">
         <f t="shared" si="40"/>
-        <v>-0.48680163697401568</v>
+        <v>-0.4390532537292009</v>
       </c>
       <c r="AD121" s="6">
         <v>-4655.8716775595331</v>
@@ -20460,11 +19409,11 @@
       </c>
       <c r="AB122" s="6">
         <f>IFERROR(VLOOKUP($I122,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="AC122" s="46">
         <f t="shared" si="40"/>
-        <v>-1</v>
+        <v>-0.97875000000000001</v>
       </c>
       <c r="AD122" s="6">
         <v>-24000</v>
@@ -20593,11 +19542,11 @@
       </c>
       <c r="AB123" s="8">
         <f>SUM(AB124:AB130)</f>
-        <v>28740.799999999999</v>
+        <v>34946.379999999997</v>
       </c>
       <c r="AC123" s="45">
         <f>(AB123*-1)/Z123-1</f>
-        <v>-0.59407435518014196</v>
+        <v>-0.50642877596936087</v>
       </c>
       <c r="AD123" s="8">
         <v>-70803.114724999963</v>
@@ -20874,11 +19823,11 @@
       </c>
       <c r="AB125" s="6">
         <f>IFERROR(VLOOKUP($I125,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>5008.41</v>
+        <v>10016.82</v>
       </c>
       <c r="AC125" s="46">
         <f t="shared" si="43"/>
-        <v>-0.75917526164213511</v>
+        <v>-0.51835052328427023</v>
       </c>
       <c r="AD125" s="6">
         <v>-20796.908299999963</v>
@@ -21294,11 +20243,11 @@
       </c>
       <c r="AB128" s="6">
         <f>IFERROR(VLOOKUP($I128,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>6648.3899999999994</v>
+        <v>7845.5599999999995</v>
       </c>
       <c r="AC128" s="46">
         <f t="shared" si="43"/>
-        <v>-0.43506434903883506</v>
+        <v>-0.333336861141588</v>
       </c>
       <c r="AD128" s="6">
         <v>-11768.402275000035</v>
@@ -21704,11 +20653,11 @@
       </c>
       <c r="X132" s="48">
         <f>X64-X66</f>
-        <v>318060.41999999969</v>
+        <v>318304.74999999965</v>
       </c>
       <c r="Y132" s="14">
         <f>X132/V132-1</f>
-        <v>-1.4686100321830486E-2</v>
+        <v>-1.3929194620994401E-2</v>
       </c>
       <c r="Z132" s="7">
         <v>166896.54889072594</v>
@@ -21718,11 +20667,11 @@
       </c>
       <c r="AB132" s="48">
         <f>AB64-AB66</f>
-        <v>157736.40000000002</v>
+        <v>-139406.00999999995</v>
       </c>
       <c r="AC132" s="14">
         <f>AB132/Z132-1</f>
-        <v>-5.4885190566303699E-2</v>
+        <v>-1.8352839583955376</v>
       </c>
       <c r="AD132" s="7">
         <v>188844.62866006279</v>
@@ -21857,11 +20806,11 @@
       </c>
       <c r="AB134" s="48">
         <f>AB143</f>
-        <v>22944.799999999996</v>
+        <v>30132.039999999994</v>
       </c>
       <c r="AC134" s="14">
         <f t="shared" ref="AC134" si="47">IFERROR((AB134*-1)/Z134-1,"")</f>
-        <v>-0.67361103384165899</v>
+        <v>-0.57137279976980504</v>
       </c>
       <c r="AD134" s="7">
         <v>-70298.945059523816</v>
@@ -22918,7 +21867,7 @@
       </c>
       <c r="AB143" s="49">
         <f>SUM(AB144:AB149)</f>
-        <v>22944.799999999996</v>
+        <v>30132.039999999994</v>
       </c>
       <c r="AC143" s="13"/>
       <c r="AD143" s="8">
@@ -23052,7 +22001,7 @@
       </c>
       <c r="AB144" s="6">
         <f>IFERROR(VLOOKUP($I144,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>5789.5699999999988</v>
+        <v>6360.23</v>
       </c>
       <c r="AD144" s="6">
         <v>-15075.204444444444</v>
@@ -23184,7 +22133,7 @@
       </c>
       <c r="AB145" s="6">
         <f>IFERROR(VLOOKUP($I145,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>17023.229999999996</v>
+        <v>18716.409999999996</v>
       </c>
       <c r="AD145" s="6">
         <v>-40249.912222222221</v>
@@ -23448,7 +22397,7 @@
       </c>
       <c r="AB147" s="6">
         <f>IFERROR(VLOOKUP($I147,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>123.10000000000001</v>
+        <v>183.16000000000003</v>
       </c>
       <c r="AD147" s="6">
         <v>-5617.2871428571434</v>
@@ -23701,7 +22650,7 @@
       </c>
       <c r="AB149" s="6">
         <f>IFERROR(VLOOKUP($I149,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>8.9</v>
+        <v>4872.24</v>
       </c>
       <c r="AD149" s="6">
         <v>-9192.6412500000006</v>
@@ -23835,11 +22784,11 @@
       </c>
       <c r="X151" s="48">
         <f>X132-X134</f>
-        <v>265974.34999999969</v>
+        <v>266218.67999999964</v>
       </c>
       <c r="Y151" s="14">
         <f t="shared" ref="Y151" si="49">IFERROR((X151*-1)/V151-1,"")</f>
-        <v>-2.0533547330684199</v>
+        <v>-2.0543223683382514</v>
       </c>
       <c r="Z151" s="7">
         <v>96597.603831202126</v>
@@ -23849,11 +22798,11 @@
       </c>
       <c r="AB151" s="48">
         <f>AB132-AB134</f>
-        <v>134791.60000000003</v>
+        <v>-169538.04999999993</v>
       </c>
       <c r="AC151" s="14">
         <f t="shared" ref="AC151" si="50">IFERROR((AB151*-1)/Z151-1,"")</f>
-        <v>-2.3953927908557584</v>
+        <v>0.75509581268968495</v>
       </c>
       <c r="AD151" s="7">
         <v>118545.68360053898</v>
@@ -24318,11 +23267,11 @@
       </c>
       <c r="X157" s="48">
         <f>X151-X153</f>
-        <v>265974.34999999969</v>
+        <v>266218.67999999964</v>
       </c>
       <c r="Y157" s="50">
         <f>X157/V157-1</f>
-        <v>5.3354733068419868E-2</v>
+        <v>5.4322368338251659E-2</v>
       </c>
       <c r="Z157" s="7">
         <v>96597.603831202126</v>
@@ -24332,11 +23281,11 @@
       </c>
       <c r="AB157" s="48">
         <f>AB151-AB153</f>
-        <v>134791.60000000003</v>
+        <v>-169538.04999999993</v>
       </c>
       <c r="AC157" s="50">
         <f>AB157/Z157-1</f>
-        <v>0.3953927908557584</v>
+        <v>-2.7550958126896852</v>
       </c>
       <c r="AD157" s="7">
         <v>118545.68360053898</v>
@@ -24462,7 +23411,7 @@
       </c>
       <c r="AB159" s="48">
         <f>SUM(AB160:AB164)</f>
-        <v>6216.37</v>
+        <v>6236.2699999999995</v>
       </c>
       <c r="AC159" s="14"/>
       <c r="AD159" s="7">
@@ -24595,7 +23544,7 @@
       </c>
       <c r="AB160" s="6">
         <f>IFERROR(VLOOKUP($I160,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>1222.06</v>
+        <v>1241.96</v>
       </c>
       <c r="AD160" s="6">
         <v>-2167</v>
@@ -24992,7 +23941,7 @@
       <c r="W166" s="14"/>
       <c r="X166" s="7">
         <f>X157+X159</f>
-        <v>292808.0499999997</v>
+        <v>293052.37999999966</v>
       </c>
       <c r="Y166" s="50"/>
       <c r="Z166" s="7">
@@ -25002,7 +23951,7 @@
       <c r="AA166" s="14"/>
       <c r="AB166" s="7">
         <f>AB157+AB159</f>
-        <v>141007.97000000003</v>
+        <v>-163301.77999999994</v>
       </c>
       <c r="AC166" s="50"/>
       <c r="AD166" s="7">

--- a/orcamento.xlsx
+++ b/orcamento.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e87dc3a59766ad95/Documentos/Karams Estofados/Relatórios/Financeiro/Orçamento 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="914" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75149217-7FBE-40ED-8486-D8EF6A60CE9F}"/>
+  <xr:revisionPtr revIDLastSave="916" documentId="13_ncr:1_{463D126B-36EC-4AC4-BFD3-846ACE3C8DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B178ABE-45CD-444B-BFFA-634274EBF1F1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{9BADCFFC-7E9F-4283-8ADA-53A2653743C8}"/>
   </bookViews>
@@ -1200,10 +1200,10 @@
             <v>29480.909999999996</v>
           </cell>
           <cell r="E13">
-            <v>5007.66</v>
+            <v>15730.630000000001</v>
           </cell>
           <cell r="F13">
-            <v>68033.119999999995</v>
+            <v>78756.09</v>
           </cell>
         </row>
         <row r="14">
@@ -1254,10 +1254,10 @@
             <v>15728.859999999995</v>
           </cell>
           <cell r="E16">
-            <v>5007.66</v>
+            <v>15730.630000000001</v>
           </cell>
           <cell r="F16">
-            <v>50211.709999999992</v>
+            <v>60934.679999999993</v>
           </cell>
         </row>
         <row r="17">
@@ -1274,10 +1274,10 @@
             <v>333045.58</v>
           </cell>
           <cell r="E17">
-            <v>35596.559999999998</v>
+            <v>37391.329999999994</v>
           </cell>
           <cell r="F17">
-            <v>1026931.9100000001</v>
+            <v>1028726.6800000002</v>
           </cell>
         </row>
         <row r="18">
@@ -1422,10 +1422,10 @@
             <v>9382.1299999999992</v>
           </cell>
           <cell r="E25">
-            <v>7049.37</v>
+            <v>8044.14</v>
           </cell>
           <cell r="F25">
-            <v>52487.56</v>
+            <v>53482.329999999994</v>
           </cell>
         </row>
         <row r="26">
@@ -1456,10 +1456,10 @@
             <v>218151.71</v>
           </cell>
           <cell r="E27">
-            <v>7266.4299999999994</v>
+            <v>8066.4299999999994</v>
           </cell>
           <cell r="F27">
-            <v>617176.28</v>
+            <v>617976.28</v>
           </cell>
         </row>
         <row r="28">
@@ -1496,10 +1496,10 @@
             <v>107667.2</v>
           </cell>
           <cell r="E29">
-            <v>19725.309999999998</v>
+            <v>33956</v>
           </cell>
           <cell r="F29">
-            <v>280562.05</v>
+            <v>294792.74</v>
           </cell>
         </row>
         <row r="30">
@@ -1614,10 +1614,10 @@
             <v>IPTU e Taxas Municipais CIF</v>
           </cell>
           <cell r="E37">
-            <v>2430.6600000000003</v>
+            <v>2849.7400000000002</v>
           </cell>
           <cell r="F37">
-            <v>2430.6600000000003</v>
+            <v>2849.7400000000002</v>
           </cell>
         </row>
         <row r="38">
@@ -1634,10 +1634,10 @@
             <v>50727.39</v>
           </cell>
           <cell r="E38">
-            <v>5803.26</v>
+            <v>6162.46</v>
           </cell>
           <cell r="F38">
-            <v>68290.62</v>
+            <v>68649.820000000007</v>
           </cell>
         </row>
         <row r="39">
@@ -1654,10 +1654,10 @@
             <v>6703.59</v>
           </cell>
           <cell r="E39">
-            <v>6555.5700000000006</v>
+            <v>6848.47</v>
           </cell>
           <cell r="F39">
-            <v>39515.129999999997</v>
+            <v>39808.03</v>
           </cell>
         </row>
         <row r="40">
@@ -1710,1369 +1710,1383 @@
         </row>
         <row r="43">
           <cell r="A43" t="str">
-            <v>Salarios e Ordenados CIF</v>
-          </cell>
-          <cell r="B43">
-            <v>36962.579999999994</v>
-          </cell>
-          <cell r="C43">
-            <v>30986.82</v>
-          </cell>
-          <cell r="D43">
-            <v>28474.9</v>
+            <v>Rescisões CIF</v>
           </cell>
           <cell r="E43">
-            <v>595.26</v>
+            <v>13159.509999999998</v>
           </cell>
           <cell r="F43">
-            <v>97019.559999999983</v>
+            <v>13159.509999999998</v>
           </cell>
         </row>
         <row r="44">
           <cell r="A44" t="str">
-            <v>Seguro de Vida CIF</v>
+            <v>Salarios e Ordenados CIF</v>
           </cell>
           <cell r="B44">
-            <v>361.18</v>
+            <v>36962.579999999994</v>
           </cell>
           <cell r="C44">
-            <v>243.78000000000003</v>
+            <v>30986.82</v>
           </cell>
           <cell r="D44">
-            <v>272.03999999999996</v>
+            <v>28474.9</v>
           </cell>
           <cell r="E44">
-            <v>276.27999999999997</v>
+            <v>595.26</v>
           </cell>
           <cell r="F44">
-            <v>1153.28</v>
+            <v>97019.559999999983</v>
           </cell>
         </row>
         <row r="45">
           <cell r="A45" t="str">
-            <v>4 - GASTOS COM PESSOAL</v>
+            <v>Seguro de Vida CIF</v>
           </cell>
           <cell r="B45">
-            <v>162457.65999999997</v>
+            <v>361.18</v>
           </cell>
           <cell r="C45">
-            <v>172282.52000000005</v>
+            <v>243.78000000000003</v>
           </cell>
           <cell r="D45">
-            <v>186773.47999999998</v>
+            <v>272.03999999999996</v>
           </cell>
           <cell r="E45">
-            <v>76539.610000000015</v>
+            <v>276.27999999999997</v>
           </cell>
           <cell r="F45">
-            <v>598053.27</v>
+            <v>1153.28</v>
           </cell>
         </row>
         <row r="46">
           <cell r="A46" t="str">
-            <v>Assistência Médica (Adm)</v>
+            <v>4 - GASTOS COM PESSOAL</v>
+          </cell>
+          <cell r="B46">
+            <v>162457.65999999997</v>
           </cell>
           <cell r="C46">
-            <v>75</v>
+            <v>172282.52000000005</v>
+          </cell>
+          <cell r="D46">
+            <v>186511.62</v>
+          </cell>
+          <cell r="E46">
+            <v>94121.010000000009</v>
           </cell>
           <cell r="F46">
-            <v>75</v>
+            <v>615372.80999999994</v>
           </cell>
         </row>
         <row r="47">
           <cell r="A47" t="str">
-            <v>Confraternização</v>
-          </cell>
-          <cell r="B47">
-            <v>3330.86</v>
+            <v>Assistência Médica (Adm)</v>
           </cell>
           <cell r="C47">
-            <v>369.46000000000004</v>
-          </cell>
-          <cell r="D47">
-            <v>1065.51</v>
-          </cell>
-          <cell r="E47">
-            <v>170.15</v>
+            <v>75</v>
           </cell>
           <cell r="F47">
-            <v>4935.9799999999996</v>
+            <v>75</v>
           </cell>
         </row>
         <row r="48">
           <cell r="A48" t="str">
-            <v>Cursos e Treinamentos (Adm)</v>
+            <v>Confraternização</v>
           </cell>
           <cell r="B48">
-            <v>2231.33</v>
+            <v>3330.86</v>
           </cell>
           <cell r="C48">
-            <v>4424.49</v>
+            <v>369.46000000000004</v>
           </cell>
           <cell r="D48">
-            <v>1873.7600000000002</v>
+            <v>1065.51</v>
           </cell>
           <cell r="E48">
-            <v>1197.0999999999999</v>
+            <v>170.15</v>
           </cell>
           <cell r="F48">
-            <v>9726.68</v>
+            <v>4935.9799999999996</v>
           </cell>
         </row>
         <row r="49">
           <cell r="A49" t="str">
-            <v>Ferias (Adm)</v>
+            <v>Cursos e Treinamentos (Adm)</v>
+          </cell>
+          <cell r="B49">
+            <v>2231.33</v>
           </cell>
           <cell r="C49">
-            <v>297.89999999999998</v>
+            <v>4424.49</v>
           </cell>
           <cell r="D49">
-            <v>1372.31</v>
+            <v>1873.7600000000002</v>
           </cell>
           <cell r="E49">
-            <v>2681.09</v>
+            <v>1197.0999999999999</v>
           </cell>
           <cell r="F49">
-            <v>4351.3</v>
+            <v>9726.68</v>
           </cell>
         </row>
         <row r="50">
           <cell r="A50" t="str">
-            <v>FGTS (Adm)</v>
-          </cell>
-          <cell r="B50">
-            <v>8774.5499999999993</v>
+            <v>Ferias (Adm)</v>
           </cell>
           <cell r="C50">
-            <v>9673.7099999999991</v>
+            <v>297.89999999999998</v>
           </cell>
           <cell r="D50">
-            <v>9088.76</v>
+            <v>1372.31</v>
+          </cell>
+          <cell r="E50">
+            <v>2681.09</v>
           </cell>
           <cell r="F50">
-            <v>27537.019999999997</v>
+            <v>4351.3</v>
           </cell>
         </row>
         <row r="51">
           <cell r="A51" t="str">
-            <v>Gratificações (Adm)</v>
+            <v>FGTS (Adm)</v>
           </cell>
           <cell r="B51">
-            <v>2919.01</v>
+            <v>8774.5499999999993</v>
           </cell>
           <cell r="C51">
-            <v>4519.01</v>
+            <v>9673.7099999999991</v>
           </cell>
           <cell r="D51">
-            <v>4955.24</v>
-          </cell>
-          <cell r="E51">
-            <v>1980.24</v>
+            <v>8826.9</v>
           </cell>
           <cell r="F51">
-            <v>14373.5</v>
+            <v>27275.159999999996</v>
           </cell>
         </row>
         <row r="52">
           <cell r="A52" t="str">
-            <v>INSS (Adm)</v>
+            <v>Gratificações (Adm)</v>
           </cell>
           <cell r="B52">
-            <v>22949.23</v>
+            <v>2919.01</v>
           </cell>
           <cell r="C52">
-            <v>17763.09</v>
+            <v>4519.01</v>
           </cell>
           <cell r="D52">
-            <v>20718.489999999998</v>
+            <v>4955.24</v>
+          </cell>
+          <cell r="E52">
+            <v>1980.24</v>
           </cell>
           <cell r="F52">
-            <v>61430.81</v>
+            <v>14373.5</v>
           </cell>
         </row>
         <row r="53">
           <cell r="A53" t="str">
-            <v>Manutenção Predial (Adm)</v>
+            <v>INSS (Adm)</v>
           </cell>
           <cell r="B53">
-            <v>2233.96</v>
+            <v>22949.23</v>
           </cell>
           <cell r="C53">
-            <v>2457.64</v>
+            <v>17763.09</v>
           </cell>
           <cell r="D53">
-            <v>1143.7600000000002</v>
-          </cell>
-          <cell r="E53">
-            <v>116</v>
+            <v>20718.489999999998</v>
           </cell>
           <cell r="F53">
-            <v>5951.3600000000006</v>
+            <v>61430.81</v>
           </cell>
         </row>
         <row r="54">
           <cell r="A54" t="str">
-            <v>Pró-Labore</v>
+            <v>Manutenção Predial (Adm)</v>
           </cell>
           <cell r="B54">
-            <v>64498.680000000008</v>
+            <v>2233.96</v>
           </cell>
           <cell r="C54">
-            <v>60318.180000000008</v>
+            <v>2457.64</v>
           </cell>
           <cell r="D54">
-            <v>59830.189999999995</v>
+            <v>1143.7600000000002</v>
           </cell>
           <cell r="E54">
-            <v>51717.240000000005</v>
+            <v>7440.3</v>
           </cell>
           <cell r="F54">
-            <v>236364.29000000004</v>
+            <v>13275.66</v>
           </cell>
         </row>
         <row r="55">
           <cell r="A55" t="str">
-            <v>Rescisões (Adm)</v>
+            <v>Pró-Labore</v>
           </cell>
           <cell r="B55">
-            <v>879.73</v>
+            <v>64498.680000000008</v>
+          </cell>
+          <cell r="C55">
+            <v>60318.180000000008</v>
           </cell>
           <cell r="D55">
-            <v>11928.27</v>
+            <v>59830.189999999995</v>
           </cell>
           <cell r="E55">
-            <v>12417.35</v>
+            <v>61974.340000000004</v>
           </cell>
           <cell r="F55">
-            <v>25225.35</v>
+            <v>246621.39</v>
           </cell>
         </row>
         <row r="56">
           <cell r="A56" t="str">
-            <v>Salarios e Ordenados (Adm)</v>
+            <v>Rescisões (Adm)</v>
           </cell>
           <cell r="B56">
-            <v>53990.009999999995</v>
-          </cell>
-          <cell r="C56">
-            <v>71662.62000000001</v>
+            <v>879.73</v>
           </cell>
           <cell r="D56">
-            <v>74200.570000000007</v>
+            <v>11928.27</v>
           </cell>
           <cell r="E56">
-            <v>5659.81</v>
+            <v>12417.35</v>
           </cell>
           <cell r="F56">
-            <v>205513.01</v>
+            <v>25225.35</v>
           </cell>
         </row>
         <row r="57">
           <cell r="A57" t="str">
-            <v>Seguro de Vida (Adm)</v>
+            <v>Salarios e Ordenados (Adm)</v>
           </cell>
           <cell r="B57">
-            <v>650.30000000000007</v>
+            <v>53990.009999999995</v>
           </cell>
           <cell r="C57">
-            <v>721.42000000000007</v>
+            <v>71662.62000000001</v>
           </cell>
           <cell r="D57">
-            <v>596.62</v>
+            <v>74200.570000000007</v>
           </cell>
           <cell r="E57">
-            <v>600.63</v>
+            <v>5659.81</v>
           </cell>
           <cell r="F57">
-            <v>2568.9700000000003</v>
+            <v>205513.01</v>
           </cell>
         </row>
         <row r="58">
           <cell r="A58" t="str">
-            <v>5 - DESPESAS ADMINISTRATIVAS</v>
+            <v>Seguro de Vida (Adm)</v>
           </cell>
           <cell r="B58">
-            <v>16694.399999999998</v>
+            <v>650.30000000000007</v>
           </cell>
           <cell r="C58">
-            <v>18621.319999999996</v>
+            <v>721.42000000000007</v>
           </cell>
           <cell r="D58">
-            <v>17985.82</v>
+            <v>596.62</v>
           </cell>
           <cell r="E58">
-            <v>5156.7999999999993</v>
+            <v>600.63</v>
           </cell>
           <cell r="F58">
-            <v>58458.34</v>
+            <v>2568.9700000000003</v>
           </cell>
         </row>
         <row r="59">
           <cell r="A59" t="str">
-            <v>Água</v>
+            <v>5 - DESPESAS ADMINISTRATIVAS</v>
           </cell>
           <cell r="B59">
-            <v>32.229999999999997</v>
+            <v>16694.399999999998</v>
           </cell>
           <cell r="C59">
-            <v>32.229999999999997</v>
+            <v>18621.319999999996</v>
           </cell>
           <cell r="D59">
-            <v>32.229999999999997</v>
+            <v>17985.82</v>
+          </cell>
+          <cell r="E59">
+            <v>8176.99</v>
           </cell>
           <cell r="F59">
-            <v>96.69</v>
+            <v>61478.53</v>
           </cell>
         </row>
         <row r="60">
           <cell r="A60" t="str">
-            <v>Alimentação</v>
+            <v>Água</v>
           </cell>
           <cell r="B60">
-            <v>295.60000000000002</v>
+            <v>32.229999999999997</v>
           </cell>
           <cell r="C60">
-            <v>338.73</v>
+            <v>32.229999999999997</v>
           </cell>
           <cell r="D60">
-            <v>782.8</v>
-          </cell>
-          <cell r="E60">
-            <v>607.5</v>
+            <v>32.229999999999997</v>
           </cell>
           <cell r="F60">
-            <v>2024.63</v>
+            <v>96.69</v>
           </cell>
         </row>
         <row r="61">
           <cell r="A61" t="str">
-            <v>Aluguel de Imóvel</v>
+            <v>Alimentação</v>
           </cell>
           <cell r="B61">
-            <v>800</v>
+            <v>295.60000000000002</v>
           </cell>
           <cell r="C61">
-            <v>900</v>
+            <v>338.73</v>
           </cell>
           <cell r="D61">
-            <v>900</v>
+            <v>782.8</v>
           </cell>
           <cell r="E61">
-            <v>900</v>
+            <v>676.5</v>
           </cell>
           <cell r="F61">
-            <v>3500</v>
+            <v>2093.63</v>
           </cell>
         </row>
         <row r="62">
           <cell r="A62" t="str">
-            <v>Combustíveis (Adm)</v>
+            <v>Aluguel de Imóvel</v>
           </cell>
           <cell r="B62">
-            <v>511.23</v>
+            <v>800</v>
           </cell>
           <cell r="C62">
-            <v>981.08999999999992</v>
+            <v>900</v>
           </cell>
           <cell r="D62">
-            <v>780.64</v>
+            <v>900</v>
           </cell>
           <cell r="E62">
-            <v>120</v>
+            <v>900</v>
           </cell>
           <cell r="F62">
-            <v>2392.96</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="63">
           <cell r="A63" t="str">
-            <v>Copa</v>
+            <v>Combustíveis (Adm)</v>
           </cell>
           <cell r="B63">
-            <v>15.99</v>
+            <v>511.23</v>
           </cell>
           <cell r="C63">
-            <v>368.6</v>
+            <v>981.08999999999992</v>
           </cell>
           <cell r="D63">
-            <v>150.63</v>
+            <v>780.64</v>
+          </cell>
+          <cell r="E63">
+            <v>863.12000000000012</v>
           </cell>
           <cell r="F63">
-            <v>535.22</v>
+            <v>3136.08</v>
           </cell>
         </row>
         <row r="64">
           <cell r="A64" t="str">
-            <v>Despesas Cartorárias</v>
+            <v>Copa</v>
           </cell>
           <cell r="B64">
-            <v>432.21</v>
+            <v>15.99</v>
           </cell>
           <cell r="C64">
-            <v>511.6699999999999</v>
+            <v>368.6</v>
           </cell>
           <cell r="D64">
-            <v>350.68</v>
+            <v>150.63</v>
           </cell>
           <cell r="F64">
-            <v>1294.56</v>
+            <v>535.22</v>
           </cell>
         </row>
         <row r="65">
           <cell r="A65" t="str">
-            <v>Doações</v>
+            <v>Despesas Cartorárias</v>
           </cell>
           <cell r="B65">
-            <v>100</v>
+            <v>432.21</v>
           </cell>
           <cell r="C65">
-            <v>100</v>
+            <v>511.6699999999999</v>
           </cell>
           <cell r="D65">
-            <v>100</v>
+            <v>350.68</v>
           </cell>
           <cell r="E65">
-            <v>100</v>
+            <v>267.95</v>
           </cell>
           <cell r="F65">
-            <v>400</v>
+            <v>1562.51</v>
           </cell>
         </row>
         <row r="66">
           <cell r="A66" t="str">
-            <v>Energia Eletrica (Adm)</v>
+            <v>Doações</v>
           </cell>
           <cell r="B66">
-            <v>98.41</v>
+            <v>100</v>
           </cell>
           <cell r="C66">
-            <v>91.95</v>
+            <v>100</v>
+          </cell>
+          <cell r="D66">
+            <v>100</v>
           </cell>
           <cell r="E66">
-            <v>60</v>
+            <v>100</v>
           </cell>
           <cell r="F66">
-            <v>250.36</v>
+            <v>400</v>
           </cell>
         </row>
         <row r="67">
           <cell r="A67" t="str">
-            <v>Material de Expediente (Adm)</v>
+            <v>Energia Eletrica (Adm)</v>
           </cell>
           <cell r="B67">
-            <v>111.89</v>
+            <v>98.41</v>
           </cell>
           <cell r="C67">
-            <v>373.27</v>
-          </cell>
-          <cell r="D67">
-            <v>382.17</v>
+            <v>91.95</v>
           </cell>
           <cell r="E67">
-            <v>388.82</v>
+            <v>60</v>
           </cell>
           <cell r="F67">
-            <v>1256.1499999999999</v>
+            <v>250.36</v>
           </cell>
         </row>
         <row r="68">
           <cell r="A68" t="str">
-            <v>Material de Limpeza (Adm)</v>
+            <v>Material de Expediente (Adm)</v>
           </cell>
           <cell r="B68">
-            <v>367.37</v>
+            <v>111.89</v>
           </cell>
           <cell r="C68">
-            <v>577.9</v>
+            <v>373.27</v>
           </cell>
           <cell r="D68">
-            <v>427.23</v>
+            <v>382.17</v>
           </cell>
           <cell r="E68">
-            <v>448.1</v>
+            <v>647.81999999999994</v>
           </cell>
           <cell r="F68">
-            <v>1820.6</v>
+            <v>1515.1499999999999</v>
           </cell>
         </row>
         <row r="69">
           <cell r="A69" t="str">
-            <v>Rastreamento de frota</v>
+            <v>Material de Limpeza (Adm)</v>
           </cell>
           <cell r="B69">
-            <v>370</v>
+            <v>367.37</v>
           </cell>
           <cell r="C69">
-            <v>370</v>
+            <v>577.9</v>
           </cell>
           <cell r="D69">
-            <v>370</v>
+            <v>427.23</v>
           </cell>
           <cell r="E69">
-            <v>370</v>
+            <v>448.1</v>
           </cell>
           <cell r="F69">
-            <v>1480</v>
+            <v>1820.6</v>
           </cell>
         </row>
         <row r="70">
           <cell r="A70" t="str">
-            <v>Seguros Veicular</v>
+            <v>Rastreamento de frota</v>
           </cell>
           <cell r="B70">
-            <v>11212.419999999998</v>
+            <v>370</v>
           </cell>
           <cell r="C70">
-            <v>11212.419999999998</v>
+            <v>370</v>
           </cell>
           <cell r="D70">
-            <v>11212.419999999998</v>
+            <v>370</v>
           </cell>
           <cell r="E70">
-            <v>1697.48</v>
+            <v>370</v>
           </cell>
           <cell r="F70">
-            <v>35334.74</v>
+            <v>1480</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71" t="str">
-            <v>SPC/Serasa/Associacao</v>
+            <v>Seguros Veicular</v>
           </cell>
           <cell r="B71">
-            <v>351</v>
+            <v>11212.419999999998</v>
           </cell>
           <cell r="C71">
-            <v>617.44000000000005</v>
+            <v>11212.419999999998</v>
           </cell>
           <cell r="D71">
-            <v>351</v>
+            <v>11212.419999999998</v>
+          </cell>
+          <cell r="E71">
+            <v>1697.48</v>
           </cell>
           <cell r="F71">
-            <v>1319.44</v>
+            <v>35334.74</v>
           </cell>
         </row>
         <row r="72">
           <cell r="A72" t="str">
-            <v>Telefone e Internet</v>
+            <v>SPC/Serasa/Associacao</v>
           </cell>
           <cell r="B72">
-            <v>1996.0500000000002</v>
+            <v>351</v>
           </cell>
           <cell r="C72">
-            <v>2146.02</v>
+            <v>617.44000000000005</v>
           </cell>
           <cell r="D72">
-            <v>2146.02</v>
-          </cell>
-          <cell r="E72">
-            <v>464.9</v>
+            <v>351</v>
           </cell>
           <cell r="F72">
-            <v>6752.99</v>
+            <v>1319.44</v>
           </cell>
         </row>
         <row r="73">
           <cell r="A73" t="str">
-            <v>6 - DESPESA COM VENDAS</v>
+            <v>Telefone e Internet</v>
           </cell>
           <cell r="B73">
-            <v>401746.28999999986</v>
+            <v>1996.0500000000002</v>
           </cell>
           <cell r="C73">
-            <v>315472.21000000002</v>
+            <v>2146.02</v>
           </cell>
           <cell r="D73">
-            <v>386595.21</v>
+            <v>2146.02</v>
           </cell>
           <cell r="E73">
-            <v>181507.31</v>
+            <v>2146.02</v>
           </cell>
           <cell r="F73">
-            <v>1285321.02</v>
+            <v>8434.11</v>
           </cell>
         </row>
         <row r="74">
           <cell r="A74" t="str">
-            <v>Brindes</v>
+            <v>6 - DESPESA COM VENDAS</v>
           </cell>
           <cell r="B74">
-            <v>1368</v>
+            <v>401746.28999999986</v>
+          </cell>
+          <cell r="C74">
+            <v>315472.21000000002</v>
+          </cell>
+          <cell r="D74">
+            <v>386595.21</v>
+          </cell>
+          <cell r="E74">
+            <v>203783.34999999998</v>
           </cell>
           <cell r="F74">
-            <v>1368</v>
+            <v>1307597.06</v>
           </cell>
         </row>
         <row r="75">
           <cell r="A75" t="str">
-            <v>Carregamento</v>
+            <v>Brindes</v>
           </cell>
           <cell r="B75">
-            <v>1955</v>
-          </cell>
-          <cell r="C75">
-            <v>2415</v>
-          </cell>
-          <cell r="D75">
-            <v>3042.48</v>
-          </cell>
-          <cell r="E75">
-            <v>86</v>
+            <v>1368</v>
           </cell>
           <cell r="F75">
-            <v>7498.48</v>
+            <v>1368</v>
           </cell>
         </row>
         <row r="76">
           <cell r="A76" t="str">
-            <v>Combustiveis Frota</v>
+            <v>Carregamento</v>
           </cell>
           <cell r="B76">
-            <v>41074.299999999996</v>
+            <v>1955</v>
           </cell>
           <cell r="C76">
-            <v>47569.919999999998</v>
+            <v>2415</v>
           </cell>
           <cell r="D76">
-            <v>69230.98000000001</v>
+            <v>3042.48</v>
           </cell>
           <cell r="E76">
-            <v>28146.19</v>
+            <v>86</v>
           </cell>
           <cell r="F76">
-            <v>186021.39</v>
+            <v>7498.48</v>
           </cell>
         </row>
         <row r="77">
           <cell r="A77" t="str">
-            <v>Comissões sobre Vendas Externo</v>
+            <v>Combustiveis Frota</v>
           </cell>
           <cell r="B77">
-            <v>117100.21999999996</v>
+            <v>41074.299999999996</v>
           </cell>
           <cell r="C77">
-            <v>78726.199999999983</v>
+            <v>47569.919999999998</v>
           </cell>
           <cell r="D77">
-            <v>88339.049999999988</v>
+            <v>69230.98000000001</v>
           </cell>
           <cell r="E77">
-            <v>54479.799999999996</v>
+            <v>43601.919999999991</v>
           </cell>
           <cell r="F77">
-            <v>338645.2699999999</v>
+            <v>201477.12</v>
           </cell>
         </row>
         <row r="78">
           <cell r="A78" t="str">
-            <v>Comissões sobre Vendas Interno</v>
+            <v>Comissões sobre Vendas Externo</v>
           </cell>
           <cell r="B78">
-            <v>7224.44</v>
+            <v>117100.21999999996</v>
           </cell>
           <cell r="C78">
-            <v>5041.3999999999996</v>
+            <v>78726.199999999983</v>
           </cell>
           <cell r="D78">
-            <v>10515.810000000001</v>
+            <v>88339.049999999988</v>
           </cell>
           <cell r="E78">
-            <v>8548.01</v>
+            <v>54479.799999999996</v>
           </cell>
           <cell r="F78">
-            <v>31329.660000000003</v>
+            <v>338645.2699999999</v>
           </cell>
         </row>
         <row r="79">
           <cell r="A79" t="str">
-            <v>Consultoria Comercial</v>
+            <v>Comissões sobre Vendas Interno</v>
           </cell>
           <cell r="B79">
-            <v>13677.889999999998</v>
+            <v>7224.44</v>
           </cell>
           <cell r="C79">
-            <v>10422.07</v>
+            <v>5041.3999999999996</v>
           </cell>
           <cell r="D79">
-            <v>13862.09</v>
+            <v>10515.810000000001</v>
           </cell>
           <cell r="E79">
-            <v>25253.83</v>
+            <v>8548.01</v>
           </cell>
           <cell r="F79">
-            <v>63215.880000000005</v>
+            <v>31329.660000000003</v>
           </cell>
         </row>
         <row r="80">
           <cell r="A80" t="str">
-            <v>Desenvolvimento de Novos Produtos</v>
+            <v>Consultoria Comercial</v>
           </cell>
           <cell r="B80">
-            <v>24000</v>
+            <v>13677.889999999998</v>
           </cell>
           <cell r="C80">
-            <v>24000</v>
+            <v>10422.07</v>
           </cell>
           <cell r="D80">
-            <v>24000</v>
+            <v>13862.09</v>
           </cell>
           <cell r="E80">
-            <v>510</v>
+            <v>25253.83</v>
           </cell>
           <cell r="F80">
-            <v>72510</v>
+            <v>63215.880000000005</v>
           </cell>
         </row>
         <row r="81">
           <cell r="A81" t="str">
-            <v>Feiras e Eventos</v>
+            <v>Desenvolvimento de Novos Produtos</v>
           </cell>
           <cell r="B81">
-            <v>119279.42999999996</v>
+            <v>24000</v>
           </cell>
           <cell r="C81">
-            <v>38472.950000000004</v>
+            <v>24000</v>
           </cell>
           <cell r="D81">
-            <v>41728.47</v>
+            <v>24000</v>
           </cell>
           <cell r="E81">
-            <v>39467.100000000006</v>
+            <v>510</v>
           </cell>
           <cell r="F81">
-            <v>238947.94999999998</v>
+            <v>72510</v>
           </cell>
         </row>
         <row r="82">
           <cell r="A82" t="str">
-            <v>Fretes</v>
+            <v>Feiras e Eventos</v>
+          </cell>
+          <cell r="B82">
+            <v>119279.42999999996</v>
           </cell>
           <cell r="C82">
-            <v>2334.16</v>
+            <v>38472.950000000004</v>
           </cell>
           <cell r="D82">
-            <v>709</v>
+            <v>41728.47</v>
+          </cell>
+          <cell r="E82">
+            <v>39467.100000000006</v>
           </cell>
           <cell r="F82">
-            <v>3043.16</v>
+            <v>238947.94999999998</v>
           </cell>
         </row>
         <row r="83">
           <cell r="A83" t="str">
-            <v>Fretes Ass. Técnica</v>
-          </cell>
-          <cell r="B83">
-            <v>673.06999999999994</v>
+            <v>Fretes</v>
           </cell>
           <cell r="C83">
-            <v>1644.02</v>
+            <v>2334.16</v>
           </cell>
           <cell r="D83">
-            <v>420.81</v>
+            <v>709</v>
           </cell>
           <cell r="F83">
-            <v>2737.9</v>
+            <v>3043.16</v>
           </cell>
         </row>
         <row r="84">
           <cell r="A84" t="str">
-            <v>Fretes Karams</v>
+            <v>Fretes Ass. Técnica</v>
           </cell>
           <cell r="B84">
-            <v>9673.85</v>
+            <v>673.06999999999994</v>
           </cell>
           <cell r="C84">
-            <v>18654.349999999999</v>
+            <v>1644.02</v>
           </cell>
           <cell r="D84">
-            <v>19808.55</v>
-          </cell>
-          <cell r="E84">
-            <v>7301</v>
+            <v>420.81</v>
           </cell>
           <cell r="F84">
-            <v>55437.75</v>
+            <v>2737.9</v>
           </cell>
         </row>
         <row r="85">
           <cell r="A85" t="str">
-            <v>IPVA e Licenciamento</v>
+            <v>Fretes Karams</v>
           </cell>
           <cell r="B85">
-            <v>4296.6099999999997</v>
+            <v>9673.85</v>
           </cell>
           <cell r="C85">
-            <v>4296.6099999999997</v>
+            <v>18654.349999999999</v>
           </cell>
           <cell r="D85">
-            <v>4296.6099999999997</v>
+            <v>19808.55</v>
           </cell>
           <cell r="E85">
-            <v>4715.6899999999996</v>
+            <v>12259.9</v>
           </cell>
           <cell r="F85">
-            <v>17605.519999999997</v>
+            <v>60396.65</v>
           </cell>
         </row>
         <row r="86">
           <cell r="A86" t="str">
-            <v>Mostruário de Tecido</v>
+            <v>IPVA e Licenciamento</v>
           </cell>
           <cell r="B86">
-            <v>7122.33</v>
+            <v>4296.6099999999997</v>
           </cell>
           <cell r="C86">
-            <v>4005.16</v>
+            <v>4296.6099999999997</v>
           </cell>
           <cell r="D86">
-            <v>4874.22</v>
+            <v>4296.6099999999997</v>
           </cell>
           <cell r="E86">
-            <v>2254.29</v>
+            <v>4296.6099999999997</v>
           </cell>
           <cell r="F86">
-            <v>18256</v>
+            <v>17186.439999999999</v>
           </cell>
         </row>
         <row r="87">
           <cell r="A87" t="str">
-            <v>Multas de Trânsito</v>
+            <v>Mostruário de Tecido</v>
           </cell>
           <cell r="B87">
-            <v>260.32</v>
+            <v>7122.33</v>
           </cell>
           <cell r="C87">
-            <v>260.32</v>
+            <v>4005.16</v>
           </cell>
           <cell r="D87">
-            <v>1564.33</v>
+            <v>4874.22</v>
           </cell>
           <cell r="E87">
-            <v>667.02</v>
+            <v>4269.8899999999994</v>
           </cell>
           <cell r="F87">
-            <v>2751.99</v>
+            <v>20271.599999999999</v>
           </cell>
         </row>
         <row r="88">
           <cell r="A88" t="str">
-            <v>Pedágio Frota</v>
+            <v>Multas de Trânsito</v>
           </cell>
           <cell r="B88">
-            <v>4450.1000000000004</v>
+            <v>260.32</v>
           </cell>
           <cell r="C88">
-            <v>10141.98</v>
+            <v>260.32</v>
           </cell>
           <cell r="D88">
-            <v>9958.6499999999978</v>
+            <v>1564.33</v>
+          </cell>
+          <cell r="E88">
+            <v>667.02</v>
           </cell>
           <cell r="F88">
-            <v>24550.729999999996</v>
+            <v>2751.99</v>
           </cell>
         </row>
         <row r="89">
           <cell r="A89" t="str">
-            <v>Publicidade e Propaganda</v>
+            <v>Pedágio Frota</v>
           </cell>
           <cell r="B89">
-            <v>1965</v>
+            <v>4450.1000000000004</v>
           </cell>
           <cell r="C89">
-            <v>1965</v>
+            <v>10141.98</v>
           </cell>
           <cell r="D89">
-            <v>7759.59</v>
-          </cell>
-          <cell r="E89">
-            <v>2492.92</v>
+            <v>9958.6499999999978</v>
           </cell>
           <cell r="F89">
-            <v>14182.51</v>
+            <v>24550.729999999996</v>
           </cell>
         </row>
         <row r="90">
           <cell r="A90" t="str">
-            <v>Royalties</v>
+            <v>Publicidade e Propaganda</v>
           </cell>
           <cell r="B90">
-            <v>35699.840000000004</v>
+            <v>1965</v>
           </cell>
           <cell r="C90">
-            <v>45445.030000000006</v>
+            <v>1965</v>
           </cell>
           <cell r="D90">
-            <v>61484.200000000004</v>
+            <v>7759.59</v>
+          </cell>
+          <cell r="E90">
+            <v>2594.91</v>
           </cell>
           <cell r="F90">
-            <v>142629.07</v>
+            <v>14284.5</v>
           </cell>
         </row>
         <row r="91">
           <cell r="A91" t="str">
-            <v>Viagens e Estadias c/ Vendas</v>
+            <v>Royalties</v>
           </cell>
           <cell r="B91">
-            <v>738.16</v>
+            <v>35699.840000000004</v>
           </cell>
           <cell r="C91">
-            <v>1807.69</v>
+            <v>45445.030000000006</v>
           </cell>
           <cell r="D91">
-            <v>2581.66</v>
-          </cell>
-          <cell r="E91">
-            <v>2175.61</v>
+            <v>61484.200000000004</v>
           </cell>
           <cell r="F91">
-            <v>7303.1200000000008</v>
+            <v>142629.07</v>
           </cell>
         </row>
         <row r="92">
           <cell r="A92" t="str">
-            <v>Manutenção com veiculos</v>
+            <v>Viagens e Estadias c/ Vendas</v>
           </cell>
           <cell r="B92">
-            <v>11187.73</v>
+            <v>738.16</v>
           </cell>
           <cell r="C92">
-            <v>18270.349999999999</v>
+            <v>1807.69</v>
           </cell>
           <cell r="D92">
-            <v>22418.71</v>
+            <v>2581.66</v>
           </cell>
           <cell r="E92">
-            <v>5409.8499999999995</v>
+            <v>2175.61</v>
           </cell>
           <cell r="F92">
-            <v>57286.639999999992</v>
+            <v>7303.1200000000008</v>
           </cell>
         </row>
         <row r="93">
           <cell r="A93" t="str">
-            <v>7 - SERVIÇOS DE TERCEIROS</v>
+            <v>Manutenção com veiculos</v>
           </cell>
           <cell r="B93">
-            <v>74180.06</v>
+            <v>11187.73</v>
           </cell>
           <cell r="C93">
-            <v>63742.03</v>
+            <v>18270.349999999999</v>
           </cell>
           <cell r="D93">
-            <v>67412.58</v>
+            <v>22418.71</v>
           </cell>
           <cell r="E93">
-            <v>41946.38</v>
+            <v>5572.7499999999991</v>
           </cell>
           <cell r="F93">
-            <v>247281.05</v>
+            <v>57449.539999999994</v>
           </cell>
         </row>
         <row r="94">
           <cell r="A94" t="str">
-            <v>Consultoria Empresarial</v>
+            <v>7 - SERVIÇOS DE TERCEIROS</v>
           </cell>
           <cell r="B94">
-            <v>16033.429999999998</v>
+            <v>74180.06</v>
           </cell>
           <cell r="C94">
-            <v>14452.9</v>
+            <v>63742.03</v>
           </cell>
           <cell r="D94">
-            <v>20130.41</v>
+            <v>67412.58</v>
           </cell>
           <cell r="E94">
-            <v>10016.82</v>
+            <v>43951.649999999994</v>
           </cell>
           <cell r="F94">
-            <v>60633.56</v>
+            <v>249286.32</v>
           </cell>
         </row>
         <row r="95">
           <cell r="A95" t="str">
-            <v>Consultoria Juridica</v>
+            <v>Consultoria Empresarial</v>
           </cell>
           <cell r="B95">
-            <v>6035.41</v>
+            <v>16033.429999999998</v>
           </cell>
           <cell r="C95">
-            <v>6035.41</v>
+            <v>14452.9</v>
           </cell>
           <cell r="D95">
-            <v>6035.41</v>
+            <v>20130.41</v>
+          </cell>
+          <cell r="E95">
+            <v>10819.23</v>
           </cell>
           <cell r="F95">
-            <v>18106.23</v>
+            <v>61435.97</v>
           </cell>
         </row>
         <row r="96">
           <cell r="A96" t="str">
-            <v>Contabilidade</v>
+            <v>Consultoria Juridica</v>
           </cell>
           <cell r="B96">
-            <v>11823</v>
+            <v>6035.41</v>
           </cell>
           <cell r="C96">
-            <v>11880</v>
+            <v>6035.41</v>
           </cell>
           <cell r="D96">
-            <v>12244</v>
-          </cell>
-          <cell r="E96">
-            <v>6748</v>
+            <v>6035.41</v>
           </cell>
           <cell r="F96">
-            <v>42695</v>
+            <v>18106.23</v>
           </cell>
         </row>
         <row r="97">
           <cell r="A97" t="str">
-            <v>Curadoria</v>
+            <v>Contabilidade</v>
           </cell>
           <cell r="B97">
-            <v>8966</v>
+            <v>11823</v>
           </cell>
           <cell r="C97">
-            <v>9436</v>
+            <v>11880</v>
           </cell>
           <cell r="D97">
-            <v>9436</v>
+            <v>12244</v>
           </cell>
           <cell r="E97">
-            <v>4718</v>
+            <v>6748</v>
           </cell>
           <cell r="F97">
-            <v>32556</v>
+            <v>42695</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98" t="str">
-            <v>Outros Serviços de Terceiros</v>
+            <v>Curadoria</v>
           </cell>
           <cell r="B98">
-            <v>6685.8499999999995</v>
+            <v>8966</v>
           </cell>
           <cell r="C98">
-            <v>9350</v>
+            <v>9436</v>
           </cell>
           <cell r="D98">
-            <v>7769.93</v>
+            <v>9436</v>
           </cell>
           <cell r="E98">
-            <v>5200</v>
+            <v>4718</v>
           </cell>
           <cell r="F98">
-            <v>29005.78</v>
+            <v>32556</v>
           </cell>
         </row>
         <row r="99">
           <cell r="A99" t="str">
-            <v>Sistemas de Informação</v>
+            <v>Outros Serviços de Terceiros</v>
           </cell>
           <cell r="B99">
-            <v>23441.37</v>
+            <v>6685.8499999999995</v>
           </cell>
           <cell r="C99">
-            <v>11505.72</v>
+            <v>9350</v>
           </cell>
           <cell r="D99">
-            <v>10818.33</v>
+            <v>7769.93</v>
           </cell>
           <cell r="E99">
-            <v>7845.5599999999995</v>
+            <v>5650</v>
           </cell>
           <cell r="F99">
-            <v>53610.979999999996</v>
+            <v>29455.78</v>
           </cell>
         </row>
         <row r="100">
           <cell r="A100" t="str">
-            <v>Vigilancia e Seguranca</v>
+            <v>Sistemas de Informação</v>
           </cell>
           <cell r="B100">
-            <v>1195</v>
+            <v>23441.37</v>
           </cell>
           <cell r="C100">
-            <v>1082</v>
+            <v>11505.72</v>
           </cell>
           <cell r="D100">
-            <v>978.5</v>
+            <v>10818.33</v>
           </cell>
           <cell r="E100">
-            <v>418</v>
+            <v>8346.4199999999983</v>
           </cell>
           <cell r="F100">
-            <v>3673.5</v>
+            <v>54111.839999999997</v>
           </cell>
         </row>
         <row r="101">
           <cell r="A101" t="str">
-            <v>Consultoria Tributaria</v>
+            <v>Vigilancia e Seguranca</v>
+          </cell>
+          <cell r="B101">
+            <v>1195</v>
+          </cell>
+          <cell r="C101">
+            <v>1082</v>
+          </cell>
+          <cell r="D101">
+            <v>978.5</v>
           </cell>
           <cell r="E101">
-            <v>7000</v>
+            <v>670</v>
           </cell>
           <cell r="F101">
-            <v>7000</v>
+            <v>3925.5</v>
           </cell>
         </row>
         <row r="102">
           <cell r="A102" t="str">
-            <v>8 - DESPESAS FINANCEIRAS</v>
-          </cell>
-          <cell r="B102">
-            <v>56553.34</v>
-          </cell>
-          <cell r="C102">
-            <v>61446.999999999985</v>
-          </cell>
-          <cell r="D102">
-            <v>55657.97</v>
+            <v>Consultoria Tributaria</v>
           </cell>
           <cell r="E102">
-            <v>45281.599999999991</v>
+            <v>7000</v>
           </cell>
           <cell r="F102">
-            <v>218939.90999999997</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="103">
           <cell r="A103" t="str">
-            <v>Despesas Bancarias</v>
+            <v>8 - DESPESAS FINANCEIRAS</v>
           </cell>
           <cell r="B103">
-            <v>9652.9900000000034</v>
+            <v>56553.34</v>
           </cell>
           <cell r="C103">
-            <v>9775.6499999999905</v>
+            <v>61446.999999999985</v>
           </cell>
           <cell r="D103">
-            <v>9300.989999999998</v>
+            <v>55657.97</v>
           </cell>
           <cell r="E103">
-            <v>6360.23</v>
+            <v>56748.95</v>
           </cell>
           <cell r="F103">
-            <v>35089.859999999986</v>
+            <v>230407.25999999998</v>
           </cell>
         </row>
         <row r="104">
           <cell r="A104" t="str">
-            <v>Despesas de Cobranca</v>
+            <v>Despesas Bancarias</v>
           </cell>
           <cell r="B104">
-            <v>143.60000000000002</v>
+            <v>9652.9900000000034</v>
           </cell>
           <cell r="C104">
-            <v>95.93</v>
+            <v>9775.6499999999905</v>
           </cell>
           <cell r="D104">
-            <v>251.57000000000002</v>
+            <v>9300.989999999998</v>
           </cell>
           <cell r="E104">
-            <v>183.16000000000003</v>
+            <v>8711.7099999999991</v>
           </cell>
           <cell r="F104">
-            <v>674.26</v>
+            <v>37441.339999999989</v>
           </cell>
         </row>
         <row r="105">
           <cell r="A105" t="str">
-            <v>Despesas de Outros Gastos Não Operacionais</v>
+            <v>Despesas de Cobranca</v>
           </cell>
           <cell r="B105">
-            <v>6672.09</v>
+            <v>143.60000000000002</v>
           </cell>
           <cell r="C105">
-            <v>11317.74</v>
+            <v>95.93</v>
           </cell>
           <cell r="D105">
-            <v>13530.41</v>
+            <v>251.57000000000002</v>
           </cell>
           <cell r="E105">
-            <v>4872.24</v>
+            <v>249.52000000000004</v>
           </cell>
           <cell r="F105">
-            <v>36392.480000000003</v>
+            <v>740.62000000000012</v>
           </cell>
         </row>
         <row r="106">
           <cell r="A106" t="str">
-            <v>Insumos de Clientes</v>
+            <v>Despesas de Outros Gastos Não Operacionais</v>
           </cell>
           <cell r="B106">
-            <v>10463.530000000001</v>
+            <v>6672.09</v>
           </cell>
           <cell r="C106">
-            <v>10819.31</v>
+            <v>11317.74</v>
           </cell>
           <cell r="D106">
-            <v>3571.8999999999996</v>
+            <v>13530.41</v>
           </cell>
           <cell r="E106">
-            <v>15149.56</v>
+            <v>7205.24</v>
           </cell>
           <cell r="F106">
-            <v>40004.299999999996</v>
+            <v>38725.480000000003</v>
           </cell>
         </row>
         <row r="107">
           <cell r="A107" t="str">
-            <v>Juros Pagos</v>
+            <v>Insumos de Clientes</v>
+          </cell>
+          <cell r="B107">
+            <v>10463.530000000001</v>
           </cell>
           <cell r="C107">
-            <v>95.75</v>
+            <v>10819.31</v>
+          </cell>
+          <cell r="D107">
+            <v>3571.8999999999996</v>
+          </cell>
+          <cell r="E107">
+            <v>15149.56</v>
           </cell>
           <cell r="F107">
-            <v>95.75</v>
+            <v>40004.299999999996</v>
           </cell>
         </row>
         <row r="108">
           <cell r="A108" t="str">
-            <v>Juros Pagos - Antecipação de Crédito</v>
-          </cell>
-          <cell r="B108">
-            <v>29621.129999999994</v>
+            <v>Juros Pagos</v>
           </cell>
           <cell r="C108">
-            <v>29342.62</v>
-          </cell>
-          <cell r="D108">
-            <v>29003.100000000002</v>
-          </cell>
-          <cell r="E108">
-            <v>18716.409999999996</v>
+            <v>95.75</v>
           </cell>
           <cell r="F108">
-            <v>106683.25999999998</v>
+            <v>95.75</v>
           </cell>
         </row>
         <row r="109">
           <cell r="A109" t="str">
-            <v>9 - INVESTIMENTOS</v>
+            <v>Juros Pagos - Antecipação de Crédito</v>
           </cell>
           <cell r="B109">
-            <v>53166.43</v>
+            <v>29621.129999999994</v>
           </cell>
           <cell r="C109">
-            <v>26411.83</v>
+            <v>29342.62</v>
           </cell>
           <cell r="D109">
-            <v>26833.7</v>
+            <v>29003.100000000002</v>
           </cell>
           <cell r="E109">
-            <v>6236.2699999999995</v>
+            <v>25432.92</v>
           </cell>
           <cell r="F109">
-            <v>112648.23000000001</v>
+            <v>113399.76999999999</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110" t="str">
-            <v>Computadores e Periféricos</v>
+            <v>9 - INVESTIMENTOS</v>
           </cell>
           <cell r="B110">
-            <v>9551.4999999999982</v>
+            <v>53166.43</v>
           </cell>
           <cell r="C110">
-            <v>4960.7299999999996</v>
+            <v>26411.83</v>
           </cell>
           <cell r="D110">
-            <v>2407.11</v>
+            <v>26833.7</v>
           </cell>
           <cell r="E110">
-            <v>1241.96</v>
+            <v>15136.27</v>
           </cell>
           <cell r="F110">
-            <v>18161.299999999996</v>
+            <v>121548.23000000001</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111" t="str">
-            <v>Consórcios</v>
+            <v>Computadores e Periféricos</v>
           </cell>
           <cell r="B111">
-            <v>3037.44</v>
+            <v>9551.4999999999982</v>
           </cell>
           <cell r="C111">
-            <v>3037.44</v>
+            <v>4960.7299999999996</v>
           </cell>
           <cell r="D111">
-            <v>3037.44</v>
+            <v>2407.11</v>
           </cell>
           <cell r="E111">
-            <v>3037.44</v>
+            <v>1241.96</v>
           </cell>
           <cell r="F111">
-            <v>12149.76</v>
+            <v>18161.299999999996</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112" t="str">
-            <v>Construções e Reformas</v>
+            <v>Consórcios</v>
           </cell>
           <cell r="B112">
-            <v>14634.46</v>
+            <v>3037.44</v>
           </cell>
           <cell r="C112">
-            <v>5089.95</v>
+            <v>3037.44</v>
           </cell>
           <cell r="D112">
-            <v>2570</v>
+            <v>3037.44</v>
+          </cell>
+          <cell r="E112">
+            <v>3037.44</v>
           </cell>
           <cell r="F112">
-            <v>22294.41</v>
+            <v>12149.76</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113" t="str">
-            <v>Maquinas e Equipamentos</v>
+            <v>Construções e Reformas</v>
           </cell>
           <cell r="B113">
-            <v>25943.030000000002</v>
+            <v>14634.46</v>
           </cell>
           <cell r="C113">
-            <v>13323.710000000001</v>
+            <v>5089.95</v>
           </cell>
           <cell r="D113">
-            <v>14734.15</v>
-          </cell>
-          <cell r="E113">
-            <v>1956.87</v>
+            <v>2570</v>
           </cell>
           <cell r="F113">
-            <v>55957.760000000009</v>
+            <v>22294.41</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114" t="str">
-            <v>Moveis e Utensilios</v>
+            <v>Maquinas e Equipamentos</v>
+          </cell>
+          <cell r="B114">
+            <v>25943.030000000002</v>
+          </cell>
+          <cell r="C114">
+            <v>13323.710000000001</v>
           </cell>
           <cell r="D114">
-            <v>4085</v>
+            <v>14734.15</v>
+          </cell>
+          <cell r="E114">
+            <v>10856.87</v>
           </cell>
           <cell r="F114">
-            <v>4085</v>
+            <v>64857.760000000009</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115" t="str">
+            <v>Moveis e Utensilios</v>
+          </cell>
+          <cell r="D115">
+            <v>4085</v>
+          </cell>
+          <cell r="F115">
+            <v>4085</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116" t="str">
             <v>Total Geral</v>
           </cell>
-          <cell r="B115">
+          <cell r="B116">
             <v>1297618.3500000003</v>
           </cell>
-          <cell r="C115">
+          <cell r="C116">
             <v>1221760.2699999996</v>
           </cell>
-          <cell r="D115">
-            <v>1380790.44</v>
-          </cell>
-          <cell r="E115">
-            <v>416997.49999999988</v>
-          </cell>
-          <cell r="F115">
-            <v>4317166.5599999996</v>
+          <cell r="D116">
+            <v>1380528.58</v>
+          </cell>
+          <cell r="E116">
+            <v>508996.18</v>
+          </cell>
+          <cell r="F116">
+            <v>4408903.38</v>
           </cell>
         </row>
       </sheetData>
@@ -5556,11 +5570,11 @@
       </c>
       <c r="AB23" s="7">
         <f>AB24+AB32+AB46</f>
-        <v>573381.71</v>
+        <v>811121.78999999992</v>
       </c>
       <c r="AC23" s="14">
         <f>IFERROR((AB23*-1)/Z23-1,"")</f>
-        <v>-0.58656024482170444</v>
+        <v>-0.41513656883582695</v>
       </c>
       <c r="AD23" s="7">
         <v>-1455440.7019585797</v>
@@ -5694,11 +5708,11 @@
       </c>
       <c r="AB24" s="8">
         <f>SUM(AB25:AB31)</f>
-        <v>518059.83999999997</v>
+        <v>739774.46</v>
       </c>
       <c r="AC24" s="45">
         <f>IFERROR((AB24*-1)/Z24-1,"")</f>
-        <v>0.83532722967612782</v>
+        <v>1.6207941736169964</v>
       </c>
       <c r="AD24" s="8">
         <v>-988112.6561191252</v>
@@ -5843,11 +5857,11 @@
         <v>-8.2750000000000004E-2</v>
       </c>
       <c r="AB25" s="47">
-        <v>513052.18</v>
+        <v>724043.83</v>
       </c>
       <c r="AC25" s="46">
         <f t="shared" ref="AC25:AC31" si="18">IFERROR((AB25*-1)/Z25-1,"")</f>
-        <v>7.4685259615367681</v>
+        <v>10.951189782773193</v>
       </c>
       <c r="AD25" s="6">
         <v>-212077.09063378972</v>
@@ -6755,11 +6769,11 @@
       </c>
       <c r="AB31" s="6">
         <f>IFERROR(VLOOKUP($I31,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>5007.66</v>
+        <v>15730.630000000001</v>
       </c>
       <c r="AC31" s="46">
         <f t="shared" si="18"/>
-        <v>0.33461269940753668</v>
+        <v>3.1924369002051218</v>
       </c>
       <c r="AD31" s="6">
         <v>-13134.683861005104</v>
@@ -6888,11 +6902,11 @@
       </c>
       <c r="AB32" s="8">
         <f>SUM(AB33:AB45)</f>
-        <v>35596.559999999998</v>
+        <v>37391.33</v>
       </c>
       <c r="AC32" s="45">
         <f>(AB32*-1)/Z32-1</f>
-        <v>-0.89814876970208046</v>
+        <v>-0.89301345514916308</v>
       </c>
       <c r="AD32" s="8">
         <v>-369175.10009796615</v>
@@ -7176,11 +7190,11 @@
       </c>
       <c r="AB34" s="6">
         <f>IFERROR(VLOOKUP($I34,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>7049.37</v>
+        <v>8044.14</v>
       </c>
       <c r="AC34" s="46">
         <f t="shared" si="24"/>
-        <v>-0.62989457848896224</v>
+        <v>-0.57766724893234445</v>
       </c>
       <c r="AD34" s="6">
         <v>-19046.924444444445</v>
@@ -7454,11 +7468,11 @@
       </c>
       <c r="AB36" s="6">
         <f>IFERROR(VLOOKUP($I36,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>7266.4299999999994</v>
+        <v>8066.4299999999994</v>
       </c>
       <c r="AC36" s="46">
         <f t="shared" si="24"/>
-        <v>-0.96509254316806437</v>
+        <v>-0.9612493952308313</v>
       </c>
       <c r="AD36" s="6">
         <v>-221693.26133550002</v>
@@ -8862,11 +8876,11 @@
       </c>
       <c r="AB46" s="8">
         <f>SUM(AB47:AB62)</f>
-        <v>19725.310000000001</v>
+        <v>33956</v>
       </c>
       <c r="AC46" s="45">
         <f>(AB46*-1)/Z46-1</f>
-        <v>-0.79057145817951324</v>
+        <v>-0.63948066894480005</v>
       </c>
       <c r="AD46" s="6">
         <v>-98152.945741488365</v>
@@ -9001,11 +9015,11 @@
       </c>
       <c r="AB47" s="6">
         <f>IFERROR(VLOOKUP($I47,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>5803.26</v>
+        <v>6162.46</v>
       </c>
       <c r="AC47" s="46">
         <f t="shared" ref="AC47:AC62" si="27">IFERROR((AB47*-1)/Z47-1,"")</f>
-        <v>-0.50257771428571574</v>
+        <v>-0.47178914285714435</v>
       </c>
       <c r="AD47" s="6">
         <v>-11666.666666666701</v>
@@ -9670,13 +9684,13 @@
       <c r="O52" s="15">
         <v>-1.750477748673235E-3</v>
       </c>
-      <c r="P52" s="6" t="str">
+      <c r="P52" s="6">
         <f>IFERROR(VLOOKUP($I52,[1]RESUMO!$A$5:$M$150,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q52" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="46">
         <f t="shared" si="12"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="R52" s="6">
         <v>-2841.8077777777767</v>
@@ -9684,13 +9698,13 @@
       <c r="S52" s="15">
         <v>-1.2766500796111283E-3</v>
       </c>
-      <c r="T52" s="6" t="str">
+      <c r="T52" s="6">
         <f>IFERROR(VLOOKUP($I52,[1]RESUMO!$A$5:$M$150,3,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="U52" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="U52" s="46">
         <f t="shared" si="25"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="V52" s="6">
         <v>-2841.8077777777767</v>
@@ -9698,13 +9712,13 @@
       <c r="W52" s="15">
         <v>-1.0147759724743832E-3</v>
       </c>
-      <c r="X52" s="6" t="str">
+      <c r="X52" s="6">
         <f>IFERROR(VLOOKUP($I52,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Y52" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="46">
         <f t="shared" si="26"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="Z52" s="6">
         <v>-2841.8077777777767</v>
@@ -9712,13 +9726,13 @@
       <c r="AA52" s="15">
         <v>-1.1616712401881651E-3</v>
       </c>
-      <c r="AB52" s="6" t="str">
+      <c r="AB52" s="6">
         <f>IFERROR(VLOOKUP($I52,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="AC52" s="46" t="str">
+        <v>13159.509999999998</v>
+      </c>
+      <c r="AC52" s="46">
         <f t="shared" si="27"/>
-        <v/>
+        <v>3.6306826601376994</v>
       </c>
       <c r="AD52" s="6">
         <v>-2841.8077777777767</v>
@@ -10975,11 +10989,11 @@
       </c>
       <c r="AB61" s="6">
         <f>IFERROR(VLOOKUP($I61,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>6555.5700000000006</v>
+        <v>6848.47</v>
       </c>
       <c r="AC61" s="46">
         <f t="shared" si="27"/>
-        <v>-6.3489999999999935E-2</v>
+        <v>-2.1647142857142865E-2</v>
       </c>
       <c r="AD61" s="6">
         <v>-7000</v>
@@ -11123,11 +11137,11 @@
       </c>
       <c r="AB62" s="6">
         <f>IFERROR(VLOOKUP($I62,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>2430.6600000000003</v>
+        <v>2849.7400000000002</v>
       </c>
       <c r="AC62" s="46">
         <f t="shared" si="27"/>
-        <v>2.4828448405562442</v>
+        <v>3.0833363185006339</v>
       </c>
       <c r="AD62" s="6">
         <v>-697.8950000000001</v>
@@ -11259,11 +11273,11 @@
       </c>
       <c r="AB64" s="48">
         <f>AB21-AB23</f>
-        <v>158744.09000000008</v>
+        <v>-78995.989999999874</v>
       </c>
       <c r="AC64" s="14">
         <f>AB64/Z64-1</f>
-        <v>-0.81735292169104345</v>
+        <v>-1.0908908594431674</v>
       </c>
       <c r="AD64" s="7">
         <v>908033.53347925539</v>
@@ -11384,11 +11398,11 @@
       </c>
       <c r="X66" s="7">
         <f>SUM(X67+X85+X101+X123)</f>
-        <v>658767.09</v>
+        <v>658505.23</v>
       </c>
       <c r="Y66" s="14">
         <f t="shared" ref="Y66" si="30">IFERROR((X66*-1)/V66-1,"")</f>
-        <v>-0.10538209044282265</v>
+        <v>-0.10573770117285575</v>
       </c>
       <c r="Z66" s="7">
         <v>-702233.64180127438</v>
@@ -11398,11 +11412,11 @@
       </c>
       <c r="AB66" s="7">
         <f>SUM(AB67+AB85+AB101+AB123)</f>
-        <v>298150.10000000003</v>
+        <v>343033</v>
       </c>
       <c r="AC66" s="14">
         <f t="shared" ref="AC66" si="31">IFERROR((AB66*-1)/Z66-1,"")</f>
-        <v>-0.57542606583867739</v>
+        <v>-0.51151158306785427</v>
       </c>
       <c r="AD66" s="7">
         <v>-719188.9048191926</v>
@@ -11518,11 +11532,11 @@
       </c>
       <c r="X67" s="8">
         <f>SUM(X68:X84)</f>
-        <v>186773.48</v>
+        <v>186511.62</v>
       </c>
       <c r="Y67" s="45">
         <f>(X67*-1)/V67-1</f>
-        <v>6.814397676358408E-2</v>
+        <v>6.6646418428453646E-2</v>
       </c>
       <c r="Z67" s="8">
         <v>-174857.96303033334</v>
@@ -11532,11 +11546,11 @@
       </c>
       <c r="AB67" s="8">
         <f>SUM(AB68:AB84)</f>
-        <v>76539.61</v>
+        <v>94121.010000000024</v>
       </c>
       <c r="AC67" s="45">
         <f>(AB67*-1)/Z67-1</f>
-        <v>-0.56227552538329428</v>
+        <v>-0.46172877477891894</v>
       </c>
       <c r="AD67" s="8">
         <v>-180578.51873174944</v>
@@ -11672,11 +11686,11 @@
       </c>
       <c r="AB68" s="6">
         <f>IFERROR(VLOOKUP($I68,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>51717.240000000005</v>
+        <v>61974.340000000004</v>
       </c>
       <c r="AC68" s="46">
         <f t="shared" ref="AC68:AC84" si="34">IFERROR((AB68*-1)/Z68-1,"")</f>
-        <v>-0.19065352112676048</v>
+        <v>-3.0135524256651003E-2</v>
       </c>
       <c r="AD68" s="6">
         <v>-63900</v>
@@ -13342,11 +13356,11 @@
       </c>
       <c r="X80" s="6">
         <f>IFERROR(VLOOKUP($I80,[1]RESUMO!$A$5:$M$150,4,FALSE),"")</f>
-        <v>9088.76</v>
+        <v>8826.9</v>
       </c>
       <c r="Y80" s="46">
         <f t="shared" si="33"/>
-        <v>0.87753016626748859</v>
+        <v>0.82343587294927967</v>
       </c>
       <c r="Z80" s="6">
         <v>-4840.8063760000005</v>
@@ -13652,11 +13666,11 @@
       </c>
       <c r="AB82" s="6">
         <f>IFERROR(VLOOKUP($I82,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>116</v>
+        <v>7440.3</v>
       </c>
       <c r="AC82" s="46">
         <f t="shared" si="34"/>
-        <v>-0.9444104553071242</v>
+        <v>2.5655421498138229</v>
       </c>
       <c r="AD82" s="6">
         <v>-2086.7233333333334</v>
@@ -14063,11 +14077,11 @@
       </c>
       <c r="AB85" s="8">
         <f>SUM(AB86:AB100)</f>
-        <v>5156.8</v>
+        <v>8176.9900000000007</v>
       </c>
       <c r="AC85" s="45">
         <f>(AB85*-1)/Z85-1</f>
-        <v>-0.74666447354541376</v>
+        <v>-0.59829311463235202</v>
       </c>
       <c r="AD85" s="8">
         <v>-20355.613253968255</v>
@@ -14647,11 +14661,11 @@
       </c>
       <c r="AB89" s="6">
         <f>IFERROR(VLOOKUP($I89,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>464.9</v>
+        <v>2146.02</v>
       </c>
       <c r="AC89" s="46">
         <f t="shared" si="37"/>
-        <v>-0.79453084026234999</v>
+        <v>-5.1535972940004782E-2</v>
       </c>
       <c r="AD89" s="6">
         <v>-2262.6266666666666</v>
@@ -14795,11 +14809,11 @@
       </c>
       <c r="AB90" s="6">
         <f>IFERROR(VLOOKUP($I90,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>388.82</v>
+        <v>647.81999999999994</v>
       </c>
       <c r="AC90" s="46">
         <f t="shared" si="37"/>
-        <v>-5.3309472505265298E-2</v>
+        <v>0.57729812643804079</v>
       </c>
       <c r="AD90" s="6">
         <v>-410.71500000000003</v>
@@ -15369,11 +15383,11 @@
       </c>
       <c r="AB94" s="6">
         <f>IFERROR(VLOOKUP($I94,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>0</v>
+        <v>267.95</v>
       </c>
       <c r="AC94" s="46">
         <f t="shared" si="37"/>
-        <v>-1</v>
+        <v>-0.35692000000000002</v>
       </c>
       <c r="AD94" s="6">
         <v>-416.66666666666669</v>
@@ -15665,11 +15679,11 @@
       </c>
       <c r="AB96" s="6">
         <f>IFERROR(VLOOKUP($I96,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>120</v>
+        <v>863.12000000000012</v>
       </c>
       <c r="AC96" s="46">
         <f t="shared" si="37"/>
-        <v>-0.8551039629066145</v>
+        <v>4.2188896133690923E-2</v>
       </c>
       <c r="AD96" s="6">
         <v>-828.18</v>
@@ -16100,11 +16114,11 @@
       </c>
       <c r="AB99" s="6">
         <f>IFERROR(VLOOKUP($I99,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>607.5</v>
+        <v>676.5</v>
       </c>
       <c r="AC99" s="46">
         <f t="shared" si="37"/>
-        <v>-0.58561965682410722</v>
+        <v>-0.53855423513005518</v>
       </c>
       <c r="AD99" s="6">
         <v>-1466.0444444444445</v>
@@ -16372,11 +16386,11 @@
       </c>
       <c r="AB101" s="8">
         <f>SUM(AB102:AB122)</f>
-        <v>181507.31000000003</v>
+        <v>203783.35</v>
       </c>
       <c r="AC101" s="45">
         <f>(AB101*-1)/Z101-1</f>
-        <v>-0.58390587603149124</v>
+        <v>-0.53283945149306655</v>
       </c>
       <c r="AD101" s="8">
         <v>-447451.65810847498</v>
@@ -16660,11 +16674,11 @@
       </c>
       <c r="AB103" s="6">
         <f>IFERROR(VLOOKUP($I103,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>28146.19</v>
+        <v>43601.919999999991</v>
       </c>
       <c r="AC103" s="46">
         <f t="shared" si="40"/>
-        <v>-0.55747806162803115</v>
+        <v>-0.31447893462171927</v>
       </c>
       <c r="AD103" s="6">
         <v>-66634.493733879543</v>
@@ -16947,11 +16961,11 @@
       </c>
       <c r="AB105" s="6">
         <f>IFERROR(VLOOKUP($I105,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>4715.6899999999996</v>
+        <v>4296.6099999999997</v>
       </c>
       <c r="AC105" s="46">
         <f t="shared" si="40"/>
-        <v>-0.76421550000000005</v>
+        <v>-0.78516950000000008</v>
       </c>
       <c r="AD105" s="6">
         <v>-20000</v>
@@ -17243,11 +17257,11 @@
       </c>
       <c r="AB107" s="6">
         <f>IFERROR(VLOOKUP($I107,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>5409.8499999999995</v>
+        <v>5572.7499999999991</v>
       </c>
       <c r="AC107" s="46">
         <f t="shared" si="40"/>
-        <v>-0.6599923979762109</v>
+        <v>-0.64975417725480922</v>
       </c>
       <c r="AD107" s="6">
         <v>-15910.96777777778</v>
@@ -17539,11 +17553,11 @@
       </c>
       <c r="AB109" s="6">
         <f>IFERROR(VLOOKUP($I109,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>7301</v>
+        <v>12259.9</v>
       </c>
       <c r="AC109" s="46">
         <f t="shared" si="40"/>
-        <v>-0.61597601493806486</v>
+        <v>-0.35514372627574053</v>
       </c>
       <c r="AD109" s="6">
         <v>-19011.833333333332</v>
@@ -19113,11 +19127,11 @@
       </c>
       <c r="AB120" s="6">
         <f>IFERROR(VLOOKUP($I120,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>2254.29</v>
+        <v>4269.8899999999994</v>
       </c>
       <c r="AC120" s="46">
         <f t="shared" si="40"/>
-        <v>-0.69220956184872606</v>
+        <v>-0.41700876375366835</v>
       </c>
       <c r="AD120" s="6">
         <v>-7324.1066666666675</v>
@@ -19261,11 +19275,11 @@
       </c>
       <c r="AB121" s="6">
         <f>IFERROR(VLOOKUP($I121,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>2492.92</v>
+        <v>2594.91</v>
       </c>
       <c r="AC121" s="46">
         <f t="shared" si="40"/>
-        <v>-0.4390532537292009</v>
+        <v>-0.41610387763523937</v>
       </c>
       <c r="AD121" s="6">
         <v>-4655.8716775595331</v>
@@ -19542,11 +19556,11 @@
       </c>
       <c r="AB123" s="8">
         <f>SUM(AB124:AB130)</f>
-        <v>34946.379999999997</v>
+        <v>36951.649999999994</v>
       </c>
       <c r="AC123" s="45">
         <f>(AB123*-1)/Z123-1</f>
-        <v>-0.50642877596936087</v>
+        <v>-0.47810699933865075</v>
       </c>
       <c r="AD123" s="8">
         <v>-70803.114724999963</v>
@@ -19823,11 +19837,11 @@
       </c>
       <c r="AB125" s="6">
         <f>IFERROR(VLOOKUP($I125,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>10016.82</v>
+        <v>10819.23</v>
       </c>
       <c r="AC125" s="46">
         <f t="shared" si="43"/>
-        <v>-0.51835052328427023</v>
+        <v>-0.47976738446262135</v>
       </c>
       <c r="AD125" s="6">
         <v>-20796.908299999963</v>
@@ -20243,11 +20257,11 @@
       </c>
       <c r="AB128" s="6">
         <f>IFERROR(VLOOKUP($I128,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>7845.5599999999995</v>
+        <v>8346.4199999999983</v>
       </c>
       <c r="AC128" s="46">
         <f t="shared" si="43"/>
-        <v>-0.333336861141588</v>
+        <v>-0.29077713312617248</v>
       </c>
       <c r="AD128" s="6">
         <v>-11768.402275000035</v>
@@ -20383,11 +20397,11 @@
       </c>
       <c r="AB129" s="6">
         <f>IFERROR(VLOOKUP($I129,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>418</v>
+        <v>670</v>
       </c>
       <c r="AC129" s="46">
         <f t="shared" si="43"/>
-        <v>-0.68786636498726828</v>
+        <v>-0.49969010655854007</v>
       </c>
       <c r="AD129" s="6">
         <v>-1339.17</v>
@@ -20523,11 +20537,11 @@
       </c>
       <c r="AB130" s="6">
         <f>IFERROR(VLOOKUP($I130,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>5200</v>
+        <v>5650</v>
       </c>
       <c r="AC130" s="46">
         <f t="shared" si="43"/>
-        <v>-0.33292737688110019</v>
+        <v>-0.27519993834196466</v>
       </c>
       <c r="AD130" s="6">
         <v>-7795.2532000000037</v>
@@ -20653,11 +20667,11 @@
       </c>
       <c r="X132" s="48">
         <f>X64-X66</f>
-        <v>318304.74999999965</v>
+        <v>318566.60999999964</v>
       </c>
       <c r="Y132" s="14">
         <f>X132/V132-1</f>
-        <v>-1.3929194620994401E-2</v>
+        <v>-1.3117983034938718E-2</v>
       </c>
       <c r="Z132" s="7">
         <v>166896.54889072594</v>
@@ -20667,11 +20681,11 @@
       </c>
       <c r="AB132" s="48">
         <f>AB64-AB66</f>
-        <v>-139406.00999999995</v>
+        <v>-422028.98999999987</v>
       </c>
       <c r="AC132" s="14">
         <f>AB132/Z132-1</f>
-        <v>-1.8352839583955376</v>
+        <v>-3.5286861400370819</v>
       </c>
       <c r="AD132" s="7">
         <v>188844.62866006279</v>
@@ -20806,11 +20820,11 @@
       </c>
       <c r="AB134" s="48">
         <f>AB143</f>
-        <v>30132.039999999994</v>
+        <v>41599.389999999992</v>
       </c>
       <c r="AC134" s="14">
         <f t="shared" ref="AC134" si="47">IFERROR((AB134*-1)/Z134-1,"")</f>
-        <v>-0.57137279976980504</v>
+        <v>-0.40825015276151322</v>
       </c>
       <c r="AD134" s="7">
         <v>-70298.945059523816</v>
@@ -21867,7 +21881,7 @@
       </c>
       <c r="AB143" s="49">
         <f>SUM(AB144:AB149)</f>
-        <v>30132.039999999994</v>
+        <v>41599.389999999992</v>
       </c>
       <c r="AC143" s="13"/>
       <c r="AD143" s="8">
@@ -22001,7 +22015,7 @@
       </c>
       <c r="AB144" s="6">
         <f>IFERROR(VLOOKUP($I144,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>6360.23</v>
+        <v>8711.7099999999991</v>
       </c>
       <c r="AD144" s="6">
         <v>-15075.204444444444</v>
@@ -22133,7 +22147,7 @@
       </c>
       <c r="AB145" s="6">
         <f>IFERROR(VLOOKUP($I145,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>18716.409999999996</v>
+        <v>25432.92</v>
       </c>
       <c r="AD145" s="6">
         <v>-40249.912222222221</v>
@@ -22397,7 +22411,7 @@
       </c>
       <c r="AB147" s="6">
         <f>IFERROR(VLOOKUP($I147,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>183.16000000000003</v>
+        <v>249.52000000000004</v>
       </c>
       <c r="AD147" s="6">
         <v>-5617.2871428571434</v>
@@ -22650,7 +22664,7 @@
       </c>
       <c r="AB149" s="6">
         <f>IFERROR(VLOOKUP($I149,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>4872.24</v>
+        <v>7205.24</v>
       </c>
       <c r="AD149" s="6">
         <v>-9192.6412500000006</v>
@@ -22784,11 +22798,11 @@
       </c>
       <c r="X151" s="48">
         <f>X132-X134</f>
-        <v>266218.67999999964</v>
+        <v>266480.53999999963</v>
       </c>
       <c r="Y151" s="14">
         <f t="shared" ref="Y151" si="49">IFERROR((X151*-1)/V151-1,"")</f>
-        <v>-2.0543223683382514</v>
+        <v>-2.0553594287555486</v>
       </c>
       <c r="Z151" s="7">
         <v>96597.603831202126</v>
@@ -22798,11 +22812,11 @@
       </c>
       <c r="AB151" s="48">
         <f>AB132-AB134</f>
-        <v>-169538.04999999993</v>
+        <v>-463628.37999999989</v>
       </c>
       <c r="AC151" s="14">
         <f t="shared" ref="AC151" si="50">IFERROR((AB151*-1)/Z151-1,"")</f>
-        <v>0.75509581268968495</v>
+        <v>3.7995846854561695</v>
       </c>
       <c r="AD151" s="7">
         <v>118545.68360053898</v>
@@ -23267,11 +23281,11 @@
       </c>
       <c r="X157" s="48">
         <f>X151-X153</f>
-        <v>266218.67999999964</v>
+        <v>266480.53999999963</v>
       </c>
       <c r="Y157" s="50">
         <f>X157/V157-1</f>
-        <v>5.4322368338251659E-2</v>
+        <v>5.5359428755548556E-2</v>
       </c>
       <c r="Z157" s="7">
         <v>96597.603831202126</v>
@@ -23281,11 +23295,11 @@
       </c>
       <c r="AB157" s="48">
         <f>AB151-AB153</f>
-        <v>-169538.04999999993</v>
+        <v>-463628.37999999989</v>
       </c>
       <c r="AC157" s="50">
         <f>AB157/Z157-1</f>
-        <v>-2.7550958126896852</v>
+        <v>-5.7995846854561695</v>
       </c>
       <c r="AD157" s="7">
         <v>118545.68360053898</v>
@@ -23411,7 +23425,7 @@
       </c>
       <c r="AB159" s="48">
         <f>SUM(AB160:AB164)</f>
-        <v>6236.2699999999995</v>
+        <v>15136.27</v>
       </c>
       <c r="AC159" s="14"/>
       <c r="AD159" s="7">
@@ -23794,7 +23808,7 @@
       </c>
       <c r="AB163" s="6">
         <f>IFERROR(VLOOKUP($I163,[1]RESUMO!$A$5:$M$150,5,FALSE),"")</f>
-        <v>1956.87</v>
+        <v>10856.87</v>
       </c>
       <c r="AD163" s="6">
         <v>-36540</v>
@@ -23941,7 +23955,7 @@
       <c r="W166" s="14"/>
       <c r="X166" s="7">
         <f>X157+X159</f>
-        <v>293052.37999999966</v>
+        <v>293314.23999999964</v>
       </c>
       <c r="Y166" s="50"/>
       <c r="Z166" s="7">
@@ -23951,7 +23965,7 @@
       <c r="AA166" s="14"/>
       <c r="AB166" s="7">
         <f>AB157+AB159</f>
-        <v>-163301.77999999994</v>
+        <v>-448492.10999999987</v>
       </c>
       <c r="AC166" s="50"/>
       <c r="AD166" s="7">
